--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14382,14 +14382,14 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-111.69</v>
+        <v>-109.5</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P5" s="11" t="inlineStr">
         <is>
-          <t>~-122.15 (unrealized)</t>
+          <t>~-119.96 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="11" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$R$196</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Trades'!$A$1:$W$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Trades'!$A$1:$W$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -106,9 +106,6 @@
     <xf numFmtId="4" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -117,6 +114,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -2358,10 +2358,10 @@
         <v>51.86</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>2</v>
@@ -13889,7 +13889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W64"/>
+  <dimension ref="A1:W65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14037,12 +14037,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>00:10:42 IST</t>
+          <t>15:01:27 IST</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -14065,83 +14065,81 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
-        <v>2439.54</v>
+      <c r="G2" s="8" t="n">
+        <v>0.3393</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I2" s="8" t="n">
-        <v>2388.36</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>2534.58</v>
+        <v>10000</v>
+      </c>
+      <c r="I2" s="9" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="J2" s="9" t="n">
+        <v>0.3518</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L2" s="2" t="n">
-        <v>2532.05</v>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-12 01:01:12 IST</t>
-        </is>
-      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>1850.11</v>
+        <v>6.8</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>146.37</v>
-      </c>
-      <c r="P2" s="5" t="n">
-        <v>1703.74</v>
-      </c>
-      <c r="Q2" s="5" t="n">
-        <v>3.49</v>
+        <v>10.18</v>
+      </c>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>~-3.38 (unrealized)</t>
+        </is>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>~+0.20%</t>
+        </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2532.765429, "BB_lo": 2393.56941, "Close": 2437.098633, "EMA20": 2404.555507, "EMA200": 2189.831855, "EMA50": 2222.045575, "EMA9": 2463.211647, "High": 2483.719971, "Low": 2406.906494, "Open": 2466.913086, "RSI14": 57.778434, "Ret": -0.012086, "SMA20": 2463.167419, "SMA50": 2147.895715, "Volume": 16781828594.0, "_provenance": {"captured_at_ist": "2026-09-12 00:10:42 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "1ef31696acc1cd4efe2bcd7470c35cf39eec58504bbcfa1e511fce897866faa4"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 2324.709473, "low50": 1821.485107}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 0.345453, "BB_lo": 0.325368, "Close": 0.338307, "EMA20": 0.336164, "EMA200": 0.325217, "EMA50": 0.333945, "EMA9": 0.3375, "High": 0.341545, "Low": 0.338295, "Open": 0.339846, "RSI14": 54.726192, "Ret": -0.004528, "SMA20": 0.33541, "SMA50": 0.333187, "Volume": 302053356.0, "_provenance": {"captured_at_ist": "2026-09-14 15:01:27 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "65ee6ec20afd1eadd50216b1a8c8746e16e10a009a93786d32249e8209218bb5"}, "high20": 0.346589, "high50": 0.349996, "low20": 0.321569, "low50": 0.321569}</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | 🎯 Target Hit (live)</t>
+          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>11:14:08 IST</t>
+          <t>00:10:42 IST</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -14151,55 +14149,55 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>DOGE-USD</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="n">
-        <v>0.083828</v>
+          <t>SWING_1d</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>2439.54</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="I3" s="10" t="n">
-        <v>0.085341</v>
-      </c>
-      <c r="J3" s="10" t="n">
-        <v>0.08155800000000001</v>
+        <v>20</v>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>2388.36</v>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>2534.58</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.08559700000000001</v>
+        <v>2532.05</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 19:38:41 IST</t>
+          <t>2026-09-12 01:01:12 IST</t>
         </is>
       </c>
       <c r="N3" s="4" t="n">
-        <v>-88.45</v>
+        <v>1850.11</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>12.57</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v>-101.02</v>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v>-2.41</v>
+        <v>146.37</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>1703.74</v>
+      </c>
+      <c r="Q3" s="5" t="n">
+        <v>3.49</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
@@ -14208,27 +14206,27 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>50.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+RSI&lt;45</t>
+          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>{"2Red": 0.0, "Close": 0.08408, "EMA20": 0.08417, "EMA50": 0.085792, "EMA9": 0.083724, "High": 0.08414, "Low": 0.08364, "Open": 0.08372, "RSI14": 44.169679, "Ret": 0.0043, "SMA20": 0.083904, "SMA50": 0.086466, "Volume": 9846336.0, "_provenance": {"captured_at_ist": "2026-09-11 11:14:08 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "52faf51891c7541754ee8666a227d22c17b888d769d3894f56f2ba75ece3eaed"}}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2532.765429, "BB_lo": 2393.56941, "Close": 2437.098633, "EMA20": 2404.555507, "EMA200": 2189.831855, "EMA50": 2222.045575, "EMA9": 2463.211647, "High": 2483.719971, "Low": 2406.906494, "Open": 2466.913086, "RSI14": 57.778434, "Ret": -0.012086, "SMA20": 2463.167419, "SMA50": 2147.895715, "Volume": 16781828594.0, "_provenance": {"captured_at_ist": "2026-09-12 00:10:42 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "1ef31696acc1cd4efe2bcd7470c35cf39eec58504bbcfa1e511fce897866faa4"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 2324.709473, "low50": 1821.485107}</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>#1ID Price&gt;SMA20+RSI&lt;45 | 🎯 SL Hit (live)</t>
+          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | 🎯 Target Hit (live)</t>
         </is>
       </c>
     </row>
@@ -14240,7 +14238,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>00:05:22 IST</t>
+          <t>11:14:08 IST</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -14250,38 +14248,38 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>DOGE-USD</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>2469.38</v>
+          <t>INTRADAY_1h</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>0.083828</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I4" s="8" t="n">
-        <v>2417.58</v>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>2565.59</v>
+        <v>50000</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>0.085341</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>0.08155800000000001</v>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2563.02</v>
+        <v>0.08559700000000001</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -14289,16 +14287,16 @@
         </is>
       </c>
       <c r="N4" s="4" t="n">
-        <v>1779.24</v>
+        <v>-88.45</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>140.75</v>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>1638.49</v>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v>3.49</v>
+        <v>12.57</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v>-101.02</v>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v>-2.41</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
@@ -14307,27 +14305,27 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>50.67</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
+          <t>Price&gt;SMA20+RSI&lt;45</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2539.244704, "BB_lo": 2394.908446, "Close": 2466.913818, "EMA20": 2401.129915, "EMA200": 2187.380698, "EMA50": 2213.267899, "EMA9": 2469.739901, "High": 2522.369629, "Low": 2443.702393, "Open": 2484.894287, "RSI14": 60.959164, "Ret": -0.007255, "SMA20": 2467.076575, "SMA50": 2137.823545, "Volume": 14955608804.0, "_provenance": {"captured_at_ist": "2026-09-11 00:05:22 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "d8d364e889190953445a4b086a4c86f37d82d8af7f1f62c9054b85772793509b"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 2222.574707, "low50": 1821.485107}</t>
+          <t>{"2Red": 0.0, "Close": 0.08408, "EMA20": 0.08417, "EMA50": 0.085792, "EMA9": 0.083724, "High": 0.08414, "Low": 0.08364, "Open": 0.08372, "RSI14": 44.169679, "Ret": 0.0043, "SMA20": 0.083904, "SMA50": 0.086466, "Volume": 9846336.0, "_provenance": {"captured_at_ist": "2026-09-11 11:14:08 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "52faf51891c7541754ee8666a227d22c17b888d769d3894f56f2ba75ece3eaed"}}</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | 🎯 Target Hit (live)</t>
+          <t>#1ID Price&gt;SMA20+RSI&lt;45 | 🎯 SL Hit (live)</t>
         </is>
       </c>
     </row>
@@ -14344,12 +14342,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -14363,68 +14361,70 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>716.38</v>
+        <v>2469.38</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="I5" s="8" t="n">
-        <v>701.98</v>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>744.96</v>
+        <v>19</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>2417.58</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>2565.59</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
+      <c r="L5" s="2" t="n">
+        <v>2563.02</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11 19:38:41 IST</t>
+        </is>
+      </c>
       <c r="N5" s="4" t="n">
-        <v>-109.5</v>
+        <v>1779.24</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>10.46</v>
-      </c>
-      <c r="P5" s="11" t="inlineStr">
-        <is>
-          <t>~-119.96 (unrealized)</t>
-        </is>
-      </c>
-      <c r="Q5" s="11" t="inlineStr">
-        <is>
-          <t>~-0.21%</t>
-        </is>
+        <v>140.75</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>1638.49</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>3.49</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>65.29</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+2Red</t>
+          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 732.086193, "BB_lo": 702.469807, "Close": 716.309998, "EMA20": 714.795564, "EMA200": 664.839596, "EMA50": 710.89305, "EMA9": 715.808843, "High": 719.700012, "Low": 714.02002, "Open": 716.400024, "RSI14": 51.664581, "Ret": -0.002854, "SMA20": 717.278, "SMA50": 711.166399, "Volume": 26659200.0, "_provenance": {"captured_at_ist": "2026-09-11 00:05:22 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "3150d3a7200210926ae4cbca12d82841d05d62f6516aa32b4a5180c4e8d61898"}, "high20": 734.580017, "high50": 737.619995, "low20": 702.700012, "low50": 661.140015}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2539.244704, "BB_lo": 2394.908446, "Close": 2466.913818, "EMA20": 2401.129915, "EMA200": 2187.380698, "EMA50": 2213.267899, "EMA9": 2469.739901, "High": 2522.369629, "Low": 2443.702393, "Open": 2484.894287, "RSI14": 60.959164, "Ret": -0.007255, "SMA20": 2467.076575, "SMA50": 2137.823545, "Volume": 14955608804.0, "_provenance": {"captured_at_ist": "2026-09-11 00:05:22 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "d8d364e889190953445a4b086a4c86f37d82d8af7f1f62c9054b85772793509b"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 2222.574707, "low50": 1821.485107}</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>#31SW Price&gt;SMA50+2Red</t>
+          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | 🎯 Target Hit (live)</t>
         </is>
       </c>
     </row>
@@ -14446,7 +14446,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -14460,16 +14460,16 @@
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>166.6</v>
+        <v>716.38</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>314</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>163.25</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>173.24</v>
+        <v>73</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>701.98</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>744.96</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
@@ -14479,19 +14479,19 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="4" t="n">
-        <v>-389.36</v>
+        <v>-109.5</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>10.46</v>
       </c>
-      <c r="P6" s="11" t="inlineStr">
-        <is>
-          <t>~-399.82 (unrealized)</t>
-        </is>
-      </c>
-      <c r="Q6" s="11" t="inlineStr">
-        <is>
-          <t>~-0.74%</t>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>~-119.96 (unrealized)</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
+          <t>~-0.21%</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -14501,49 +14501,49 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>65.29</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 177.039339, "BB_lo": 165.311657, "Close": 166.580002, "EMA20": 169.967704, "EMA200": 155.06167, "EMA50": 165.803089, "EMA9": 170.19262, "High": 167.410004, "Low": 166.389999, "Open": 167.309998, "RSI14": 43.5919, "Ret": -0.003291, "SMA20": 171.175498, "SMA50": 165.980599, "Volume": 8018100.0, "_provenance": {"captured_at_ist": "2026-09-11 00:05:22 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "b1bd4acf19438d5c9145df22921236f8ae2c9a49fd069b3fdf994b5e8ccf5871"}, "high20": 176.600006, "high50": 176.600006, "low20": 165.759995, "low50": 157.229996}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 732.086193, "BB_lo": 702.469807, "Close": 716.309998, "EMA20": 714.795564, "EMA200": 664.839596, "EMA50": 710.89305, "EMA9": 715.808843, "High": 719.700012, "Low": 714.02002, "Open": 716.400024, "RSI14": 51.664581, "Ret": -0.002854, "SMA20": 717.278, "SMA50": 711.166399, "Volume": 26659200.0, "_provenance": {"captured_at_ist": "2026-09-11 00:05:22 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "3150d3a7200210926ae4cbca12d82841d05d62f6516aa32b4a5180c4e8d61898"}, "high20": 734.580017, "high50": 737.619995, "low20": 702.700012, "low50": 661.140015}</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>#31SW Price&gt;SMA50+2Red</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>04:11:58 IST</t>
+          <t>00:05:22 IST</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -14557,82 +14557,80 @@
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2487.43</v>
+        <v>166.6</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>2435.24</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>2584.34</v>
+        <v>314</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>163.25</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>173.24</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L7" s="2" t="n">
-        <v>2432.8</v>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10 18:11:52 IST</t>
-        </is>
-      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="4" t="n">
-        <v>-1037.88</v>
+        <v>-389.36</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>141.78</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v>-1179.66</v>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v>-2.5</v>
+        <v>10.46</v>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>~-399.82 (unrealized)</t>
+        </is>
+      </c>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>~-0.74%</t>
+        </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+Range&gt;1.5%+2Red</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2555.797457, "BB_lo": 2364.302788, "Close": 2484.941406, "EMA20": 2394.205294, "EMA200": 2184.550101, "EMA50": 2202.915005, "EMA9": 2470.446422, "High": 2506.753174, "Low": 2441.328857, "Open": 2490.919678, "RSI14": 62.903407, "Ret": -0.002415, "SMA20": 2460.050122, "SMA50": 2127.052944, "Volume": 13471038160.0, "_provenance": {"captured_at_ist": "2026-09-10 04:11:58 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "9d935e01f058e194edc4cbc5b22f08a0e6b38c3f190d3dd9f1551d28266ed601"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 1905.082397, "low50": 1821.485107}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 177.039339, "BB_lo": 165.311657, "Close": 166.580002, "EMA20": 169.967704, "EMA200": 155.06167, "EMA50": 165.803089, "EMA9": 170.19262, "High": 167.410004, "Low": 166.389999, "Open": 167.309998, "RSI14": 43.5919, "Ret": -0.003291, "SMA20": 171.175498, "SMA50": 165.980599, "Volume": 8018100.0, "_provenance": {"captured_at_ist": "2026-09-11 00:05:22 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "b1bd4acf19438d5c9145df22921236f8ae2c9a49fd069b3fdf994b5e8ccf5871"}, "high20": 176.600006, "high50": 176.600006, "low20": 165.759995, "low50": 157.229996}</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>#14SW Price&gt;SMA50+Range&gt;1.5%+2Red | SL Hit (intraday)</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>17:10:43 IST</t>
+          <t>04:11:58 IST</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -14642,55 +14640,55 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>SOL-USD</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>103.63</v>
+        <v>2487.43</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1217</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>105.35</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>100.68</v>
+        <v>19</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>2435.24</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>2584.34</v>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>100.83</v>
+        <v>2432.8</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 03:42:13 IST</t>
+          <t>2026-09-10 18:11:52 IST</t>
         </is>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3406.36</v>
+        <v>-1037.88</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>378.35</v>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v>3028.01</v>
-      </c>
-      <c r="Q8" s="5" t="n">
-        <v>2.4</v>
+        <v>141.78</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>-1179.66</v>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v>-2.5</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
@@ -14699,27 +14697,27 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>47.24</t>
+          <t>63.36</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
+          <t>Price&gt;SMA50+Range&gt;1.5%+2Red</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>{"2Red": 0.0, "Close": 103.790001, "EMA20": 103.838416, "EMA50": 103.876237, "EMA9": 103.993741, "High": 104.050003, "Low": 103.480003, "Open": 103.489998, "RSI14": 49.770588, "Ret": 0.002802, "SMA20": 103.7825, "SMA50": 103.7752, "Volume": 17383936.0, "_provenance": {"captured_at_ist": "2026-09-09 17:10:43 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "9aaf3858637b395153a1eb6f1f3f5a4337236e3bc92c730aee983cd6ceb4eec1"}}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2555.797457, "BB_lo": 2364.302788, "Close": 2484.941406, "EMA20": 2394.205294, "EMA200": 2184.550101, "EMA50": 2202.915005, "EMA9": 2470.446422, "High": 2506.753174, "Low": 2441.328857, "Open": 2490.919678, "RSI14": 62.903407, "Ret": -0.002415, "SMA20": 2460.050122, "SMA50": 2127.052944, "Volume": 13471038160.0, "_provenance": {"captured_at_ist": "2026-09-10 04:11:58 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "9d935e01f058e194edc4cbc5b22f08a0e6b38c3f190d3dd9f1551d28266ed601"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 1905.082397, "low50": 1821.485107}</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>#1ID EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50 | 🎯 Target Hit (live)</t>
+          <t>#14SW Price&gt;SMA50+Range&gt;1.5%+2Red | SL Hit (intraday)</t>
         </is>
       </c>
     </row>
@@ -14731,65 +14729,65 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>00:20:42 IST</t>
+          <t>17:10:43 IST</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>SOL-USD</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
-        <v>171.47</v>
+        <v>103.63</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>314</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>168.02</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>178.31</v>
+        <v>1217</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>100.68</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>168</v>
+        <v>100.83</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 01:02:44 IST</t>
+          <t>2026-09-10 03:42:13 IST</t>
         </is>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1088.58</v>
+        <v>3406.36</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>10.77</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v>-1099.35</v>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v>-2.04</v>
+        <v>378.35</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>3028.01</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>2.4</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
@@ -14798,49 +14796,49 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>47.24</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 176.798755, "BB_lo": 165.82624, "Close": 171.449997, "EMA20": 170.660546, "EMA200": 154.818785, "EMA50": 165.715924, "EMA9": 172.087216, "High": 172.529999, "Low": 171.240005, "Open": 171.389999, "RSI14": 55.529727, "Ret": -0.010447, "SMA20": 171.312498, "SMA50": 165.727999, "Volume": 6083000.0, "_provenance": {"captured_at_ist": "2026-09-09 00:20:42 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "44670098855ad96888cc2dab18b682407e5130dfe00fe74e11bc4ccf032eec28"}, "high20": 176.600006, "high50": 176.600006, "low20": 162.919998, "low50": 153.589996}</t>
+          <t>{"2Red": 0.0, "Close": 103.790001, "EMA20": 103.838416, "EMA50": 103.876237, "EMA9": 103.993741, "High": 104.050003, "Low": 103.480003, "Open": 103.489998, "RSI14": 49.770588, "Ret": 0.002802, "SMA20": 103.7825, "SMA50": 103.7752, "Volume": 17383936.0, "_provenance": {"captured_at_ist": "2026-09-09 17:10:43 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "9aaf3858637b395153a1eb6f1f3f5a4337236e3bc92c730aee983cd6ceb4eec1"}}</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | 🎯 SL Hit (live)</t>
+          <t>#1ID EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50 | 🎯 Target Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>11:22:34 IST</t>
+          <t>00:20:42 IST</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -14853,17 +14851,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G10" s="9" t="n">
-        <v>0.3349</v>
+      <c r="G10" s="4" t="n">
+        <v>171.47</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>0.3272</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>0.3473</v>
+        <v>314</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>168.02</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>178.31</v>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
@@ -14871,24 +14869,24 @@
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0.3384</v>
+        <v>168</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 16:01:47 IST</t>
+          <t>2026-09-09 01:02:44 IST</t>
         </is>
       </c>
       <c r="N10" s="4" t="n">
-        <v>35.01</v>
+        <v>-1088.58</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>24.96</v>
-      </c>
-      <c r="Q10" s="12" t="n">
-        <v>0.75</v>
+        <v>10.77</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>-1099.35</v>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v>-2.04</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -14897,49 +14895,49 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>66.28</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 0.34818, "BB_lo": 0.323418, "Close": 0.333927, "EMA20": 0.333584, "EMA200": 0.324153, "EMA50": 0.332375, "EMA9": 0.332427, "High": 0.334747, "Low": 0.331477, "Open": 0.331539, "RSI14": 50.659837, "Ret": 0.007209, "SMA20": 0.335799, "SMA50": 0.331667, "Volume": 308281984.0, "_provenance": {"captured_at_ist": "2026-09-07 11:22:34 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "7600fa929fe73fa7401d6bfbe86db098b69cda878289f54ac466b6c9a918540c"}, "high20": 0.349996, "high50": 0.349996, "low20": 0.321569, "low50": 0.321457}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 176.798755, "BB_lo": 165.82624, "Close": 171.449997, "EMA20": 170.660546, "EMA200": 154.818785, "EMA50": 165.715924, "EMA9": 172.087216, "High": 172.529999, "Low": 171.240005, "Open": 171.389999, "RSI14": 55.529727, "Ret": -0.010447, "SMA20": 171.312498, "SMA50": 165.727999, "Volume": 6083000.0, "_provenance": {"captured_at_ist": "2026-09-09 00:20:42 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "44670098855ad96888cc2dab18b682407e5130dfe00fe74e11bc4ccf032eec28"}, "high20": 176.600006, "high50": 176.600006, "low20": 162.919998, "low50": 153.589996}</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>#2SW Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | 🎯 SL Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>00:01:07 IST</t>
+          <t>11:22:34 IST</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -14952,17 +14950,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
-        <v>384.36</v>
+      <c r="G11" s="8" t="n">
+        <v>0.3349</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>133</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>376.63</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>399.69</v>
+        <v>10000</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.3473</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
@@ -14970,24 +14968,24 @@
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>378.76</v>
+        <v>0.3384</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 00:01:43 IST</t>
+          <t>2026-09-12 16:01:47 IST</t>
         </is>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-744.52</v>
+        <v>35.01</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v>-754.74</v>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v>-1.48</v>
+        <v>10.05</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="Q11" s="12" t="n">
+        <v>0.75</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -14996,27 +14994,27 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>66.28</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 384.914412, "BB_lo": 375.582585, "Close": 384.320007, "EMA20": 378.7841, "EMA200": 352.821272, "EMA50": 374.004443, "EMA9": 380.273856, "High": 385.049988, "Low": 381.329987, "Open": 381.329987, "RSI14": 62.100647, "Ret": 0.011235, "SMA20": 380.248499, "SMA50": 373.018998, "Volume": 152400.0, "_provenance": {"captured_at_ist": "2026-09-05 00:01:07 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "abfffaa65e4253b95842b79cc0c4fd24b91e723a3bb5a1c71936a4e0ad957b60"}, "high20": 384.809998, "high50": 384.820007, "low20": 376.040009, "low50": 354.809998}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 0.34818, "BB_lo": 0.323418, "Close": 0.333927, "EMA20": 0.333584, "EMA200": 0.324153, "EMA50": 0.332375, "EMA9": 0.332427, "High": 0.334747, "Low": 0.331477, "Open": 0.331539, "RSI14": 50.659837, "Ret": 0.007209, "SMA20": 0.335799, "SMA50": 0.331667, "Volume": 308281984.0, "_provenance": {"captured_at_ist": "2026-09-07 11:22:34 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "7600fa929fe73fa7401d6bfbe86db098b69cda878289f54ac466b6c9a918540c"}, "high20": 0.349996, "high50": 0.349996, "low20": 0.321569, "low50": 0.321457}</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#2SW Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -15038,7 +15036,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -15052,16 +15050,16 @@
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>69.12</v>
+        <v>384.36</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>744</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>67.73</v>
-      </c>
-      <c r="J12" s="8" t="n">
-        <v>71.87</v>
+        <v>133</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>376.63</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>399.69</v>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
@@ -15069,24 +15067,24 @@
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>67.72</v>
+        <v>378.76</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 19:02:45 IST</t>
+          <t>2026-09-10 00:01:43 IST</t>
         </is>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1039.2</v>
+        <v>-744.52</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>10.29</v>
+        <v>10.22</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-1049.49</v>
+        <v>-754.74</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>-2.04</v>
+        <v>-1.48</v>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
@@ -15095,39 +15093,39 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>50.67</t>
+          <t>59.53</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>EMA9&lt;EMA50+Price&gt;EMA50</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 71.993154, "BB_lo": 66.775846, "Close": 69.110001, "EMA20": 68.962509, "EMA200": 64.180507, "EMA50": 68.553847, "EMA9": 68.515681, "High": 69.43, "Low": 68.519997, "Open": 68.690002, "RSI14": 50.566608, "Ret": 0.011119, "SMA20": 69.3845, "SMA50": 69.3494, "Volume": 1003500.0, "_provenance": {"captured_at_ist": "2026-09-05 00:01:07 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "06ac2e6e1d165122d46e93bfcd73629fb535999a67502c91a31dd356f9c3e061"}, "high20": 71.919998, "high50": 71.919998, "low20": 66.809998, "low50": 66.809998}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 384.914412, "BB_lo": 375.582585, "Close": 384.320007, "EMA20": 378.7841, "EMA200": 352.821272, "EMA50": 374.004443, "EMA9": 380.273856, "High": 385.049988, "Low": 381.329987, "Open": 381.329987, "RSI14": 62.100647, "Ret": 0.011235, "SMA20": 380.248499, "SMA50": 373.018998, "Volume": 152400.0, "_provenance": {"captured_at_ist": "2026-09-05 00:01:07 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "abfffaa65e4253b95842b79cc0c4fd24b91e723a3bb5a1c71936a4e0ad957b60"}, "high20": 384.809998, "high50": 384.820007, "low20": 376.040009, "low50": 354.809998}</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>#5SW EMA9&lt;EMA50+Price&gt;EMA50 | 🎯 SL Hit (live)</t>
+          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>00:18:23 IST</t>
+          <t>00:01:07 IST</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -15137,7 +15135,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -15151,16 +15149,16 @@
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>183.62</v>
+        <v>69.12</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>280</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>179.93</v>
-      </c>
-      <c r="J13" s="8" t="n">
-        <v>190.94</v>
+        <v>744</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>67.73</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>71.87</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
@@ -15168,24 +15166,24 @@
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>188.07</v>
+        <v>67.72</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:20:41 IST</t>
+          <t>2026-09-09 19:02:45 IST</t>
         </is>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1245.66</v>
+        <v>-1039.2</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>10.28</v>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v>1235.38</v>
-      </c>
-      <c r="Q13" s="5" t="n">
-        <v>2.4</v>
+        <v>10.29</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>-1049.49</v>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v>-2.04</v>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
@@ -15194,27 +15192,27 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>63.73</t>
+          <t>50.67</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
+          <t>EMA9&lt;EMA50+Price&gt;EMA50</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 191.712855, "BB_lo": 179.688148, "Close": 183.600006, "EMA20": 184.253928, "EMA200": 163.733288, "EMA50": 182.113823, "EMA9": 184.580211, "High": 183.779999, "Low": 182.270004, "Open": 183.460007, "RSI14": 49.503374, "Ret": -0.000218, "SMA20": 185.700501, "SMA50": 182.494601, "Volume": 5698700.0, "_provenance": {"captured_at_ist": "2026-09-04 00:18:23 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "6b9dec175776d38099bfb1914d0a25629c9baa7f345badebe6a04ece751808ef"}, "high20": 191.75, "high50": 191.75, "low20": 178.820007, "low50": 166.460007}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 71.993154, "BB_lo": 66.775846, "Close": 69.110001, "EMA20": 68.962509, "EMA200": 64.180507, "EMA50": 68.553847, "EMA9": 68.515681, "High": 69.43, "Low": 68.519997, "Open": 68.690002, "RSI14": 50.566608, "Ret": 0.011119, "SMA20": 69.3845, "SMA50": 69.3494, "Volume": 1003500.0, "_provenance": {"captured_at_ist": "2026-09-05 00:01:07 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "06ac2e6e1d165122d46e93bfcd73629fb535999a67502c91a31dd356f9c3e061"}, "high20": 71.919998, "high50": 71.919998, "low20": 66.809998, "low50": 66.809998}</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>#28SW Price&gt;SMA50+EMA20&gt;EMA50+2Red | Expiry 5d</t>
+          <t>#5SW EMA9&lt;EMA50+Price&gt;EMA50 | 🎯 SL Hit (live)</t>
         </is>
       </c>
     </row>
@@ -15231,12 +15229,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -15250,16 +15248,16 @@
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2393.89</v>
+        <v>183.62</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>2343.67</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>2487.16</v>
+        <v>280</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>179.93</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>190.94</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
@@ -15267,24 +15265,24 @@
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2484.67</v>
+        <v>188.07</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 01:13:45 IST</t>
+          <t>2026-09-09 00:20:41 IST</t>
         </is>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1815.66</v>
+        <v>1245.66</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>143.63</v>
+        <v>10.28</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>1672.03</v>
+        <v>1235.38</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>3.49</v>
+        <v>2.4</v>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
@@ -15293,49 +15291,49 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>63.73</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+Range&gt;1.5%+2Red</t>
+          <t>Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2795.732764, "BB_lo": 1802.401318, "Close": 2391.500977, "EMA20": 2315.842983, "EMA200": 2165.750484, "EMA50": 2125.223481, "EMA9": 2416.411271, "High": 2427.401611, "Low": 2356.188232, "Open": 2417.828369, "RSI14": 61.419955, "Ret": -0.010894, "SMA20": 2299.067041, "SMA50": 2053.502986, "Volume": 14227785690.0, "_provenance": {"captured_at_ist": "2026-09-04 00:18:23 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "bceb614e24f483f8b97a38b58fddecc676f19d19395d1082c77cf9b320b6f87a"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 1861.92041, "low50": 1772.0177}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 191.712855, "BB_lo": 179.688148, "Close": 183.600006, "EMA20": 184.253928, "EMA200": 163.733288, "EMA50": 182.113823, "EMA9": 184.580211, "High": 183.779999, "Low": 182.270004, "Open": 183.460007, "RSI14": 49.503374, "Ret": -0.000218, "SMA20": 185.700501, "SMA50": 182.494601, "Volume": 5698700.0, "_provenance": {"captured_at_ist": "2026-09-04 00:18:23 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "6b9dec175776d38099bfb1914d0a25629c9baa7f345badebe6a04ece751808ef"}, "high20": 191.75, "high50": 191.75, "low20": 178.820007, "low50": 166.460007}</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>#14SW Price&gt;SMA50+Range&gt;1.5%+2Red | 🎯 Target Hit (live)</t>
+          <t>#28SW Price&gt;SMA50+EMA20&gt;EMA50+2Red | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>00:20:14 IST</t>
+          <t>00:18:23 IST</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -15349,16 +15347,16 @@
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>52.08</v>
+        <v>2393.89</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>966</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>51.03</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>54.15</v>
+        <v>20</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>2343.67</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>2487.16</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
@@ -15366,24 +15364,24 @@
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>52.43</v>
+        <v>2484.67</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:47:43 IST</t>
+          <t>2026-09-04 01:13:45 IST</t>
         </is>
       </c>
       <c r="N15" s="4" t="n">
-        <v>342.69</v>
+        <v>1815.66</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>10.06</v>
+        <v>143.63</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>332.63</v>
-      </c>
-      <c r="Q15" s="12" t="n">
-        <v>0.66</v>
+        <v>1672.03</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>3.49</v>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
@@ -15392,97 +15390,97 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>63.36</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+Range&gt;1.5%+2Red</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 53.933542, "BB_lo": 51.668459, "Close": 52.07, "EMA20": 52.631511, "EMA200": 49.788698, "EMA50": 52.014955, "EMA9": 52.846097, "High": 52.459999, "Low": 52.02, "Open": 52.439999, "RSI14": 46.449627, "Ret": -0.011767, "SMA20": 52.801, "SMA50": 51.74, "Volume": 15500500.0, "_provenance": {"captured_at_ist": "2026-09-03 00:20:14 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "4c008560e6adf2a2b92f03ff3aba914bff4c1422744acab60897e94b0403e513"}, "high20": 54.189999, "high50": 54.189999, "low20": 51.029999, "low50": 49.849998}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2795.732764, "BB_lo": 1802.401318, "Close": 2391.500977, "EMA20": 2315.842983, "EMA200": 2165.750484, "EMA50": 2125.223481, "EMA9": 2416.411271, "High": 2427.401611, "Low": 2356.188232, "Open": 2417.828369, "RSI14": 61.419955, "Ret": -0.010894, "SMA20": 2299.067041, "SMA50": 2053.502986, "Volume": 14227785690.0, "_provenance": {"captured_at_ist": "2026-09-04 00:18:23 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "bceb614e24f483f8b97a38b58fddecc676f19d19395d1082c77cf9b320b6f87a"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 1861.92041, "low50": 1772.0177}</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>#5SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#14SW Price&gt;SMA50+Range&gt;1.5%+2Red | 🎯 Target Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>04:45:09 IST</t>
+          <t>00:20:14 IST</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>SOL-USD</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>103.03</v>
+        <v>52.08</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>630</v>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>104.73</v>
-      </c>
-      <c r="J16" s="8" t="n">
-        <v>100.08</v>
+        <v>966</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>51.03</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>54.15</v>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>102.43</v>
+        <v>52.43</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 16:46:47 IST</t>
+          <t>2026-09-08 00:47:43 IST</t>
         </is>
       </c>
       <c r="N16" s="4" t="n">
-        <v>375.85</v>
+        <v>342.69</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>194.73</v>
+        <v>10.06</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>181.12</v>
+        <v>332.63</v>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>0.28</v>
+        <v>0.66</v>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
@@ -15491,97 +15489,97 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>47.24</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>{"2Red": 1.0, "Close": 103.18, "EMA20": 103.411299, "EMA50": 103.800477, "EMA9": 103.432655, "High": 103.779999, "Low": 103.099998, "Open": 103.720001, "RSI14": 47.470892, "Ret": -0.004438, "SMA20": 103.072001, "SMA50": 104.206801, "Volume": 1157376.0, "_provenance": {"captured_at_ist": "2026-09-01 04:45:09 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "ef6d7a045ffc2750af734b317d97fc5a28f2a347c94512fa8743ba341861e0eb"}}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 53.933542, "BB_lo": 51.668459, "Close": 52.07, "EMA20": 52.631511, "EMA200": 49.788698, "EMA50": 52.014955, "EMA9": 52.846097, "High": 52.459999, "Low": 52.02, "Open": 52.439999, "RSI14": 46.449627, "Ret": -0.011767, "SMA20": 52.801, "SMA50": 51.74, "Volume": 15500500.0, "_provenance": {"captured_at_ist": "2026-09-03 00:20:14 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "4c008560e6adf2a2b92f03ff3aba914bff4c1422744acab60897e94b0403e513"}, "high20": 54.189999, "high50": 54.189999, "low20": 51.029999, "low50": 49.849998}</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>#1ID EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50 | Expiry 12h</t>
+          <t>#5SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>20:17:47 IST</t>
+          <t>04:45:09 IST</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>SOL-USD</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>171.18</v>
+        <v>103.03</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>299</v>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>167.74</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>178.01</v>
+        <v>630</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>104.73</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>100.08</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>171.43</v>
+        <v>102.43</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05 05:30:00 IST</t>
+          <t>2026-09-01 16:46:47 IST</t>
         </is>
       </c>
       <c r="N17" s="4" t="n">
-        <v>75.59999999999999</v>
+        <v>375.85</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>10.24</v>
+        <v>194.73</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>65.36</v>
+        <v>181.12</v>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
@@ -15590,27 +15588,27 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>47.24</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 177.80833, "BB_lo": 160.692668, "Close": 171.160004, "EMA20": 169.767931, "EMA200": 153.951283, "EMA50": 164.324372, "EMA9": 172.083661, "High": 171.710007, "Low": 170.589996, "Open": 171.429993, "RSI14": 57.156114, "Ret": -0.002448, "SMA20": 169.250499, "SMA50": 163.729879, "Volume": 4879300.0, "_provenance": {"captured_at_ist": "2026-08-31 20:17:47 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "9c5b13218a3d2ce328cb2f2e7d32803533390f839d04812e416383140bb7e387"}, "high20": 176.600006, "high50": 176.600006, "low20": 160.729996, "low50": 148.136666}</t>
+          <t>{"2Red": 1.0, "Close": 103.18, "EMA20": 103.411299, "EMA50": 103.800477, "EMA9": 103.432655, "High": 103.779999, "Low": 103.099998, "Open": 103.720001, "RSI14": 47.470892, "Ret": -0.004438, "SMA20": 103.072001, "SMA50": 104.206801, "Volume": 1157376.0, "_provenance": {"captured_at_ist": "2026-09-01 04:45:09 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "ef6d7a045ffc2750af734b317d97fc5a28f2a347c94512fa8743ba341861e0eb"}}</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#1ID EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50 | Expiry 12h</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15630,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -15646,16 +15644,16 @@
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>62.69</v>
+        <v>171.18</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>818</v>
-      </c>
-      <c r="I18" s="8" t="n">
-        <v>61.43</v>
-      </c>
-      <c r="J18" s="8" t="n">
-        <v>65.19</v>
+        <v>299</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>167.74</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>178.01</v>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
@@ -15663,24 +15661,24 @@
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>65.18000000000001</v>
+        <v>171.43</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:56:58 IST</t>
+          <t>2026-09-05 05:30:00 IST</t>
         </is>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2039.67</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>10.26</v>
+        <v>10.24</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>2029.41</v>
-      </c>
-      <c r="Q18" s="5" t="n">
-        <v>3.96</v>
+        <v>65.36</v>
+      </c>
+      <c r="Q18" s="12" t="n">
+        <v>0.13</v>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
@@ -15689,39 +15687,39 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA50+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 65.566256, "BB_lo": 56.952745, "Close": 62.68, "EMA20": 61.482668, "EMA200": 54.449219, "EMA50": 59.472604, "EMA9": 62.477193, "High": 62.740002, "Low": 62.119999, "Open": 62.349998, "RSI14": 62.129968, "Ret": 0.006261, "SMA20": 61.259501, "SMA50": 58.1441, "Volume": 20599600.0, "_provenance": {"captured_at_ist": "2026-08-31 20:17:47 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "f528add80b6c836a8e80c29430bea8d83def03a9307763f51342341e85b6e147"}, "high20": 64.699997, "high50": 64.699997, "low20": 57.110001, "low50": 52.619999}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 177.80833, "BB_lo": 160.692668, "Close": 171.160004, "EMA20": 169.767931, "EMA200": 153.951283, "EMA50": 164.324372, "EMA9": 172.083661, "High": 171.710007, "Low": 170.589996, "Open": 171.429993, "RSI14": 57.156114, "Ret": -0.002448, "SMA20": 169.250499, "SMA50": 163.729879, "Volume": 4879300.0, "_provenance": {"captured_at_ist": "2026-08-31 20:17:47 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "9c5b13218a3d2ce328cb2f2e7d32803533390f839d04812e416383140bb7e387"}, "high20": 176.600006, "high50": 176.600006, "low20": 160.729996, "low50": 148.136666}</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>#3SW EMA9&gt;EMA50+Range&lt;1% | Target Hit</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>01:26:29 IST</t>
+          <t>20:17:47 IST</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -15731,7 +15729,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -15741,45 +15739,45 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>767.04</v>
+        <v>62.69</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>136</v>
-      </c>
-      <c r="I19" s="8" t="n">
-        <v>759.22</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>782.23</v>
+        <v>818</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>61.43</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>65.19</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>769.79</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 00:57:20 IST</t>
+          <t>2026-09-03 00:56:58 IST</t>
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>373.46</v>
+        <v>2039.67</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>20.86</v>
+        <v>10.26</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>352.6</v>
-      </c>
-      <c r="Q19" s="12" t="n">
-        <v>0.34</v>
+        <v>2029.41</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>3.96</v>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
@@ -15788,27 +15786,27 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>62.35</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
+          <t>EMA9&gt;EMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>{"2Red": 0.0, "Close": 766.890015, "EMA20": 765.466694, "EMA50": 766.617135, "EMA9": 765.635192, "High": 767.349976, "Low": 765.52002, "Open": 765.609985, "RSI14": 55.731638, "Ret": 0.001672, "SMA20": 764.880759, "SMA50": 766.460079, "Volume": 3674140.0, "_provenance": {"captured_at_ist": "2026-08-27 01:26:29 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "3784c4c96c4bf403350ccfce032c365669554989a59e5f375dc6129ba567d139"}}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 65.566256, "BB_lo": 56.952745, "Close": 62.68, "EMA20": 61.482668, "EMA200": 54.449219, "EMA50": 59.472604, "EMA9": 62.477193, "High": 62.740002, "Low": 62.119999, "Open": 62.349998, "RSI14": 62.129968, "Ret": 0.006261, "SMA20": 61.259501, "SMA50": 58.1441, "Volume": 20599600.0, "_provenance": {"captured_at_ist": "2026-08-31 20:17:47 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "f528add80b6c836a8e80c29430bea8d83def03a9307763f51342341e85b6e147"}, "high20": 64.699997, "high50": 64.699997, "low20": 57.110001, "low50": 52.619999}</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>#16ID Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | Expiry 6h</t>
+          <t>#3SW EMA9&gt;EMA50+Range&lt;1% | Target Hit</t>
         </is>
       </c>
     </row>
@@ -15820,7 +15818,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>01:26:20 IST</t>
+          <t>01:26:29 IST</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -15830,7 +15828,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -15840,45 +15838,45 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>86.53</v>
+        <v>767.04</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>596</v>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>84.79000000000001</v>
-      </c>
-      <c r="J20" s="8" t="n">
-        <v>89.98</v>
+        <v>136</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>759.22</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>782.23</v>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>85.03</v>
+        <v>769.79</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 01:27:38 IST</t>
+          <t>2026-08-28 00:57:20 IST</t>
         </is>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-893.11</v>
+        <v>373.46</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v>-903.42</v>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v>-1.75</v>
+        <v>20.86</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>352.6</v>
+      </c>
+      <c r="Q20" s="12" t="n">
+        <v>0.34</v>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
@@ -15887,27 +15885,27 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>62.35</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>Range&lt;1%+SMA20&lt;EMA20</t>
+          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 87.262889, "BB_lo": 83.993112, "Close": 86.519997, "EMA20": 85.651886, "EMA200": 82.697308, "EMA50": 84.933173, "EMA9": 86.092409, "High": 87.010002, "Low": 86.25, "Open": 86.860001, "RSI14": 55.279506, "Ret": -0.010635, "SMA20": 85.628, "SMA50": 84.784211, "Volume": 7022700.0, "_provenance": {"captured_at_ist": "2026-08-27 01:26:20 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "4ec100efbb7eae0f145aebe59fea065b45da569430baeb0ea99b3a12db3915e9"}, "high20": 88.779999, "high50": 88.779999, "low20": 83.860001, "low50": 82.150002}</t>
+          <t>{"2Red": 0.0, "Close": 766.890015, "EMA20": 765.466694, "EMA50": 766.617135, "EMA9": 765.635192, "High": 767.349976, "Low": 765.52002, "Open": 765.609985, "RSI14": 55.731638, "Ret": 0.001672, "SMA20": 764.880759, "SMA50": 766.460079, "Volume": 3674140.0, "_provenance": {"captured_at_ist": "2026-08-27 01:26:29 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "3784c4c96c4bf403350ccfce032c365669554989a59e5f375dc6129ba567d139"}}</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>#5SW Range&lt;1%+SMA20&lt;EMA20 | Expiry 5d</t>
+          <t>#16ID Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -15929,7 +15927,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -15943,16 +15941,16 @@
         </is>
       </c>
       <c r="G21" s="4" t="n">
-        <v>113.19</v>
+        <v>86.53</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>456</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>110.92</v>
-      </c>
-      <c r="J21" s="8" t="n">
-        <v>117.71</v>
+        <v>596</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>89.98</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
@@ -15960,7 +15958,7 @@
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>111.54</v>
+        <v>85.03</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -15968,16 +15966,16 @@
         </is>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-750.65</v>
+        <v>-893.11</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>10.32</v>
+        <v>10.31</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-760.97</v>
+        <v>-903.42</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>-1.47</v>
+        <v>-1.75</v>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
@@ -15986,39 +15984,39 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>58.26</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;EMA9+Range&lt;1%</t>
+          <t>Range&lt;1%+SMA20&lt;EMA20</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 114.093707, "BB_lo": 107.914293, "Close": 113.18, "EMA20": 111.174983, "EMA200": 111.655481, "EMA50": 111.050282, "EMA9": 111.73869, "High": 113.275002, "Low": 112.294998, "Open": 112.410004, "RSI14": 58.133522, "Ret": 0.007657, "SMA20": 111.004, "SMA50": 110.009402, "Volume": 2701500.0, "_provenance": {"captured_at_ist": "2026-08-27 01:26:20 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "6517b7ae823c6f80e30c2d50df07393a2cb922775b5ebecb2ca0cf654bc08aff"}, "high20": 113.5, "high50": 114.029999, "low20": 105.492996, "low50": 105.029999}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 87.262889, "BB_lo": 83.993112, "Close": 86.519997, "EMA20": 85.651886, "EMA200": 82.697308, "EMA50": 84.933173, "EMA9": 86.092409, "High": 87.010002, "Low": 86.25, "Open": 86.860001, "RSI14": 55.279506, "Ret": -0.010635, "SMA20": 85.628, "SMA50": 84.784211, "Volume": 7022700.0, "_provenance": {"captured_at_ist": "2026-08-27 01:26:20 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "4ec100efbb7eae0f145aebe59fea065b45da569430baeb0ea99b3a12db3915e9"}, "high20": 88.779999, "high50": 88.779999, "low20": 83.860001, "low50": 82.150002}</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>#3SW Price&gt;EMA9+Range&lt;1% | Expiry 5d</t>
+          <t>#5SW Range&lt;1%+SMA20&lt;EMA20 | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>00:19:41 IST</t>
+          <t>01:26:20 IST</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -16028,7 +16026,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -16042,16 +16040,16 @@
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>377.11</v>
+        <v>113.19</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>133</v>
-      </c>
-      <c r="I22" s="8" t="n">
-        <v>369.53</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>392.15</v>
+        <v>456</v>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>110.92</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>117.71</v>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
@@ -16059,24 +16057,24 @@
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>379.32</v>
+        <v>111.54</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31 12:20:47 IST</t>
+          <t>2026-09-01 01:27:38 IST</t>
         </is>
       </c>
       <c r="N22" s="4" t="n">
-        <v>294.2</v>
+        <v>-750.65</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v>284.17</v>
-      </c>
-      <c r="Q22" s="12" t="n">
-        <v>0.57</v>
+        <v>10.32</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v>-760.97</v>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v>-1.47</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
@@ -16090,34 +16088,34 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>Range&lt;1%+SMA20&lt;EMA20</t>
+          <t>Price&gt;EMA9+Range&lt;1%</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 390.418284, "BB_lo": 363.717712, "Close": 377.070007, "EMA20": 377.20007, "EMA200": 349.68499, "EMA50": 371.828667, "EMA9": 378.840176, "High": 378.0, "Low": 376.480011, "Open": 377.920013, "RSI14": 52.14451, "Ret": -0.003093, "SMA20": 377.067998, "SMA50": 371.565996, "Volume": 2963600.0, "_provenance": {"captured_at_ist": "2026-08-26 00:19:41 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "7d4507f7724401cf8e473ac67923b34d856a349cb42c70c444777355cfcb7c9b"}, "high20": 385.119995, "high50": 385.119995, "low20": 360.200012, "low50": 356.723865}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 114.093707, "BB_lo": 107.914293, "Close": 113.18, "EMA20": 111.174983, "EMA200": 111.655481, "EMA50": 111.050282, "EMA9": 111.73869, "High": 113.275002, "Low": 112.294998, "Open": 112.410004, "RSI14": 58.133522, "Ret": 0.007657, "SMA20": 111.004, "SMA50": 110.009402, "Volume": 2701500.0, "_provenance": {"captured_at_ist": "2026-08-27 01:26:20 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "6517b7ae823c6f80e30c2d50df07393a2cb922775b5ebecb2ca0cf654bc08aff"}, "high20": 113.5, "high50": 114.029999, "low20": 105.492996, "low50": 105.029999}</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>#3SW Range&lt;1%+SMA20&lt;EMA20 | Expiry 5d</t>
+          <t>#3SW Price&gt;EMA9+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>00:21:29 IST</t>
+          <t>00:19:41 IST</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -16127,7 +16125,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>VTI</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -16141,16 +16139,16 @@
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>174.55</v>
+        <v>377.11</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>275</v>
-      </c>
-      <c r="I23" s="8" t="n">
-        <v>171.04</v>
-      </c>
-      <c r="J23" s="8" t="n">
-        <v>181.51</v>
+        <v>133</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>369.53</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>392.15</v>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
@@ -16158,24 +16156,24 @@
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>171.02</v>
+        <v>379.32</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:08:12 IST</t>
+          <t>2026-08-31 12:20:47 IST</t>
         </is>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-969.95</v>
+        <v>294.2</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v>-979.55</v>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v>-2.04</v>
+        <v>10.03</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>284.17</v>
+      </c>
+      <c r="Q23" s="12" t="n">
+        <v>0.57</v>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
@@ -16184,39 +16182,39 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>Range&lt;1%+SMA20&lt;EMA20</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 175.864131, "BB_lo": 159.419869, "Close": 174.529999, "EMA20": 168.30809, "EMA200": 154.030413, "EMA50": 162.961143, "EMA9": 171.440751, "High": 174.830002, "Low": 173.330002, "Open": 174.410004, "RSI14": 68.059204, "Ret": -0.000515, "SMA20": 167.642, "SMA50": 162.1152, "Volume": 4415397.0, "_provenance": {"captured_at_ist": "2026-08-25 00:21:29 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "0e5a554d6cdf867147a863dbaa87285229b6bdde8405ef04e62d923f28408cf2"}, "high20": 176.600006, "high50": 176.600006, "low20": 160.729996, "low50": 148.789993}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 390.418284, "BB_lo": 363.717712, "Close": 377.070007, "EMA20": 377.20007, "EMA200": 349.68499, "EMA50": 371.828667, "EMA9": 378.840176, "High": 378.0, "Low": 376.480011, "Open": 377.920013, "RSI14": 52.14451, "Ret": -0.003093, "SMA20": 377.067998, "SMA50": 371.565996, "Volume": 2963600.0, "_provenance": {"captured_at_ist": "2026-08-26 00:19:41 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "7d4507f7724401cf8e473ac67923b34d856a349cb42c70c444777355cfcb7c9b"}, "high20": 385.119995, "high50": 385.119995, "low20": 360.200012, "low50": 356.723865}</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | ðŸŽ¯ SL Hit (live)</t>
+          <t>#3SW Range&lt;1%+SMA20&lt;EMA20 | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>07:49:44 IST</t>
+          <t>00:21:29 IST</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -16226,7 +16224,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -16240,16 +16238,16 @@
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>713.51</v>
+        <v>174.55</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="I24" s="8" t="n">
-        <v>699.17</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>741.98</v>
+        <v>275</v>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>171.04</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>181.51</v>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
@@ -16257,24 +16255,24 @@
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>716.36</v>
+        <v>171.02</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 08:16:22 IST</t>
+          <t>2026-08-28 21:08:12 IST</t>
         </is>
       </c>
       <c r="N24" s="4" t="n">
-        <v>193.69</v>
+        <v>-969.95</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>183.99</v>
-      </c>
-      <c r="Q24" s="12" t="n">
-        <v>0.38</v>
+        <v>9.6</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v>-979.55</v>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v>-2.04</v>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
@@ -16283,39 +16281,39 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>RSI&gt;50+SMA20&lt;SMA50</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 749.746157, "BB_lo": 668.630845, "Close": 713.440002, "EMA20": 714.415351, "EMA200": 659.614421, "EMA50": 708.78849, "EMA9": 717.391898, "High": 715.669983, "Low": 709.200012, "Open": 715.22998, "RSI14": 50.149844, "Ret": 0.003531, "SMA20": 709.188501, "SMA50": 713.441602, "Volume": 33297600.0, "_provenance": {"captured_at_ist": "2026-08-24 07:49:44 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "89a195f1c565d7eeec6103b45df5fc0c4a8cd08b92109c8f6c78f6dbe7e34347"}, "high20": 734.580017, "high50": 745.450012, "low20": 661.140015, "low50": 661.140015}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 175.864131, "BB_lo": 159.419869, "Close": 174.529999, "EMA20": 168.30809, "EMA200": 154.030413, "EMA50": 162.961143, "EMA9": 171.440751, "High": 174.830002, "Low": 173.330002, "Open": 174.410004, "RSI14": 68.059204, "Ret": -0.000515, "SMA20": 167.642, "SMA50": 162.1152, "Volume": 4415397.0, "_provenance": {"captured_at_ist": "2026-08-25 00:21:29 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "0e5a554d6cdf867147a863dbaa87285229b6bdde8405ef04e62d923f28408cf2"}, "high20": 176.600006, "high50": 176.600006, "low20": 160.729996, "low50": 148.789993}</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>#66SW RSI&gt;50+SMA20&lt;SMA50 | Expiry 5d</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | ðŸŽ¯ SL Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>07:51:10 IST</t>
+          <t>07:49:44 IST</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -16325,7 +16323,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -16339,16 +16337,16 @@
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>45.08</v>
+        <v>713.51</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1105</v>
-      </c>
-      <c r="I25" s="8" t="n">
-        <v>44.18</v>
-      </c>
-      <c r="J25" s="8" t="n">
-        <v>46.88</v>
+        <v>68</v>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>699.17</v>
+      </c>
+      <c r="J25" s="11" t="n">
+        <v>741.98</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
@@ -16356,24 +16354,24 @@
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>44.66</v>
+        <v>716.36</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 09:07:28 IST</t>
+          <t>2026-08-29 08:16:22 IST</t>
         </is>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-469.04</v>
+        <v>193.69</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v>-479</v>
-      </c>
-      <c r="Q25" s="13" t="n">
-        <v>-0.96</v>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="P25" s="5" t="n">
+        <v>183.99</v>
+      </c>
+      <c r="Q25" s="12" t="n">
+        <v>0.38</v>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
@@ -16382,27 +16380,27 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>66</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&lt;Open</t>
+          <t>RSI&gt;50+SMA20&lt;SMA50</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 46.03132, "BB_lo": 44.109681, "Close": 45.080002, "EMA20": 44.957695, "EMA200": 43.466243, "EMA50": 44.780011, "EMA9": 44.94812, "High": 45.255001, "Low": 44.933998, "Open": 45.200001, "RSI14": 51.888379, "Ret": 0.0, "SMA20": 45.0705, "SMA50": 44.8678, "Volume": 3968900.0, "_provenance": {"captured_at_ist": "2026-08-23 07:51:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "45c6a11f08d41357e9b6038a6644a0c54ee887b4d9d2010526bd8ea4b0ea5250"}, "high20": 46.455002, "high50": 46.455002, "low20": 44.009998, "low50": 43.48}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 749.746157, "BB_lo": 668.630845, "Close": 713.440002, "EMA20": 714.415351, "EMA200": 659.614421, "EMA50": 708.78849, "EMA9": 717.391898, "High": 715.669983, "Low": 709.200012, "Open": 715.22998, "RSI14": 50.149844, "Ret": 0.003531, "SMA20": 709.188501, "SMA50": 713.441602, "Volume": 33297600.0, "_provenance": {"captured_at_ist": "2026-08-24 07:49:44 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "89a195f1c565d7eeec6103b45df5fc0c4a8cd08b92109c8f6c78f6dbe7e34347"}, "high20": 734.580017, "high50": 745.450012, "low20": 661.140015, "low50": 661.140015}</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>#57SW Price&gt;SMA20+EMA9&lt;EMA20+Close&lt;Open | Expiry 5d</t>
+          <t>#66SW RSI&gt;50+SMA20&lt;SMA50 | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -16419,12 +16417,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -16437,17 +16435,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G26" s="9" t="n">
-        <v>0.3462</v>
+      <c r="G26" s="4" t="n">
+        <v>45.08</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I26" s="10" t="n">
-        <v>0.3382</v>
-      </c>
-      <c r="J26" s="10" t="n">
-        <v>0.3589</v>
+        <v>1105</v>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>44.18</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>46.88</v>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
@@ -16455,24 +16453,24 @@
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0.3372</v>
+        <v>44.66</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 02:06:32 IST</t>
+          <t>2026-08-28 09:07:28 IST</t>
         </is>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-90.15000000000001</v>
+        <v>-469.04</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>10.39</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-100.54</v>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v>-2.9</v>
+        <v>-479</v>
+      </c>
+      <c r="Q26" s="13" t="n">
+        <v>-0.96</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
@@ -16481,27 +16479,27 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>57</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&lt;Open</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 0.342604, "BB_lo": 0.322249, "Close": 0.345137, "EMA20": 0.333753, "EMA200": 0.322532, "EMA50": 0.330808, "EMA9": 0.337211, "High": 0.345367, "Low": 0.34419, "Open": 0.344229, "RSI14": 75.347643, "Ret": 0.005205, "SMA20": 0.332427, "SMA50": 0.329547, "Volume": 896564352.0, "_provenance": {"captured_at_ist": "2026-08-23 07:51:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "841d75978c0b90d3d955daa219375d748b86c110612710892971f186fbc6b405"}, "high20": 0.34335, "high50": 0.34335, "low20": 0.325217, "low50": 0.316794}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 46.03132, "BB_lo": 44.109681, "Close": 45.080002, "EMA20": 44.957695, "EMA200": 43.466243, "EMA50": 44.780011, "EMA9": 44.94812, "High": 45.255001, "Low": 44.933998, "Open": 45.200001, "RSI14": 51.888379, "Ret": 0.0, "SMA20": 45.0705, "SMA50": 44.8678, "Volume": 3968900.0, "_provenance": {"captured_at_ist": "2026-08-23 07:51:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "45c6a11f08d41357e9b6038a6644a0c54ee887b4d9d2010526bd8ea4b0ea5250"}, "high20": 46.455002, "high50": 46.455002, "low20": 44.009998, "low50": 43.48}</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | ðŸŽ¯ SL Hit (live)</t>
+          <t>#57SW Price&gt;SMA20+EMA9&lt;EMA20+Close&lt;Open | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -16518,12 +16516,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -16536,17 +16534,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
-        <v>377.9</v>
+      <c r="G27" s="8" t="n">
+        <v>0.3462</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>130</v>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>370.3</v>
-      </c>
-      <c r="J27" s="8" t="n">
-        <v>392.97</v>
+        <v>10000</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0.3589</v>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
@@ -16554,24 +16552,24 @@
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>380.85</v>
+        <v>0.3372</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 09:07:28 IST</t>
+          <t>2026-08-26 02:06:32 IST</t>
         </is>
       </c>
       <c r="N27" s="4" t="n">
-        <v>383.75</v>
+        <v>-90.15000000000001</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="P27" s="5" t="n">
-        <v>373.92</v>
-      </c>
-      <c r="Q27" s="12" t="n">
-        <v>0.76</v>
+        <v>10.39</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v>-100.54</v>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v>-2.9</v>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
@@ -16580,39 +16578,39 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 391.993875, "BB_lo": 360.752118, "Close": 377.859985, "EMA20": 377.034739, "EMA200": 351.317404, "EMA50": 371.633734, "EMA9": 379.076055, "High": 379.179993, "Low": 376.839996, "Open": 377.890015, "RSI14": 53.807886, "Ret": 0.003106, "SMA20": 376.372997, "SMA50": 370.408998, "Volume": 141700.0, "_provenance": {"captured_at_ist": "2026-08-23 07:51:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "dc46343d0c2668e3d0437189c8457963c0a5445a4be1eb6c84facfbc8ebd4d16"}, "high20": 384.820007, "high50": 384.820007, "low20": 358.170013, "low50": 354.809998}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 0.342604, "BB_lo": 0.322249, "Close": 0.345137, "EMA20": 0.333753, "EMA200": 0.322532, "EMA50": 0.330808, "EMA9": 0.337211, "High": 0.345367, "Low": 0.34419, "Open": 0.344229, "RSI14": 75.347643, "Ret": 0.005205, "SMA20": 0.332427, "SMA50": 0.329547, "Volume": 896564352.0, "_provenance": {"captured_at_ist": "2026-08-23 07:51:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "841d75978c0b90d3d955daa219375d748b86c110612710892971f186fbc6b405"}, "high20": 0.34335, "high50": 0.34335, "low20": 0.325217, "low50": 0.316794}</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | ðŸŽ¯ SL Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>00:19:34 IST</t>
+          <t>07:51:10 IST</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -16622,7 +16620,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -16636,16 +16634,16 @@
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>63.56</v>
+        <v>377.9</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>782</v>
-      </c>
-      <c r="I28" s="8" t="n">
-        <v>62.28</v>
-      </c>
-      <c r="J28" s="8" t="n">
-        <v>66.09999999999999</v>
+        <v>130</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>370.3</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>392.97</v>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
@@ -16653,24 +16651,24 @@
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>63.62</v>
+        <v>380.85</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24 00:57:24 IST</t>
+          <t>2026-08-28 09:07:28 IST</t>
         </is>
       </c>
       <c r="N28" s="4" t="n">
-        <v>45.85</v>
+        <v>383.75</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>9.94</v>
+        <v>9.83</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>35.91</v>
+        <v>373.92</v>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
@@ -16679,27 +16677,27 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>59.53</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA50+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>{"EMA200": 54.253942, "Open": 63.41, "2Red": 0.0, "Volume": 20822618.0, "EMA20": 59.820197, "BB_lo": 56.181538, "EMA50": 58.261513, "SMA50": 57.1629, "low20": 57.110001, "RSI14": 72.551139, "low50": 52.619999, "EMA9": 61.242966, "2Green": 1.0, "Ret": 0.01558, "Low": 63.115002, "high50": 62.689999, "High": 63.709999, "Close": 63.555, "BB_hi": 63.099963, "SMA20": 59.64075, "high20": 62.689999}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 391.993875, "BB_lo": 360.752118, "Close": 377.859985, "EMA20": 377.034739, "EMA200": 351.317404, "EMA50": 371.633734, "EMA9": 379.076055, "High": 379.179993, "Low": 376.839996, "Open": 377.890015, "RSI14": 53.807886, "Ret": 0.003106, "SMA20": 376.372997, "SMA50": 370.408998, "Volume": 141700.0, "_provenance": {"captured_at_ist": "2026-08-23 07:51:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "dc46343d0c2668e3d0437189c8457963c0a5445a4be1eb6c84facfbc8ebd4d16"}, "high20": 384.820007, "high50": 384.820007, "low20": 358.170013, "low50": 354.809998}</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>#3SW EMA9&gt;EMA50+Range&lt;1% | Expiry 5d</t>
+          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -16711,7 +16709,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>00:19:33 IST</t>
+          <t>00:19:34 IST</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -16721,7 +16719,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -16735,16 +16733,16 @@
         </is>
       </c>
       <c r="G29" s="4" t="n">
-        <v>717.71</v>
+        <v>63.56</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="I29" s="8" t="n">
-        <v>703.29</v>
-      </c>
-      <c r="J29" s="8" t="n">
-        <v>746.35</v>
+        <v>782</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>62.28</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>66.09999999999999</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
@@ -16752,7 +16750,7 @@
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>713.34</v>
+        <v>63.62</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
@@ -16760,16 +16758,16 @@
         </is>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-301.62</v>
+        <v>45.85</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v>-311.52</v>
-      </c>
-      <c r="Q29" s="13" t="n">
-        <v>-0.63</v>
+        <v>9.94</v>
+      </c>
+      <c r="P29" s="5" t="n">
+        <v>35.91</v>
+      </c>
+      <c r="Q29" s="12" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
@@ -16778,39 +16776,39 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>60.94</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA9&gt;EMA20+2Red</t>
+          <t>EMA9&gt;EMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t>{"EMA200": 658.01956, "Open": 720.219971, "2Red": 1.0, "Volume": 38190856.0, "EMA20": 714.783424, "BB_lo": 663.9257, "EMA50": 708.199326, "SMA50": 712.987002, "low20": 661.140015, "RSI14": 52.242633, "low50": 661.140015, "EMA9": 721.308924, "2Green": 0.0, "Ret": -0.016756, "Low": 715.919983, "high50": 745.450012, "High": 722.130005, "Close": 717.640015, "BB_hi": 748.573299, "SMA20": 706.2495, "high20": 734.580017}</t>
+          <t>{"EMA200": 54.253942, "Open": 63.41, "2Red": 0.0, "Volume": 20822618.0, "EMA20": 59.820197, "BB_lo": 56.181538, "EMA50": 58.261513, "SMA50": 57.1629, "low20": 57.110001, "RSI14": 72.551139, "low50": 52.619999, "EMA9": 61.242966, "2Green": 1.0, "Ret": 0.01558, "Low": 63.115002, "high50": 62.689999, "High": 63.709999, "Close": 63.555, "BB_hi": 63.099963, "SMA20": 59.64075, "high20": 62.689999}</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>#37SW Price&gt;SMA50+EMA9&gt;EMA20+2Red | Expiry 5d</t>
+          <t>#3SW EMA9&gt;EMA50+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>00:20:52 IST</t>
+          <t>00:19:33 IST</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -16820,7 +16818,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -16834,16 +16832,16 @@
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>380.99</v>
+        <v>717.71</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>135</v>
-      </c>
-      <c r="I30" s="8" t="n">
-        <v>373.33</v>
-      </c>
-      <c r="J30" s="8" t="n">
-        <v>396.19</v>
+        <v>69</v>
+      </c>
+      <c r="I30" s="11" t="n">
+        <v>703.29</v>
+      </c>
+      <c r="J30" s="11" t="n">
+        <v>746.35</v>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
@@ -16851,24 +16849,24 @@
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>377.74</v>
+        <v>713.34</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23 00:57:48 IST</t>
+          <t>2026-08-24 00:57:24 IST</t>
         </is>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-438.45</v>
+        <v>-301.62</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.29</v>
+        <v>9.9</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-448.74</v>
+        <v>-311.52</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>-0.87</v>
+        <v>-0.63</v>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
@@ -16877,49 +16875,49 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>37</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>60.94</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+EMA9&gt;EMA20+2Red</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "BB_lo": 356.336918, "BB_hi": 391.566088, "EMA50": 370.481576, "SMA50": 369.201801, "high20": 384.820007, "low50": 354.809998, "Open": 382.649994, "Volume": 101666.0, "2Red": 1.0, "EMA200": 350.231559, "RSI14": 60.286192, "low20": 358.170013, "Ret": -0.00413, "EMA20": 376.443558, "high50": 384.820007, "Low": 380.609985, "Close": 380.950104, "EMA9": 380.399819, "SMA20": 373.951503, "High": 382.875}</t>
+          <t>{"EMA200": 658.01956, "Open": 720.219971, "2Red": 1.0, "Volume": 38190856.0, "EMA20": 714.783424, "BB_lo": 663.9257, "EMA50": 708.199326, "SMA50": 712.987002, "low20": 661.140015, "RSI14": 52.242633, "low50": 661.140015, "EMA9": 721.308924, "2Green": 0.0, "Ret": -0.016756, "Low": 715.919983, "high50": 745.450012, "High": 722.130005, "Close": 717.640015, "BB_hi": 748.573299, "SMA20": 706.2495, "high20": 734.580017}</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#37SW Price&gt;SMA50+EMA9&gt;EMA20+2Red | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>11:52:58 IST</t>
+          <t>00:20:52 IST</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>VASWANI.NS</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -16929,45 +16927,45 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>LONG_BOUNCE_5m</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>46.63</v>
+        <v>380.99</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1333</v>
-      </c>
-      <c r="I31" s="8" t="n">
-        <v>45.88</v>
-      </c>
-      <c r="J31" s="8" t="n">
-        <v>48.33</v>
+        <v>135</v>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>373.33</v>
+      </c>
+      <c r="J31" s="11" t="n">
+        <v>396.19</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>45.83</v>
+        <v>377.74</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17 12:09:41 IST</t>
+          <t>2026-08-23 00:57:48 IST</t>
         </is>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1066.4</v>
+        <v>-438.45</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>186.47</v>
+        <v>10.29</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-1252.87</v>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v>-2.02</v>
+        <v>-448.74</v>
+      </c>
+      <c r="Q31" s="13" t="n">
+        <v>-0.87</v>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
@@ -16976,27 +16974,27 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>59.53</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down 10:30-12:30</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>{"Close": 46.58, "Volume": 1153, "VolAvg20": 237.0, "RSI14": 31.4, "Drop_pct": 8.31, "BelowVWAP": true, "VWAPDown": true, "NIFTY_gap_pct": -0.09}</t>
+          <t>{"2Green": 0.0, "BB_lo": 356.336918, "BB_hi": 391.566088, "EMA50": 370.481576, "SMA50": 369.201801, "high20": 384.820007, "low50": 354.809998, "Open": 382.649994, "Volume": 101666.0, "2Red": 1.0, "EMA200": 350.231559, "RSI14": 60.286192, "low20": 358.170013, "Ret": -0.00413, "EMA20": 376.443558, "high50": 384.820007, "Low": 380.609985, "Close": 380.950104, "EMA9": 380.399819, "SMA20": 373.951503, "High": 382.875}</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>#935ID Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down | ðŸŽ¯ SL Hit (live)</t>
+          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -17008,7 +17006,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>11:10:50 IST</t>
+          <t>11:52:58 IST</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -17018,7 +17016,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>LAXMIINDIA.NS</t>
+          <t>VASWANI.NS</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -17032,16 +17030,16 @@
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>124.98</v>
+        <v>46.63</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>510</v>
-      </c>
-      <c r="I32" s="8" t="n">
-        <v>123.02</v>
-      </c>
-      <c r="J32" s="8" t="n">
-        <v>129.57</v>
+        <v>1333</v>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="J32" s="11" t="n">
+        <v>48.33</v>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
@@ -17049,24 +17047,24 @@
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>129.47</v>
+        <v>45.83</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17 14:43:12 IST</t>
+          <t>2026-08-17 12:09:41 IST</t>
         </is>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2289.9</v>
+        <v>-1066.4</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>191.22</v>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>2098.68</v>
-      </c>
-      <c r="Q32" s="5" t="n">
-        <v>3.29</v>
+        <v>186.47</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v>-1252.87</v>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v>-2.02</v>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
@@ -17090,34 +17088,34 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>{"Close": 124.89, "Volume": 16581, "VolAvg20": 2144.0, "RSI14": 40.9, "Drop_pct": 3.7, "BelowVWAP": true, "VWAPDown": true, "NIFTY_gap_pct": -0.09}</t>
+          <t>{"Close": 46.58, "Volume": 1153, "VolAvg20": 237.0, "RSI14": 31.4, "Drop_pct": 8.31, "BelowVWAP": true, "VWAPDown": true, "NIFTY_gap_pct": -0.09}</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>#935ID Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down | ðŸŽ¯ Target Hit (live)</t>
+          <t>#935ID Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down | ðŸŽ¯ SL Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>07:48:23 IST</t>
+          <t>11:10:50 IST</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>LAXMIINDIA.NS</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -17127,45 +17125,45 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>LONG_BOUNCE_5m</t>
         </is>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1880</v>
+        <v>124.98</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I33" s="8" t="n">
-        <v>1840.56</v>
-      </c>
-      <c r="J33" s="8" t="n">
-        <v>1953.24</v>
+        <v>510</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>123.02</v>
+      </c>
+      <c r="J33" s="11" t="n">
+        <v>129.57</v>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1951.29</v>
+        <v>129.47</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 20:30:05 IST</t>
+          <t>2026-08-17 14:43:12 IST</t>
         </is>
       </c>
       <c r="N33" s="4" t="n">
-        <v>1782.17</v>
+        <v>2289.9</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>141</v>
+        <v>191.22</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>1641.17</v>
+        <v>2098.68</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>3.49</v>
+        <v>3.29</v>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
@@ -17174,27 +17172,27 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
+          <t>Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down 10:30-12:30</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t>{"High": 1881.228882, "Ret": -0.001345, "low20": 1821.485107, "2Green": 0.0, "high50": 1976.460205, "RSI14": 50.528767, "EMA50": 1864.50293, "Close": 1878.119995, "EMA200": 2128.981002, "SMA20": 1888.450458, "Open": 1880.982056, "low50": 1510.505859, "high20": 1976.460205, "BB_hi": 1932.730084, "Volume": 3153563392.0, "BB_lo": 1844.170831, "Low": 1876.0802, "EMA9": 1884.579071, "EMA20": 1882.056983, "SMA50": 1830.116287, "2Red": 1.0}</t>
+          <t>{"Close": 124.89, "Volume": 16581, "VolAvg20": 2144.0, "RSI14": 40.9, "Drop_pct": 3.7, "BelowVWAP": true, "VWAPDown": true, "NIFTY_gap_pct": -0.09}</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | ðŸŽ¯ Target Hit (live)</t>
+          <t>#935ID Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down | ðŸŽ¯ Target Hit (live)</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17214,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -17229,17 +17227,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G34" s="9" t="n">
-        <v>0.332</v>
+      <c r="G34" s="4" t="n">
+        <v>1880</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I34" s="10" t="n">
-        <v>0.3244</v>
-      </c>
-      <c r="J34" s="10" t="n">
-        <v>0.3442</v>
+        <v>25</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>1840.56</v>
+      </c>
+      <c r="J34" s="11" t="n">
+        <v>1953.24</v>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
@@ -17247,24 +17245,24 @@
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0.3369</v>
+        <v>1951.29</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21 07:50:22 IST</t>
+          <t>2026-08-19 20:30:05 IST</t>
         </is>
       </c>
       <c r="N34" s="4" t="n">
-        <v>48.75</v>
+        <v>1782.17</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>141</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>38.79</v>
+        <v>1641.17</v>
       </c>
       <c r="Q34" s="5" t="n">
-        <v>1.17</v>
+        <v>3.49</v>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
@@ -17273,27 +17271,27 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t>{"High": 0.330999, "Ret": -0.004433, "low20": 0.323269, "2Green": 0.0, "high50": 0.337903, "RSI14": 53.511744, "EMA50": 0.328876, "Close": 0.330981, "EMA200": 0.321504, "SMA20": 0.32883, "Open": 0.330921, "low50": 0.314034, "high20": 0.337903, "BB_hi": 0.335516, "Volume": 317728800.0, "BB_lo": 0.322143, "Low": 0.330715, "EMA9": 0.331613, "EMA20": 0.33003, "SMA50": 0.327135, "2Red": 1.0}</t>
+          <t>{"High": 1881.228882, "Ret": -0.001345, "low20": 1821.485107, "2Green": 0.0, "high50": 1976.460205, "RSI14": 50.528767, "EMA50": 1864.50293, "Close": 1878.119995, "EMA200": 2128.981002, "SMA20": 1888.450458, "Open": 1880.982056, "low50": 1510.505859, "high20": 1976.460205, "BB_hi": 1932.730084, "Volume": 3153563392.0, "BB_lo": 1844.170831, "Low": 1876.0802, "EMA9": 1884.579071, "EMA20": 1882.056983, "SMA50": 1830.116287, "2Red": 1.0}</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
+          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | ðŸŽ¯ Target Hit (live)</t>
         </is>
       </c>
     </row>
@@ -17310,12 +17308,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -17328,17 +17326,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
-        <v>167.39</v>
+      <c r="G35" s="8" t="n">
+        <v>0.332</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>305</v>
-      </c>
-      <c r="I35" s="8" t="n">
-        <v>164.02</v>
-      </c>
-      <c r="J35" s="8" t="n">
-        <v>174.06</v>
+        <v>10000</v>
+      </c>
+      <c r="I35" s="9" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>0.3442</v>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
@@ -17346,24 +17344,24 @@
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>174.04</v>
+        <v>0.3369</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 19:18:22 IST</t>
+          <t>2026-08-21 07:50:22 IST</t>
         </is>
       </c>
       <c r="N35" s="4" t="n">
-        <v>2029.04</v>
+        <v>48.75</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>10.21</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="P35" s="5" t="n">
-        <v>2018.83</v>
+        <v>38.79</v>
       </c>
       <c r="Q35" s="5" t="n">
-        <v>3.95</v>
+        <v>1.17</v>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
@@ -17372,27 +17370,27 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t>{"High": 167.770004, "Ret": -0.005998, "low20": 157.229996, "2Green": 0.0, "high50": 169.710007, "RSI14": 61.944112, "EMA50": 160.375176, "Close": 167.369995, "EMA200": 152.877762, "SMA20": 164.259, "Open": 167.660004, "low50": 146.070007, "high20": 169.710007, "BB_hi": 170.39623, "Volume": 5020700.0, "BB_lo": 158.121771, "Low": 166.449997, "EMA9": 166.656228, "EMA20": 164.675214, "SMA50": 159.8202, "2Red": 1.0}</t>
+          <t>{"High": 0.330999, "Ret": -0.004433, "low20": 0.323269, "2Green": 0.0, "high50": 0.337903, "RSI14": 53.511744, "EMA50": 0.328876, "Close": 0.330981, "EMA200": 0.321504, "SMA20": 0.32883, "Open": 0.330921, "low50": 0.314034, "high20": 0.337903, "BB_hi": 0.335516, "Volume": 317728800.0, "BB_lo": 0.322143, "Low": 0.330715, "EMA9": 0.331613, "EMA20": 0.33003, "SMA50": 0.327135, "2Red": 1.0}</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | ðŸŽ¯ Target Hit (live)</t>
+          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -17414,7 +17412,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -17428,16 +17426,16 @@
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>52.55</v>
+        <v>167.39</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>972</v>
-      </c>
-      <c r="I36" s="8" t="n">
-        <v>51.49</v>
-      </c>
-      <c r="J36" s="8" t="n">
-        <v>54.64</v>
+        <v>305</v>
+      </c>
+      <c r="I36" s="11" t="n">
+        <v>164.02</v>
+      </c>
+      <c r="J36" s="11" t="n">
+        <v>174.06</v>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
@@ -17445,24 +17443,24 @@
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>52.41</v>
+        <v>174.04</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21 07:50:22 IST</t>
+          <t>2026-08-19 19:18:22 IST</t>
         </is>
       </c>
       <c r="N36" s="4" t="n">
-        <v>-131.46</v>
+        <v>2029.04</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v>-141.68</v>
-      </c>
-      <c r="Q36" s="13" t="n">
-        <v>-0.28</v>
+        <v>10.21</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>2018.83</v>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>3.95</v>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
@@ -17471,39 +17469,39 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t>{"High": 52.650002, "Ret": 0.004397, "low20": 49.849998, "2Green": 0.0, "high50": 53.599998, "RSI14": 55.668613, "EMA50": 51.516289, "Close": 52.540001, "EMA200": 49.67764, "SMA20": 51.7285, "Open": 52.459999, "low50": 49.57, "high20": 53.599998, "BB_hi": 53.772381, "Volume": 7479000.0, "BB_lo": 49.684619, "Low": 52.27, "EMA9": 52.4289, "EMA20": 51.988963, "SMA50": 51.383, "2Red": 0.0}</t>
+          <t>{"High": 167.770004, "Ret": -0.005998, "low20": 157.229996, "2Green": 0.0, "high50": 169.710007, "RSI14": 61.944112, "EMA50": 160.375176, "Close": 167.369995, "EMA200": 152.877762, "SMA20": 164.259, "Open": 167.660004, "low50": 146.070007, "high20": 169.710007, "BB_hi": 170.39623, "Volume": 5020700.0, "BB_lo": 158.121771, "Low": 166.449997, "EMA9": 166.656228, "EMA20": 164.675214, "SMA50": 159.8202, "2Red": 1.0}</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>#2SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | ðŸŽ¯ Target Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>00:20:31 IST</t>
+          <t>07:48:23 IST</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -17513,7 +17511,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -17527,16 +17525,16 @@
         </is>
       </c>
       <c r="G37" s="4" t="n">
-        <v>381.8</v>
+        <v>52.55</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>131</v>
-      </c>
-      <c r="I37" s="8" t="n">
-        <v>374.12</v>
-      </c>
-      <c r="J37" s="8" t="n">
-        <v>397.03</v>
+        <v>972</v>
+      </c>
+      <c r="I37" s="11" t="n">
+        <v>51.49</v>
+      </c>
+      <c r="J37" s="11" t="n">
+        <v>54.64</v>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
@@ -17544,24 +17542,24 @@
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>380.91</v>
+        <v>52.41</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18 00:20:50 IST</t>
+          <t>2026-08-21 07:50:22 IST</t>
         </is>
       </c>
       <c r="N37" s="4" t="n">
-        <v>-116.33</v>
+        <v>-131.46</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>10</v>
+        <v>10.22</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-126.33</v>
+        <v>-141.68</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>-0.25</v>
+        <v>-0.28</v>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
@@ -17570,12 +17568,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
@@ -17585,24 +17583,24 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>{"Low": 380.838501, "EMA9": 378.755146, "Ret": 0.002468, "High": 382.554993, "BB_lo": 355.440257, "SMA20": 371.858, "RSI14": 63.686748, "EMA20": 374.422536, "low20": 358.170013, "high50": 384.820007, "2Red": 0.0, "SMA50": 368.8264, "Open": 382.660004, "2Green": 0.0, "high20": 384.820007, "EMA200": 349.15793, "Close": 381.76001, "low50": 354.809998, "BB_hi": 388.275744, "Volume": 171118.0, "EMA50": 368.980107}</t>
+          <t>{"High": 52.650002, "Ret": 0.004397, "low20": 49.849998, "2Green": 0.0, "high50": 53.599998, "RSI14": 55.668613, "EMA50": 51.516289, "Close": 52.540001, "EMA200": 49.67764, "SMA20": 51.7285, "Open": 52.459999, "low50": 49.57, "high20": 53.599998, "BB_hi": 53.772381, "Volume": 7479000.0, "BB_lo": 49.684619, "Low": 52.27, "EMA9": 52.4289, "EMA20": 51.988963, "SMA50": 51.383, "2Red": 0.0}</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#2SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>00:43:12 IST</t>
+          <t>00:20:31 IST</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -17612,7 +17610,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -17626,16 +17624,16 @@
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>717.42</v>
+        <v>381.8</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="I38" s="8" t="n">
-        <v>703</v>
-      </c>
-      <c r="J38" s="8" t="n">
-        <v>746.04</v>
+        <v>131</v>
+      </c>
+      <c r="I38" s="11" t="n">
+        <v>374.12</v>
+      </c>
+      <c r="J38" s="11" t="n">
+        <v>397.03</v>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
@@ -17643,24 +17641,24 @@
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>730.98</v>
+        <v>380.91</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17 00:56:07 IST</t>
+          <t>2026-08-18 00:20:50 IST</t>
         </is>
       </c>
       <c r="N38" s="4" t="n">
-        <v>935.42</v>
+        <v>-116.33</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v>925.52</v>
-      </c>
-      <c r="Q38" s="5" t="n">
-        <v>1.87</v>
+        <v>10</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v>-126.33</v>
+      </c>
+      <c r="Q38" s="13" t="n">
+        <v>-0.25</v>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
@@ -17669,49 +17667,49 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>60.94</t>
+          <t>59.53</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA9&gt;EMA20+2Red</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t>{"Volume": 22313421.0, "BB_lo": 665.286184, "SMA20": 700.678995, "high20": 728.539978, "low20": 661.140015, "low50": 661.140015, "High": 723.299988, "2Red": 1.0, "RSI14": 54.565075, "high50": 748.650024, "SMA50": 713.8536, "2Green": 0.0, "Open": 723.299988, "EMA200": 654.275205, "EMA50": 704.048659, "BB_hi": 736.071805, "Low": 715.789978, "EMA9": 711.374496, "Ret": -0.004883, "Close": 717.349976, "EMA20": 707.041668}</t>
+          <t>{"Low": 380.838501, "EMA9": 378.755146, "Ret": 0.002468, "High": 382.554993, "BB_lo": 355.440257, "SMA20": 371.858, "RSI14": 63.686748, "EMA20": 374.422536, "low20": 358.170013, "high50": 384.820007, "2Red": 0.0, "SMA50": 368.8264, "Open": 382.660004, "2Green": 0.0, "high20": 384.820007, "EMA200": 349.15793, "Close": 381.76001, "low50": 354.809998, "BB_hi": 388.275744, "Volume": 171118.0, "EMA50": 368.980107}</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>#37SW Price&gt;SMA50+EMA9&gt;EMA20+2Red | Expiry 5d</t>
+          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>00:37:04 IST</t>
+          <t>00:43:12 IST</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -17725,16 +17723,16 @@
         </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v>1874.1</v>
+        <v>717.42</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I39" s="8" t="n">
-        <v>1834.79</v>
-      </c>
-      <c r="J39" s="8" t="n">
-        <v>1947.12</v>
+        <v>69</v>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>703</v>
+      </c>
+      <c r="J39" s="11" t="n">
+        <v>746.04</v>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
@@ -17742,24 +17740,24 @@
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1880.51</v>
+        <v>730.98</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16 00:56:05 IST</t>
+          <t>2026-08-17 00:56:07 IST</t>
         </is>
       </c>
       <c r="N39" s="4" t="n">
-        <v>160.19</v>
+        <v>935.42</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>140.56</v>
+        <v>9.9</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>19.63</v>
-      </c>
-      <c r="Q39" s="12" t="n">
-        <v>0.04</v>
+        <v>925.52</v>
+      </c>
+      <c r="Q39" s="5" t="n">
+        <v>1.87</v>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
@@ -17768,27 +17766,27 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>60.94</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
+          <t>Price&gt;SMA50+EMA9&gt;EMA20+2Red</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t>{"BB_hi": 1951.082913, "EMA20": 1883.245495, "high20": 1976.460205, "Open": 1908.93103, "EMA200": 2141.746334, "Volume": 9096837120.0, "low50": 1510.505859, "Low": 1868.057739, "2Red": 1.0, "RSI14": 49.831146, "EMA9": 1893.674853, "BB_lo": 1835.426218, "2Green": 0.0, "high50": 1976.460205, "Close": 1872.22998, "SMA20": 1893.254565, "High": 1928.543091, "EMA50": 1861.015458, "low20": 1821.485107, "SMA50": 1805.156021, "Ret": -0.019098}</t>
+          <t>{"Volume": 22313421.0, "BB_lo": 665.286184, "SMA20": 700.678995, "high20": 728.539978, "low20": 661.140015, "low50": 661.140015, "High": 723.299988, "2Red": 1.0, "RSI14": 54.565075, "high50": 748.650024, "SMA50": 713.8536, "2Green": 0.0, "Open": 723.299988, "EMA200": 654.275205, "EMA50": 704.048659, "BB_hi": 736.071805, "Low": 715.789978, "EMA9": 711.374496, "Ret": -0.004883, "Close": 717.349976, "EMA20": 707.041668}</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | Expiry 5d</t>
+          <t>#37SW Price&gt;SMA50+EMA9&gt;EMA20+2Red | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -17810,7 +17808,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -17823,17 +17821,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G40" s="9" t="n">
-        <v>0.331</v>
+      <c r="G40" s="4" t="n">
+        <v>1874.1</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I40" s="10" t="n">
-        <v>0.3241</v>
-      </c>
-      <c r="J40" s="10" t="n">
-        <v>0.3439</v>
+        <v>25</v>
+      </c>
+      <c r="I40" s="11" t="n">
+        <v>1834.79</v>
+      </c>
+      <c r="J40" s="11" t="n">
+        <v>1947.12</v>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
@@ -17841,7 +17839,7 @@
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0.3304</v>
+        <v>1880.51</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
@@ -17849,16 +17847,16 @@
         </is>
       </c>
       <c r="N40" s="4" t="n">
-        <v>-5.56</v>
+        <v>160.19</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v>-15.49</v>
-      </c>
-      <c r="Q40" s="13" t="n">
-        <v>-0.47</v>
+        <v>140.56</v>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="Q40" s="12" t="n">
+        <v>0.04</v>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
@@ -17867,27 +17865,27 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t>{"BB_hi": 0.332258, "EMA20": 0.327832, "high20": 0.333079, "Open": 0.329585, "EMA200": 0.32088, "Volume": 869478144.0, "low50": 0.314034, "Low": 0.329472, "2Red": 0.0, "RSI14": 57.524103, "EMA9": 0.328473, "BB_lo": 0.323712, "2Green": 1.0, "high50": 0.333832, "Close": 0.330694, "SMA20": 0.327985, "High": 0.331578, "EMA50": 0.327842, "low20": 0.323269, "SMA50": 0.326432, "Ret": 0.003357}</t>
+          <t>{"BB_hi": 1951.082913, "EMA20": 1883.245495, "high20": 1976.460205, "Open": 1908.93103, "EMA200": 2141.746334, "Volume": 9096837120.0, "low50": 1510.505859, "Low": 1868.057739, "2Red": 1.0, "RSI14": 49.831146, "EMA9": 1893.674853, "BB_lo": 1835.426218, "2Green": 0.0, "high50": 1976.460205, "Close": 1872.22998, "SMA20": 1893.254565, "High": 1928.543091, "EMA50": 1861.015458, "low20": 1821.485107, "SMA50": 1805.156021, "Ret": -0.019098}</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
+          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -17904,12 +17902,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -17922,17 +17920,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
-        <v>84.8</v>
+      <c r="G41" s="8" t="n">
+        <v>0.331</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>587</v>
-      </c>
-      <c r="I41" s="8" t="n">
-        <v>83.09</v>
-      </c>
-      <c r="J41" s="8" t="n">
-        <v>88.18000000000001</v>
+        <v>10000</v>
+      </c>
+      <c r="I41" s="9" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>0.3439</v>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
@@ -17940,7 +17938,7 @@
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>86.06999999999999</v>
+        <v>0.3304</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
@@ -17948,16 +17946,16 @@
         </is>
       </c>
       <c r="N41" s="4" t="n">
-        <v>743.37</v>
+        <v>-5.56</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="P41" s="5" t="n">
-        <v>733.41</v>
-      </c>
-      <c r="Q41" s="5" t="n">
-        <v>1.47</v>
+        <v>9.93</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v>-15.49</v>
+      </c>
+      <c r="Q41" s="13" t="n">
+        <v>-0.47</v>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
@@ -17966,39 +17964,39 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t>Range&lt;1%+SMA20&lt;EMA20</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>{"BB_hi": 87.086251, "EMA20": 84.986252, "high20": 88.779999, "Open": 84.660004, "EMA200": 83.124135, "Volume": 4681010.0, "low50": 81.480003, "Low": 84.330002, "2Red": 0.0, "RSI14": 49.564668, "EMA9": 85.140171, "BB_lo": 82.854749, "2Green": 0.0, "high50": 88.779999, "Close": 84.790001, "SMA20": 84.9705, "High": 85.044998, "EMA50": 84.555905, "low20": 82.809998, "SMA50": 84.312, "Ret": -0.003877}</t>
+          <t>{"BB_hi": 0.332258, "EMA20": 0.327832, "high20": 0.333079, "Open": 0.329585, "EMA200": 0.32088, "Volume": 869478144.0, "low50": 0.314034, "Low": 0.329472, "2Red": 0.0, "RSI14": 57.524103, "EMA9": 0.328473, "BB_lo": 0.323712, "2Green": 1.0, "high50": 0.333832, "Close": 0.330694, "SMA20": 0.327985, "High": 0.331578, "EMA50": 0.327842, "low20": 0.323269, "SMA50": 0.326432, "Ret": 0.003357}</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>#5SW Range&lt;1%+SMA20&lt;EMA20 | Expiry 5d</t>
+          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>05:40:03 IST</t>
+          <t>00:37:04 IST</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -18008,7 +18006,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -18022,16 +18020,16 @@
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>185.35</v>
+        <v>84.8</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>265</v>
-      </c>
-      <c r="I42" s="8" t="n">
-        <v>181.62</v>
-      </c>
-      <c r="J42" s="8" t="n">
-        <v>192.74</v>
+        <v>587</v>
+      </c>
+      <c r="I42" s="11" t="n">
+        <v>83.09</v>
+      </c>
+      <c r="J42" s="11" t="n">
+        <v>88.18000000000001</v>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
@@ -18039,24 +18037,24 @@
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>186.12</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 08:36:01 IST</t>
+          <t>2026-08-16 00:56:05 IST</t>
         </is>
       </c>
       <c r="N42" s="4" t="n">
-        <v>204.42</v>
+        <v>743.37</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>9.82</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>194.6</v>
-      </c>
-      <c r="Q42" s="12" t="n">
-        <v>0.4</v>
+        <v>733.41</v>
+      </c>
+      <c r="Q42" s="5" t="n">
+        <v>1.47</v>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
@@ -18065,27 +18063,27 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>63.73</t>
+          <t>58.26</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
+          <t>Range&lt;1%+SMA20&lt;EMA20</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t>{"EMA50": 178.417894, "Close": 185.330002, "Volume": 6431938.0, "RSI14": 56.546346, "High": 186.910004, "2Red": 1.0, "Ret": -0.00312, "Low": 182.070007, "EMA20": 179.791718, "EMA9": 180.620244, "Open": 183.190002, "SMA50": 183.268401, "SMA20": 178.784}</t>
+          <t>{"BB_hi": 87.086251, "EMA20": 84.986252, "high20": 88.779999, "Open": 84.660004, "EMA200": 83.124135, "Volume": 4681010.0, "low50": 81.480003, "Low": 84.330002, "2Red": 0.0, "RSI14": 49.564668, "EMA9": 85.140171, "BB_lo": 82.854749, "2Green": 0.0, "high50": 88.779999, "Close": 84.790001, "SMA20": 84.9705, "High": 85.044998, "EMA50": 84.555905, "low20": 82.809998, "SMA50": 84.312, "Ret": -0.003877}</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>#28SW Price&gt;SMA50+EMA20&gt;EMA50+2Red | Expiry 5d</t>
+          <t>#5SW Range&lt;1%+SMA20&lt;EMA20 | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -18107,7 +18105,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -18121,16 +18119,16 @@
         </is>
       </c>
       <c r="G43" s="4" t="n">
-        <v>381.22</v>
+        <v>185.35</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>129</v>
-      </c>
-      <c r="I43" s="8" t="n">
-        <v>373.56</v>
-      </c>
-      <c r="J43" s="8" t="n">
-        <v>396.43</v>
+        <v>265</v>
+      </c>
+      <c r="I43" s="11" t="n">
+        <v>181.62</v>
+      </c>
+      <c r="J43" s="11" t="n">
+        <v>192.74</v>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
@@ -18138,7 +18136,7 @@
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>380.7</v>
+        <v>186.12</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -18146,16 +18144,16 @@
         </is>
       </c>
       <c r="N43" s="4" t="n">
-        <v>-66.83</v>
+        <v>204.42</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v>-76.67</v>
-      </c>
-      <c r="Q43" s="13" t="n">
-        <v>-0.16</v>
+        <v>9.82</v>
+      </c>
+      <c r="P43" s="5" t="n">
+        <v>194.6</v>
+      </c>
+      <c r="Q43" s="12" t="n">
+        <v>0.4</v>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
@@ -18164,39 +18162,39 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>63.73</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t>{"EMA50": 366.698569, "Close": 381.179993, "Volume": 145727.0, "RSI14": 65.09971, "High": 382.63501, "2Red": 0.0, "Ret": 0.001129, "Low": 380.350006, "EMA20": 370.650953, "EMA9": 374.081113, "Open": 381.549988, "SMA50": 368.3698, "SMA20": 369.739}</t>
+          <t>{"EMA50": 178.417894, "Close": 185.330002, "Volume": 6431938.0, "RSI14": 56.546346, "High": 186.910004, "2Red": 1.0, "Ret": -0.00312, "Low": 182.070007, "EMA20": 179.791718, "EMA9": 180.620244, "Open": 183.190002, "SMA50": 183.268401, "SMA20": 178.784}</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#28SW Price&gt;SMA50+EMA20&gt;EMA50+2Red | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>01:17:18 IST</t>
+          <t>05:40:03 IST</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -18206,7 +18204,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -18220,16 +18218,16 @@
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>719.29</v>
+        <v>381.22</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="I44" s="8" t="n">
-        <v>704.9</v>
-      </c>
-      <c r="J44" s="8" t="n">
-        <v>748.0599999999999</v>
+        <v>129</v>
+      </c>
+      <c r="I44" s="11" t="n">
+        <v>373.56</v>
+      </c>
+      <c r="J44" s="11" t="n">
+        <v>396.43</v>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
@@ -18237,24 +18235,24 @@
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>720.8</v>
+        <v>380.7</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 01:36:05 IST</t>
+          <t>2026-08-12 08:36:01 IST</t>
         </is>
       </c>
       <c r="N44" s="4" t="n">
-        <v>105.55</v>
+        <v>-66.83</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>10.07</v>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v>95.48</v>
-      </c>
-      <c r="Q44" s="12" t="n">
-        <v>0.19</v>
+        <v>9.84</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v>-76.67</v>
+      </c>
+      <c r="Q44" s="13" t="n">
+        <v>-0.16</v>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
@@ -18263,27 +18261,27 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>59.53</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA9&lt;EMA20</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t>{"Volume": 28061644.0, "RSI14": 56.167234, "EMA20": 701.326904, "EMA9": 700.684364, "Low": 719.26001, "SMA50": 715.048199, "EMA50": 701.5317, "High": 728.539978, "2Red": 0.0, "Close": 719.289978, "SMA20": 700.994495, "Open": 726.224976, "Ret": -0.0063}</t>
+          <t>{"EMA50": 366.698569, "Close": 381.179993, "Volume": 145727.0, "RSI14": 65.09971, "High": 382.63501, "2Red": 0.0, "Ret": 0.001129, "Low": 380.350006, "EMA20": 370.650953, "EMA9": 374.081113, "Open": 381.549988, "SMA50": 368.3698, "SMA20": 369.739}</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>#50SW Price&gt;SMA50+EMA9&lt;EMA20 | Expiry 5d</t>
+          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18303,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -18319,16 +18317,16 @@
         </is>
       </c>
       <c r="G45" s="4" t="n">
-        <v>52.72</v>
+        <v>719.29</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>969</v>
-      </c>
-      <c r="I45" s="8" t="n">
-        <v>51.67</v>
-      </c>
-      <c r="J45" s="8" t="n">
-        <v>54.83</v>
+        <v>70</v>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>704.9</v>
+      </c>
+      <c r="J45" s="11" t="n">
+        <v>748.0599999999999</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
@@ -18336,7 +18334,7 @@
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>53.18</v>
+        <v>720.8</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -18344,16 +18342,16 @@
         </is>
       </c>
       <c r="N45" s="4" t="n">
-        <v>450.27</v>
+        <v>105.55</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>10.22</v>
+        <v>10.07</v>
       </c>
       <c r="P45" s="5" t="n">
-        <v>440.05</v>
+        <v>95.48</v>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>0.86</v>
+        <v>0.19</v>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
@@ -18362,49 +18360,49 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+EMA9&lt;EMA20</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t>{"Volume": 9101653.0, "RSI14": 59.972956, "EMA20": 51.291376, "EMA9": 51.578998, "Low": 52.474998, "SMA50": 51.1821, "EMA50": 51.139325, "High": 52.959999, "2Red": 0.0, "Close": 52.724998, "SMA20": 51.00325, "Open": 52.59, "Ret": 0.013942}</t>
+          <t>{"Volume": 28061644.0, "RSI14": 56.167234, "EMA20": 701.326904, "EMA9": 700.684364, "Low": 719.26001, "SMA50": 715.048199, "EMA50": 701.5317, "High": 728.539978, "2Red": 0.0, "Close": 719.289978, "SMA20": 700.994495, "Open": 726.224976, "Ret": -0.0063}</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>#2SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#50SW Price&gt;SMA50+EMA9&lt;EMA20 | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>15:13:11 IST</t>
+          <t>01:17:18 IST</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -18417,17 +18415,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G46" s="9" t="n">
-        <v>0.3281</v>
+      <c r="G46" s="4" t="n">
+        <v>52.72</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I46" s="10" t="n">
-        <v>0.3215</v>
-      </c>
-      <c r="J46" s="10" t="n">
-        <v>0.3412</v>
+        <v>969</v>
+      </c>
+      <c r="I46" s="11" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="J46" s="11" t="n">
+        <v>54.83</v>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
@@ -18435,24 +18433,24 @@
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0.33</v>
+        <v>53.18</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 15:13:13 IST</t>
+          <t>2026-08-11 01:36:05 IST</t>
         </is>
       </c>
       <c r="N46" s="4" t="n">
-        <v>19.32</v>
+        <v>450.27</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>9.84</v>
+        <v>10.22</v>
       </c>
       <c r="P46" s="5" t="n">
-        <v>9.48</v>
+        <v>440.05</v>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>0.29</v>
+        <v>0.86</v>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
@@ -18461,27 +18459,27 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>{"Open": 0.326938, "2Red": 0.0, "Low": 0.326183, "EMA50": 0.327684, "High": 0.328078, "Volume": 546277952.0, "Close": 0.328078, "SMA20": 0.327438, "SMA50": 0.32597, "EMA9": 0.327405, "Ret": 0.003497, "RSI14": 51.70969, "EMA20": 0.327265}</t>
+          <t>{"Volume": 9101653.0, "RSI14": 59.972956, "EMA20": 51.291376, "EMA9": 51.578998, "Low": 52.474998, "SMA50": 51.1821, "EMA50": 51.139325, "High": 52.959999, "2Red": 0.0, "Close": 52.724998, "SMA20": 51.00325, "Open": 52.59, "Ret": 0.013942}</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
+          <t>#2SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -18498,12 +18496,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -18516,17 +18514,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G47" s="4" t="n">
-        <v>118.29</v>
+      <c r="G47" s="8" t="n">
+        <v>0.3281</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>420</v>
-      </c>
-      <c r="I47" s="8" t="n">
-        <v>115.92</v>
-      </c>
-      <c r="J47" s="8" t="n">
-        <v>123.02</v>
+        <v>10000</v>
+      </c>
+      <c r="I47" s="9" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>0.3412</v>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
@@ -18534,7 +18532,7 @@
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>119.8</v>
+        <v>0.33</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
@@ -18542,16 +18540,16 @@
         </is>
       </c>
       <c r="N47" s="4" t="n">
-        <v>633.37</v>
+        <v>19.32</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>9.94</v>
+        <v>9.84</v>
       </c>
       <c r="P47" s="5" t="n">
-        <v>623.4299999999999</v>
-      </c>
-      <c r="Q47" s="5" t="n">
-        <v>1.25</v>
+        <v>9.48</v>
+      </c>
+      <c r="Q47" s="12" t="n">
+        <v>0.29</v>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
@@ -18565,22 +18563,22 @@
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>58.65</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="U47" s="3" t="inlineStr">
         <is>
-          <t>EMA9&lt;EMA50+RSI&gt;50</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V47" s="3" t="inlineStr">
         <is>
-          <t>{"Open": 117.529999, "2Red": 0.0, "Low": 117.120003, "EMA50": 115.501689, "High": 118.57, "Volume": 10500800.0, "Close": 118.290001, "SMA20": 114.6345, "SMA50": 116.0852, "EMA9": 115.004317, "Ret": 0.000677, "RSI14": 59.157988, "EMA20": 114.786415}</t>
+          <t>{"Open": 0.326938, "2Red": 0.0, "Low": 0.326183, "EMA50": 0.327684, "High": 0.328078, "Volume": 546277952.0, "Close": 0.328078, "SMA20": 0.327438, "SMA50": 0.32597, "EMA9": 0.327405, "Ret": 0.003497, "RSI14": 51.70969, "EMA20": 0.327265}</t>
         </is>
       </c>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>#1SW EMA9&lt;EMA50+RSI&gt;50 | Expiry 5d</t>
+          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -18602,7 +18600,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -18616,16 +18614,16 @@
         </is>
       </c>
       <c r="G48" s="4" t="n">
-        <v>162.1</v>
+        <v>118.29</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>307</v>
-      </c>
-      <c r="I48" s="8" t="n">
-        <v>158.86</v>
-      </c>
-      <c r="J48" s="8" t="n">
-        <v>168.58</v>
+        <v>420</v>
+      </c>
+      <c r="I48" s="11" t="n">
+        <v>115.92</v>
+      </c>
+      <c r="J48" s="11" t="n">
+        <v>123.02</v>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
@@ -18633,7 +18631,7 @@
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>165.65</v>
+        <v>119.8</v>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
@@ -18641,16 +18639,16 @@
         </is>
       </c>
       <c r="N48" s="4" t="n">
-        <v>1090.9</v>
+        <v>633.37</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.94</v>
       </c>
       <c r="P48" s="5" t="n">
-        <v>1080.95</v>
+        <v>623.4299999999999</v>
       </c>
       <c r="Q48" s="5" t="n">
-        <v>2.17</v>
+        <v>1.25</v>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
@@ -18659,39 +18657,39 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>58.65</t>
         </is>
       </c>
       <c r="U48" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>EMA9&lt;EMA50+RSI&gt;50</t>
         </is>
       </c>
       <c r="V48" s="3" t="inlineStr">
         <is>
-          <t>{"Open": 162.0, "2Red": 1.0, "Low": 160.970001, "EMA50": 157.880967, "High": 162.490005, "Volume": 15121700.0, "Close": 162.100006, "SMA20": 161.822, "SMA50": 156.9082, "EMA9": 162.798107, "Ret": -0.000863, "RSI14": 53.812337, "EMA20": 161.631372}</t>
+          <t>{"Open": 117.529999, "2Red": 0.0, "Low": 117.120003, "EMA50": 115.501689, "High": 118.57, "Volume": 10500800.0, "Close": 118.290001, "SMA20": 114.6345, "SMA50": 116.0852, "EMA9": 115.004317, "Ret": 0.000677, "RSI14": 59.157988, "EMA20": 114.786415}</t>
         </is>
       </c>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#1SW EMA9&lt;EMA50+RSI&gt;50 | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>01:18:05 IST</t>
+          <t>15:13:11 IST</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -18701,7 +18699,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -18715,16 +18713,16 @@
         </is>
       </c>
       <c r="G49" s="4" t="n">
-        <v>700.39</v>
+        <v>162.1</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="I49" s="8" t="n">
-        <v>686.38</v>
-      </c>
-      <c r="J49" s="8" t="n">
-        <v>728.41</v>
+        <v>307</v>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>158.86</v>
+      </c>
+      <c r="J49" s="11" t="n">
+        <v>168.58</v>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
@@ -18732,24 +18730,24 @@
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>728.41</v>
+        <v>165.65</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>19:55:15 IST</t>
+          <t>2026-08-10 15:13:13 IST</t>
         </is>
       </c>
       <c r="N49" s="4" t="n">
-        <v>1989.42</v>
+        <v>1090.9</v>
       </c>
       <c r="O49" s="4" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="P49" s="5" t="n">
-        <v>1979.47</v>
+        <v>1080.95</v>
       </c>
       <c r="Q49" s="5" t="n">
-        <v>3.98</v>
+        <v>2.17</v>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
@@ -18758,39 +18756,39 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="U49" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&gt;Open</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V49" s="3" t="inlineStr">
         <is>
-          <t>{"Close": 700.390015, "Ret": 0.018024, "Low": 685.820007, "High": 701.590027, "Volume": 36459876.0, "EMA20": 696.896645, "SMA20": 699.896997, "2Red": 0.0, "EMA9": 689.142707, "RSI14": 50.141657, "SMA50": 714.8328, "Open": 688.340027, "EMA50": 699.878887}</t>
+          <t>{"Open": 162.0, "2Red": 1.0, "Low": 160.970001, "EMA50": 157.880967, "High": 162.490005, "Volume": 15121700.0, "Close": 162.100006, "SMA20": 161.822, "SMA50": 156.9082, "EMA9": 162.798107, "Ret": -0.000863, "RSI14": 53.812337, "EMA20": 161.631372}</t>
         </is>
       </c>
       <c r="W49" s="3" t="inlineStr">
         <is>
-          <t>#52SW Price&gt;SMA20+EMA9&lt;EMA20+Close&gt;Open | ðŸŽ¯ Target Hit (live)</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>23:32:54 IST</t>
+          <t>01:18:05 IST</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -18800,7 +18798,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -18810,45 +18808,45 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>745.84</v>
+        <v>700.39</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>119</v>
-      </c>
-      <c r="I50" s="8" t="n">
-        <v>738.38</v>
-      </c>
-      <c r="J50" s="8" t="n">
-        <v>760.76</v>
+        <v>71</v>
+      </c>
+      <c r="I50" s="11" t="n">
+        <v>686.38</v>
+      </c>
+      <c r="J50" s="11" t="n">
+        <v>728.41</v>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>757.5700000000001</v>
+        <v>728.41</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>23:00:00 IST</t>
+          <t>19:55:15 IST</t>
         </is>
       </c>
       <c r="N50" s="4" t="n">
-        <v>1395.87</v>
+        <v>1989.42</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>17.75</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>1378.12</v>
+        <v>1979.47</v>
       </c>
       <c r="Q50" s="5" t="n">
-        <v>1.55</v>
+        <v>3.98</v>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
@@ -18857,27 +18855,27 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>52</t>
         </is>
       </c>
       <c r="T50" s="3" t="inlineStr">
         <is>
-          <t>60.24</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="U50" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
+          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&gt;Open</t>
         </is>
       </c>
       <c r="V50" s="3" t="inlineStr">
         <is>
-          <t>{"EMA9": 741.70706, "Open": 744.429993, "Low": 743.98999, "Volume": 4072705.0, "RSI14": 62.13446, "Ret": 0.002512, "EMA50": 740.609545, "High": 746.400024, "SMA50": 739.652488, "2Red": 0.0, "SMA20": 738.535001, "EMA20": 740.044973, "Close": 746.289978}</t>
+          <t>{"Close": 700.390015, "Ret": 0.018024, "Low": 685.820007, "High": 701.590027, "Volume": 36459876.0, "EMA20": 696.896645, "SMA20": 699.896997, "2Red": 0.0, "EMA9": 689.142707, "RSI14": 50.141657, "SMA50": 714.8328, "Open": 688.340027, "EMA50": 699.878887}</t>
         </is>
       </c>
       <c r="W50" s="3" t="inlineStr">
         <is>
-          <t>#32ID Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | Expiry 6h</t>
+          <t>#52SW Price&gt;SMA20+EMA9&lt;EMA20+Close&gt;Open | ðŸŽ¯ Target Hit (live)</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18887,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>21:47:39 IST</t>
+          <t>23:32:54 IST</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -18899,7 +18897,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -18913,16 +18911,16 @@
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>174.29</v>
+        <v>745.84</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>497</v>
-      </c>
-      <c r="I51" s="8" t="n">
-        <v>172.55</v>
-      </c>
-      <c r="J51" s="8" t="n">
-        <v>177.78</v>
+        <v>119</v>
+      </c>
+      <c r="I51" s="11" t="n">
+        <v>738.38</v>
+      </c>
+      <c r="J51" s="11" t="n">
+        <v>760.76</v>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
@@ -18930,24 +18928,24 @@
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>177.6</v>
+        <v>757.5700000000001</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>21:00:00 IST</t>
+          <t>23:00:00 IST</t>
         </is>
       </c>
       <c r="N51" s="4" t="n">
-        <v>1646.31</v>
+        <v>1395.87</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>17.32</v>
+        <v>17.75</v>
       </c>
       <c r="P51" s="5" t="n">
-        <v>1628.99</v>
+        <v>1378.12</v>
       </c>
       <c r="Q51" s="5" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
@@ -18956,27 +18954,27 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T51" s="3" t="inlineStr">
         <is>
-          <t>67.35</t>
+          <t>60.24</t>
         </is>
       </c>
       <c r="U51" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20</t>
+          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
         </is>
       </c>
       <c r="V51" s="3" t="inlineStr">
         <is>
-          <t>{"SMA20": 171.96953, "EMA9": 173.971593, "EMA20": 173.252314, "Ret": -0.00379, "SMA50": 174.765609, "High": 174.869995, "Volume": 1112891.0, "Close": 173.5, "Open": 174.179993, "2Red": 1.0, "RSI14": 50.495204, "Low": 173.100006, "EMA50": 174.378064}</t>
+          <t>{"EMA9": 741.70706, "Open": 744.429993, "Low": 743.98999, "Volume": 4072705.0, "RSI14": 62.13446, "Ret": 0.002512, "EMA50": 740.609545, "High": 746.400024, "SMA50": 739.652488, "2Red": 0.0, "SMA20": 738.535001, "EMA20": 740.044973, "Close": 746.289978}</t>
         </is>
       </c>
       <c r="W51" s="3" t="inlineStr">
         <is>
-          <t>#3ID Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20 | Expiry 6h</t>
+          <t>#32ID Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -18988,7 +18986,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>21:07:14 IST</t>
+          <t>21:47:39 IST</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -19012,16 +19010,16 @@
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>173.95</v>
+        <v>174.29</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>487</v>
-      </c>
-      <c r="I52" s="8" t="n">
-        <v>172.21</v>
-      </c>
-      <c r="J52" s="8" t="n">
-        <v>177.43</v>
+        <v>497</v>
+      </c>
+      <c r="I52" s="11" t="n">
+        <v>172.55</v>
+      </c>
+      <c r="J52" s="11" t="n">
+        <v>177.78</v>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
@@ -19029,24 +19027,24 @@
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>176.43</v>
+        <v>177.6</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>20:00:00 IST</t>
+          <t>21:00:00 IST</t>
         </is>
       </c>
       <c r="N52" s="4" t="n">
-        <v>1207.76</v>
+        <v>1646.31</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>16.94</v>
+        <v>17.32</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>1190.82</v>
+        <v>1628.99</v>
       </c>
       <c r="Q52" s="5" t="n">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
@@ -19070,7 +19068,7 @@
       </c>
       <c r="V52" s="3" t="inlineStr">
         <is>
-          <t>{"RSI14": 50.452183, "2Red": 1.0, "High": 174.869995, "EMA50": 174.377476, "Ret": -0.003876, "SMA50": 174.765309, "Low": 173.100006, "Close": 173.485001, "Volume": 1102438.0, "SMA20": 171.96878, "EMA20": 173.250885, "Open": 174.179993, "EMA9": 173.968593}</t>
+          <t>{"SMA20": 171.96953, "EMA9": 173.971593, "EMA20": 173.252314, "Ret": -0.00379, "SMA50": 174.765609, "High": 174.869995, "Volume": 1112891.0, "Close": 173.5, "Open": 174.179993, "2Red": 1.0, "RSI14": 50.495204, "Low": 173.100006, "EMA50": 174.378064}</t>
         </is>
       </c>
       <c r="W52" s="3" t="inlineStr">
@@ -19087,7 +19085,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>20:27:40 IST</t>
+          <t>21:07:14 IST</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -19111,16 +19109,16 @@
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>174.64</v>
+        <v>173.95</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>490</v>
-      </c>
-      <c r="I53" s="8" t="n">
-        <v>172.89</v>
-      </c>
-      <c r="J53" s="8" t="n">
-        <v>178.13</v>
+        <v>487</v>
+      </c>
+      <c r="I53" s="11" t="n">
+        <v>172.21</v>
+      </c>
+      <c r="J53" s="11" t="n">
+        <v>177.43</v>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
@@ -19128,24 +19126,24 @@
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>176.19</v>
+        <v>176.43</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>19:00:00 IST</t>
+          <t>20:00:00 IST</t>
         </is>
       </c>
       <c r="N53" s="4" t="n">
-        <v>759.5</v>
+        <v>1207.76</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>17.11</v>
+        <v>16.94</v>
       </c>
       <c r="P53" s="5" t="n">
-        <v>742.39</v>
-      </c>
-      <c r="Q53" s="12" t="n">
-        <v>0.87</v>
+        <v>1190.82</v>
+      </c>
+      <c r="Q53" s="5" t="n">
+        <v>1.41</v>
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
@@ -19169,7 +19167,7 @@
       </c>
       <c r="V53" s="3" t="inlineStr">
         <is>
-          <t>{"SMA20": 171.86253, "RSI14": 52.463695, "Ret": -0.008821, "EMA9": 174.089491, "2Red": 0.0, "Low": 172.699997, "Close": 174.160004, "SMA50": 174.896011, "EMA20": 173.226242, "EMA50": 174.413903, "Open": 177.460007, "Volume": 2974398.0, "High": 178.619995}</t>
+          <t>{"RSI14": 50.452183, "2Red": 1.0, "High": 174.869995, "EMA50": 174.377476, "Ret": -0.003876, "SMA50": 174.765309, "Low": 173.100006, "Close": 173.485001, "Volume": 1102438.0, "SMA20": 171.96878, "EMA20": 173.250885, "Open": 174.179993, "EMA9": 173.968593}</t>
         </is>
       </c>
       <c r="W53" s="3" t="inlineStr">
@@ -19186,7 +19184,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>02:09:08 IST</t>
+          <t>20:27:40 IST</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -19196,7 +19194,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -19210,16 +19208,16 @@
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>683.6</v>
+        <v>174.64</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>132</v>
-      </c>
-      <c r="I54" s="8" t="n">
-        <v>676.76</v>
-      </c>
-      <c r="J54" s="8" t="n">
-        <v>697.27</v>
+        <v>490</v>
+      </c>
+      <c r="I54" s="11" t="n">
+        <v>172.89</v>
+      </c>
+      <c r="J54" s="11" t="n">
+        <v>178.13</v>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
@@ -19227,21 +19225,21 @@
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>689.7</v>
+        <v>176.19</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>00:00:00 IST</t>
+          <t>19:00:00 IST</t>
         </is>
       </c>
       <c r="N54" s="4" t="n">
-        <v>805.2</v>
+        <v>759.5</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>18.05</v>
+        <v>17.11</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>787.15</v>
+        <v>742.39</v>
       </c>
       <c r="Q54" s="12" t="n">
         <v>0.87</v>
@@ -19253,27 +19251,27 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T54" s="3" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>67.35</t>
         </is>
       </c>
       <c r="U54" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50</t>
+          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20</t>
         </is>
       </c>
       <c r="V54" s="3" t="inlineStr">
         <is>
-          <t>{"Volume": 10064291.0, "SMA20": 675.475238, "EMA20": 678.396981, "EMA50": 684.292339, "Close": 683.599976, "Low": 682.900024, "Open": 683.820007, "High": 684.349976, "Ret": -0.000351, "SMA50": 685.204755, "2Red": 0.0, "RSI14": 54.801846, "EMA9": 679.813964}</t>
+          <t>{"SMA20": 171.86253, "RSI14": 52.463695, "Ret": -0.008821, "EMA9": 174.089491, "2Red": 0.0, "Low": 172.699997, "Close": 174.160004, "SMA50": 174.896011, "EMA20": 173.226242, "EMA50": 174.413903, "Open": 177.460007, "Volume": 2974398.0, "High": 178.619995}</t>
         </is>
       </c>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>#5ID Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50 | Expiry 6h</t>
+          <t>#3ID Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20 | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -19295,7 +19293,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -19309,16 +19307,16 @@
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>741.73</v>
+        <v>683.6</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>121</v>
-      </c>
-      <c r="I55" s="8" t="n">
-        <v>734.3099999999999</v>
-      </c>
-      <c r="J55" s="8" t="n">
-        <v>756.5599999999999</v>
+        <v>132</v>
+      </c>
+      <c r="I55" s="11" t="n">
+        <v>676.76</v>
+      </c>
+      <c r="J55" s="11" t="n">
+        <v>697.27</v>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
@@ -19326,7 +19324,7 @@
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>747.49</v>
+        <v>689.7</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -19334,16 +19332,16 @@
         </is>
       </c>
       <c r="N55" s="4" t="n">
-        <v>696.96</v>
+        <v>805.2</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>17.95</v>
+        <v>18.05</v>
       </c>
       <c r="P55" s="5" t="n">
-        <v>679.01</v>
+        <v>787.15</v>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>0.76</v>
+        <v>0.87</v>
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
@@ -19352,27 +19350,27 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T55" s="3" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>63.38</t>
         </is>
       </c>
       <c r="U55" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open</t>
+          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50</t>
         </is>
       </c>
       <c r="V55" s="3" t="inlineStr">
         <is>
-          <t>{"Volume": 12583754.0, "SMA20": 738.175507, "EMA20": 738.518298, "EMA50": 740.197673, "Close": 741.72998, "Low": 741.0, "Open": 741.77002, "High": 742.099976, "Ret": -6.7e-05, "SMA50": 740.120288, "2Red": 0.0, "RSI14": 55.502244, "EMA9": 739.15355}</t>
+          <t>{"Volume": 10064291.0, "SMA20": 675.475238, "EMA20": 678.396981, "EMA50": 684.292339, "Close": 683.599976, "Low": 682.900024, "Open": 683.820007, "High": 684.349976, "Ret": -0.000351, "SMA50": 685.204755, "2Red": 0.0, "RSI14": 54.801846, "EMA9": 679.813964}</t>
         </is>
       </c>
       <c r="W55" s="3" t="inlineStr">
         <is>
-          <t>#31ID Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open | Expiry 6h</t>
+          <t>#5ID Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50 | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -19384,7 +19382,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>01:14:10 IST</t>
+          <t>02:09:08 IST</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -19394,7 +19392,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -19408,16 +19406,16 @@
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>683.6900000000001</v>
+        <v>741.73</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>134</v>
-      </c>
-      <c r="I56" s="8" t="n">
-        <v>676.85</v>
-      </c>
-      <c r="J56" s="8" t="n">
-        <v>697.36</v>
+        <v>121</v>
+      </c>
+      <c r="I56" s="11" t="n">
+        <v>734.3099999999999</v>
+      </c>
+      <c r="J56" s="11" t="n">
+        <v>756.5599999999999</v>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
@@ -19425,7 +19423,7 @@
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>689.7</v>
+        <v>747.49</v>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
@@ -19433,16 +19431,16 @@
         </is>
       </c>
       <c r="N56" s="4" t="n">
-        <v>805.34</v>
+        <v>696.96</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>18.32</v>
+        <v>17.95</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>787.02</v>
+        <v>679.01</v>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
@@ -19451,39 +19449,39 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T56" s="3" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="U56" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50</t>
+          <t>Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open</t>
         </is>
       </c>
       <c r="V56" s="3" t="inlineStr">
         <is>
-          <t>{"Volume": 6303349.0, "Ret": 0.002213, "EMA20": 677.849297, "EMA9": 678.867461, "2Red": 0.0, "SMA50": 685.700555, "SMA20": 674.813739, "Low": 681.51001, "EMA50": 684.320598, "Open": 682.325012, "High": 685.119995, "RSI14": 55.076392, "Close": 683.840027}</t>
+          <t>{"Volume": 12583754.0, "SMA20": 738.175507, "EMA20": 738.518298, "EMA50": 740.197673, "Close": 741.72998, "Low": 741.0, "Open": 741.77002, "High": 742.099976, "Ret": -6.7e-05, "SMA50": 740.120288, "2Red": 0.0, "RSI14": 55.502244, "EMA9": 739.15355}</t>
         </is>
       </c>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>#5ID Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50 | Expiry 6h</t>
+          <t>#31ID Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open | Expiry 6h</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>22:16:13 IST</t>
+          <t>01:14:10 IST</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -19493,7 +19491,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -19507,16 +19505,16 @@
         </is>
       </c>
       <c r="G57" s="4" t="n">
-        <v>517.88</v>
+        <v>683.6900000000001</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>179</v>
-      </c>
-      <c r="I57" s="8" t="n">
-        <v>512.7</v>
-      </c>
-      <c r="J57" s="8" t="n">
-        <v>528.24</v>
+        <v>134</v>
+      </c>
+      <c r="I57" s="11" t="n">
+        <v>676.85</v>
+      </c>
+      <c r="J57" s="11" t="n">
+        <v>697.36</v>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
@@ -19524,24 +19522,24 @@
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>519.65</v>
+        <v>689.7</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>21:00:00 IST</t>
+          <t>00:00:00 IST</t>
         </is>
       </c>
       <c r="N57" s="4" t="n">
-        <v>316.83</v>
+        <v>805.34</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>18.54</v>
+        <v>18.32</v>
       </c>
       <c r="P57" s="5" t="n">
-        <v>298.29</v>
+        <v>787.02</v>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>0.32</v>
+        <v>0.86</v>
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
@@ -19550,23 +19548,27 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T57" s="3" t="inlineStr">
         <is>
-          <t>60.16</t>
+          <t>63.38</t>
         </is>
       </c>
       <c r="U57" s="3" t="inlineStr">
         <is>
-          <t>RSI&lt;45+EMA20&gt;EMA50+Close&lt;Open+2Red</t>
-        </is>
-      </c>
-      <c r="V57" s="3" t="inlineStr"/>
+          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>{"Volume": 6303349.0, "Ret": 0.002213, "EMA20": 677.849297, "EMA9": 678.867461, "2Red": 0.0, "SMA50": 685.700555, "SMA20": 674.813739, "Low": 681.51001, "EMA50": 684.320598, "Open": 682.325012, "High": 685.119995, "RSI14": 55.076392, "Close": 683.840027}</t>
+        </is>
+      </c>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>#13ID RSI&lt;45+EMA20&gt;EMA50+Close&lt;Open+2Red | Expiry 6h</t>
+          <t>#5ID Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50 | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -19578,7 +19580,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>21:32:32 IST</t>
+          <t>22:16:13 IST</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -19602,16 +19604,16 @@
         </is>
       </c>
       <c r="G58" s="4" t="n">
-        <v>517.9</v>
+        <v>517.88</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="I58" s="8" t="n">
-        <v>512.72</v>
-      </c>
-      <c r="J58" s="8" t="n">
-        <v>528.26</v>
+        <v>179</v>
+      </c>
+      <c r="I58" s="11" t="n">
+        <v>512.7</v>
+      </c>
+      <c r="J58" s="11" t="n">
+        <v>528.24</v>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
@@ -19627,13 +19629,13 @@
         </is>
       </c>
       <c r="N58" s="4" t="n">
-        <v>316.75</v>
+        <v>316.83</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>18.75</v>
+        <v>18.54</v>
       </c>
       <c r="P58" s="5" t="n">
-        <v>298</v>
+        <v>298.29</v>
       </c>
       <c r="Q58" s="12" t="n">
         <v>0.32</v>
@@ -19645,23 +19647,23 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>13</t>
         </is>
       </c>
       <c r="T58" s="3" t="inlineStr">
         <is>
-          <t>67.86</t>
+          <t>60.16</t>
         </is>
       </c>
       <c r="U58" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red</t>
+          <t>RSI&lt;45+EMA20&gt;EMA50+Close&lt;Open+2Red</t>
         </is>
       </c>
       <c r="V58" s="3" t="inlineStr"/>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>#36ID Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red | Expiry 6h</t>
+          <t>#13ID RSI&lt;45+EMA20&gt;EMA50+Close&lt;Open+2Red | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -19673,7 +19675,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>20:59:02 IST</t>
+          <t>21:32:32 IST</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -19697,16 +19699,16 @@
         </is>
       </c>
       <c r="G59" s="4" t="n">
-        <v>518.55</v>
+        <v>517.9</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>183</v>
-      </c>
-      <c r="I59" s="8" t="n">
-        <v>513.37</v>
-      </c>
-      <c r="J59" s="8" t="n">
-        <v>528.9299999999999</v>
+        <v>181</v>
+      </c>
+      <c r="I59" s="11" t="n">
+        <v>512.72</v>
+      </c>
+      <c r="J59" s="11" t="n">
+        <v>528.26</v>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
@@ -19714,24 +19716,24 @@
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>516.52</v>
+        <v>519.65</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>20:00:00 IST</t>
+          <t>21:00:00 IST</t>
         </is>
       </c>
       <c r="N59" s="4" t="n">
-        <v>-372.4</v>
+        <v>316.75</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>18.98</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v>-391.38</v>
-      </c>
-      <c r="Q59" s="13" t="n">
-        <v>-0.41</v>
+        <v>18.75</v>
+      </c>
+      <c r="P59" s="5" t="n">
+        <v>298</v>
+      </c>
+      <c r="Q59" s="12" t="n">
+        <v>0.32</v>
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
@@ -19768,7 +19770,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>20:11:02 IST</t>
+          <t>20:59:02 IST</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -19792,16 +19794,16 @@
         </is>
       </c>
       <c r="G60" s="4" t="n">
-        <v>518.47</v>
+        <v>518.55</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>184</v>
-      </c>
-      <c r="I60" s="8" t="n">
-        <v>513.28</v>
-      </c>
-      <c r="J60" s="8" t="n">
-        <v>528.83</v>
+        <v>183</v>
+      </c>
+      <c r="I60" s="11" t="n">
+        <v>513.37</v>
+      </c>
+      <c r="J60" s="11" t="n">
+        <v>528.9299999999999</v>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
@@ -19809,24 +19811,24 @@
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>518.47</v>
+        <v>516.52</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>19:00:00 IST</t>
-        </is>
-      </c>
-      <c r="N60" s="9" t="n">
-        <v>-0.92</v>
+          <t>20:00:00 IST</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="n">
+        <v>-372.4</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>19.08</v>
+        <v>18.98</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>-20</v>
+        <v>-391.38</v>
       </c>
       <c r="Q60" s="13" t="n">
-        <v>-0.02</v>
+        <v>-0.41</v>
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
@@ -19863,7 +19865,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>01:14:16 IST</t>
+          <t>20:11:02 IST</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -19873,7 +19875,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -19887,16 +19889,16 @@
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>741.2</v>
+        <v>518.47</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>133</v>
-      </c>
-      <c r="I61" s="8" t="n">
-        <v>733.79</v>
-      </c>
-      <c r="J61" s="8" t="n">
-        <v>756.02</v>
+        <v>184</v>
+      </c>
+      <c r="I61" s="11" t="n">
+        <v>513.28</v>
+      </c>
+      <c r="J61" s="11" t="n">
+        <v>528.83</v>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
@@ -19904,24 +19906,24 @@
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>733.79</v>
+        <v>518.47</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>20:00:00 IST</t>
-        </is>
-      </c>
-      <c r="N61" s="4" t="n">
-        <v>-985.53</v>
+          <t>19:00:00 IST</t>
+        </is>
+      </c>
+      <c r="N61" s="8" t="n">
+        <v>-0.92</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>19.72</v>
+        <v>19.08</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>-1005.25</v>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v>-1.02</v>
+        <v>-20</v>
+      </c>
+      <c r="Q61" s="13" t="n">
+        <v>-0.02</v>
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
@@ -19930,35 +19932,35 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T61" s="3" t="inlineStr">
         <is>
-          <t>60.24</t>
+          <t>67.86</t>
         </is>
       </c>
       <c r="U61" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
+          <t>Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red</t>
         </is>
       </c>
       <c r="V61" s="3" t="inlineStr"/>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>#32ID Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | SL Hit</t>
+          <t>#36ID Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red | Expiry 6h</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>23:22:38 IST</t>
+          <t>01:14:16 IST</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -19968,12 +19970,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -19982,16 +19984,16 @@
         </is>
       </c>
       <c r="G62" s="4" t="n">
-        <v>293.1</v>
+        <v>741.2</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>337</v>
-      </c>
-      <c r="I62" s="8" t="n">
-        <v>296.03</v>
-      </c>
-      <c r="J62" s="8" t="n">
-        <v>287.24</v>
+        <v>133</v>
+      </c>
+      <c r="I62" s="11" t="n">
+        <v>733.79</v>
+      </c>
+      <c r="J62" s="11" t="n">
+        <v>756.02</v>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
@@ -19999,24 +20001,24 @@
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>289.59</v>
+        <v>733.79</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>22:00:00 IST</t>
+          <t>20:00:00 IST</t>
         </is>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1182.87</v>
+        <v>-985.53</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="P62" s="5" t="n">
-        <v>1163.12</v>
-      </c>
-      <c r="Q62" s="5" t="n">
-        <v>1.18</v>
+        <v>19.72</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v>-1005.25</v>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v>-1.02</v>
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
@@ -20025,35 +20027,35 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T62" s="3" t="inlineStr">
         <is>
-          <t>63.41</t>
+          <t>60.24</t>
         </is>
       </c>
       <c r="U62" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
+          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
         </is>
       </c>
       <c r="V62" s="3" t="inlineStr"/>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>#14ID Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | Expiry 6h</t>
+          <t>#32ID Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | SL Hit</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>23:32:56 IST</t>
+          <t>23:22:38 IST</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -20063,12 +20065,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -20077,16 +20079,16 @@
         </is>
       </c>
       <c r="G63" s="4" t="n">
-        <v>520.27</v>
+        <v>293.1</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>191</v>
-      </c>
-      <c r="I63" s="8" t="n">
-        <v>515.0599999999999</v>
-      </c>
-      <c r="J63" s="8" t="n">
-        <v>530.67</v>
+        <v>337</v>
+      </c>
+      <c r="I63" s="11" t="n">
+        <v>296.03</v>
+      </c>
+      <c r="J63" s="11" t="n">
+        <v>287.24</v>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
@@ -20094,24 +20096,24 @@
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>526.96</v>
+        <v>289.59</v>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>23:00:00 IST</t>
+          <t>22:00:00 IST</t>
         </is>
       </c>
       <c r="N63" s="4" t="n">
-        <v>1277.79</v>
+        <v>1182.87</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>19.87</v>
+        <v>19.75</v>
       </c>
       <c r="P63" s="5" t="n">
-        <v>1257.92</v>
+        <v>1163.12</v>
       </c>
       <c r="Q63" s="5" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
@@ -20120,67 +20122,162 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T63" s="3" t="inlineStr">
         <is>
-          <t>67.86</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="U63" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red</t>
+          <t>Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
         </is>
       </c>
       <c r="V63" s="3" t="inlineStr"/>
       <c r="W63" s="3" t="inlineStr">
         <is>
+          <t>#14ID Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | Expiry 6h</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>23:32:56 IST</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>DIA</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>INTRADAY_1h</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>520.27</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>191</v>
+      </c>
+      <c r="I64" s="11" t="n">
+        <v>515.0599999999999</v>
+      </c>
+      <c r="J64" s="11" t="n">
+        <v>530.67</v>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>526.96</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>23:00:00 IST</t>
+        </is>
+      </c>
+      <c r="N64" s="4" t="n">
+        <v>1277.79</v>
+      </c>
+      <c r="O64" s="4" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="P64" s="5" t="n">
+        <v>1257.92</v>
+      </c>
+      <c r="Q64" s="5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="T64" s="3" t="inlineStr">
+        <is>
+          <t>67.86</t>
+        </is>
+      </c>
+      <c r="U64" s="3" t="inlineStr">
+        <is>
+          <t>Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red</t>
+        </is>
+      </c>
+      <c r="V64" s="3" t="inlineStr"/>
+      <c r="W64" s="3" t="inlineStr">
+        <is>
           <t>#36ID Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red | Expiry 6h</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="14" t="inlineStr"/>
-      <c r="B64" s="14" t="inlineStr"/>
-      <c r="C64" s="15" t="inlineStr"/>
-      <c r="D64" s="15" t="inlineStr"/>
-      <c r="E64" s="15" t="inlineStr"/>
-      <c r="F64" s="15" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr"/>
+      <c r="B65" s="14" t="inlineStr"/>
+      <c r="C65" s="15" t="inlineStr"/>
+      <c r="D65" s="15" t="inlineStr"/>
+      <c r="E65" s="15" t="inlineStr"/>
+      <c r="F65" s="15" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="G64" s="16" t="inlineStr"/>
-      <c r="H64" s="16" t="inlineStr"/>
-      <c r="I64" s="15" t="inlineStr"/>
-      <c r="J64" s="15" t="inlineStr"/>
-      <c r="K64" s="14" t="inlineStr"/>
-      <c r="L64" s="15" t="inlineStr"/>
-      <c r="M64" s="14" t="inlineStr"/>
-      <c r="N64" s="17" t="n">
+      <c r="G65" s="16" t="inlineStr"/>
+      <c r="H65" s="16" t="inlineStr"/>
+      <c r="I65" s="15" t="inlineStr"/>
+      <c r="J65" s="15" t="inlineStr"/>
+      <c r="K65" s="14" t="inlineStr"/>
+      <c r="L65" s="15" t="inlineStr"/>
+      <c r="M65" s="14" t="inlineStr"/>
+      <c r="N65" s="17" t="n">
         <v>26493.04</v>
       </c>
-      <c r="O64" s="17" t="n">
+      <c r="O65" s="17" t="n">
         <v>2438.67</v>
       </c>
-      <c r="P64" s="18" t="n">
+      <c r="P65" s="18" t="n">
         <v>24054.37</v>
       </c>
-      <c r="Q64" s="16" t="inlineStr"/>
-      <c r="R64" s="15" t="inlineStr">
-        <is>
-          <t>62 trades (60 closed / 2 open)</t>
-        </is>
-      </c>
-      <c r="S64" s="15" t="inlineStr"/>
-      <c r="T64" s="14" t="inlineStr"/>
-      <c r="U64" s="14" t="inlineStr"/>
-      <c r="V64" s="14" t="inlineStr"/>
-      <c r="W64" s="14" t="inlineStr"/>
+      <c r="Q65" s="16" t="inlineStr"/>
+      <c r="R65" s="15" t="inlineStr">
+        <is>
+          <t>63 trades (60 closed / 3 open)</t>
+        </is>
+      </c>
+      <c r="S65" s="15" t="inlineStr"/>
+      <c r="T65" s="14" t="inlineStr"/>
+      <c r="U65" s="14" t="inlineStr"/>
+      <c r="V65" s="14" t="inlineStr"/>
+      <c r="W65" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W63"/>
+  <autoFilter ref="A1:W64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14085,19 +14085,19 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>6.8</v>
+        <v>10.21</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P2" s="10" t="inlineStr">
         <is>
-          <t>~-3.38 (unrealized)</t>
+          <t>~0.03 (unrealized)</t>
         </is>
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
-          <t>~+0.20%</t>
+          <t>~+0.30%</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -14479,19 +14479,19 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="4" t="n">
-        <v>-109.5</v>
+        <v>-429.97</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P6" s="10" t="inlineStr">
         <is>
-          <t>~-119.96 (unrealized)</t>
+          <t>~-440.43 (unrealized)</t>
         </is>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
-          <t>~-0.21%</t>
+          <t>~-0.82%</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -14576,19 +14576,19 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="4" t="n">
-        <v>-389.36</v>
+        <v>401.92</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P7" s="10" t="inlineStr">
         <is>
-          <t>~-399.82 (unrealized)</t>
+          <t>~391.46 (unrealized)</t>
         </is>
       </c>
       <c r="Q7" s="10" t="inlineStr">
         <is>
-          <t>~-0.74%</t>
+          <t>~+0.77%</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14085,19 +14085,19 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>10.21</v>
+        <v>13.25</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P2" s="10" t="inlineStr">
         <is>
-          <t>~0.03 (unrealized)</t>
+          <t>~3.07 (unrealized)</t>
         </is>
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
-          <t>~+0.30%</t>
+          <t>~+0.39%</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -14479,19 +14479,19 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="4" t="n">
-        <v>-429.97</v>
+        <v>-289.81</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P6" s="10" t="inlineStr">
         <is>
-          <t>~-440.43 (unrealized)</t>
+          <t>~-300.27 (unrealized)</t>
         </is>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
-          <t>~-0.82%</t>
+          <t>~-0.55%</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -14576,19 +14576,19 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="4" t="n">
-        <v>401.92</v>
+        <v>320.28</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P7" s="10" t="inlineStr">
         <is>
-          <t>~391.46 (unrealized)</t>
+          <t>~309.82 (unrealized)</t>
         </is>
       </c>
       <c r="Q7" s="10" t="inlineStr">
         <is>
-          <t>~+0.77%</t>
+          <t>~+0.61%</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14085,19 +14085,19 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>-127.41</v>
+        <v>-158.92</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P2" s="9" t="inlineStr">
         <is>
-          <t>~-137.83 (unrealized)</t>
+          <t>~-169.34 (unrealized)</t>
         </is>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>~-0.24%</t>
+          <t>~-0.30%</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -14182,19 +14182,19 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="4" t="n">
-        <v>1097.43</v>
+        <v>1144.08</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>~1,086.93 (unrealized)</t>
+          <t>~1,133.58 (unrealized)</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>~+2.09%</t>
+          <t>~+2.18%</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -14279,19 +14279,19 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="4" t="n">
-        <v>733.59</v>
+        <v>724.1799999999999</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>~723.13 (unrealized)</t>
+          <t>~713.72 (unrealized)</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>~+1.40%</t>
+          <t>~+1.39%</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>13.3</v>
+        <v>10.68</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~3.12 (unrealized)</t>
+          <t>~0.50 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~+0.39%</t>
+          <t>~+0.31%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -14770,19 +14770,19 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>-319.74</v>
+        <v>-382.52</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>~-330.20 (unrealized)</t>
+          <t>~-392.98 (unrealized)</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>~-0.61%</t>
+          <t>~-0.73%</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -14867,19 +14867,19 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="4" t="n">
-        <v>348.54</v>
+        <v>395.67</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>~338.08 (unrealized)</t>
+          <t>~385.21 (unrealized)</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>~+0.67%</t>
+          <t>~+0.76%</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14085,19 +14085,19 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>-158.92</v>
+        <v>-184.26</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P2" s="9" t="inlineStr">
         <is>
-          <t>~-169.34 (unrealized)</t>
+          <t>~-194.68 (unrealized)</t>
         </is>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>~-0.30%</t>
+          <t>~-0.35%</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -14182,14 +14182,14 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="4" t="n">
-        <v>1144.08</v>
+        <v>1141.7</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>~1,133.58 (unrealized)</t>
+          <t>~1,131.20 (unrealized)</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
@@ -14279,19 +14279,19 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="4" t="n">
-        <v>724.1799999999999</v>
+        <v>667.76</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>~713.72 (unrealized)</t>
+          <t>~657.30 (unrealized)</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>~+1.39%</t>
+          <t>~+1.28%</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>10.68</v>
+        <v>11.18</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~0.50 (unrealized)</t>
+          <t>~1.00 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~+0.31%</t>
+          <t>~+0.33%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -14770,19 +14770,19 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>-382.52</v>
+        <v>-448.22</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>~-392.98 (unrealized)</t>
+          <t>~-458.68 (unrealized)</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>~-0.73%</t>
+          <t>~-0.86%</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -14867,19 +14867,19 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="4" t="n">
-        <v>395.67</v>
+        <v>329.7</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>~385.21 (unrealized)</t>
+          <t>~319.24 (unrealized)</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>~+0.76%</t>
+          <t>~+0.63%</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14085,19 +14085,19 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>-184.26</v>
+        <v>-220.57</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P2" s="9" t="inlineStr">
         <is>
-          <t>~-194.68 (unrealized)</t>
+          <t>~-230.99 (unrealized)</t>
         </is>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>~-0.35%</t>
+          <t>~-0.42%</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -14182,14 +14182,14 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="4" t="n">
-        <v>1141.7</v>
+        <v>1146.36</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>~1,131.20 (unrealized)</t>
+          <t>~1,135.86 (unrealized)</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
@@ -14279,19 +14279,19 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="4" t="n">
-        <v>667.76</v>
+        <v>645.8099999999999</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>~657.30 (unrealized)</t>
+          <t>~635.35 (unrealized)</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>~+1.28%</t>
+          <t>~+1.24%</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>11.18</v>
+        <v>14.84</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~1.00 (unrealized)</t>
+          <t>~4.66 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~+0.33%</t>
+          <t>~+0.44%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -14770,19 +14770,19 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>-448.22</v>
+        <v>-527.0599999999999</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>~-458.68 (unrealized)</t>
+          <t>~-537.52 (unrealized)</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>~-0.86%</t>
+          <t>~-1.01%</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -14867,19 +14867,19 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="4" t="n">
-        <v>329.7</v>
+        <v>361.1</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>~319.24 (unrealized)</t>
+          <t>~350.64 (unrealized)</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>~+0.63%</t>
+          <t>~+0.69%</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>14.84</v>
+        <v>-1.04</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~4.66 (unrealized)</t>
+          <t>~-11.22 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~+0.44%</t>
+          <t>~-0.03%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-1.04</v>
+        <v>-6.44</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-11.22 (unrealized)</t>
+          <t>~-16.62 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-0.03%</t>
+          <t>~-0.19%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-6.44</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-16.62 (unrealized)</t>
+          <t>~-18.97 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-0.19%</t>
+          <t>~-0.26%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-8.789999999999999</v>
+        <v>-16.67</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-18.97 (unrealized)</t>
+          <t>~-26.85 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-0.26%</t>
+          <t>~-0.49%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-16.67</v>
+        <v>-15.64</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-26.85 (unrealized)</t>
+          <t>~-25.82 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-0.49%</t>
+          <t>~-0.46%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14085,19 +14085,19 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>-220.57</v>
+        <v>-605.54</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P2" s="9" t="inlineStr">
         <is>
-          <t>~-230.99 (unrealized)</t>
+          <t>~-615.96 (unrealized)</t>
         </is>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>~-0.42%</t>
+          <t>~-1.16%</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -14182,19 +14182,19 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="4" t="n">
-        <v>1146.36</v>
+        <v>608.13</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>~1,135.86 (unrealized)</t>
+          <t>~597.63 (unrealized)</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>~+2.18%</t>
+          <t>~+1.16%</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -14279,19 +14279,19 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="4" t="n">
-        <v>645.8099999999999</v>
+        <v>316.63</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>~635.35 (unrealized)</t>
+          <t>~306.17 (unrealized)</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>~+1.24%</t>
+          <t>~+0.61%</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-15.64</v>
+        <v>-28.47</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-25.82 (unrealized)</t>
+          <t>~-38.65 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-0.46%</t>
+          <t>~-0.84%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -14770,19 +14770,19 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>-527.0599999999999</v>
+        <v>-858.85</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>~-537.52 (unrealized)</t>
+          <t>~-869.31 (unrealized)</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>~-1.01%</t>
+          <t>~-1.64%</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -14867,19 +14867,19 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="4" t="n">
-        <v>361.1</v>
+        <v>106.76</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>~350.64 (unrealized)</t>
+          <t>~96.30 (unrealized)</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>~+0.69%</t>
+          <t>~+0.20%</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14085,19 +14085,19 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>-605.54</v>
+        <v>-595.95</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P2" s="9" t="inlineStr">
         <is>
-          <t>~-615.96 (unrealized)</t>
+          <t>~-606.37 (unrealized)</t>
         </is>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>~-1.16%</t>
+          <t>~-1.14%</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -14182,19 +14182,19 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="4" t="n">
-        <v>608.13</v>
+        <v>734.1799999999999</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>~597.63 (unrealized)</t>
+          <t>~723.68 (unrealized)</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>~+1.16%</t>
+          <t>~+1.40%</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -14279,19 +14279,19 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="4" t="n">
-        <v>316.63</v>
+        <v>347.98</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>~306.17 (unrealized)</t>
+          <t>~337.52 (unrealized)</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>~+0.61%</t>
+          <t>~+0.67%</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-28.47</v>
+        <v>-41.44</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-38.65 (unrealized)</t>
+          <t>~-51.62 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-0.84%</t>
+          <t>~-1.22%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -14770,19 +14770,19 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>-858.85</v>
+        <v>-816.87</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>~-869.31 (unrealized)</t>
+          <t>~-827.33 (unrealized)</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>~-1.64%</t>
+          <t>~-1.56%</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -14867,19 +14867,19 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="4" t="n">
-        <v>106.76</v>
+        <v>392.5</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>~96.30 (unrealized)</t>
+          <t>~382.04 (unrealized)</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>~+0.20%</t>
+          <t>~+0.75%</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14182,19 +14182,19 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="4" t="n">
-        <v>734.1799999999999</v>
+        <v>729.29</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>~723.68 (unrealized)</t>
+          <t>~718.79 (unrealized)</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>~+1.40%</t>
+          <t>~+1.39%</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-41.44</v>
+        <v>-48.37</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-51.62 (unrealized)</t>
+          <t>~-58.55 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-1.22%</t>
+          <t>~-1.43%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -14770,19 +14770,19 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>-816.87</v>
+        <v>-851.91</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>~-827.33 (unrealized)</t>
+          <t>~-862.37 (unrealized)</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>~-1.56%</t>
+          <t>~-1.63%</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -14867,19 +14867,19 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="4" t="n">
-        <v>392.5</v>
+        <v>310.86</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>~382.04 (unrealized)</t>
+          <t>~300.40 (unrealized)</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>~+0.75%</t>
+          <t>~+0.59%</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14085,19 +14085,19 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>-595.95</v>
+        <v>-580.63</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P2" s="9" t="inlineStr">
         <is>
-          <t>~-606.37 (unrealized)</t>
+          <t>~-591.05 (unrealized)</t>
         </is>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>~-1.14%</t>
+          <t>~-1.11%</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -14182,19 +14182,19 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="4" t="n">
-        <v>729.29</v>
+        <v>785.21</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>~718.79 (unrealized)</t>
+          <t>~774.71 (unrealized)</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>~+1.39%</t>
+          <t>~+1.50%</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-48.37</v>
+        <v>-67.45</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-58.55 (unrealized)</t>
+          <t>~-77.63 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-1.43%</t>
+          <t>~-1.99%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -14770,19 +14770,19 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>-851.91</v>
+        <v>-819.79</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>~-862.37 (unrealized)</t>
+          <t>~-830.25 (unrealized)</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>~-1.63%</t>
+          <t>~-1.57%</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -14867,19 +14867,19 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="4" t="n">
-        <v>310.86</v>
+        <v>351.68</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>~300.40 (unrealized)</t>
+          <t>~341.22 (unrealized)</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>~+0.59%</t>
+          <t>~+0.67%</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -1099,17 +1099,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>#14ID IWM SHORT</t>
+          <t>#4SW XLV LONG</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1119,46 +1119,46 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>63.41</v>
+        <v>52.32</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>7.5</v>
+        <v>23.85</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1182.87</v>
+        <v>1420.63</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>19.75</v>
+        <v>61.23</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>1163.12</v>
+        <v>1359.4</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1163.12</v>
+        <v>226.57</v>
       </c>
     </row>
     <row r="10">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>#36ID DIA LONG</t>
+          <t>#14ID IWM SHORT</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1187,46 +1187,46 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red</t>
+          <t>Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>67.86</v>
+        <v>63.41</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2.52</v>
+        <v>7.5</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1221.22</v>
+        <v>1182.87</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>76.68000000000001</v>
+        <v>19.75</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>1144.54</v>
+        <v>1163.12</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>286.13</v>
+        <v>1163.12</v>
       </c>
     </row>
     <row r="11">
@@ -1235,17 +1235,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>#4SW XLV LONG</t>
+          <t>#36ID DIA LONG</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1260,41 +1260,41 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>52.32</v>
+        <v>67.86</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>23.85</v>
+        <v>2.52</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1137.01</v>
+        <v>1221.22</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>50.77</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>1086.24</v>
+        <v>1144.54</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>217.25</v>
+        <v>286.13</v>
       </c>
     </row>
     <row r="12">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>#31SW QQQ LONG</t>
+          <t>#4SW XLP LONG</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2280,14 +2280,14 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+2Red</t>
+          <t>EMA20&lt;EMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>65.29000000000001</v>
+        <v>61.78</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>48.57</v>
+        <v>70.52</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>1</v>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>#4SW XLP LONG</t>
+          <t>#1SW TRX-USD LONG</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2348,41 +2348,41 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>EMA20&lt;EMA50+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>61.78</v>
+        <v>66.67</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>70.52</v>
+        <v>51.86</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0</v>
+        <v>-27.64</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="4" t="n">
-        <v>0</v>
+        <v>40.12</v>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v>-67.76000000000001</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0</v>
+        <v>-16.94</v>
       </c>
     </row>
     <row r="28">
@@ -2391,17 +2391,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>#1SW TRX-USD LONG</t>
+          <t>#1ID DOGE-USD SHORT</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>DOGE-USD</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2411,46 +2411,46 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>Price&gt;SMA20+RSI&lt;45</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>66.67</v>
+        <v>50.67</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>51.86</v>
+        <v>31.42</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="N28" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-27.64</v>
+        <v>-88.45</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>40.12</v>
+        <v>12.57</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>-67.76000000000001</v>
+        <v>-101.02</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-16.94</v>
+        <v>-101.02</v>
       </c>
     </row>
     <row r="29">
@@ -2459,66 +2459,66 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>#1ID DOGE-USD SHORT</t>
+          <t>#5SW XLP LONG</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>DOGE-USD</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+RSI&lt;45</t>
+          <t>Range&lt;1%+SMA20&lt;EMA20</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>50.67</v>
+        <v>58.26</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>31.42</v>
+        <v>67.47</v>
       </c>
       <c r="J29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-88.45</v>
+        <v>-149.74</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>12.57</v>
+        <v>20.27</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>-101.02</v>
+        <v>-170.01</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-101.02</v>
+        <v>-85</v>
       </c>
     </row>
     <row r="30">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>#5SW XLP LONG</t>
+          <t>#57SW XLRE LONG</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2552,41 +2552,41 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Range&lt;1%+SMA20&lt;EMA20</t>
+          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&lt;Open</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>58.26</v>
+        <v>69.23</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>67.47</v>
+        <v>16.84</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-149.74</v>
+        <v>-469.04</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>20.27</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>-170.01</v>
+        <v>-479</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-85</v>
+        <v>-479</v>
       </c>
     </row>
     <row r="31">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>#57SW XLRE LONG</t>
+          <t>#3SW XLC LONG</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2620,20 +2620,20 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&lt;Open</t>
+          <t>Price&gt;EMA9+Range&lt;1%</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>69.23</v>
+        <v>53.98</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16.84</v>
+        <v>68.92</v>
       </c>
       <c r="J31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2645,16 +2645,16 @@
         <v>0</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-469.04</v>
+        <v>-750.65</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>10.32</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>-479</v>
+        <v>-760.97</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-479</v>
+        <v>-760.97</v>
       </c>
     </row>
     <row r="32">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>#3SW XLC LONG</t>
+          <t>#31SW QQQ LONG</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2688,20 +2688,20 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;EMA9+Range&lt;1%</t>
+          <t>Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>53.98</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>68.92</v>
+        <v>48.57</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2713,16 +2713,16 @@
         <v>0</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-750.65</v>
+        <v>-865.8099999999999</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.32</v>
+        <v>10.46</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>-760.97</v>
+        <v>-876.27</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-760.97</v>
+        <v>-876.27</v>
       </c>
     </row>
     <row r="33">
@@ -14085,19 +14085,19 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>-580.63</v>
+        <v>-572.66</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P2" s="9" t="inlineStr">
         <is>
-          <t>~-591.05 (unrealized)</t>
+          <t>~-583.08 (unrealized)</t>
         </is>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>~-1.11%</t>
+          <t>~-1.10%</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -14182,19 +14182,19 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="4" t="n">
-        <v>785.21</v>
+        <v>745.6</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>~774.71 (unrealized)</t>
+          <t>~735.10 (unrealized)</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>~+1.50%</t>
+          <t>~+1.42%</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -14279,19 +14279,19 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="4" t="n">
-        <v>347.98</v>
+        <v>366.79</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>~337.52 (unrealized)</t>
+          <t>~356.33 (unrealized)</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>~+0.67%</t>
+          <t>~+0.70%</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-67.45</v>
+        <v>-68.56999999999999</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-77.63 (unrealized)</t>
+          <t>~-78.75 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-1.99%</t>
+          <t>~-2.02%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -14767,27 +14767,29 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
+      <c r="L9" s="2" t="n">
+        <v>704.52</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:37:33 IST</t>
+        </is>
+      </c>
       <c r="N9" s="4" t="n">
-        <v>-819.79</v>
+        <v>-865.8099999999999</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.46</v>
       </c>
-      <c r="P9" s="9" t="inlineStr">
-        <is>
-          <t>~-830.25 (unrealized)</t>
-        </is>
-      </c>
-      <c r="Q9" s="9" t="inlineStr">
-        <is>
-          <t>~-1.57%</t>
-        </is>
+      <c r="P9" s="6" t="n">
+        <v>-876.27</v>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v>-1.68</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -14812,7 +14814,7 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>#31SW Price&gt;SMA50+2Red</t>
+          <t>#31SW Price&gt;SMA50+2Red | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -14864,27 +14866,29 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
+      <c r="L10" s="2" t="n">
+        <v>167.5</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:37:33 IST</t>
+        </is>
+      </c>
       <c r="N10" s="4" t="n">
-        <v>351.68</v>
+        <v>283.62</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.46</v>
       </c>
-      <c r="P10" s="9" t="inlineStr">
-        <is>
-          <t>~341.22 (unrealized)</t>
-        </is>
-      </c>
-      <c r="Q10" s="9" t="inlineStr">
-        <is>
-          <t>~+0.67%</t>
-        </is>
+      <c r="P10" s="5" t="n">
+        <v>273.16</v>
+      </c>
+      <c r="Q10" s="12" t="n">
+        <v>0.52</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -14909,7 +14913,7 @@
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -20547,18 +20551,18 @@
       <c r="L68" s="15" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
       <c r="N68" s="17" t="n">
-        <v>26493.04</v>
+        <v>25910.85</v>
       </c>
       <c r="O68" s="17" t="n">
-        <v>2438.67</v>
+        <v>2459.59</v>
       </c>
       <c r="P68" s="18" t="n">
-        <v>24054.37</v>
+        <v>23451.26</v>
       </c>
       <c r="Q68" s="16" t="inlineStr"/>
       <c r="R68" s="15" t="inlineStr">
         <is>
-          <t>66 trades (60 closed / 6 open)</t>
+          <t>66 trades (62 closed / 4 open)</t>
         </is>
       </c>
       <c r="S68" s="15" t="inlineStr"/>

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14085,19 +14085,19 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>-572.66</v>
+        <v>-628.83</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P2" s="9" t="inlineStr">
         <is>
-          <t>~-583.08 (unrealized)</t>
+          <t>~-639.25 (unrealized)</t>
         </is>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>~-1.10%</t>
+          <t>~-1.21%</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -14182,19 +14182,19 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="4" t="n">
-        <v>745.6</v>
+        <v>605.8</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>~735.10 (unrealized)</t>
+          <t>~595.30 (unrealized)</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>~+1.42%</t>
+          <t>~+1.15%</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -14279,19 +14279,19 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="4" t="n">
-        <v>366.79</v>
+        <v>241.4</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>~356.33 (unrealized)</t>
+          <t>~230.94 (unrealized)</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>~+0.70%</t>
+          <t>~+0.46%</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-68.56999999999999</v>
+        <v>-65.62</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-78.75 (unrealized)</t>
+          <t>~-75.80 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-2.02%</t>
+          <t>~-1.93%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14085,19 +14085,19 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>-628.83</v>
+        <v>-557.59</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P2" s="9" t="inlineStr">
         <is>
-          <t>~-639.25 (unrealized)</t>
+          <t>~-568.01 (unrealized)</t>
         </is>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>~-1.21%</t>
+          <t>~-1.07%</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -14182,19 +14182,19 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="4" t="n">
-        <v>605.8</v>
+        <v>661.72</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>~595.30 (unrealized)</t>
+          <t>~651.22 (unrealized)</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>~+1.15%</t>
+          <t>~+1.26%</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -14279,19 +14279,19 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="4" t="n">
-        <v>241.4</v>
+        <v>213.18</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>~230.94 (unrealized)</t>
+          <t>~202.72 (unrealized)</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>~+0.46%</t>
+          <t>~+0.41%</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-65.62</v>
+        <v>-70.47</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-75.80 (unrealized)</t>
+          <t>~-80.65 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-1.93%</t>
+          <t>~-2.08%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-70.47</v>
+        <v>-68.98999999999999</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-80.65 (unrealized)</t>
+          <t>~-79.17 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-2.08%</t>
+          <t>~-2.03%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-68.98999999999999</v>
+        <v>-62.56</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-79.17 (unrealized)</t>
+          <t>~-72.74 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-2.03%</t>
+          <t>~-1.84%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-62.56</v>
+        <v>-64.42</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-72.74 (unrealized)</t>
+          <t>~-74.60 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-1.84%</t>
+          <t>~-1.90%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-64.42</v>
+        <v>-50.01</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-74.60 (unrealized)</t>
+          <t>~-60.19 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-1.90%</t>
+          <t>~-1.47%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-50.01</v>
+        <v>-45.93</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-60.19 (unrealized)</t>
+          <t>~-56.11 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-1.47%</t>
+          <t>~-1.35%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-45.93</v>
+        <v>-48.51</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-56.11 (unrealized)</t>
+          <t>~-58.69 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-1.35%</t>
+          <t>~-1.43%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14085,19 +14085,19 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>-557.59</v>
+        <v>-346.61</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P2" s="9" t="inlineStr">
         <is>
-          <t>~-568.01 (unrealized)</t>
+          <t>~-357.03 (unrealized)</t>
         </is>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>~-1.07%</t>
+          <t>~-0.67%</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -14182,19 +14182,19 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="4" t="n">
-        <v>661.72</v>
+        <v>801.52</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>~651.22 (unrealized)</t>
+          <t>~791.02 (unrealized)</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>~+1.26%</t>
+          <t>~+1.53%</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -14279,14 +14279,14 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="4" t="n">
-        <v>213.18</v>
+        <v>216.32</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>~202.72 (unrealized)</t>
+          <t>~205.86 (unrealized)</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-48.51</v>
+        <v>-47.97</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-58.69 (unrealized)</t>
+          <t>~-58.15 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-1.43%</t>
+          <t>~-1.41%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14085,19 +14085,19 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>-346.61</v>
+        <v>-397.3</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P2" s="9" t="inlineStr">
         <is>
-          <t>~-357.03 (unrealized)</t>
+          <t>~-407.72 (unrealized)</t>
         </is>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>~-0.67%</t>
+          <t>~-0.76%</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -14182,19 +14182,19 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="4" t="n">
-        <v>801.52</v>
+        <v>771.23</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>~791.02 (unrealized)</t>
+          <t>~760.73 (unrealized)</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>~+1.53%</t>
+          <t>~+1.47%</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -14279,19 +14279,19 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="4" t="n">
-        <v>216.32</v>
+        <v>225.72</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>~205.86 (unrealized)</t>
+          <t>~215.26 (unrealized)</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>~+0.41%</t>
+          <t>~+0.43%</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-47.97</v>
+        <v>-47.11</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-58.15 (unrealized)</t>
+          <t>~-57.29 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-1.41%</t>
+          <t>~-1.39%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14085,19 +14085,19 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>-397.3</v>
+        <v>-426.07</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P2" s="9" t="inlineStr">
         <is>
-          <t>~-407.72 (unrealized)</t>
+          <t>~-436.49 (unrealized)</t>
         </is>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>~-0.76%</t>
+          <t>~-0.82%</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -14182,19 +14182,19 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="4" t="n">
-        <v>771.23</v>
+        <v>652.4</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>~760.73 (unrealized)</t>
+          <t>~641.90 (unrealized)</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>~+1.47%</t>
+          <t>~+1.24%</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -14279,19 +14279,19 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="4" t="n">
-        <v>225.72</v>
+        <v>319.77</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>~215.26 (unrealized)</t>
+          <t>~309.31 (unrealized)</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>~+0.43%</t>
+          <t>~+0.61%</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-47.11</v>
+        <v>-36.68</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-57.29 (unrealized)</t>
+          <t>~-46.86 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-1.39%</t>
+          <t>~-1.08%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14085,19 +14085,19 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>-426.07</v>
+        <v>-430.18</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P2" s="9" t="inlineStr">
         <is>
-          <t>~-436.49 (unrealized)</t>
+          <t>~-440.60 (unrealized)</t>
         </is>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>~-0.82%</t>
+          <t>~-0.83%</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -14182,19 +14182,19 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="4" t="n">
-        <v>652.4</v>
+        <v>570.85</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>~641.90 (unrealized)</t>
+          <t>~560.35 (unrealized)</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>~+1.24%</t>
+          <t>~+1.09%</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -14279,19 +14279,19 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="4" t="n">
-        <v>319.77</v>
+        <v>363.72</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>~309.31 (unrealized)</t>
+          <t>~353.26 (unrealized)</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>~+0.61%</t>
+          <t>~+0.70%</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-36.68</v>
+        <v>-37.57</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-46.86 (unrealized)</t>
+          <t>~-47.75 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-1.08%</t>
+          <t>~-1.11%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14085,19 +14085,19 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>-430.18</v>
+        <v>-387.7</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P2" s="9" t="inlineStr">
         <is>
-          <t>~-440.60 (unrealized)</t>
+          <t>~-398.12 (unrealized)</t>
         </is>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>~-0.83%</t>
+          <t>~-0.74%</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -14182,19 +14182,19 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="4" t="n">
-        <v>570.85</v>
+        <v>643.08</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>~560.35 (unrealized)</t>
+          <t>~632.58 (unrealized)</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>~+1.09%</t>
+          <t>~+1.23%</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -14279,19 +14279,19 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="4" t="n">
-        <v>363.72</v>
+        <v>385.6</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>~353.26 (unrealized)</t>
+          <t>~375.14 (unrealized)</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>~+0.70%</t>
+          <t>~+0.74%</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-37.57</v>
+        <v>-41.8</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-47.75 (unrealized)</t>
+          <t>~-51.98 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-1.11%</t>
+          <t>~-1.23%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$R$196</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Trades'!$A$1:$W$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Trades'!$A$1:$W$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1066,10 +1066,10 @@
         <v>50.46</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>2</v>
@@ -13889,7 +13889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W68"/>
+  <dimension ref="A1:W69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14037,12 +14037,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>00:18:16 IST</t>
+          <t>00:28:17 IST</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -14066,16 +14066,16 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>380.39</v>
+        <v>183.76</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>137</v>
+        <v>284</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>372.74</v>
+        <v>180.07</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>395.56</v>
+        <v>191.09</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -14085,19 +14085,19 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>-387.7</v>
+        <v>56.8</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>10.42</v>
+        <v>10.44</v>
       </c>
       <c r="P2" s="9" t="inlineStr">
         <is>
-          <t>~-398.12 (unrealized)</t>
+          <t>~46.36 (unrealized)</t>
         </is>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>~-0.74%</t>
+          <t>~+0.11%</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -14107,27 +14107,27 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>63.73</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 383.727455, "BB_lo": 375.490547, "Close": 380.350006, "EMA20": 379.149401, "EMA200": 354.178396, "EMA50": 375.052856, "EMA9": 379.809738, "High": 381.670013, "Low": 380.200012, "Open": 380.519989, "RSI14": 53.707446, "Ret": 0.008351, "SMA20": 379.609001, "SMA50": 374.815799, "Volume": 202800.0, "_provenance": {"captured_at_ist": "2026-09-15 00:18:16 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "fd0e07c7006d9e581a4d30f0d710b0d5f91f55641de9d507f3b73b03768e2faa"}, "high20": 385.049988, "high50": 385.049988, "low20": 376.040009, "low50": 358.170013}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 189.495838, "BB_lo": 180.328162, "Close": 183.740005, "EMA20": 185.220461, "EMA200": 165.492268, "EMA50": 183.219192, "EMA9": 185.51008, "High": 185.070007, "Low": 183.460007, "Open": 184.5, "RSI14": 47.830673, "Ret": -0.00293, "SMA20": 184.912, "SMA50": 182.8038, "Volume": 6147600.0, "_provenance": {"captured_at_ist": "2026-09-17 00:28:17 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "40b5431cf114a047302613b8978e7d5624cfcad2013f8ae927bbc041828a6677"}, "high20": 191.75, "high50": 191.75, "low20": 178.820007, "low50": 166.460007}</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>#28SW Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
         </is>
       </c>
     </row>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -14163,16 +14163,16 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>112.61</v>
+        <v>380.39</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>466</v>
+        <v>137</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>110.35</v>
+        <v>372.74</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>117.1</v>
+        <v>395.56</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
@@ -14182,19 +14182,19 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="4" t="n">
-        <v>643.08</v>
+        <v>-753.5</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>10.5</v>
+        <v>10.42</v>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>~632.58 (unrealized)</t>
+          <t>~-763.92 (unrealized)</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>~+1.23%</t>
+          <t>~-1.45%</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -14204,27 +14204,27 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>59.53</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;EMA9+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 113.656097, "BB_lo": 110.021903, "Close": 112.599998, "EMA20": 111.705223, "EMA200": 111.692649, "EMA50": 111.394685, "EMA9": 111.897336, "High": 113.040001, "Low": 112.309998, "Open": 112.339996, "RSI14": 53.98306, "Ret": 0.009865, "SMA20": 111.839, "SMA50": 110.8982, "Volume": 3979800.0, "_provenance": {"captured_at_ist": "2026-09-15 00:18:16 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "d624b259f32b23afed94634d2f685958792df81f76287970bd56314d73deee6e"}, "high20": 114.290001, "high50": 114.290001, "low20": 110.25, "low50": 105.254997}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 383.727455, "BB_lo": 375.490547, "Close": 380.350006, "EMA20": 379.149401, "EMA200": 354.178396, "EMA50": 375.052856, "EMA9": 379.809738, "High": 381.670013, "Low": 380.200012, "Open": 380.519989, "RSI14": 53.707446, "Ret": 0.008351, "SMA20": 379.609001, "SMA50": 374.815799, "Volume": 202800.0, "_provenance": {"captured_at_ist": "2026-09-15 00:18:16 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "fd0e07c7006d9e581a4d30f0d710b0d5f91f55641de9d507f3b73b03768e2faa"}, "high20": 385.049988, "high50": 385.049988, "low20": 376.040009, "low50": 358.170013}</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>#3SW Price&gt;EMA9+Range&lt;1%</t>
+          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
     </row>
@@ -14236,7 +14236,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>00:18:15 IST</t>
+          <t>00:18:16 IST</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -14246,7 +14246,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -14260,16 +14260,16 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>83.39</v>
+        <v>112.61</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>627</v>
+        <v>466</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>81.70999999999999</v>
+        <v>110.35</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>86.72</v>
+        <v>117.1</v>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
@@ -14279,19 +14279,19 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="4" t="n">
-        <v>385.6</v>
+        <v>314.55</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>10.46</v>
+        <v>10.5</v>
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>~375.14 (unrealized)</t>
+          <t>~304.05 (unrealized)</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>~+0.74%</t>
+          <t>~+0.60%</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -14301,49 +14301,49 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>61.78</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>EMA20&lt;EMA50+Range&lt;1%</t>
+          <t>Price&gt;EMA9+Range&lt;1%</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 87.544832, "BB_lo": 82.866166, "Close": 83.379997, "EMA20": 84.743425, "EMA200": 82.927356, "EMA50": 84.782471, "EMA9": 84.151368, "High": 83.690002, "Low": 83.040001, "Open": 83.510002, "RSI14": 40.412033, "Ret": 0.00349, "SMA20": 85.205499, "SMA50": 84.994, "Volume": 10836500.0, "_provenance": {"captured_at_ist": "2026-09-15 00:18:15 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "0799e2a4d605288db1a0c1ff7b2ca5488b29bfdd8b1fd343b412e39dd964746b"}, "high20": 87.470001, "high50": 88.779999, "low20": 82.849998, "low50": 82.769997}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 113.656097, "BB_lo": 110.021903, "Close": 112.599998, "EMA20": 111.705223, "EMA200": 111.692649, "EMA50": 111.394685, "EMA9": 111.897336, "High": 113.040001, "Low": 112.309998, "Open": 112.339996, "RSI14": 53.98306, "Ret": 0.009865, "SMA20": 111.839, "SMA50": 110.8982, "Volume": 3979800.0, "_provenance": {"captured_at_ist": "2026-09-15 00:18:16 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "d624b259f32b23afed94634d2f685958792df81f76287970bd56314d73deee6e"}, "high20": 114.290001, "high50": 114.290001, "low20": 110.25, "low50": 105.254997}</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA20&lt;EMA50+Range&lt;1%</t>
+          <t>#3SW Price&gt;EMA9+Range&lt;1%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>15:01:27 IST</t>
+          <t>00:18:15 IST</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -14356,17 +14356,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G5" s="10" t="n">
-        <v>0.3393</v>
+      <c r="G5" s="4" t="n">
+        <v>83.39</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>0.3315</v>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>0.3518</v>
+        <v>627</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>81.70999999999999</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>86.72</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
@@ -14376,19 +14376,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>-41.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>10.18</v>
+        <v>10.46</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~-51.98 (unrealized)</t>
+          <t>~61.64 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~-1.23%</t>
+          <t>~+0.14%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -14398,39 +14398,39 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>61.78</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>EMA20&lt;EMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 0.345453, "BB_lo": 0.325368, "Close": 0.338307, "EMA20": 0.336164, "EMA200": 0.325217, "EMA50": 0.333945, "EMA9": 0.3375, "High": 0.341545, "Low": 0.338295, "Open": 0.339846, "RSI14": 54.726192, "Ret": -0.004528, "SMA20": 0.33541, "SMA50": 0.333187, "Volume": 302053356.0, "_provenance": {"captured_at_ist": "2026-09-14 15:01:27 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "65ee6ec20afd1eadd50216b1a8c8746e16e10a009a93786d32249e8209218bb5"}, "high20": 0.346589, "high50": 0.349996, "low20": 0.321569, "low50": 0.321569}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 87.544832, "BB_lo": 82.866166, "Close": 83.379997, "EMA20": 84.743425, "EMA200": 82.927356, "EMA50": 84.782471, "EMA9": 84.151368, "High": 83.690002, "Low": 83.040001, "Open": 83.510002, "RSI14": 40.412033, "Ret": 0.00349, "SMA20": 85.205499, "SMA50": 84.994, "Volume": 10836500.0, "_provenance": {"captured_at_ist": "2026-09-15 00:18:15 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "0799e2a4d605288db1a0c1ff7b2ca5488b29bfdd8b1fd343b412e39dd964746b"}, "high20": 87.470001, "high50": 88.779999, "low20": 82.849998, "low50": 82.769997}</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>#4SW EMA20&lt;EMA50+Range&lt;1%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>00:10:42 IST</t>
+          <t>15:01:27 IST</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -14453,83 +14453,81 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>2439.54</v>
+      <c r="G6" s="10" t="n">
+        <v>0.3393</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>2388.36</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>2534.58</v>
+        <v>10000</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>0.3518</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L6" s="2" t="n">
-        <v>2532.05</v>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-12 01:01:12 IST</t>
-        </is>
-      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="4" t="n">
-        <v>1850.11</v>
+        <v>-41.25</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>146.37</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>1703.74</v>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v>3.49</v>
+        <v>10.18</v>
+      </c>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t>~-51.43 (unrealized)</t>
+        </is>
+      </c>
+      <c r="Q6" s="9" t="inlineStr">
+        <is>
+          <t>~-1.22%</t>
+        </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2532.765429, "BB_lo": 2393.56941, "Close": 2437.098633, "EMA20": 2404.555507, "EMA200": 2189.831855, "EMA50": 2222.045575, "EMA9": 2463.211647, "High": 2483.719971, "Low": 2406.906494, "Open": 2466.913086, "RSI14": 57.778434, "Ret": -0.012086, "SMA20": 2463.167419, "SMA50": 2147.895715, "Volume": 16781828594.0, "_provenance": {"captured_at_ist": "2026-09-12 00:10:42 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "1ef31696acc1cd4efe2bcd7470c35cf39eec58504bbcfa1e511fce897866faa4"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 2324.709473, "low50": 1821.485107}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 0.345453, "BB_lo": 0.325368, "Close": 0.338307, "EMA20": 0.336164, "EMA200": 0.325217, "EMA50": 0.333945, "EMA9": 0.3375, "High": 0.341545, "Low": 0.338295, "Open": 0.339846, "RSI14": 54.726192, "Ret": -0.004528, "SMA20": 0.33541, "SMA50": 0.333187, "Volume": 302053356.0, "_provenance": {"captured_at_ist": "2026-09-14 15:01:27 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "65ee6ec20afd1eadd50216b1a8c8746e16e10a009a93786d32249e8209218bb5"}, "high20": 0.346589, "high50": 0.349996, "low20": 0.321569, "low50": 0.321569}</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | 🎯 Target Hit (live)</t>
+          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>11:14:08 IST</t>
+          <t>00:10:42 IST</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -14539,55 +14537,55 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>DOGE-USD</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>0.083828</v>
+          <t>SWING_1d</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>2439.54</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>0.085341</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>0.08155800000000001</v>
+        <v>20</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>2388.36</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>2534.58</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.08559700000000001</v>
+        <v>2532.05</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 19:38:41 IST</t>
+          <t>2026-09-12 01:01:12 IST</t>
         </is>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-88.45</v>
+        <v>1850.11</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>12.57</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v>-101.02</v>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v>-2.41</v>
+        <v>146.37</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>1703.74</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>3.49</v>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
@@ -14596,27 +14594,27 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>50.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+RSI&lt;45</t>
+          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>{"2Red": 0.0, "Close": 0.08408, "EMA20": 0.08417, "EMA50": 0.085792, "EMA9": 0.083724, "High": 0.08414, "Low": 0.08364, "Open": 0.08372, "RSI14": 44.169679, "Ret": 0.0043, "SMA20": 0.083904, "SMA50": 0.086466, "Volume": 9846336.0, "_provenance": {"captured_at_ist": "2026-09-11 11:14:08 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "52faf51891c7541754ee8666a227d22c17b888d769d3894f56f2ba75ece3eaed"}}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2532.765429, "BB_lo": 2393.56941, "Close": 2437.098633, "EMA20": 2404.555507, "EMA200": 2189.831855, "EMA50": 2222.045575, "EMA9": 2463.211647, "High": 2483.719971, "Low": 2406.906494, "Open": 2466.913086, "RSI14": 57.778434, "Ret": -0.012086, "SMA20": 2463.167419, "SMA50": 2147.895715, "Volume": 16781828594.0, "_provenance": {"captured_at_ist": "2026-09-12 00:10:42 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "1ef31696acc1cd4efe2bcd7470c35cf39eec58504bbcfa1e511fce897866faa4"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 2324.709473, "low50": 1821.485107}</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>#1ID Price&gt;SMA20+RSI&lt;45 | 🎯 SL Hit (live)</t>
+          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | 🎯 Target Hit (live)</t>
         </is>
       </c>
     </row>
@@ -14628,7 +14626,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>00:05:22 IST</t>
+          <t>11:14:08 IST</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -14638,38 +14636,38 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>DOGE-USD</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>2469.38</v>
+          <t>INTRADAY_1h</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>0.083828</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>2417.58</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>2565.59</v>
+        <v>50000</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>0.085341</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>0.08155800000000001</v>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2563.02</v>
+        <v>0.08559700000000001</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -14677,16 +14675,16 @@
         </is>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1779.24</v>
+        <v>-88.45</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>140.75</v>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v>1638.49</v>
-      </c>
-      <c r="Q8" s="5" t="n">
-        <v>3.49</v>
+        <v>12.57</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>-101.02</v>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v>-2.41</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
@@ -14695,27 +14693,27 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>50.67</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
+          <t>Price&gt;SMA20+RSI&lt;45</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2539.244704, "BB_lo": 2394.908446, "Close": 2466.913818, "EMA20": 2401.129915, "EMA200": 2187.380698, "EMA50": 2213.267899, "EMA9": 2469.739901, "High": 2522.369629, "Low": 2443.702393, "Open": 2484.894287, "RSI14": 60.959164, "Ret": -0.007255, "SMA20": 2467.076575, "SMA50": 2137.823545, "Volume": 14955608804.0, "_provenance": {"captured_at_ist": "2026-09-11 00:05:22 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "d8d364e889190953445a4b086a4c86f37d82d8af7f1f62c9054b85772793509b"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 2222.574707, "low50": 1821.485107}</t>
+          <t>{"2Red": 0.0, "Close": 0.08408, "EMA20": 0.08417, "EMA50": 0.085792, "EMA9": 0.083724, "High": 0.08414, "Low": 0.08364, "Open": 0.08372, "RSI14": 44.169679, "Ret": 0.0043, "SMA20": 0.083904, "SMA50": 0.086466, "Volume": 9846336.0, "_provenance": {"captured_at_ist": "2026-09-11 11:14:08 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "52faf51891c7541754ee8666a227d22c17b888d769d3894f56f2ba75ece3eaed"}}</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | 🎯 Target Hit (live)</t>
+          <t>#1ID Price&gt;SMA20+RSI&lt;45 | 🎯 SL Hit (live)</t>
         </is>
       </c>
     </row>
@@ -14732,12 +14730,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -14751,16 +14749,16 @@
         </is>
       </c>
       <c r="G9" s="4" t="n">
-        <v>716.38</v>
+        <v>2469.38</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>701.98</v>
+        <v>2417.58</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>744.96</v>
+        <v>2565.59</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
@@ -14768,24 +14766,24 @@
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>704.52</v>
+        <v>2563.02</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:37:33 IST</t>
+          <t>2026-09-11 19:38:41 IST</t>
         </is>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-865.8099999999999</v>
+        <v>1779.24</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>10.46</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v>-876.27</v>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v>-1.68</v>
+        <v>140.75</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>1638.49</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>3.49</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
@@ -14794,27 +14792,27 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>65.29</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+2Red</t>
+          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 732.086193, "BB_lo": 702.469807, "Close": 716.309998, "EMA20": 714.795564, "EMA200": 664.839596, "EMA50": 710.89305, "EMA9": 715.808843, "High": 719.700012, "Low": 714.02002, "Open": 716.400024, "RSI14": 51.664581, "Ret": -0.002854, "SMA20": 717.278, "SMA50": 711.166399, "Volume": 26659200.0, "_provenance": {"captured_at_ist": "2026-09-11 00:05:22 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "3150d3a7200210926ae4cbca12d82841d05d62f6516aa32b4a5180c4e8d61898"}, "high20": 734.580017, "high50": 737.619995, "low20": 702.700012, "low50": 661.140015}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2539.244704, "BB_lo": 2394.908446, "Close": 2466.913818, "EMA20": 2401.129915, "EMA200": 2187.380698, "EMA50": 2213.267899, "EMA9": 2469.739901, "High": 2522.369629, "Low": 2443.702393, "Open": 2484.894287, "RSI14": 60.959164, "Ret": -0.007255, "SMA20": 2467.076575, "SMA50": 2137.823545, "Volume": 14955608804.0, "_provenance": {"captured_at_ist": "2026-09-11 00:05:22 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "d8d364e889190953445a4b086a4c86f37d82d8af7f1f62c9054b85772793509b"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 2222.574707, "low50": 1821.485107}</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>#31SW Price&gt;SMA50+2Red | Expiry 5d</t>
+          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | 🎯 Target Hit (live)</t>
         </is>
       </c>
     </row>
@@ -14836,7 +14834,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -14850,16 +14848,16 @@
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>166.6</v>
+        <v>716.38</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>314</v>
+        <v>73</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>163.25</v>
+        <v>701.98</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>173.24</v>
+        <v>744.96</v>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
@@ -14867,7 +14865,7 @@
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>167.5</v>
+        <v>704.52</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -14875,16 +14873,16 @@
         </is>
       </c>
       <c r="N10" s="4" t="n">
-        <v>283.62</v>
+        <v>-865.8099999999999</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.46</v>
       </c>
-      <c r="P10" s="5" t="n">
-        <v>273.16</v>
-      </c>
-      <c r="Q10" s="12" t="n">
-        <v>0.52</v>
+      <c r="P10" s="6" t="n">
+        <v>-876.27</v>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v>-1.68</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -14893,49 +14891,49 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>65.29</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 177.039339, "BB_lo": 165.311657, "Close": 166.580002, "EMA20": 169.967704, "EMA200": 155.06167, "EMA50": 165.803089, "EMA9": 170.19262, "High": 167.410004, "Low": 166.389999, "Open": 167.309998, "RSI14": 43.5919, "Ret": -0.003291, "SMA20": 171.175498, "SMA50": 165.980599, "Volume": 8018100.0, "_provenance": {"captured_at_ist": "2026-09-11 00:05:22 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "b1bd4acf19438d5c9145df22921236f8ae2c9a49fd069b3fdf994b5e8ccf5871"}, "high20": 176.600006, "high50": 176.600006, "low20": 165.759995, "low50": 157.229996}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 732.086193, "BB_lo": 702.469807, "Close": 716.309998, "EMA20": 714.795564, "EMA200": 664.839596, "EMA50": 710.89305, "EMA9": 715.808843, "High": 719.700012, "Low": 714.02002, "Open": 716.400024, "RSI14": 51.664581, "Ret": -0.002854, "SMA20": 717.278, "SMA50": 711.166399, "Volume": 26659200.0, "_provenance": {"captured_at_ist": "2026-09-11 00:05:22 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "3150d3a7200210926ae4cbca12d82841d05d62f6516aa32b4a5180c4e8d61898"}, "high20": 734.580017, "high50": 737.619995, "low20": 702.700012, "low50": 661.140015}</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#31SW Price&gt;SMA50+2Red | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>04:11:58 IST</t>
+          <t>00:05:22 IST</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -14949,16 +14947,16 @@
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2487.43</v>
+        <v>166.6</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>19</v>
+        <v>314</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>2435.24</v>
+        <v>163.25</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>2584.34</v>
+        <v>173.24</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
@@ -14966,24 +14964,24 @@
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>2432.8</v>
+        <v>167.5</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 18:11:52 IST</t>
+          <t>2026-09-16 00:37:33 IST</t>
         </is>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1037.88</v>
+        <v>283.62</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>141.78</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v>-1179.66</v>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v>-2.5</v>
+        <v>10.46</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>273.16</v>
+      </c>
+      <c r="Q11" s="12" t="n">
+        <v>0.52</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -14992,39 +14990,39 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+Range&gt;1.5%+2Red</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2555.797457, "BB_lo": 2364.302788, "Close": 2484.941406, "EMA20": 2394.205294, "EMA200": 2184.550101, "EMA50": 2202.915005, "EMA9": 2470.446422, "High": 2506.753174, "Low": 2441.328857, "Open": 2490.919678, "RSI14": 62.903407, "Ret": -0.002415, "SMA20": 2460.050122, "SMA50": 2127.052944, "Volume": 13471038160.0, "_provenance": {"captured_at_ist": "2026-09-10 04:11:58 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "9d935e01f058e194edc4cbc5b22f08a0e6b38c3f190d3dd9f1551d28266ed601"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 1905.082397, "low50": 1821.485107}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 177.039339, "BB_lo": 165.311657, "Close": 166.580002, "EMA20": 169.967704, "EMA200": 155.06167, "EMA50": 165.803089, "EMA9": 170.19262, "High": 167.410004, "Low": 166.389999, "Open": 167.309998, "RSI14": 43.5919, "Ret": -0.003291, "SMA20": 171.175498, "SMA50": 165.980599, "Volume": 8018100.0, "_provenance": {"captured_at_ist": "2026-09-11 00:05:22 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "b1bd4acf19438d5c9145df22921236f8ae2c9a49fd069b3fdf994b5e8ccf5871"}, "high20": 176.600006, "high50": 176.600006, "low20": 165.759995, "low50": 157.229996}</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>#14SW Price&gt;SMA50+Range&gt;1.5%+2Red | SL Hit (intraday)</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>17:10:43 IST</t>
+          <t>04:11:58 IST</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -15034,55 +15032,55 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>SOL-USD</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>103.63</v>
+        <v>2487.43</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1217</v>
+        <v>19</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>105.35</v>
+        <v>2435.24</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>100.68</v>
+        <v>2584.34</v>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>100.83</v>
+        <v>2432.8</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 03:42:13 IST</t>
+          <t>2026-09-10 18:11:52 IST</t>
         </is>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3406.36</v>
+        <v>-1037.88</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>378.35</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>3028.01</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>2.4</v>
+        <v>141.78</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>-1179.66</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>-2.5</v>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
@@ -15091,27 +15089,27 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>47.24</t>
+          <t>63.36</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
+          <t>Price&gt;SMA50+Range&gt;1.5%+2Red</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>{"2Red": 0.0, "Close": 103.790001, "EMA20": 103.838416, "EMA50": 103.876237, "EMA9": 103.993741, "High": 104.050003, "Low": 103.480003, "Open": 103.489998, "RSI14": 49.770588, "Ret": 0.002802, "SMA20": 103.7825, "SMA50": 103.7752, "Volume": 17383936.0, "_provenance": {"captured_at_ist": "2026-09-09 17:10:43 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "9aaf3858637b395153a1eb6f1f3f5a4337236e3bc92c730aee983cd6ceb4eec1"}}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2555.797457, "BB_lo": 2364.302788, "Close": 2484.941406, "EMA20": 2394.205294, "EMA200": 2184.550101, "EMA50": 2202.915005, "EMA9": 2470.446422, "High": 2506.753174, "Low": 2441.328857, "Open": 2490.919678, "RSI14": 62.903407, "Ret": -0.002415, "SMA20": 2460.050122, "SMA50": 2127.052944, "Volume": 13471038160.0, "_provenance": {"captured_at_ist": "2026-09-10 04:11:58 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "9d935e01f058e194edc4cbc5b22f08a0e6b38c3f190d3dd9f1551d28266ed601"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 1905.082397, "low50": 1821.485107}</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>#1ID EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50 | 🎯 Target Hit (live)</t>
+          <t>#14SW Price&gt;SMA50+Range&gt;1.5%+2Red | SL Hit (intraday)</t>
         </is>
       </c>
     </row>
@@ -15123,65 +15121,65 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>00:20:42 IST</t>
+          <t>17:10:43 IST</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>SOL-USD</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>171.47</v>
+        <v>103.63</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>314</v>
+        <v>1217</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>168.02</v>
+        <v>105.35</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>178.31</v>
+        <v>100.68</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>168</v>
+        <v>100.83</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 01:02:44 IST</t>
+          <t>2026-09-10 03:42:13 IST</t>
         </is>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1088.58</v>
+        <v>3406.36</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>10.77</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v>-1099.35</v>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v>-2.04</v>
+        <v>378.35</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>3028.01</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>2.4</v>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
@@ -15190,49 +15188,49 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>47.24</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 176.798755, "BB_lo": 165.82624, "Close": 171.449997, "EMA20": 170.660546, "EMA200": 154.818785, "EMA50": 165.715924, "EMA9": 172.087216, "High": 172.529999, "Low": 171.240005, "Open": 171.389999, "RSI14": 55.529727, "Ret": -0.010447, "SMA20": 171.312498, "SMA50": 165.727999, "Volume": 6083000.0, "_provenance": {"captured_at_ist": "2026-09-09 00:20:42 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "44670098855ad96888cc2dab18b682407e5130dfe00fe74e11bc4ccf032eec28"}, "high20": 176.600006, "high50": 176.600006, "low20": 162.919998, "low50": 153.589996}</t>
+          <t>{"2Red": 0.0, "Close": 103.790001, "EMA20": 103.838416, "EMA50": 103.876237, "EMA9": 103.993741, "High": 104.050003, "Low": 103.480003, "Open": 103.489998, "RSI14": 49.770588, "Ret": 0.002802, "SMA20": 103.7825, "SMA50": 103.7752, "Volume": 17383936.0, "_provenance": {"captured_at_ist": "2026-09-09 17:10:43 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "9aaf3858637b395153a1eb6f1f3f5a4337236e3bc92c730aee983cd6ceb4eec1"}}</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | 🎯 SL Hit (live)</t>
+          <t>#1ID EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50 | 🎯 Target Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>11:22:34 IST</t>
+          <t>00:20:42 IST</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -15245,17 +15243,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G14" s="10" t="n">
-        <v>0.3349</v>
+      <c r="G14" s="4" t="n">
+        <v>171.47</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="11" t="n">
-        <v>0.3272</v>
-      </c>
-      <c r="J14" s="11" t="n">
-        <v>0.3473</v>
+        <v>314</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>168.02</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>178.31</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
@@ -15263,24 +15261,24 @@
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0.3384</v>
+        <v>168</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 16:01:47 IST</t>
+          <t>2026-09-09 01:02:44 IST</t>
         </is>
       </c>
       <c r="N14" s="4" t="n">
-        <v>35.01</v>
+        <v>-1088.58</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>24.96</v>
-      </c>
-      <c r="Q14" s="12" t="n">
-        <v>0.75</v>
+        <v>10.77</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>-1099.35</v>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v>-2.04</v>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
@@ -15289,49 +15287,49 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>66.28</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 0.34818, "BB_lo": 0.323418, "Close": 0.333927, "EMA20": 0.333584, "EMA200": 0.324153, "EMA50": 0.332375, "EMA9": 0.332427, "High": 0.334747, "Low": 0.331477, "Open": 0.331539, "RSI14": 50.659837, "Ret": 0.007209, "SMA20": 0.335799, "SMA50": 0.331667, "Volume": 308281984.0, "_provenance": {"captured_at_ist": "2026-09-07 11:22:34 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "7600fa929fe73fa7401d6bfbe86db098b69cda878289f54ac466b6c9a918540c"}, "high20": 0.349996, "high50": 0.349996, "low20": 0.321569, "low50": 0.321457}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 176.798755, "BB_lo": 165.82624, "Close": 171.449997, "EMA20": 170.660546, "EMA200": 154.818785, "EMA50": 165.715924, "EMA9": 172.087216, "High": 172.529999, "Low": 171.240005, "Open": 171.389999, "RSI14": 55.529727, "Ret": -0.010447, "SMA20": 171.312498, "SMA50": 165.727999, "Volume": 6083000.0, "_provenance": {"captured_at_ist": "2026-09-09 00:20:42 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "44670098855ad96888cc2dab18b682407e5130dfe00fe74e11bc4ccf032eec28"}, "high20": 176.600006, "high50": 176.600006, "low20": 162.919998, "low50": 153.589996}</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>#2SW Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | 🎯 SL Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>00:01:07 IST</t>
+          <t>11:22:34 IST</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -15344,17 +15342,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
-        <v>384.36</v>
+      <c r="G15" s="10" t="n">
+        <v>0.3349</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>133</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>376.63</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>399.69</v>
+        <v>10000</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>0.3473</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
@@ -15362,24 +15360,24 @@
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>378.76</v>
+        <v>0.3384</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 00:01:43 IST</t>
+          <t>2026-09-12 16:01:47 IST</t>
         </is>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-744.52</v>
+        <v>35.01</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v>-754.74</v>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v>-1.48</v>
+        <v>10.05</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="Q15" s="12" t="n">
+        <v>0.75</v>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
@@ -15388,27 +15386,27 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>66.28</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 384.914412, "BB_lo": 375.582585, "Close": 384.320007, "EMA20": 378.7841, "EMA200": 352.821272, "EMA50": 374.004443, "EMA9": 380.273856, "High": 385.049988, "Low": 381.329987, "Open": 381.329987, "RSI14": 62.100647, "Ret": 0.011235, "SMA20": 380.248499, "SMA50": 373.018998, "Volume": 152400.0, "_provenance": {"captured_at_ist": "2026-09-05 00:01:07 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "abfffaa65e4253b95842b79cc0c4fd24b91e723a3bb5a1c71936a4e0ad957b60"}, "high20": 384.809998, "high50": 384.820007, "low20": 376.040009, "low50": 354.809998}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 0.34818, "BB_lo": 0.323418, "Close": 0.333927, "EMA20": 0.333584, "EMA200": 0.324153, "EMA50": 0.332375, "EMA9": 0.332427, "High": 0.334747, "Low": 0.331477, "Open": 0.331539, "RSI14": 50.659837, "Ret": 0.007209, "SMA20": 0.335799, "SMA50": 0.331667, "Volume": 308281984.0, "_provenance": {"captured_at_ist": "2026-09-07 11:22:34 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "7600fa929fe73fa7401d6bfbe86db098b69cda878289f54ac466b6c9a918540c"}, "high20": 0.349996, "high50": 0.349996, "low20": 0.321569, "low50": 0.321457}</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#2SW Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -15430,7 +15428,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -15444,16 +15442,16 @@
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>69.12</v>
+        <v>384.36</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>744</v>
+        <v>133</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>67.73</v>
+        <v>376.63</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>71.87</v>
+        <v>399.69</v>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
@@ -15461,24 +15459,24 @@
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>67.72</v>
+        <v>378.76</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 19:02:45 IST</t>
+          <t>2026-09-10 00:01:43 IST</t>
         </is>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1039.2</v>
+        <v>-744.52</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>10.29</v>
+        <v>10.22</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-1049.49</v>
+        <v>-754.74</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>-2.04</v>
+        <v>-1.48</v>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
@@ -15487,39 +15485,39 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>50.67</t>
+          <t>59.53</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>EMA9&lt;EMA50+Price&gt;EMA50</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 71.993154, "BB_lo": 66.775846, "Close": 69.110001, "EMA20": 68.962509, "EMA200": 64.180507, "EMA50": 68.553847, "EMA9": 68.515681, "High": 69.43, "Low": 68.519997, "Open": 68.690002, "RSI14": 50.566608, "Ret": 0.011119, "SMA20": 69.3845, "SMA50": 69.3494, "Volume": 1003500.0, "_provenance": {"captured_at_ist": "2026-09-05 00:01:07 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "06ac2e6e1d165122d46e93bfcd73629fb535999a67502c91a31dd356f9c3e061"}, "high20": 71.919998, "high50": 71.919998, "low20": 66.809998, "low50": 66.809998}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 384.914412, "BB_lo": 375.582585, "Close": 384.320007, "EMA20": 378.7841, "EMA200": 352.821272, "EMA50": 374.004443, "EMA9": 380.273856, "High": 385.049988, "Low": 381.329987, "Open": 381.329987, "RSI14": 62.100647, "Ret": 0.011235, "SMA20": 380.248499, "SMA50": 373.018998, "Volume": 152400.0, "_provenance": {"captured_at_ist": "2026-09-05 00:01:07 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "abfffaa65e4253b95842b79cc0c4fd24b91e723a3bb5a1c71936a4e0ad957b60"}, "high20": 384.809998, "high50": 384.820007, "low20": 376.040009, "low50": 354.809998}</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>#5SW EMA9&lt;EMA50+Price&gt;EMA50 | 🎯 SL Hit (live)</t>
+          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>00:18:23 IST</t>
+          <t>00:01:07 IST</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -15529,7 +15527,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -15543,16 +15541,16 @@
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>183.62</v>
+        <v>69.12</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>280</v>
+        <v>744</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>179.93</v>
+        <v>67.73</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>190.94</v>
+        <v>71.87</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
@@ -15560,24 +15558,24 @@
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>188.07</v>
+        <v>67.72</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:20:41 IST</t>
+          <t>2026-09-09 19:02:45 IST</t>
         </is>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1245.66</v>
+        <v>-1039.2</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>10.28</v>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v>1235.38</v>
-      </c>
-      <c r="Q17" s="5" t="n">
-        <v>2.4</v>
+        <v>10.29</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>-1049.49</v>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v>-2.04</v>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
@@ -15586,27 +15584,27 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>63.73</t>
+          <t>50.67</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
+          <t>EMA9&lt;EMA50+Price&gt;EMA50</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 191.712855, "BB_lo": 179.688148, "Close": 183.600006, "EMA20": 184.253928, "EMA200": 163.733288, "EMA50": 182.113823, "EMA9": 184.580211, "High": 183.779999, "Low": 182.270004, "Open": 183.460007, "RSI14": 49.503374, "Ret": -0.000218, "SMA20": 185.700501, "SMA50": 182.494601, "Volume": 5698700.0, "_provenance": {"captured_at_ist": "2026-09-04 00:18:23 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "6b9dec175776d38099bfb1914d0a25629c9baa7f345badebe6a04ece751808ef"}, "high20": 191.75, "high50": 191.75, "low20": 178.820007, "low50": 166.460007}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 71.993154, "BB_lo": 66.775846, "Close": 69.110001, "EMA20": 68.962509, "EMA200": 64.180507, "EMA50": 68.553847, "EMA9": 68.515681, "High": 69.43, "Low": 68.519997, "Open": 68.690002, "RSI14": 50.566608, "Ret": 0.011119, "SMA20": 69.3845, "SMA50": 69.3494, "Volume": 1003500.0, "_provenance": {"captured_at_ist": "2026-09-05 00:01:07 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "06ac2e6e1d165122d46e93bfcd73629fb535999a67502c91a31dd356f9c3e061"}, "high20": 71.919998, "high50": 71.919998, "low20": 66.809998, "low50": 66.809998}</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>#28SW Price&gt;SMA50+EMA20&gt;EMA50+2Red | Expiry 5d</t>
+          <t>#5SW EMA9&lt;EMA50+Price&gt;EMA50 | 🎯 SL Hit (live)</t>
         </is>
       </c>
     </row>
@@ -15623,12 +15621,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -15642,16 +15640,16 @@
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2393.89</v>
+        <v>183.62</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>2343.67</v>
+        <v>179.93</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>2487.16</v>
+        <v>190.94</v>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
@@ -15659,24 +15657,24 @@
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2484.67</v>
+        <v>188.07</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 01:13:45 IST</t>
+          <t>2026-09-09 00:20:41 IST</t>
         </is>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1815.66</v>
+        <v>1245.66</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>143.63</v>
+        <v>10.28</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>1672.03</v>
+        <v>1235.38</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>3.49</v>
+        <v>2.4</v>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
@@ -15685,49 +15683,49 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>63.73</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+Range&gt;1.5%+2Red</t>
+          <t>Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2795.732764, "BB_lo": 1802.401318, "Close": 2391.500977, "EMA20": 2315.842983, "EMA200": 2165.750484, "EMA50": 2125.223481, "EMA9": 2416.411271, "High": 2427.401611, "Low": 2356.188232, "Open": 2417.828369, "RSI14": 61.419955, "Ret": -0.010894, "SMA20": 2299.067041, "SMA50": 2053.502986, "Volume": 14227785690.0, "_provenance": {"captured_at_ist": "2026-09-04 00:18:23 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "bceb614e24f483f8b97a38b58fddecc676f19d19395d1082c77cf9b320b6f87a"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 1861.92041, "low50": 1772.0177}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 191.712855, "BB_lo": 179.688148, "Close": 183.600006, "EMA20": 184.253928, "EMA200": 163.733288, "EMA50": 182.113823, "EMA9": 184.580211, "High": 183.779999, "Low": 182.270004, "Open": 183.460007, "RSI14": 49.503374, "Ret": -0.000218, "SMA20": 185.700501, "SMA50": 182.494601, "Volume": 5698700.0, "_provenance": {"captured_at_ist": "2026-09-04 00:18:23 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "6b9dec175776d38099bfb1914d0a25629c9baa7f345badebe6a04ece751808ef"}, "high20": 191.75, "high50": 191.75, "low20": 178.820007, "low50": 166.460007}</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>#14SW Price&gt;SMA50+Range&gt;1.5%+2Red | 🎯 Target Hit (live)</t>
+          <t>#28SW Price&gt;SMA50+EMA20&gt;EMA50+2Red | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>00:20:14 IST</t>
+          <t>00:18:23 IST</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -15741,16 +15739,16 @@
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>52.08</v>
+        <v>2393.89</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>966</v>
+        <v>20</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>51.03</v>
+        <v>2343.67</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>54.15</v>
+        <v>2487.16</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
@@ -15758,24 +15756,24 @@
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>52.43</v>
+        <v>2484.67</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:47:43 IST</t>
+          <t>2026-09-04 01:13:45 IST</t>
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>342.69</v>
+        <v>1815.66</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>10.06</v>
+        <v>143.63</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>332.63</v>
-      </c>
-      <c r="Q19" s="12" t="n">
-        <v>0.66</v>
+        <v>1672.03</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>3.49</v>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
@@ -15784,97 +15782,97 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>63.36</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+Range&gt;1.5%+2Red</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 53.933542, "BB_lo": 51.668459, "Close": 52.07, "EMA20": 52.631511, "EMA200": 49.788698, "EMA50": 52.014955, "EMA9": 52.846097, "High": 52.459999, "Low": 52.02, "Open": 52.439999, "RSI14": 46.449627, "Ret": -0.011767, "SMA20": 52.801, "SMA50": 51.74, "Volume": 15500500.0, "_provenance": {"captured_at_ist": "2026-09-03 00:20:14 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "4c008560e6adf2a2b92f03ff3aba914bff4c1422744acab60897e94b0403e513"}, "high20": 54.189999, "high50": 54.189999, "low20": 51.029999, "low50": 49.849998}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2795.732764, "BB_lo": 1802.401318, "Close": 2391.500977, "EMA20": 2315.842983, "EMA200": 2165.750484, "EMA50": 2125.223481, "EMA9": 2416.411271, "High": 2427.401611, "Low": 2356.188232, "Open": 2417.828369, "RSI14": 61.419955, "Ret": -0.010894, "SMA20": 2299.067041, "SMA50": 2053.502986, "Volume": 14227785690.0, "_provenance": {"captured_at_ist": "2026-09-04 00:18:23 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "bceb614e24f483f8b97a38b58fddecc676f19d19395d1082c77cf9b320b6f87a"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 1861.92041, "low50": 1772.0177}</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>#5SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#14SW Price&gt;SMA50+Range&gt;1.5%+2Red | 🎯 Target Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>04:45:09 IST</t>
+          <t>00:20:14 IST</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>SOL-USD</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>103.03</v>
+        <v>52.08</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>630</v>
+        <v>966</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>104.73</v>
+        <v>51.03</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>100.08</v>
+        <v>54.15</v>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>102.43</v>
+        <v>52.43</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 16:46:47 IST</t>
+          <t>2026-09-08 00:47:43 IST</t>
         </is>
       </c>
       <c r="N20" s="4" t="n">
-        <v>375.85</v>
+        <v>342.69</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>194.73</v>
+        <v>10.06</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>181.12</v>
+        <v>332.63</v>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>0.28</v>
+        <v>0.66</v>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
@@ -15883,97 +15881,97 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>47.24</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t>{"2Red": 1.0, "Close": 103.18, "EMA20": 103.411299, "EMA50": 103.800477, "EMA9": 103.432655, "High": 103.779999, "Low": 103.099998, "Open": 103.720001, "RSI14": 47.470892, "Ret": -0.004438, "SMA20": 103.072001, "SMA50": 104.206801, "Volume": 1157376.0, "_provenance": {"captured_at_ist": "2026-09-01 04:45:09 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "ef6d7a045ffc2750af734b317d97fc5a28f2a347c94512fa8743ba341861e0eb"}}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 53.933542, "BB_lo": 51.668459, "Close": 52.07, "EMA20": 52.631511, "EMA200": 49.788698, "EMA50": 52.014955, "EMA9": 52.846097, "High": 52.459999, "Low": 52.02, "Open": 52.439999, "RSI14": 46.449627, "Ret": -0.011767, "SMA20": 52.801, "SMA50": 51.74, "Volume": 15500500.0, "_provenance": {"captured_at_ist": "2026-09-03 00:20:14 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "4c008560e6adf2a2b92f03ff3aba914bff4c1422744acab60897e94b0403e513"}, "high20": 54.189999, "high50": 54.189999, "low20": 51.029999, "low50": 49.849998}</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>#1ID EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50 | Expiry 12h</t>
+          <t>#5SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>20:17:47 IST</t>
+          <t>04:45:09 IST</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>SOL-USD</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
-        <v>171.18</v>
+        <v>103.03</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>299</v>
+        <v>630</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>167.74</v>
+        <v>104.73</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>178.01</v>
+        <v>100.08</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>171.43</v>
+        <v>102.43</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05 05:30:00 IST</t>
+          <t>2026-09-01 16:46:47 IST</t>
         </is>
       </c>
       <c r="N21" s="4" t="n">
-        <v>75.59999999999999</v>
+        <v>375.85</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>10.24</v>
+        <v>194.73</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>65.36</v>
+        <v>181.12</v>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
@@ -15982,27 +15980,27 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>47.24</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 177.80833, "BB_lo": 160.692668, "Close": 171.160004, "EMA20": 169.767931, "EMA200": 153.951283, "EMA50": 164.324372, "EMA9": 172.083661, "High": 171.710007, "Low": 170.589996, "Open": 171.429993, "RSI14": 57.156114, "Ret": -0.002448, "SMA20": 169.250499, "SMA50": 163.729879, "Volume": 4879300.0, "_provenance": {"captured_at_ist": "2026-08-31 20:17:47 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "9c5b13218a3d2ce328cb2f2e7d32803533390f839d04812e416383140bb7e387"}, "high20": 176.600006, "high50": 176.600006, "low20": 160.729996, "low50": 148.136666}</t>
+          <t>{"2Red": 1.0, "Close": 103.18, "EMA20": 103.411299, "EMA50": 103.800477, "EMA9": 103.432655, "High": 103.779999, "Low": 103.099998, "Open": 103.720001, "RSI14": 47.470892, "Ret": -0.004438, "SMA20": 103.072001, "SMA50": 104.206801, "Volume": 1157376.0, "_provenance": {"captured_at_ist": "2026-09-01 04:45:09 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "ef6d7a045ffc2750af734b317d97fc5a28f2a347c94512fa8743ba341861e0eb"}}</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#1ID EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50 | Expiry 12h</t>
         </is>
       </c>
     </row>
@@ -16024,7 +16022,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -16038,16 +16036,16 @@
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>62.69</v>
+        <v>171.18</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>818</v>
+        <v>299</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>61.43</v>
+        <v>167.74</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>65.19</v>
+        <v>178.01</v>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
@@ -16055,24 +16053,24 @@
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>65.18000000000001</v>
+        <v>171.43</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:56:58 IST</t>
+          <t>2026-09-05 05:30:00 IST</t>
         </is>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2039.67</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>10.26</v>
+        <v>10.24</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>2029.41</v>
-      </c>
-      <c r="Q22" s="5" t="n">
-        <v>3.96</v>
+        <v>65.36</v>
+      </c>
+      <c r="Q22" s="12" t="n">
+        <v>0.13</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
@@ -16081,39 +16079,39 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA50+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 65.566256, "BB_lo": 56.952745, "Close": 62.68, "EMA20": 61.482668, "EMA200": 54.449219, "EMA50": 59.472604, "EMA9": 62.477193, "High": 62.740002, "Low": 62.119999, "Open": 62.349998, "RSI14": 62.129968, "Ret": 0.006261, "SMA20": 61.259501, "SMA50": 58.1441, "Volume": 20599600.0, "_provenance": {"captured_at_ist": "2026-08-31 20:17:47 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "f528add80b6c836a8e80c29430bea8d83def03a9307763f51342341e85b6e147"}, "high20": 64.699997, "high50": 64.699997, "low20": 57.110001, "low50": 52.619999}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 177.80833, "BB_lo": 160.692668, "Close": 171.160004, "EMA20": 169.767931, "EMA200": 153.951283, "EMA50": 164.324372, "EMA9": 172.083661, "High": 171.710007, "Low": 170.589996, "Open": 171.429993, "RSI14": 57.156114, "Ret": -0.002448, "SMA20": 169.250499, "SMA50": 163.729879, "Volume": 4879300.0, "_provenance": {"captured_at_ist": "2026-08-31 20:17:47 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "9c5b13218a3d2ce328cb2f2e7d32803533390f839d04812e416383140bb7e387"}, "high20": 176.600006, "high50": 176.600006, "low20": 160.729996, "low50": 148.136666}</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>#3SW EMA9&gt;EMA50+Range&lt;1% | Target Hit</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>01:26:29 IST</t>
+          <t>20:17:47 IST</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -16123,7 +16121,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -16133,45 +16131,45 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>767.04</v>
+        <v>62.69</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>136</v>
+        <v>818</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>759.22</v>
+        <v>61.43</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>782.23</v>
+        <v>65.19</v>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>769.79</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 00:57:20 IST</t>
+          <t>2026-09-03 00:56:58 IST</t>
         </is>
       </c>
       <c r="N23" s="4" t="n">
-        <v>373.46</v>
+        <v>2039.67</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>20.86</v>
+        <v>10.26</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>352.6</v>
-      </c>
-      <c r="Q23" s="12" t="n">
-        <v>0.34</v>
+        <v>2029.41</v>
+      </c>
+      <c r="Q23" s="5" t="n">
+        <v>3.96</v>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
@@ -16180,27 +16178,27 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>62.35</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
+          <t>EMA9&gt;EMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t>{"2Red": 0.0, "Close": 766.890015, "EMA20": 765.466694, "EMA50": 766.617135, "EMA9": 765.635192, "High": 767.349976, "Low": 765.52002, "Open": 765.609985, "RSI14": 55.731638, "Ret": 0.001672, "SMA20": 764.880759, "SMA50": 766.460079, "Volume": 3674140.0, "_provenance": {"captured_at_ist": "2026-08-27 01:26:29 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "3784c4c96c4bf403350ccfce032c365669554989a59e5f375dc6129ba567d139"}}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 65.566256, "BB_lo": 56.952745, "Close": 62.68, "EMA20": 61.482668, "EMA200": 54.449219, "EMA50": 59.472604, "EMA9": 62.477193, "High": 62.740002, "Low": 62.119999, "Open": 62.349998, "RSI14": 62.129968, "Ret": 0.006261, "SMA20": 61.259501, "SMA50": 58.1441, "Volume": 20599600.0, "_provenance": {"captured_at_ist": "2026-08-31 20:17:47 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "f528add80b6c836a8e80c29430bea8d83def03a9307763f51342341e85b6e147"}, "high20": 64.699997, "high50": 64.699997, "low20": 57.110001, "low50": 52.619999}</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>#16ID Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | Expiry 6h</t>
+          <t>#3SW EMA9&gt;EMA50+Range&lt;1% | Target Hit</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16210,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>01:26:20 IST</t>
+          <t>01:26:29 IST</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -16222,7 +16220,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -16232,45 +16230,45 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>86.53</v>
+        <v>767.04</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>596</v>
+        <v>136</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>84.79000000000001</v>
+        <v>759.22</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>89.98</v>
+        <v>782.23</v>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>85.03</v>
+        <v>769.79</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 01:27:38 IST</t>
+          <t>2026-08-28 00:57:20 IST</t>
         </is>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-893.11</v>
+        <v>373.46</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v>-903.42</v>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v>-1.75</v>
+        <v>20.86</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>352.6</v>
+      </c>
+      <c r="Q24" s="12" t="n">
+        <v>0.34</v>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
@@ -16279,27 +16277,27 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>62.35</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>Range&lt;1%+SMA20&lt;EMA20</t>
+          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 87.262889, "BB_lo": 83.993112, "Close": 86.519997, "EMA20": 85.651886, "EMA200": 82.697308, "EMA50": 84.933173, "EMA9": 86.092409, "High": 87.010002, "Low": 86.25, "Open": 86.860001, "RSI14": 55.279506, "Ret": -0.010635, "SMA20": 85.628, "SMA50": 84.784211, "Volume": 7022700.0, "_provenance": {"captured_at_ist": "2026-08-27 01:26:20 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "4ec100efbb7eae0f145aebe59fea065b45da569430baeb0ea99b3a12db3915e9"}, "high20": 88.779999, "high50": 88.779999, "low20": 83.860001, "low50": 82.150002}</t>
+          <t>{"2Red": 0.0, "Close": 766.890015, "EMA20": 765.466694, "EMA50": 766.617135, "EMA9": 765.635192, "High": 767.349976, "Low": 765.52002, "Open": 765.609985, "RSI14": 55.731638, "Ret": 0.001672, "SMA20": 764.880759, "SMA50": 766.460079, "Volume": 3674140.0, "_provenance": {"captured_at_ist": "2026-08-27 01:26:29 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "3784c4c96c4bf403350ccfce032c365669554989a59e5f375dc6129ba567d139"}}</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>#5SW Range&lt;1%+SMA20&lt;EMA20 | Expiry 5d</t>
+          <t>#16ID Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -16321,7 +16319,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -16335,16 +16333,16 @@
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>113.19</v>
+        <v>86.53</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>456</v>
+        <v>596</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>110.92</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>117.71</v>
+        <v>89.98</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
@@ -16352,7 +16350,7 @@
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>111.54</v>
+        <v>85.03</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -16360,16 +16358,16 @@
         </is>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-750.65</v>
+        <v>-893.11</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>10.32</v>
+        <v>10.31</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-760.97</v>
+        <v>-903.42</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>-1.47</v>
+        <v>-1.75</v>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
@@ -16378,39 +16376,39 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>58.26</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;EMA9+Range&lt;1%</t>
+          <t>Range&lt;1%+SMA20&lt;EMA20</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 114.093707, "BB_lo": 107.914293, "Close": 113.18, "EMA20": 111.174983, "EMA200": 111.655481, "EMA50": 111.050282, "EMA9": 111.73869, "High": 113.275002, "Low": 112.294998, "Open": 112.410004, "RSI14": 58.133522, "Ret": 0.007657, "SMA20": 111.004, "SMA50": 110.009402, "Volume": 2701500.0, "_provenance": {"captured_at_ist": "2026-08-27 01:26:20 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "6517b7ae823c6f80e30c2d50df07393a2cb922775b5ebecb2ca0cf654bc08aff"}, "high20": 113.5, "high50": 114.029999, "low20": 105.492996, "low50": 105.029999}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 87.262889, "BB_lo": 83.993112, "Close": 86.519997, "EMA20": 85.651886, "EMA200": 82.697308, "EMA50": 84.933173, "EMA9": 86.092409, "High": 87.010002, "Low": 86.25, "Open": 86.860001, "RSI14": 55.279506, "Ret": -0.010635, "SMA20": 85.628, "SMA50": 84.784211, "Volume": 7022700.0, "_provenance": {"captured_at_ist": "2026-08-27 01:26:20 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "4ec100efbb7eae0f145aebe59fea065b45da569430baeb0ea99b3a12db3915e9"}, "high20": 88.779999, "high50": 88.779999, "low20": 83.860001, "low50": 82.150002}</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>#3SW Price&gt;EMA9+Range&lt;1% | Expiry 5d</t>
+          <t>#5SW Range&lt;1%+SMA20&lt;EMA20 | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>00:19:41 IST</t>
+          <t>01:26:20 IST</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -16420,7 +16418,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -16434,16 +16432,16 @@
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>377.11</v>
+        <v>113.19</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>133</v>
+        <v>456</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>369.53</v>
+        <v>110.92</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>392.15</v>
+        <v>117.71</v>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
@@ -16451,24 +16449,24 @@
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>379.32</v>
+        <v>111.54</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31 12:20:47 IST</t>
+          <t>2026-09-01 01:27:38 IST</t>
         </is>
       </c>
       <c r="N26" s="4" t="n">
-        <v>294.2</v>
+        <v>-750.65</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>284.17</v>
-      </c>
-      <c r="Q26" s="12" t="n">
-        <v>0.57</v>
+        <v>10.32</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v>-760.97</v>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v>-1.47</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
@@ -16482,34 +16480,34 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>Range&lt;1%+SMA20&lt;EMA20</t>
+          <t>Price&gt;EMA9+Range&lt;1%</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 390.418284, "BB_lo": 363.717712, "Close": 377.070007, "EMA20": 377.20007, "EMA200": 349.68499, "EMA50": 371.828667, "EMA9": 378.840176, "High": 378.0, "Low": 376.480011, "Open": 377.920013, "RSI14": 52.14451, "Ret": -0.003093, "SMA20": 377.067998, "SMA50": 371.565996, "Volume": 2963600.0, "_provenance": {"captured_at_ist": "2026-08-26 00:19:41 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "7d4507f7724401cf8e473ac67923b34d856a349cb42c70c444777355cfcb7c9b"}, "high20": 385.119995, "high50": 385.119995, "low20": 360.200012, "low50": 356.723865}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 114.093707, "BB_lo": 107.914293, "Close": 113.18, "EMA20": 111.174983, "EMA200": 111.655481, "EMA50": 111.050282, "EMA9": 111.73869, "High": 113.275002, "Low": 112.294998, "Open": 112.410004, "RSI14": 58.133522, "Ret": 0.007657, "SMA20": 111.004, "SMA50": 110.009402, "Volume": 2701500.0, "_provenance": {"captured_at_ist": "2026-08-27 01:26:20 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "6517b7ae823c6f80e30c2d50df07393a2cb922775b5ebecb2ca0cf654bc08aff"}, "high20": 113.5, "high50": 114.029999, "low20": 105.492996, "low50": 105.029999}</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>#3SW Range&lt;1%+SMA20&lt;EMA20 | Expiry 5d</t>
+          <t>#3SW Price&gt;EMA9+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>00:21:29 IST</t>
+          <t>00:19:41 IST</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -16519,7 +16517,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>VTI</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -16533,16 +16531,16 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>174.55</v>
+        <v>377.11</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>275</v>
+        <v>133</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>171.04</v>
+        <v>369.53</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>181.51</v>
+        <v>392.15</v>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
@@ -16550,24 +16548,24 @@
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>171.02</v>
+        <v>379.32</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:08:12 IST</t>
+          <t>2026-08-31 12:20:47 IST</t>
         </is>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-969.95</v>
+        <v>294.2</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v>-979.55</v>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v>-2.04</v>
+        <v>10.03</v>
+      </c>
+      <c r="P27" s="5" t="n">
+        <v>284.17</v>
+      </c>
+      <c r="Q27" s="12" t="n">
+        <v>0.57</v>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
@@ -16576,39 +16574,39 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>Range&lt;1%+SMA20&lt;EMA20</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 175.864131, "BB_lo": 159.419869, "Close": 174.529999, "EMA20": 168.30809, "EMA200": 154.030413, "EMA50": 162.961143, "EMA9": 171.440751, "High": 174.830002, "Low": 173.330002, "Open": 174.410004, "RSI14": 68.059204, "Ret": -0.000515, "SMA20": 167.642, "SMA50": 162.1152, "Volume": 4415397.0, "_provenance": {"captured_at_ist": "2026-08-25 00:21:29 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "0e5a554d6cdf867147a863dbaa87285229b6bdde8405ef04e62d923f28408cf2"}, "high20": 176.600006, "high50": 176.600006, "low20": 160.729996, "low50": 148.789993}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 390.418284, "BB_lo": 363.717712, "Close": 377.070007, "EMA20": 377.20007, "EMA200": 349.68499, "EMA50": 371.828667, "EMA9": 378.840176, "High": 378.0, "Low": 376.480011, "Open": 377.920013, "RSI14": 52.14451, "Ret": -0.003093, "SMA20": 377.067998, "SMA50": 371.565996, "Volume": 2963600.0, "_provenance": {"captured_at_ist": "2026-08-26 00:19:41 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "7d4507f7724401cf8e473ac67923b34d856a349cb42c70c444777355cfcb7c9b"}, "high20": 385.119995, "high50": 385.119995, "low20": 360.200012, "low50": 356.723865}</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | ðŸŽ¯ SL Hit (live)</t>
+          <t>#3SW Range&lt;1%+SMA20&lt;EMA20 | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>07:49:44 IST</t>
+          <t>00:21:29 IST</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -16618,7 +16616,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -16632,16 +16630,16 @@
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>713.51</v>
+        <v>174.55</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>68</v>
+        <v>275</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>699.17</v>
+        <v>171.04</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>741.98</v>
+        <v>181.51</v>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
@@ -16649,24 +16647,24 @@
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>716.36</v>
+        <v>171.02</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 08:16:22 IST</t>
+          <t>2026-08-28 21:08:12 IST</t>
         </is>
       </c>
       <c r="N28" s="4" t="n">
-        <v>193.69</v>
+        <v>-969.95</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v>183.99</v>
-      </c>
-      <c r="Q28" s="12" t="n">
-        <v>0.38</v>
+        <v>9.6</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v>-979.55</v>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v>-2.04</v>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
@@ -16675,39 +16673,39 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>RSI&gt;50+SMA20&lt;SMA50</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 749.746157, "BB_lo": 668.630845, "Close": 713.440002, "EMA20": 714.415351, "EMA200": 659.614421, "EMA50": 708.78849, "EMA9": 717.391898, "High": 715.669983, "Low": 709.200012, "Open": 715.22998, "RSI14": 50.149844, "Ret": 0.003531, "SMA20": 709.188501, "SMA50": 713.441602, "Volume": 33297600.0, "_provenance": {"captured_at_ist": "2026-08-24 07:49:44 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "89a195f1c565d7eeec6103b45df5fc0c4a8cd08b92109c8f6c78f6dbe7e34347"}, "high20": 734.580017, "high50": 745.450012, "low20": 661.140015, "low50": 661.140015}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 175.864131, "BB_lo": 159.419869, "Close": 174.529999, "EMA20": 168.30809, "EMA200": 154.030413, "EMA50": 162.961143, "EMA9": 171.440751, "High": 174.830002, "Low": 173.330002, "Open": 174.410004, "RSI14": 68.059204, "Ret": -0.000515, "SMA20": 167.642, "SMA50": 162.1152, "Volume": 4415397.0, "_provenance": {"captured_at_ist": "2026-08-25 00:21:29 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "0e5a554d6cdf867147a863dbaa87285229b6bdde8405ef04e62d923f28408cf2"}, "high20": 176.600006, "high50": 176.600006, "low20": 160.729996, "low50": 148.789993}</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>#66SW RSI&gt;50+SMA20&lt;SMA50 | Expiry 5d</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | ðŸŽ¯ SL Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>07:51:10 IST</t>
+          <t>07:49:44 IST</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -16717,7 +16715,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -16731,16 +16729,16 @@
         </is>
       </c>
       <c r="G29" s="4" t="n">
-        <v>45.08</v>
+        <v>713.51</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1105</v>
+        <v>68</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>44.18</v>
+        <v>699.17</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>46.88</v>
+        <v>741.98</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
@@ -16748,24 +16746,24 @@
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>44.66</v>
+        <v>716.36</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 09:07:28 IST</t>
+          <t>2026-08-29 08:16:22 IST</t>
         </is>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-469.04</v>
+        <v>193.69</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v>-479</v>
-      </c>
-      <c r="Q29" s="13" t="n">
-        <v>-0.96</v>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="P29" s="5" t="n">
+        <v>183.99</v>
+      </c>
+      <c r="Q29" s="12" t="n">
+        <v>0.38</v>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
@@ -16774,27 +16772,27 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>66</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&lt;Open</t>
+          <t>RSI&gt;50+SMA20&lt;SMA50</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 46.03132, "BB_lo": 44.109681, "Close": 45.080002, "EMA20": 44.957695, "EMA200": 43.466243, "EMA50": 44.780011, "EMA9": 44.94812, "High": 45.255001, "Low": 44.933998, "Open": 45.200001, "RSI14": 51.888379, "Ret": 0.0, "SMA20": 45.0705, "SMA50": 44.8678, "Volume": 3968900.0, "_provenance": {"captured_at_ist": "2026-08-23 07:51:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "45c6a11f08d41357e9b6038a6644a0c54ee887b4d9d2010526bd8ea4b0ea5250"}, "high20": 46.455002, "high50": 46.455002, "low20": 44.009998, "low50": 43.48}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 749.746157, "BB_lo": 668.630845, "Close": 713.440002, "EMA20": 714.415351, "EMA200": 659.614421, "EMA50": 708.78849, "EMA9": 717.391898, "High": 715.669983, "Low": 709.200012, "Open": 715.22998, "RSI14": 50.149844, "Ret": 0.003531, "SMA20": 709.188501, "SMA50": 713.441602, "Volume": 33297600.0, "_provenance": {"captured_at_ist": "2026-08-24 07:49:44 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "89a195f1c565d7eeec6103b45df5fc0c4a8cd08b92109c8f6c78f6dbe7e34347"}, "high20": 734.580017, "high50": 745.450012, "low20": 661.140015, "low50": 661.140015}</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>#57SW Price&gt;SMA20+EMA9&lt;EMA20+Close&lt;Open | Expiry 5d</t>
+          <t>#66SW RSI&gt;50+SMA20&lt;SMA50 | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -16811,12 +16809,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -16829,17 +16827,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G30" s="10" t="n">
-        <v>0.3462</v>
+      <c r="G30" s="4" t="n">
+        <v>45.08</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I30" s="11" t="n">
-        <v>0.3382</v>
-      </c>
-      <c r="J30" s="11" t="n">
-        <v>0.3589</v>
+        <v>1105</v>
+      </c>
+      <c r="I30" s="8" t="n">
+        <v>44.18</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>46.88</v>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
@@ -16847,24 +16845,24 @@
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0.3372</v>
+        <v>44.66</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 02:06:32 IST</t>
+          <t>2026-08-28 09:07:28 IST</t>
         </is>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-90.15000000000001</v>
+        <v>-469.04</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.39</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-100.54</v>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v>-2.9</v>
+        <v>-479</v>
+      </c>
+      <c r="Q30" s="13" t="n">
+        <v>-0.96</v>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
@@ -16873,27 +16871,27 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>57</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&lt;Open</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 0.342604, "BB_lo": 0.322249, "Close": 0.345137, "EMA20": 0.333753, "EMA200": 0.322532, "EMA50": 0.330808, "EMA9": 0.337211, "High": 0.345367, "Low": 0.34419, "Open": 0.344229, "RSI14": 75.347643, "Ret": 0.005205, "SMA20": 0.332427, "SMA50": 0.329547, "Volume": 896564352.0, "_provenance": {"captured_at_ist": "2026-08-23 07:51:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "841d75978c0b90d3d955daa219375d748b86c110612710892971f186fbc6b405"}, "high20": 0.34335, "high50": 0.34335, "low20": 0.325217, "low50": 0.316794}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 46.03132, "BB_lo": 44.109681, "Close": 45.080002, "EMA20": 44.957695, "EMA200": 43.466243, "EMA50": 44.780011, "EMA9": 44.94812, "High": 45.255001, "Low": 44.933998, "Open": 45.200001, "RSI14": 51.888379, "Ret": 0.0, "SMA20": 45.0705, "SMA50": 44.8678, "Volume": 3968900.0, "_provenance": {"captured_at_ist": "2026-08-23 07:51:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "45c6a11f08d41357e9b6038a6644a0c54ee887b4d9d2010526bd8ea4b0ea5250"}, "high20": 46.455002, "high50": 46.455002, "low20": 44.009998, "low50": 43.48}</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | ðŸŽ¯ SL Hit (live)</t>
+          <t>#57SW Price&gt;SMA20+EMA9&lt;EMA20+Close&lt;Open | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -16910,12 +16908,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -16928,17 +16926,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
-        <v>377.9</v>
+      <c r="G31" s="10" t="n">
+        <v>0.3462</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>130</v>
-      </c>
-      <c r="I31" s="8" t="n">
-        <v>370.3</v>
-      </c>
-      <c r="J31" s="8" t="n">
-        <v>392.97</v>
+        <v>10000</v>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="J31" s="11" t="n">
+        <v>0.3589</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
@@ -16946,24 +16944,24 @@
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>380.85</v>
+        <v>0.3372</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 09:07:28 IST</t>
+          <t>2026-08-26 02:06:32 IST</t>
         </is>
       </c>
       <c r="N31" s="4" t="n">
-        <v>383.75</v>
+        <v>-90.15000000000001</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="P31" s="5" t="n">
-        <v>373.92</v>
-      </c>
-      <c r="Q31" s="12" t="n">
-        <v>0.76</v>
+        <v>10.39</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v>-100.54</v>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v>-2.9</v>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
@@ -16972,39 +16970,39 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 391.993875, "BB_lo": 360.752118, "Close": 377.859985, "EMA20": 377.034739, "EMA200": 351.317404, "EMA50": 371.633734, "EMA9": 379.076055, "High": 379.179993, "Low": 376.839996, "Open": 377.890015, "RSI14": 53.807886, "Ret": 0.003106, "SMA20": 376.372997, "SMA50": 370.408998, "Volume": 141700.0, "_provenance": {"captured_at_ist": "2026-08-23 07:51:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "dc46343d0c2668e3d0437189c8457963c0a5445a4be1eb6c84facfbc8ebd4d16"}, "high20": 384.820007, "high50": 384.820007, "low20": 358.170013, "low50": 354.809998}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 0.342604, "BB_lo": 0.322249, "Close": 0.345137, "EMA20": 0.333753, "EMA200": 0.322532, "EMA50": 0.330808, "EMA9": 0.337211, "High": 0.345367, "Low": 0.34419, "Open": 0.344229, "RSI14": 75.347643, "Ret": 0.005205, "SMA20": 0.332427, "SMA50": 0.329547, "Volume": 896564352.0, "_provenance": {"captured_at_ist": "2026-08-23 07:51:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "841d75978c0b90d3d955daa219375d748b86c110612710892971f186fbc6b405"}, "high20": 0.34335, "high50": 0.34335, "low20": 0.325217, "low50": 0.316794}</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | ðŸŽ¯ SL Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>00:19:34 IST</t>
+          <t>07:51:10 IST</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -17014,7 +17012,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -17028,16 +17026,16 @@
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>63.56</v>
+        <v>377.9</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>782</v>
+        <v>130</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>62.28</v>
+        <v>370.3</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>66.09999999999999</v>
+        <v>392.97</v>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
@@ -17045,24 +17043,24 @@
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>63.62</v>
+        <v>380.85</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24 00:57:24 IST</t>
+          <t>2026-08-28 09:07:28 IST</t>
         </is>
       </c>
       <c r="N32" s="4" t="n">
-        <v>45.85</v>
+        <v>383.75</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>9.94</v>
+        <v>9.83</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>35.91</v>
+        <v>373.92</v>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
@@ -17071,27 +17069,27 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>59.53</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA50+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>{"EMA200": 54.253942, "Open": 63.41, "2Red": 0.0, "Volume": 20822618.0, "EMA20": 59.820197, "BB_lo": 56.181538, "EMA50": 58.261513, "SMA50": 57.1629, "low20": 57.110001, "RSI14": 72.551139, "low50": 52.619999, "EMA9": 61.242966, "2Green": 1.0, "Ret": 0.01558, "Low": 63.115002, "high50": 62.689999, "High": 63.709999, "Close": 63.555, "BB_hi": 63.099963, "SMA20": 59.64075, "high20": 62.689999}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 391.993875, "BB_lo": 360.752118, "Close": 377.859985, "EMA20": 377.034739, "EMA200": 351.317404, "EMA50": 371.633734, "EMA9": 379.076055, "High": 379.179993, "Low": 376.839996, "Open": 377.890015, "RSI14": 53.807886, "Ret": 0.003106, "SMA20": 376.372997, "SMA50": 370.408998, "Volume": 141700.0, "_provenance": {"captured_at_ist": "2026-08-23 07:51:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "dc46343d0c2668e3d0437189c8457963c0a5445a4be1eb6c84facfbc8ebd4d16"}, "high20": 384.820007, "high50": 384.820007, "low20": 358.170013, "low50": 354.809998}</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>#3SW EMA9&gt;EMA50+Range&lt;1% | Expiry 5d</t>
+          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -17103,7 +17101,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>00:19:33 IST</t>
+          <t>00:19:34 IST</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -17113,7 +17111,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -17127,16 +17125,16 @@
         </is>
       </c>
       <c r="G33" s="4" t="n">
-        <v>717.71</v>
+        <v>63.56</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>69</v>
+        <v>782</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>703.29</v>
+        <v>62.28</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>746.35</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
@@ -17144,7 +17142,7 @@
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>713.34</v>
+        <v>63.62</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -17152,16 +17150,16 @@
         </is>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-301.62</v>
+        <v>45.85</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v>-311.52</v>
-      </c>
-      <c r="Q33" s="13" t="n">
-        <v>-0.63</v>
+        <v>9.94</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>35.91</v>
+      </c>
+      <c r="Q33" s="12" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
@@ -17170,39 +17168,39 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>60.94</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA9&gt;EMA20+2Red</t>
+          <t>EMA9&gt;EMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t>{"EMA200": 658.01956, "Open": 720.219971, "2Red": 1.0, "Volume": 38190856.0, "EMA20": 714.783424, "BB_lo": 663.9257, "EMA50": 708.199326, "SMA50": 712.987002, "low20": 661.140015, "RSI14": 52.242633, "low50": 661.140015, "EMA9": 721.308924, "2Green": 0.0, "Ret": -0.016756, "Low": 715.919983, "high50": 745.450012, "High": 722.130005, "Close": 717.640015, "BB_hi": 748.573299, "SMA20": 706.2495, "high20": 734.580017}</t>
+          <t>{"EMA200": 54.253942, "Open": 63.41, "2Red": 0.0, "Volume": 20822618.0, "EMA20": 59.820197, "BB_lo": 56.181538, "EMA50": 58.261513, "SMA50": 57.1629, "low20": 57.110001, "RSI14": 72.551139, "low50": 52.619999, "EMA9": 61.242966, "2Green": 1.0, "Ret": 0.01558, "Low": 63.115002, "high50": 62.689999, "High": 63.709999, "Close": 63.555, "BB_hi": 63.099963, "SMA20": 59.64075, "high20": 62.689999}</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>#37SW Price&gt;SMA50+EMA9&gt;EMA20+2Red | Expiry 5d</t>
+          <t>#3SW EMA9&gt;EMA50+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>00:20:52 IST</t>
+          <t>00:19:33 IST</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -17212,7 +17210,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -17226,16 +17224,16 @@
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>380.99</v>
+        <v>717.71</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>373.33</v>
+        <v>703.29</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>396.19</v>
+        <v>746.35</v>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
@@ -17243,24 +17241,24 @@
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>377.74</v>
+        <v>713.34</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23 00:57:48 IST</t>
+          <t>2026-08-24 00:57:24 IST</t>
         </is>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-438.45</v>
+        <v>-301.62</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>10.29</v>
+        <v>9.9</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-448.74</v>
+        <v>-311.52</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>-0.87</v>
+        <v>-0.63</v>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
@@ -17269,49 +17267,49 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>37</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>60.94</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+EMA9&gt;EMA20+2Red</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "BB_lo": 356.336918, "BB_hi": 391.566088, "EMA50": 370.481576, "SMA50": 369.201801, "high20": 384.820007, "low50": 354.809998, "Open": 382.649994, "Volume": 101666.0, "2Red": 1.0, "EMA200": 350.231559, "RSI14": 60.286192, "low20": 358.170013, "Ret": -0.00413, "EMA20": 376.443558, "high50": 384.820007, "Low": 380.609985, "Close": 380.950104, "EMA9": 380.399819, "SMA20": 373.951503, "High": 382.875}</t>
+          <t>{"EMA200": 658.01956, "Open": 720.219971, "2Red": 1.0, "Volume": 38190856.0, "EMA20": 714.783424, "BB_lo": 663.9257, "EMA50": 708.199326, "SMA50": 712.987002, "low20": 661.140015, "RSI14": 52.242633, "low50": 661.140015, "EMA9": 721.308924, "2Green": 0.0, "Ret": -0.016756, "Low": 715.919983, "high50": 745.450012, "High": 722.130005, "Close": 717.640015, "BB_hi": 748.573299, "SMA20": 706.2495, "high20": 734.580017}</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#37SW Price&gt;SMA50+EMA9&gt;EMA20+2Red | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>11:52:58 IST</t>
+          <t>00:20:52 IST</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>VASWANI.NS</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -17321,45 +17319,45 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>LONG_BOUNCE_5m</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="G35" s="4" t="n">
-        <v>46.63</v>
+        <v>380.99</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1333</v>
+        <v>135</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>45.88</v>
+        <v>373.33</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>48.33</v>
+        <v>396.19</v>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>45.83</v>
+        <v>377.74</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17 12:09:41 IST</t>
+          <t>2026-08-23 00:57:48 IST</t>
         </is>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-1066.4</v>
+        <v>-438.45</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>186.47</v>
+        <v>10.29</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-1252.87</v>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v>-2.02</v>
+        <v>-448.74</v>
+      </c>
+      <c r="Q35" s="13" t="n">
+        <v>-0.87</v>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
@@ -17368,27 +17366,27 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>59.53</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t>Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down 10:30-12:30</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t>{"Close": 46.58, "Volume": 1153, "VolAvg20": 237.0, "RSI14": 31.4, "Drop_pct": 8.31, "BelowVWAP": true, "VWAPDown": true, "NIFTY_gap_pct": -0.09}</t>
+          <t>{"2Green": 0.0, "BB_lo": 356.336918, "BB_hi": 391.566088, "EMA50": 370.481576, "SMA50": 369.201801, "high20": 384.820007, "low50": 354.809998, "Open": 382.649994, "Volume": 101666.0, "2Red": 1.0, "EMA200": 350.231559, "RSI14": 60.286192, "low20": 358.170013, "Ret": -0.00413, "EMA20": 376.443558, "high50": 384.820007, "Low": 380.609985, "Close": 380.950104, "EMA9": 380.399819, "SMA20": 373.951503, "High": 382.875}</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>#935ID Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down | ðŸŽ¯ SL Hit (live)</t>
+          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17398,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>11:10:50 IST</t>
+          <t>11:52:58 IST</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -17410,7 +17408,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>LAXMIINDIA.NS</t>
+          <t>VASWANI.NS</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -17424,16 +17422,16 @@
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>124.98</v>
+        <v>46.63</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>510</v>
+        <v>1333</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>123.02</v>
+        <v>45.88</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>129.57</v>
+        <v>48.33</v>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
@@ -17441,24 +17439,24 @@
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>129.47</v>
+        <v>45.83</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17 14:43:12 IST</t>
+          <t>2026-08-17 12:09:41 IST</t>
         </is>
       </c>
       <c r="N36" s="4" t="n">
-        <v>2289.9</v>
+        <v>-1066.4</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>191.22</v>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v>2098.68</v>
-      </c>
-      <c r="Q36" s="5" t="n">
-        <v>3.29</v>
+        <v>186.47</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v>-1252.87</v>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v>-2.02</v>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
@@ -17482,34 +17480,34 @@
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t>{"Close": 124.89, "Volume": 16581, "VolAvg20": 2144.0, "RSI14": 40.9, "Drop_pct": 3.7, "BelowVWAP": true, "VWAPDown": true, "NIFTY_gap_pct": -0.09}</t>
+          <t>{"Close": 46.58, "Volume": 1153, "VolAvg20": 237.0, "RSI14": 31.4, "Drop_pct": 8.31, "BelowVWAP": true, "VWAPDown": true, "NIFTY_gap_pct": -0.09}</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>#935ID Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down | ðŸŽ¯ Target Hit (live)</t>
+          <t>#935ID Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down | ðŸŽ¯ SL Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>07:48:23 IST</t>
+          <t>11:10:50 IST</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>LAXMIINDIA.NS</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -17519,45 +17517,45 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>LONG_BOUNCE_5m</t>
         </is>
       </c>
       <c r="G37" s="4" t="n">
-        <v>1880</v>
+        <v>124.98</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>25</v>
+        <v>510</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>1840.56</v>
+        <v>123.02</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>1953.24</v>
+        <v>129.57</v>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1951.29</v>
+        <v>129.47</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 20:30:05 IST</t>
+          <t>2026-08-17 14:43:12 IST</t>
         </is>
       </c>
       <c r="N37" s="4" t="n">
-        <v>1782.17</v>
+        <v>2289.9</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>141</v>
+        <v>191.22</v>
       </c>
       <c r="P37" s="5" t="n">
-        <v>1641.17</v>
+        <v>2098.68</v>
       </c>
       <c r="Q37" s="5" t="n">
-        <v>3.49</v>
+        <v>3.29</v>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
@@ -17566,27 +17564,27 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
+          <t>Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down 10:30-12:30</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>{"High": 1881.228882, "Ret": -0.001345, "low20": 1821.485107, "2Green": 0.0, "high50": 1976.460205, "RSI14": 50.528767, "EMA50": 1864.50293, "Close": 1878.119995, "EMA200": 2128.981002, "SMA20": 1888.450458, "Open": 1880.982056, "low50": 1510.505859, "high20": 1976.460205, "BB_hi": 1932.730084, "Volume": 3153563392.0, "BB_lo": 1844.170831, "Low": 1876.0802, "EMA9": 1884.579071, "EMA20": 1882.056983, "SMA50": 1830.116287, "2Red": 1.0}</t>
+          <t>{"Close": 124.89, "Volume": 16581, "VolAvg20": 2144.0, "RSI14": 40.9, "Drop_pct": 3.7, "BelowVWAP": true, "VWAPDown": true, "NIFTY_gap_pct": -0.09}</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | ðŸŽ¯ Target Hit (live)</t>
+          <t>#935ID Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down | ðŸŽ¯ Target Hit (live)</t>
         </is>
       </c>
     </row>
@@ -17608,7 +17606,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -17621,17 +17619,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G38" s="10" t="n">
-        <v>0.332</v>
+      <c r="G38" s="4" t="n">
+        <v>1880</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I38" s="11" t="n">
-        <v>0.3244</v>
-      </c>
-      <c r="J38" s="11" t="n">
-        <v>0.3442</v>
+        <v>25</v>
+      </c>
+      <c r="I38" s="8" t="n">
+        <v>1840.56</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>1953.24</v>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
@@ -17639,24 +17637,24 @@
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0.3369</v>
+        <v>1951.29</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21 07:50:22 IST</t>
+          <t>2026-08-19 20:30:05 IST</t>
         </is>
       </c>
       <c r="N38" s="4" t="n">
-        <v>48.75</v>
+        <v>1782.17</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>141</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>38.79</v>
+        <v>1641.17</v>
       </c>
       <c r="Q38" s="5" t="n">
-        <v>1.17</v>
+        <v>3.49</v>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
@@ -17665,27 +17663,27 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t>{"High": 0.330999, "Ret": -0.004433, "low20": 0.323269, "2Green": 0.0, "high50": 0.337903, "RSI14": 53.511744, "EMA50": 0.328876, "Close": 0.330981, "EMA200": 0.321504, "SMA20": 0.32883, "Open": 0.330921, "low50": 0.314034, "high20": 0.337903, "BB_hi": 0.335516, "Volume": 317728800.0, "BB_lo": 0.322143, "Low": 0.330715, "EMA9": 0.331613, "EMA20": 0.33003, "SMA50": 0.327135, "2Red": 1.0}</t>
+          <t>{"High": 1881.228882, "Ret": -0.001345, "low20": 1821.485107, "2Green": 0.0, "high50": 1976.460205, "RSI14": 50.528767, "EMA50": 1864.50293, "Close": 1878.119995, "EMA200": 2128.981002, "SMA20": 1888.450458, "Open": 1880.982056, "low50": 1510.505859, "high20": 1976.460205, "BB_hi": 1932.730084, "Volume": 3153563392.0, "BB_lo": 1844.170831, "Low": 1876.0802, "EMA9": 1884.579071, "EMA20": 1882.056983, "SMA50": 1830.116287, "2Red": 1.0}</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
+          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | ðŸŽ¯ Target Hit (live)</t>
         </is>
       </c>
     </row>
@@ -17702,12 +17700,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -17720,17 +17718,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n">
-        <v>167.39</v>
+      <c r="G39" s="10" t="n">
+        <v>0.332</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>305</v>
-      </c>
-      <c r="I39" s="8" t="n">
-        <v>164.02</v>
-      </c>
-      <c r="J39" s="8" t="n">
-        <v>174.06</v>
+        <v>10000</v>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="J39" s="11" t="n">
+        <v>0.3442</v>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
@@ -17738,24 +17736,24 @@
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>174.04</v>
+        <v>0.3369</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 19:18:22 IST</t>
+          <t>2026-08-21 07:50:22 IST</t>
         </is>
       </c>
       <c r="N39" s="4" t="n">
-        <v>2029.04</v>
+        <v>48.75</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>10.21</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>2018.83</v>
+        <v>38.79</v>
       </c>
       <c r="Q39" s="5" t="n">
-        <v>3.95</v>
+        <v>1.17</v>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
@@ -17764,27 +17762,27 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t>{"High": 167.770004, "Ret": -0.005998, "low20": 157.229996, "2Green": 0.0, "high50": 169.710007, "RSI14": 61.944112, "EMA50": 160.375176, "Close": 167.369995, "EMA200": 152.877762, "SMA20": 164.259, "Open": 167.660004, "low50": 146.070007, "high20": 169.710007, "BB_hi": 170.39623, "Volume": 5020700.0, "BB_lo": 158.121771, "Low": 166.449997, "EMA9": 166.656228, "EMA20": 164.675214, "SMA50": 159.8202, "2Red": 1.0}</t>
+          <t>{"High": 0.330999, "Ret": -0.004433, "low20": 0.323269, "2Green": 0.0, "high50": 0.337903, "RSI14": 53.511744, "EMA50": 0.328876, "Close": 0.330981, "EMA200": 0.321504, "SMA20": 0.32883, "Open": 0.330921, "low50": 0.314034, "high20": 0.337903, "BB_hi": 0.335516, "Volume": 317728800.0, "BB_lo": 0.322143, "Low": 0.330715, "EMA9": 0.331613, "EMA20": 0.33003, "SMA50": 0.327135, "2Red": 1.0}</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | ðŸŽ¯ Target Hit (live)</t>
+          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -17806,7 +17804,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -17820,16 +17818,16 @@
         </is>
       </c>
       <c r="G40" s="4" t="n">
-        <v>52.55</v>
+        <v>167.39</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>972</v>
+        <v>305</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>51.49</v>
+        <v>164.02</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>54.64</v>
+        <v>174.06</v>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
@@ -17837,24 +17835,24 @@
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>52.41</v>
+        <v>174.04</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21 07:50:22 IST</t>
+          <t>2026-08-19 19:18:22 IST</t>
         </is>
       </c>
       <c r="N40" s="4" t="n">
-        <v>-131.46</v>
+        <v>2029.04</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v>-141.68</v>
-      </c>
-      <c r="Q40" s="13" t="n">
-        <v>-0.28</v>
+        <v>10.21</v>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>2018.83</v>
+      </c>
+      <c r="Q40" s="5" t="n">
+        <v>3.95</v>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
@@ -17863,39 +17861,39 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t>{"High": 52.650002, "Ret": 0.004397, "low20": 49.849998, "2Green": 0.0, "high50": 53.599998, "RSI14": 55.668613, "EMA50": 51.516289, "Close": 52.540001, "EMA200": 49.67764, "SMA20": 51.7285, "Open": 52.459999, "low50": 49.57, "high20": 53.599998, "BB_hi": 53.772381, "Volume": 7479000.0, "BB_lo": 49.684619, "Low": 52.27, "EMA9": 52.4289, "EMA20": 51.988963, "SMA50": 51.383, "2Red": 0.0}</t>
+          <t>{"High": 167.770004, "Ret": -0.005998, "low20": 157.229996, "2Green": 0.0, "high50": 169.710007, "RSI14": 61.944112, "EMA50": 160.375176, "Close": 167.369995, "EMA200": 152.877762, "SMA20": 164.259, "Open": 167.660004, "low50": 146.070007, "high20": 169.710007, "BB_hi": 170.39623, "Volume": 5020700.0, "BB_lo": 158.121771, "Low": 166.449997, "EMA9": 166.656228, "EMA20": 164.675214, "SMA50": 159.8202, "2Red": 1.0}</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>#2SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | ðŸŽ¯ Target Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>00:20:31 IST</t>
+          <t>07:48:23 IST</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -17905,7 +17903,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -17919,16 +17917,16 @@
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>381.8</v>
+        <v>52.55</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>131</v>
+        <v>972</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>374.12</v>
+        <v>51.49</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>397.03</v>
+        <v>54.64</v>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
@@ -17936,24 +17934,24 @@
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>380.91</v>
+        <v>52.41</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18 00:20:50 IST</t>
+          <t>2026-08-21 07:50:22 IST</t>
         </is>
       </c>
       <c r="N41" s="4" t="n">
-        <v>-116.33</v>
+        <v>-131.46</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>10</v>
+        <v>10.22</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-126.33</v>
+        <v>-141.68</v>
       </c>
       <c r="Q41" s="13" t="n">
-        <v>-0.25</v>
+        <v>-0.28</v>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
@@ -17962,12 +17960,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -17977,24 +17975,24 @@
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>{"Low": 380.838501, "EMA9": 378.755146, "Ret": 0.002468, "High": 382.554993, "BB_lo": 355.440257, "SMA20": 371.858, "RSI14": 63.686748, "EMA20": 374.422536, "low20": 358.170013, "high50": 384.820007, "2Red": 0.0, "SMA50": 368.8264, "Open": 382.660004, "2Green": 0.0, "high20": 384.820007, "EMA200": 349.15793, "Close": 381.76001, "low50": 354.809998, "BB_hi": 388.275744, "Volume": 171118.0, "EMA50": 368.980107}</t>
+          <t>{"High": 52.650002, "Ret": 0.004397, "low20": 49.849998, "2Green": 0.0, "high50": 53.599998, "RSI14": 55.668613, "EMA50": 51.516289, "Close": 52.540001, "EMA200": 49.67764, "SMA20": 51.7285, "Open": 52.459999, "low50": 49.57, "high20": 53.599998, "BB_hi": 53.772381, "Volume": 7479000.0, "BB_lo": 49.684619, "Low": 52.27, "EMA9": 52.4289, "EMA20": 51.988963, "SMA50": 51.383, "2Red": 0.0}</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#2SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>00:43:12 IST</t>
+          <t>00:20:31 IST</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -18004,7 +18002,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -18018,16 +18016,16 @@
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>717.42</v>
+        <v>381.8</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>69</v>
+        <v>131</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>703</v>
+        <v>374.12</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>746.04</v>
+        <v>397.03</v>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
@@ -18035,24 +18033,24 @@
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>730.98</v>
+        <v>380.91</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17 00:56:07 IST</t>
+          <t>2026-08-18 00:20:50 IST</t>
         </is>
       </c>
       <c r="N42" s="4" t="n">
-        <v>935.42</v>
+        <v>-116.33</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="P42" s="5" t="n">
-        <v>925.52</v>
-      </c>
-      <c r="Q42" s="5" t="n">
-        <v>1.87</v>
+        <v>10</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v>-126.33</v>
+      </c>
+      <c r="Q42" s="13" t="n">
+        <v>-0.25</v>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
@@ -18061,49 +18059,49 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>60.94</t>
+          <t>59.53</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA9&gt;EMA20+2Red</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t>{"Volume": 22313421.0, "BB_lo": 665.286184, "SMA20": 700.678995, "high20": 728.539978, "low20": 661.140015, "low50": 661.140015, "High": 723.299988, "2Red": 1.0, "RSI14": 54.565075, "high50": 748.650024, "SMA50": 713.8536, "2Green": 0.0, "Open": 723.299988, "EMA200": 654.275205, "EMA50": 704.048659, "BB_hi": 736.071805, "Low": 715.789978, "EMA9": 711.374496, "Ret": -0.004883, "Close": 717.349976, "EMA20": 707.041668}</t>
+          <t>{"Low": 380.838501, "EMA9": 378.755146, "Ret": 0.002468, "High": 382.554993, "BB_lo": 355.440257, "SMA20": 371.858, "RSI14": 63.686748, "EMA20": 374.422536, "low20": 358.170013, "high50": 384.820007, "2Red": 0.0, "SMA50": 368.8264, "Open": 382.660004, "2Green": 0.0, "high20": 384.820007, "EMA200": 349.15793, "Close": 381.76001, "low50": 354.809998, "BB_hi": 388.275744, "Volume": 171118.0, "EMA50": 368.980107}</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>#37SW Price&gt;SMA50+EMA9&gt;EMA20+2Red | Expiry 5d</t>
+          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>00:37:04 IST</t>
+          <t>00:43:12 IST</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -18117,16 +18115,16 @@
         </is>
       </c>
       <c r="G43" s="4" t="n">
-        <v>1874.1</v>
+        <v>717.42</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>1834.79</v>
+        <v>703</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>1947.12</v>
+        <v>746.04</v>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
@@ -18134,24 +18132,24 @@
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>1880.51</v>
+        <v>730.98</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16 00:56:05 IST</t>
+          <t>2026-08-17 00:56:07 IST</t>
         </is>
       </c>
       <c r="N43" s="4" t="n">
-        <v>160.19</v>
+        <v>935.42</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>140.56</v>
+        <v>9.9</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>19.63</v>
-      </c>
-      <c r="Q43" s="12" t="n">
-        <v>0.04</v>
+        <v>925.52</v>
+      </c>
+      <c r="Q43" s="5" t="n">
+        <v>1.87</v>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
@@ -18160,27 +18158,27 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>60.94</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
+          <t>Price&gt;SMA50+EMA9&gt;EMA20+2Red</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t>{"BB_hi": 1951.082913, "EMA20": 1883.245495, "high20": 1976.460205, "Open": 1908.93103, "EMA200": 2141.746334, "Volume": 9096837120.0, "low50": 1510.505859, "Low": 1868.057739, "2Red": 1.0, "RSI14": 49.831146, "EMA9": 1893.674853, "BB_lo": 1835.426218, "2Green": 0.0, "high50": 1976.460205, "Close": 1872.22998, "SMA20": 1893.254565, "High": 1928.543091, "EMA50": 1861.015458, "low20": 1821.485107, "SMA50": 1805.156021, "Ret": -0.019098}</t>
+          <t>{"Volume": 22313421.0, "BB_lo": 665.286184, "SMA20": 700.678995, "high20": 728.539978, "low20": 661.140015, "low50": 661.140015, "High": 723.299988, "2Red": 1.0, "RSI14": 54.565075, "high50": 748.650024, "SMA50": 713.8536, "2Green": 0.0, "Open": 723.299988, "EMA200": 654.275205, "EMA50": 704.048659, "BB_hi": 736.071805, "Low": 715.789978, "EMA9": 711.374496, "Ret": -0.004883, "Close": 717.349976, "EMA20": 707.041668}</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | Expiry 5d</t>
+          <t>#37SW Price&gt;SMA50+EMA9&gt;EMA20+2Red | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -18202,7 +18200,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -18215,17 +18213,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G44" s="10" t="n">
-        <v>0.331</v>
+      <c r="G44" s="4" t="n">
+        <v>1874.1</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I44" s="11" t="n">
-        <v>0.3241</v>
-      </c>
-      <c r="J44" s="11" t="n">
-        <v>0.3439</v>
+        <v>25</v>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>1834.79</v>
+      </c>
+      <c r="J44" s="8" t="n">
+        <v>1947.12</v>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
@@ -18233,7 +18231,7 @@
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.3304</v>
+        <v>1880.51</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -18241,16 +18239,16 @@
         </is>
       </c>
       <c r="N44" s="4" t="n">
-        <v>-5.56</v>
+        <v>160.19</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v>-15.49</v>
-      </c>
-      <c r="Q44" s="13" t="n">
-        <v>-0.47</v>
+        <v>140.56</v>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="Q44" s="12" t="n">
+        <v>0.04</v>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
@@ -18259,27 +18257,27 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t>{"BB_hi": 0.332258, "EMA20": 0.327832, "high20": 0.333079, "Open": 0.329585, "EMA200": 0.32088, "Volume": 869478144.0, "low50": 0.314034, "Low": 0.329472, "2Red": 0.0, "RSI14": 57.524103, "EMA9": 0.328473, "BB_lo": 0.323712, "2Green": 1.0, "high50": 0.333832, "Close": 0.330694, "SMA20": 0.327985, "High": 0.331578, "EMA50": 0.327842, "low20": 0.323269, "SMA50": 0.326432, "Ret": 0.003357}</t>
+          <t>{"BB_hi": 1951.082913, "EMA20": 1883.245495, "high20": 1976.460205, "Open": 1908.93103, "EMA200": 2141.746334, "Volume": 9096837120.0, "low50": 1510.505859, "Low": 1868.057739, "2Red": 1.0, "RSI14": 49.831146, "EMA9": 1893.674853, "BB_lo": 1835.426218, "2Green": 0.0, "high50": 1976.460205, "Close": 1872.22998, "SMA20": 1893.254565, "High": 1928.543091, "EMA50": 1861.015458, "low20": 1821.485107, "SMA50": 1805.156021, "Ret": -0.019098}</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
+          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -18296,12 +18294,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -18314,17 +18312,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G45" s="4" t="n">
-        <v>84.8</v>
+      <c r="G45" s="10" t="n">
+        <v>0.331</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>587</v>
-      </c>
-      <c r="I45" s="8" t="n">
-        <v>83.09</v>
-      </c>
-      <c r="J45" s="8" t="n">
-        <v>88.18000000000001</v>
+        <v>10000</v>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="J45" s="11" t="n">
+        <v>0.3439</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
@@ -18332,7 +18330,7 @@
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>86.06999999999999</v>
+        <v>0.3304</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -18340,16 +18338,16 @@
         </is>
       </c>
       <c r="N45" s="4" t="n">
-        <v>743.37</v>
+        <v>-5.56</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="P45" s="5" t="n">
-        <v>733.41</v>
-      </c>
-      <c r="Q45" s="5" t="n">
-        <v>1.47</v>
+        <v>9.93</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v>-15.49</v>
+      </c>
+      <c r="Q45" s="13" t="n">
+        <v>-0.47</v>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
@@ -18358,39 +18356,39 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>Range&lt;1%+SMA20&lt;EMA20</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t>{"BB_hi": 87.086251, "EMA20": 84.986252, "high20": 88.779999, "Open": 84.660004, "EMA200": 83.124135, "Volume": 4681010.0, "low50": 81.480003, "Low": 84.330002, "2Red": 0.0, "RSI14": 49.564668, "EMA9": 85.140171, "BB_lo": 82.854749, "2Green": 0.0, "high50": 88.779999, "Close": 84.790001, "SMA20": 84.9705, "High": 85.044998, "EMA50": 84.555905, "low20": 82.809998, "SMA50": 84.312, "Ret": -0.003877}</t>
+          <t>{"BB_hi": 0.332258, "EMA20": 0.327832, "high20": 0.333079, "Open": 0.329585, "EMA200": 0.32088, "Volume": 869478144.0, "low50": 0.314034, "Low": 0.329472, "2Red": 0.0, "RSI14": 57.524103, "EMA9": 0.328473, "BB_lo": 0.323712, "2Green": 1.0, "high50": 0.333832, "Close": 0.330694, "SMA20": 0.327985, "High": 0.331578, "EMA50": 0.327842, "low20": 0.323269, "SMA50": 0.326432, "Ret": 0.003357}</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>#5SW Range&lt;1%+SMA20&lt;EMA20 | Expiry 5d</t>
+          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>05:40:03 IST</t>
+          <t>00:37:04 IST</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -18400,7 +18398,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -18414,16 +18412,16 @@
         </is>
       </c>
       <c r="G46" s="4" t="n">
-        <v>185.35</v>
+        <v>84.8</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>265</v>
+        <v>587</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>181.62</v>
+        <v>83.09</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>192.74</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
@@ -18431,24 +18429,24 @@
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>186.12</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 08:36:01 IST</t>
+          <t>2026-08-16 00:56:05 IST</t>
         </is>
       </c>
       <c r="N46" s="4" t="n">
-        <v>204.42</v>
+        <v>743.37</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>9.82</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="P46" s="5" t="n">
-        <v>194.6</v>
-      </c>
-      <c r="Q46" s="12" t="n">
-        <v>0.4</v>
+        <v>733.41</v>
+      </c>
+      <c r="Q46" s="5" t="n">
+        <v>1.47</v>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
@@ -18457,27 +18455,27 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>63.73</t>
+          <t>58.26</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
+          <t>Range&lt;1%+SMA20&lt;EMA20</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>{"EMA50": 178.417894, "Close": 185.330002, "Volume": 6431938.0, "RSI14": 56.546346, "High": 186.910004, "2Red": 1.0, "Ret": -0.00312, "Low": 182.070007, "EMA20": 179.791718, "EMA9": 180.620244, "Open": 183.190002, "SMA50": 183.268401, "SMA20": 178.784}</t>
+          <t>{"BB_hi": 87.086251, "EMA20": 84.986252, "high20": 88.779999, "Open": 84.660004, "EMA200": 83.124135, "Volume": 4681010.0, "low50": 81.480003, "Low": 84.330002, "2Red": 0.0, "RSI14": 49.564668, "EMA9": 85.140171, "BB_lo": 82.854749, "2Green": 0.0, "high50": 88.779999, "Close": 84.790001, "SMA20": 84.9705, "High": 85.044998, "EMA50": 84.555905, "low20": 82.809998, "SMA50": 84.312, "Ret": -0.003877}</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>#28SW Price&gt;SMA50+EMA20&gt;EMA50+2Red | Expiry 5d</t>
+          <t>#5SW Range&lt;1%+SMA20&lt;EMA20 | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -18499,7 +18497,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -18513,16 +18511,16 @@
         </is>
       </c>
       <c r="G47" s="4" t="n">
-        <v>381.22</v>
+        <v>185.35</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>129</v>
+        <v>265</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>373.56</v>
+        <v>181.62</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>396.43</v>
+        <v>192.74</v>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
@@ -18530,7 +18528,7 @@
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>380.7</v>
+        <v>186.12</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
@@ -18538,16 +18536,16 @@
         </is>
       </c>
       <c r="N47" s="4" t="n">
-        <v>-66.83</v>
+        <v>204.42</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v>-76.67</v>
-      </c>
-      <c r="Q47" s="13" t="n">
-        <v>-0.16</v>
+        <v>9.82</v>
+      </c>
+      <c r="P47" s="5" t="n">
+        <v>194.6</v>
+      </c>
+      <c r="Q47" s="12" t="n">
+        <v>0.4</v>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
@@ -18556,39 +18554,39 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>63.73</t>
         </is>
       </c>
       <c r="U47" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
         </is>
       </c>
       <c r="V47" s="3" t="inlineStr">
         <is>
-          <t>{"EMA50": 366.698569, "Close": 381.179993, "Volume": 145727.0, "RSI14": 65.09971, "High": 382.63501, "2Red": 0.0, "Ret": 0.001129, "Low": 380.350006, "EMA20": 370.650953, "EMA9": 374.081113, "Open": 381.549988, "SMA50": 368.3698, "SMA20": 369.739}</t>
+          <t>{"EMA50": 178.417894, "Close": 185.330002, "Volume": 6431938.0, "RSI14": 56.546346, "High": 186.910004, "2Red": 1.0, "Ret": -0.00312, "Low": 182.070007, "EMA20": 179.791718, "EMA9": 180.620244, "Open": 183.190002, "SMA50": 183.268401, "SMA20": 178.784}</t>
         </is>
       </c>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#28SW Price&gt;SMA50+EMA20&gt;EMA50+2Red | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>01:17:18 IST</t>
+          <t>05:40:03 IST</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -18598,7 +18596,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -18612,16 +18610,16 @@
         </is>
       </c>
       <c r="G48" s="4" t="n">
-        <v>719.29</v>
+        <v>381.22</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>704.9</v>
+        <v>373.56</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>748.0599999999999</v>
+        <v>396.43</v>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
@@ -18629,24 +18627,24 @@
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>720.8</v>
+        <v>380.7</v>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 01:36:05 IST</t>
+          <t>2026-08-12 08:36:01 IST</t>
         </is>
       </c>
       <c r="N48" s="4" t="n">
-        <v>105.55</v>
+        <v>-66.83</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>10.07</v>
-      </c>
-      <c r="P48" s="5" t="n">
-        <v>95.48</v>
-      </c>
-      <c r="Q48" s="12" t="n">
-        <v>0.19</v>
+        <v>9.84</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v>-76.67</v>
+      </c>
+      <c r="Q48" s="13" t="n">
+        <v>-0.16</v>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
@@ -18655,27 +18653,27 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>59.53</t>
         </is>
       </c>
       <c r="U48" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA9&lt;EMA20</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V48" s="3" t="inlineStr">
         <is>
-          <t>{"Volume": 28061644.0, "RSI14": 56.167234, "EMA20": 701.326904, "EMA9": 700.684364, "Low": 719.26001, "SMA50": 715.048199, "EMA50": 701.5317, "High": 728.539978, "2Red": 0.0, "Close": 719.289978, "SMA20": 700.994495, "Open": 726.224976, "Ret": -0.0063}</t>
+          <t>{"EMA50": 366.698569, "Close": 381.179993, "Volume": 145727.0, "RSI14": 65.09971, "High": 382.63501, "2Red": 0.0, "Ret": 0.001129, "Low": 380.350006, "EMA20": 370.650953, "EMA9": 374.081113, "Open": 381.549988, "SMA50": 368.3698, "SMA20": 369.739}</t>
         </is>
       </c>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>#50SW Price&gt;SMA50+EMA9&lt;EMA20 | Expiry 5d</t>
+          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -18697,7 +18695,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -18711,16 +18709,16 @@
         </is>
       </c>
       <c r="G49" s="4" t="n">
-        <v>52.72</v>
+        <v>719.29</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>969</v>
+        <v>70</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>51.67</v>
+        <v>704.9</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>54.83</v>
+        <v>748.0599999999999</v>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
@@ -18728,7 +18726,7 @@
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>53.18</v>
+        <v>720.8</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -18736,16 +18734,16 @@
         </is>
       </c>
       <c r="N49" s="4" t="n">
-        <v>450.27</v>
+        <v>105.55</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>10.22</v>
+        <v>10.07</v>
       </c>
       <c r="P49" s="5" t="n">
-        <v>440.05</v>
+        <v>95.48</v>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>0.86</v>
+        <v>0.19</v>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
@@ -18754,49 +18752,49 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="U49" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+EMA9&lt;EMA20</t>
         </is>
       </c>
       <c r="V49" s="3" t="inlineStr">
         <is>
-          <t>{"Volume": 9101653.0, "RSI14": 59.972956, "EMA20": 51.291376, "EMA9": 51.578998, "Low": 52.474998, "SMA50": 51.1821, "EMA50": 51.139325, "High": 52.959999, "2Red": 0.0, "Close": 52.724998, "SMA20": 51.00325, "Open": 52.59, "Ret": 0.013942}</t>
+          <t>{"Volume": 28061644.0, "RSI14": 56.167234, "EMA20": 701.326904, "EMA9": 700.684364, "Low": 719.26001, "SMA50": 715.048199, "EMA50": 701.5317, "High": 728.539978, "2Red": 0.0, "Close": 719.289978, "SMA20": 700.994495, "Open": 726.224976, "Ret": -0.0063}</t>
         </is>
       </c>
       <c r="W49" s="3" t="inlineStr">
         <is>
-          <t>#2SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#50SW Price&gt;SMA50+EMA9&lt;EMA20 | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>15:13:11 IST</t>
+          <t>01:17:18 IST</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -18809,17 +18807,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G50" s="10" t="n">
-        <v>0.3281</v>
+      <c r="G50" s="4" t="n">
+        <v>52.72</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I50" s="11" t="n">
-        <v>0.3215</v>
-      </c>
-      <c r="J50" s="11" t="n">
-        <v>0.3412</v>
+        <v>969</v>
+      </c>
+      <c r="I50" s="8" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="J50" s="8" t="n">
+        <v>54.83</v>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
@@ -18827,24 +18825,24 @@
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0.33</v>
+        <v>53.18</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 15:13:13 IST</t>
+          <t>2026-08-11 01:36:05 IST</t>
         </is>
       </c>
       <c r="N50" s="4" t="n">
-        <v>19.32</v>
+        <v>450.27</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>9.84</v>
+        <v>10.22</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>9.48</v>
+        <v>440.05</v>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>0.29</v>
+        <v>0.86</v>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
@@ -18853,27 +18851,27 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T50" s="3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="U50" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V50" s="3" t="inlineStr">
         <is>
-          <t>{"Open": 0.326938, "2Red": 0.0, "Low": 0.326183, "EMA50": 0.327684, "High": 0.328078, "Volume": 546277952.0, "Close": 0.328078, "SMA20": 0.327438, "SMA50": 0.32597, "EMA9": 0.327405, "Ret": 0.003497, "RSI14": 51.70969, "EMA20": 0.327265}</t>
+          <t>{"Volume": 9101653.0, "RSI14": 59.972956, "EMA20": 51.291376, "EMA9": 51.578998, "Low": 52.474998, "SMA50": 51.1821, "EMA50": 51.139325, "High": 52.959999, "2Red": 0.0, "Close": 52.724998, "SMA20": 51.00325, "Open": 52.59, "Ret": 0.013942}</t>
         </is>
       </c>
       <c r="W50" s="3" t="inlineStr">
         <is>
-          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
+          <t>#2SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -18890,12 +18888,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -18908,17 +18906,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G51" s="4" t="n">
-        <v>118.29</v>
+      <c r="G51" s="10" t="n">
+        <v>0.3281</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>420</v>
-      </c>
-      <c r="I51" s="8" t="n">
-        <v>115.92</v>
-      </c>
-      <c r="J51" s="8" t="n">
-        <v>123.02</v>
+        <v>10000</v>
+      </c>
+      <c r="I51" s="11" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="J51" s="11" t="n">
+        <v>0.3412</v>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
@@ -18926,7 +18924,7 @@
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>119.8</v>
+        <v>0.33</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -18934,16 +18932,16 @@
         </is>
       </c>
       <c r="N51" s="4" t="n">
-        <v>633.37</v>
+        <v>19.32</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>9.94</v>
+        <v>9.84</v>
       </c>
       <c r="P51" s="5" t="n">
-        <v>623.4299999999999</v>
-      </c>
-      <c r="Q51" s="5" t="n">
-        <v>1.25</v>
+        <v>9.48</v>
+      </c>
+      <c r="Q51" s="12" t="n">
+        <v>0.29</v>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
@@ -18957,22 +18955,22 @@
       </c>
       <c r="T51" s="3" t="inlineStr">
         <is>
-          <t>58.65</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="U51" s="3" t="inlineStr">
         <is>
-          <t>EMA9&lt;EMA50+RSI&gt;50</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V51" s="3" t="inlineStr">
         <is>
-          <t>{"Open": 117.529999, "2Red": 0.0, "Low": 117.120003, "EMA50": 115.501689, "High": 118.57, "Volume": 10500800.0, "Close": 118.290001, "SMA20": 114.6345, "SMA50": 116.0852, "EMA9": 115.004317, "Ret": 0.000677, "RSI14": 59.157988, "EMA20": 114.786415}</t>
+          <t>{"Open": 0.326938, "2Red": 0.0, "Low": 0.326183, "EMA50": 0.327684, "High": 0.328078, "Volume": 546277952.0, "Close": 0.328078, "SMA20": 0.327438, "SMA50": 0.32597, "EMA9": 0.327405, "Ret": 0.003497, "RSI14": 51.70969, "EMA20": 0.327265}</t>
         </is>
       </c>
       <c r="W51" s="3" t="inlineStr">
         <is>
-          <t>#1SW EMA9&lt;EMA50+RSI&gt;50 | Expiry 5d</t>
+          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -18994,7 +18992,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -19008,16 +19006,16 @@
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>162.1</v>
+        <v>118.29</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>307</v>
+        <v>420</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>158.86</v>
+        <v>115.92</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>168.58</v>
+        <v>123.02</v>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
@@ -19025,7 +19023,7 @@
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>165.65</v>
+        <v>119.8</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
@@ -19033,16 +19031,16 @@
         </is>
       </c>
       <c r="N52" s="4" t="n">
-        <v>1090.9</v>
+        <v>633.37</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.94</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>1080.95</v>
+        <v>623.4299999999999</v>
       </c>
       <c r="Q52" s="5" t="n">
-        <v>2.17</v>
+        <v>1.25</v>
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
@@ -19051,39 +19049,39 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T52" s="3" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>58.65</t>
         </is>
       </c>
       <c r="U52" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>EMA9&lt;EMA50+RSI&gt;50</t>
         </is>
       </c>
       <c r="V52" s="3" t="inlineStr">
         <is>
-          <t>{"Open": 162.0, "2Red": 1.0, "Low": 160.970001, "EMA50": 157.880967, "High": 162.490005, "Volume": 15121700.0, "Close": 162.100006, "SMA20": 161.822, "SMA50": 156.9082, "EMA9": 162.798107, "Ret": -0.000863, "RSI14": 53.812337, "EMA20": 161.631372}</t>
+          <t>{"Open": 117.529999, "2Red": 0.0, "Low": 117.120003, "EMA50": 115.501689, "High": 118.57, "Volume": 10500800.0, "Close": 118.290001, "SMA20": 114.6345, "SMA50": 116.0852, "EMA9": 115.004317, "Ret": 0.000677, "RSI14": 59.157988, "EMA20": 114.786415}</t>
         </is>
       </c>
       <c r="W52" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#1SW EMA9&lt;EMA50+RSI&gt;50 | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>01:18:05 IST</t>
+          <t>15:13:11 IST</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -19093,7 +19091,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -19107,16 +19105,16 @@
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>700.39</v>
+        <v>162.1</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>71</v>
+        <v>307</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>686.38</v>
+        <v>158.86</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>728.41</v>
+        <v>168.58</v>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
@@ -19124,24 +19122,24 @@
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>728.41</v>
+        <v>165.65</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>19:55:15 IST</t>
+          <t>2026-08-10 15:13:13 IST</t>
         </is>
       </c>
       <c r="N53" s="4" t="n">
-        <v>1989.42</v>
+        <v>1090.9</v>
       </c>
       <c r="O53" s="4" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="P53" s="5" t="n">
-        <v>1979.47</v>
+        <v>1080.95</v>
       </c>
       <c r="Q53" s="5" t="n">
-        <v>3.98</v>
+        <v>2.17</v>
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
@@ -19150,39 +19148,39 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T53" s="3" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="U53" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&gt;Open</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V53" s="3" t="inlineStr">
         <is>
-          <t>{"Close": 700.390015, "Ret": 0.018024, "Low": 685.820007, "High": 701.590027, "Volume": 36459876.0, "EMA20": 696.896645, "SMA20": 699.896997, "2Red": 0.0, "EMA9": 689.142707, "RSI14": 50.141657, "SMA50": 714.8328, "Open": 688.340027, "EMA50": 699.878887}</t>
+          <t>{"Open": 162.0, "2Red": 1.0, "Low": 160.970001, "EMA50": 157.880967, "High": 162.490005, "Volume": 15121700.0, "Close": 162.100006, "SMA20": 161.822, "SMA50": 156.9082, "EMA9": 162.798107, "Ret": -0.000863, "RSI14": 53.812337, "EMA20": 161.631372}</t>
         </is>
       </c>
       <c r="W53" s="3" t="inlineStr">
         <is>
-          <t>#52SW Price&gt;SMA20+EMA9&lt;EMA20+Close&gt;Open | ðŸŽ¯ Target Hit (live)</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>23:32:54 IST</t>
+          <t>01:18:05 IST</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -19192,7 +19190,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -19202,45 +19200,45 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>745.84</v>
+        <v>700.39</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>738.38</v>
+        <v>686.38</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>760.76</v>
+        <v>728.41</v>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>757.5700000000001</v>
+        <v>728.41</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>23:00:00 IST</t>
+          <t>19:55:15 IST</t>
         </is>
       </c>
       <c r="N54" s="4" t="n">
-        <v>1395.87</v>
+        <v>1989.42</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>17.75</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>1378.12</v>
+        <v>1979.47</v>
       </c>
       <c r="Q54" s="5" t="n">
-        <v>1.55</v>
+        <v>3.98</v>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
@@ -19249,27 +19247,27 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>52</t>
         </is>
       </c>
       <c r="T54" s="3" t="inlineStr">
         <is>
-          <t>60.24</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="U54" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
+          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&gt;Open</t>
         </is>
       </c>
       <c r="V54" s="3" t="inlineStr">
         <is>
-          <t>{"EMA9": 741.70706, "Open": 744.429993, "Low": 743.98999, "Volume": 4072705.0, "RSI14": 62.13446, "Ret": 0.002512, "EMA50": 740.609545, "High": 746.400024, "SMA50": 739.652488, "2Red": 0.0, "SMA20": 738.535001, "EMA20": 740.044973, "Close": 746.289978}</t>
+          <t>{"Close": 700.390015, "Ret": 0.018024, "Low": 685.820007, "High": 701.590027, "Volume": 36459876.0, "EMA20": 696.896645, "SMA20": 699.896997, "2Red": 0.0, "EMA9": 689.142707, "RSI14": 50.141657, "SMA50": 714.8328, "Open": 688.340027, "EMA50": 699.878887}</t>
         </is>
       </c>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>#32ID Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | Expiry 6h</t>
+          <t>#52SW Price&gt;SMA20+EMA9&lt;EMA20+Close&gt;Open | ðŸŽ¯ Target Hit (live)</t>
         </is>
       </c>
     </row>
@@ -19281,7 +19279,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>21:47:39 IST</t>
+          <t>23:32:54 IST</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -19291,7 +19289,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -19305,16 +19303,16 @@
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>174.29</v>
+        <v>745.84</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>497</v>
+        <v>119</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>172.55</v>
+        <v>738.38</v>
       </c>
       <c r="J55" s="8" t="n">
-        <v>177.78</v>
+        <v>760.76</v>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
@@ -19322,24 +19320,24 @@
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>177.6</v>
+        <v>757.5700000000001</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>21:00:00 IST</t>
+          <t>23:00:00 IST</t>
         </is>
       </c>
       <c r="N55" s="4" t="n">
-        <v>1646.31</v>
+        <v>1395.87</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>17.32</v>
+        <v>17.75</v>
       </c>
       <c r="P55" s="5" t="n">
-        <v>1628.99</v>
+        <v>1378.12</v>
       </c>
       <c r="Q55" s="5" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
@@ -19348,27 +19346,27 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T55" s="3" t="inlineStr">
         <is>
-          <t>67.35</t>
+          <t>60.24</t>
         </is>
       </c>
       <c r="U55" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20</t>
+          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
         </is>
       </c>
       <c r="V55" s="3" t="inlineStr">
         <is>
-          <t>{"SMA20": 171.96953, "EMA9": 173.971593, "EMA20": 173.252314, "Ret": -0.00379, "SMA50": 174.765609, "High": 174.869995, "Volume": 1112891.0, "Close": 173.5, "Open": 174.179993, "2Red": 1.0, "RSI14": 50.495204, "Low": 173.100006, "EMA50": 174.378064}</t>
+          <t>{"EMA9": 741.70706, "Open": 744.429993, "Low": 743.98999, "Volume": 4072705.0, "RSI14": 62.13446, "Ret": 0.002512, "EMA50": 740.609545, "High": 746.400024, "SMA50": 739.652488, "2Red": 0.0, "SMA20": 738.535001, "EMA20": 740.044973, "Close": 746.289978}</t>
         </is>
       </c>
       <c r="W55" s="3" t="inlineStr">
         <is>
-          <t>#3ID Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20 | Expiry 6h</t>
+          <t>#32ID Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -19380,7 +19378,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>21:07:14 IST</t>
+          <t>21:47:39 IST</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -19404,16 +19402,16 @@
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>173.95</v>
+        <v>174.29</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>172.21</v>
+        <v>172.55</v>
       </c>
       <c r="J56" s="8" t="n">
-        <v>177.43</v>
+        <v>177.78</v>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
@@ -19421,24 +19419,24 @@
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>176.43</v>
+        <v>177.6</v>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>20:00:00 IST</t>
+          <t>21:00:00 IST</t>
         </is>
       </c>
       <c r="N56" s="4" t="n">
-        <v>1207.76</v>
+        <v>1646.31</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>16.94</v>
+        <v>17.32</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>1190.82</v>
+        <v>1628.99</v>
       </c>
       <c r="Q56" s="5" t="n">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
@@ -19462,7 +19460,7 @@
       </c>
       <c r="V56" s="3" t="inlineStr">
         <is>
-          <t>{"RSI14": 50.452183, "2Red": 1.0, "High": 174.869995, "EMA50": 174.377476, "Ret": -0.003876, "SMA50": 174.765309, "Low": 173.100006, "Close": 173.485001, "Volume": 1102438.0, "SMA20": 171.96878, "EMA20": 173.250885, "Open": 174.179993, "EMA9": 173.968593}</t>
+          <t>{"SMA20": 171.96953, "EMA9": 173.971593, "EMA20": 173.252314, "Ret": -0.00379, "SMA50": 174.765609, "High": 174.869995, "Volume": 1112891.0, "Close": 173.5, "Open": 174.179993, "2Red": 1.0, "RSI14": 50.495204, "Low": 173.100006, "EMA50": 174.378064}</t>
         </is>
       </c>
       <c r="W56" s="3" t="inlineStr">
@@ -19479,7 +19477,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>20:27:40 IST</t>
+          <t>21:07:14 IST</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -19503,16 +19501,16 @@
         </is>
       </c>
       <c r="G57" s="4" t="n">
-        <v>174.64</v>
+        <v>173.95</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>172.89</v>
+        <v>172.21</v>
       </c>
       <c r="J57" s="8" t="n">
-        <v>178.13</v>
+        <v>177.43</v>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
@@ -19520,24 +19518,24 @@
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>176.19</v>
+        <v>176.43</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>19:00:00 IST</t>
+          <t>20:00:00 IST</t>
         </is>
       </c>
       <c r="N57" s="4" t="n">
-        <v>759.5</v>
+        <v>1207.76</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>17.11</v>
+        <v>16.94</v>
       </c>
       <c r="P57" s="5" t="n">
-        <v>742.39</v>
-      </c>
-      <c r="Q57" s="12" t="n">
-        <v>0.87</v>
+        <v>1190.82</v>
+      </c>
+      <c r="Q57" s="5" t="n">
+        <v>1.41</v>
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
@@ -19561,7 +19559,7 @@
       </c>
       <c r="V57" s="3" t="inlineStr">
         <is>
-          <t>{"SMA20": 171.86253, "RSI14": 52.463695, "Ret": -0.008821, "EMA9": 174.089491, "2Red": 0.0, "Low": 172.699997, "Close": 174.160004, "SMA50": 174.896011, "EMA20": 173.226242, "EMA50": 174.413903, "Open": 177.460007, "Volume": 2974398.0, "High": 178.619995}</t>
+          <t>{"RSI14": 50.452183, "2Red": 1.0, "High": 174.869995, "EMA50": 174.377476, "Ret": -0.003876, "SMA50": 174.765309, "Low": 173.100006, "Close": 173.485001, "Volume": 1102438.0, "SMA20": 171.96878, "EMA20": 173.250885, "Open": 174.179993, "EMA9": 173.968593}</t>
         </is>
       </c>
       <c r="W57" s="3" t="inlineStr">
@@ -19578,7 +19576,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>02:09:08 IST</t>
+          <t>20:27:40 IST</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -19588,7 +19586,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -19602,16 +19600,16 @@
         </is>
       </c>
       <c r="G58" s="4" t="n">
-        <v>683.6</v>
+        <v>174.64</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>132</v>
+        <v>490</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>676.76</v>
+        <v>172.89</v>
       </c>
       <c r="J58" s="8" t="n">
-        <v>697.27</v>
+        <v>178.13</v>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
@@ -19619,21 +19617,21 @@
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>689.7</v>
+        <v>176.19</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>00:00:00 IST</t>
+          <t>19:00:00 IST</t>
         </is>
       </c>
       <c r="N58" s="4" t="n">
-        <v>805.2</v>
+        <v>759.5</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>18.05</v>
+        <v>17.11</v>
       </c>
       <c r="P58" s="5" t="n">
-        <v>787.15</v>
+        <v>742.39</v>
       </c>
       <c r="Q58" s="12" t="n">
         <v>0.87</v>
@@ -19645,27 +19643,27 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T58" s="3" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>67.35</t>
         </is>
       </c>
       <c r="U58" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50</t>
+          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20</t>
         </is>
       </c>
       <c r="V58" s="3" t="inlineStr">
         <is>
-          <t>{"Volume": 10064291.0, "SMA20": 675.475238, "EMA20": 678.396981, "EMA50": 684.292339, "Close": 683.599976, "Low": 682.900024, "Open": 683.820007, "High": 684.349976, "Ret": -0.000351, "SMA50": 685.204755, "2Red": 0.0, "RSI14": 54.801846, "EMA9": 679.813964}</t>
+          <t>{"SMA20": 171.86253, "RSI14": 52.463695, "Ret": -0.008821, "EMA9": 174.089491, "2Red": 0.0, "Low": 172.699997, "Close": 174.160004, "SMA50": 174.896011, "EMA20": 173.226242, "EMA50": 174.413903, "Open": 177.460007, "Volume": 2974398.0, "High": 178.619995}</t>
         </is>
       </c>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>#5ID Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50 | Expiry 6h</t>
+          <t>#3ID Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20 | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -19687,7 +19685,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -19701,16 +19699,16 @@
         </is>
       </c>
       <c r="G59" s="4" t="n">
-        <v>741.73</v>
+        <v>683.6</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>734.3099999999999</v>
+        <v>676.76</v>
       </c>
       <c r="J59" s="8" t="n">
-        <v>756.5599999999999</v>
+        <v>697.27</v>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
@@ -19718,7 +19716,7 @@
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>747.49</v>
+        <v>689.7</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
@@ -19726,16 +19724,16 @@
         </is>
       </c>
       <c r="N59" s="4" t="n">
-        <v>696.96</v>
+        <v>805.2</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>17.95</v>
+        <v>18.05</v>
       </c>
       <c r="P59" s="5" t="n">
-        <v>679.01</v>
+        <v>787.15</v>
       </c>
       <c r="Q59" s="12" t="n">
-        <v>0.76</v>
+        <v>0.87</v>
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
@@ -19744,27 +19742,27 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T59" s="3" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>63.38</t>
         </is>
       </c>
       <c r="U59" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open</t>
+          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50</t>
         </is>
       </c>
       <c r="V59" s="3" t="inlineStr">
         <is>
-          <t>{"Volume": 12583754.0, "SMA20": 738.175507, "EMA20": 738.518298, "EMA50": 740.197673, "Close": 741.72998, "Low": 741.0, "Open": 741.77002, "High": 742.099976, "Ret": -6.7e-05, "SMA50": 740.120288, "2Red": 0.0, "RSI14": 55.502244, "EMA9": 739.15355}</t>
+          <t>{"Volume": 10064291.0, "SMA20": 675.475238, "EMA20": 678.396981, "EMA50": 684.292339, "Close": 683.599976, "Low": 682.900024, "Open": 683.820007, "High": 684.349976, "Ret": -0.000351, "SMA50": 685.204755, "2Red": 0.0, "RSI14": 54.801846, "EMA9": 679.813964}</t>
         </is>
       </c>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>#31ID Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open | Expiry 6h</t>
+          <t>#5ID Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50 | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -19776,7 +19774,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>01:14:10 IST</t>
+          <t>02:09:08 IST</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -19786,7 +19784,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -19800,16 +19798,16 @@
         </is>
       </c>
       <c r="G60" s="4" t="n">
-        <v>683.6900000000001</v>
+        <v>741.73</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="I60" s="8" t="n">
-        <v>676.85</v>
+        <v>734.3099999999999</v>
       </c>
       <c r="J60" s="8" t="n">
-        <v>697.36</v>
+        <v>756.5599999999999</v>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
@@ -19817,7 +19815,7 @@
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>689.7</v>
+        <v>747.49</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -19825,16 +19823,16 @@
         </is>
       </c>
       <c r="N60" s="4" t="n">
-        <v>805.34</v>
+        <v>696.96</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>18.32</v>
+        <v>17.95</v>
       </c>
       <c r="P60" s="5" t="n">
-        <v>787.02</v>
+        <v>679.01</v>
       </c>
       <c r="Q60" s="12" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
@@ -19843,39 +19841,39 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T60" s="3" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="U60" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50</t>
+          <t>Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open</t>
         </is>
       </c>
       <c r="V60" s="3" t="inlineStr">
         <is>
-          <t>{"Volume": 6303349.0, "Ret": 0.002213, "EMA20": 677.849297, "EMA9": 678.867461, "2Red": 0.0, "SMA50": 685.700555, "SMA20": 674.813739, "Low": 681.51001, "EMA50": 684.320598, "Open": 682.325012, "High": 685.119995, "RSI14": 55.076392, "Close": 683.840027}</t>
+          <t>{"Volume": 12583754.0, "SMA20": 738.175507, "EMA20": 738.518298, "EMA50": 740.197673, "Close": 741.72998, "Low": 741.0, "Open": 741.77002, "High": 742.099976, "Ret": -6.7e-05, "SMA50": 740.120288, "2Red": 0.0, "RSI14": 55.502244, "EMA9": 739.15355}</t>
         </is>
       </c>
       <c r="W60" s="3" t="inlineStr">
         <is>
-          <t>#5ID Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50 | Expiry 6h</t>
+          <t>#31ID Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open | Expiry 6h</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>22:16:13 IST</t>
+          <t>01:14:10 IST</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -19885,7 +19883,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -19899,16 +19897,16 @@
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>517.88</v>
+        <v>683.6900000000001</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>512.7</v>
+        <v>676.85</v>
       </c>
       <c r="J61" s="8" t="n">
-        <v>528.24</v>
+        <v>697.36</v>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
@@ -19916,24 +19914,24 @@
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>519.65</v>
+        <v>689.7</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>21:00:00 IST</t>
+          <t>00:00:00 IST</t>
         </is>
       </c>
       <c r="N61" s="4" t="n">
-        <v>316.83</v>
+        <v>805.34</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>18.54</v>
+        <v>18.32</v>
       </c>
       <c r="P61" s="5" t="n">
-        <v>298.29</v>
+        <v>787.02</v>
       </c>
       <c r="Q61" s="12" t="n">
-        <v>0.32</v>
+        <v>0.86</v>
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
@@ -19942,23 +19940,27 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T61" s="3" t="inlineStr">
         <is>
-          <t>60.16</t>
+          <t>63.38</t>
         </is>
       </c>
       <c r="U61" s="3" t="inlineStr">
         <is>
-          <t>RSI&lt;45+EMA20&gt;EMA50+Close&lt;Open+2Red</t>
-        </is>
-      </c>
-      <c r="V61" s="3" t="inlineStr"/>
+          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50</t>
+        </is>
+      </c>
+      <c r="V61" s="3" t="inlineStr">
+        <is>
+          <t>{"Volume": 6303349.0, "Ret": 0.002213, "EMA20": 677.849297, "EMA9": 678.867461, "2Red": 0.0, "SMA50": 685.700555, "SMA20": 674.813739, "Low": 681.51001, "EMA50": 684.320598, "Open": 682.325012, "High": 685.119995, "RSI14": 55.076392, "Close": 683.840027}</t>
+        </is>
+      </c>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>#13ID RSI&lt;45+EMA20&gt;EMA50+Close&lt;Open+2Red | Expiry 6h</t>
+          <t>#5ID Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50 | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -19970,7 +19972,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>21:32:32 IST</t>
+          <t>22:16:13 IST</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -19994,16 +19996,16 @@
         </is>
       </c>
       <c r="G62" s="4" t="n">
-        <v>517.9</v>
+        <v>517.88</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I62" s="8" t="n">
-        <v>512.72</v>
+        <v>512.7</v>
       </c>
       <c r="J62" s="8" t="n">
-        <v>528.26</v>
+        <v>528.24</v>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
@@ -20019,13 +20021,13 @@
         </is>
       </c>
       <c r="N62" s="4" t="n">
-        <v>316.75</v>
+        <v>316.83</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>18.75</v>
+        <v>18.54</v>
       </c>
       <c r="P62" s="5" t="n">
-        <v>298</v>
+        <v>298.29</v>
       </c>
       <c r="Q62" s="12" t="n">
         <v>0.32</v>
@@ -20037,23 +20039,23 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>13</t>
         </is>
       </c>
       <c r="T62" s="3" t="inlineStr">
         <is>
-          <t>67.86</t>
+          <t>60.16</t>
         </is>
       </c>
       <c r="U62" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red</t>
+          <t>RSI&lt;45+EMA20&gt;EMA50+Close&lt;Open+2Red</t>
         </is>
       </c>
       <c r="V62" s="3" t="inlineStr"/>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>#36ID Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red | Expiry 6h</t>
+          <t>#13ID RSI&lt;45+EMA20&gt;EMA50+Close&lt;Open+2Red | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -20065,7 +20067,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>20:59:02 IST</t>
+          <t>21:32:32 IST</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -20089,16 +20091,16 @@
         </is>
       </c>
       <c r="G63" s="4" t="n">
-        <v>518.55</v>
+        <v>517.9</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I63" s="8" t="n">
-        <v>513.37</v>
+        <v>512.72</v>
       </c>
       <c r="J63" s="8" t="n">
-        <v>528.9299999999999</v>
+        <v>528.26</v>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
@@ -20106,24 +20108,24 @@
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>516.52</v>
+        <v>519.65</v>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>20:00:00 IST</t>
+          <t>21:00:00 IST</t>
         </is>
       </c>
       <c r="N63" s="4" t="n">
-        <v>-372.4</v>
+        <v>316.75</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>18.98</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v>-391.38</v>
-      </c>
-      <c r="Q63" s="13" t="n">
-        <v>-0.41</v>
+        <v>18.75</v>
+      </c>
+      <c r="P63" s="5" t="n">
+        <v>298</v>
+      </c>
+      <c r="Q63" s="12" t="n">
+        <v>0.32</v>
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
@@ -20160,7 +20162,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>20:11:02 IST</t>
+          <t>20:59:02 IST</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -20184,16 +20186,16 @@
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>518.47</v>
+        <v>518.55</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I64" s="8" t="n">
-        <v>513.28</v>
+        <v>513.37</v>
       </c>
       <c r="J64" s="8" t="n">
-        <v>528.83</v>
+        <v>528.9299999999999</v>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
@@ -20201,24 +20203,24 @@
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>518.47</v>
+        <v>516.52</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>19:00:00 IST</t>
-        </is>
-      </c>
-      <c r="N64" s="10" t="n">
-        <v>-0.92</v>
+          <t>20:00:00 IST</t>
+        </is>
+      </c>
+      <c r="N64" s="4" t="n">
+        <v>-372.4</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>19.08</v>
+        <v>18.98</v>
       </c>
       <c r="P64" s="6" t="n">
-        <v>-20</v>
+        <v>-391.38</v>
       </c>
       <c r="Q64" s="13" t="n">
-        <v>-0.02</v>
+        <v>-0.41</v>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
@@ -20255,7 +20257,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>01:14:16 IST</t>
+          <t>20:11:02 IST</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -20265,7 +20267,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -20279,16 +20281,16 @@
         </is>
       </c>
       <c r="G65" s="4" t="n">
-        <v>741.2</v>
+        <v>518.47</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>133</v>
+        <v>184</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>733.79</v>
+        <v>513.28</v>
       </c>
       <c r="J65" s="8" t="n">
-        <v>756.02</v>
+        <v>528.83</v>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
@@ -20296,24 +20298,24 @@
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>733.79</v>
+        <v>518.47</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>20:00:00 IST</t>
-        </is>
-      </c>
-      <c r="N65" s="4" t="n">
-        <v>-985.53</v>
+          <t>19:00:00 IST</t>
+        </is>
+      </c>
+      <c r="N65" s="10" t="n">
+        <v>-0.92</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>19.72</v>
+        <v>19.08</v>
       </c>
       <c r="P65" s="6" t="n">
-        <v>-1005.25</v>
-      </c>
-      <c r="Q65" s="6" t="n">
-        <v>-1.02</v>
+        <v>-20</v>
+      </c>
+      <c r="Q65" s="13" t="n">
+        <v>-0.02</v>
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
@@ -20322,35 +20324,35 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T65" s="3" t="inlineStr">
         <is>
-          <t>60.24</t>
+          <t>67.86</t>
         </is>
       </c>
       <c r="U65" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
+          <t>Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red</t>
         </is>
       </c>
       <c r="V65" s="3" t="inlineStr"/>
       <c r="W65" s="3" t="inlineStr">
         <is>
-          <t>#32ID Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | SL Hit</t>
+          <t>#36ID Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red | Expiry 6h</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>23:22:38 IST</t>
+          <t>01:14:16 IST</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -20360,12 +20362,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -20374,16 +20376,16 @@
         </is>
       </c>
       <c r="G66" s="4" t="n">
-        <v>293.1</v>
+        <v>741.2</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>337</v>
+        <v>133</v>
       </c>
       <c r="I66" s="8" t="n">
-        <v>296.03</v>
+        <v>733.79</v>
       </c>
       <c r="J66" s="8" t="n">
-        <v>287.24</v>
+        <v>756.02</v>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
@@ -20391,24 +20393,24 @@
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>289.59</v>
+        <v>733.79</v>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>22:00:00 IST</t>
+          <t>20:00:00 IST</t>
         </is>
       </c>
       <c r="N66" s="4" t="n">
-        <v>1182.87</v>
+        <v>-985.53</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="P66" s="5" t="n">
-        <v>1163.12</v>
-      </c>
-      <c r="Q66" s="5" t="n">
-        <v>1.18</v>
+        <v>19.72</v>
+      </c>
+      <c r="P66" s="6" t="n">
+        <v>-1005.25</v>
+      </c>
+      <c r="Q66" s="6" t="n">
+        <v>-1.02</v>
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
@@ -20417,35 +20419,35 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T66" s="3" t="inlineStr">
         <is>
-          <t>63.41</t>
+          <t>60.24</t>
         </is>
       </c>
       <c r="U66" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
+          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
         </is>
       </c>
       <c r="V66" s="3" t="inlineStr"/>
       <c r="W66" s="3" t="inlineStr">
         <is>
-          <t>#14ID Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | Expiry 6h</t>
+          <t>#32ID Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | SL Hit</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>23:32:56 IST</t>
+          <t>23:22:38 IST</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -20455,12 +20457,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -20469,16 +20471,16 @@
         </is>
       </c>
       <c r="G67" s="4" t="n">
-        <v>520.27</v>
+        <v>293.1</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>191</v>
+        <v>337</v>
       </c>
       <c r="I67" s="8" t="n">
-        <v>515.0599999999999</v>
+        <v>296.03</v>
       </c>
       <c r="J67" s="8" t="n">
-        <v>530.67</v>
+        <v>287.24</v>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
@@ -20486,24 +20488,24 @@
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>526.96</v>
+        <v>289.59</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>23:00:00 IST</t>
+          <t>22:00:00 IST</t>
         </is>
       </c>
       <c r="N67" s="4" t="n">
-        <v>1277.79</v>
+        <v>1182.87</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>19.87</v>
+        <v>19.75</v>
       </c>
       <c r="P67" s="5" t="n">
-        <v>1257.92</v>
+        <v>1163.12</v>
       </c>
       <c r="Q67" s="5" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
@@ -20512,67 +20514,162 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T67" s="3" t="inlineStr">
         <is>
-          <t>67.86</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="U67" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red</t>
+          <t>Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
         </is>
       </c>
       <c r="V67" s="3" t="inlineStr"/>
       <c r="W67" s="3" t="inlineStr">
         <is>
+          <t>#14ID Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | Expiry 6h</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>23:32:56 IST</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>DIA</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>INTRADAY_1h</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>520.27</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>191</v>
+      </c>
+      <c r="I68" s="8" t="n">
+        <v>515.0599999999999</v>
+      </c>
+      <c r="J68" s="8" t="n">
+        <v>530.67</v>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>526.96</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>23:00:00 IST</t>
+        </is>
+      </c>
+      <c r="N68" s="4" t="n">
+        <v>1277.79</v>
+      </c>
+      <c r="O68" s="4" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="P68" s="5" t="n">
+        <v>1257.92</v>
+      </c>
+      <c r="Q68" s="5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="T68" s="3" t="inlineStr">
+        <is>
+          <t>67.86</t>
+        </is>
+      </c>
+      <c r="U68" s="3" t="inlineStr">
+        <is>
+          <t>Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red</t>
+        </is>
+      </c>
+      <c r="V68" s="3" t="inlineStr"/>
+      <c r="W68" s="3" t="inlineStr">
+        <is>
           <t>#36ID Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red | Expiry 6h</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="14" t="inlineStr"/>
-      <c r="B68" s="14" t="inlineStr"/>
-      <c r="C68" s="15" t="inlineStr"/>
-      <c r="D68" s="15" t="inlineStr"/>
-      <c r="E68" s="15" t="inlineStr"/>
-      <c r="F68" s="15" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="14" t="inlineStr"/>
+      <c r="B69" s="14" t="inlineStr"/>
+      <c r="C69" s="15" t="inlineStr"/>
+      <c r="D69" s="15" t="inlineStr"/>
+      <c r="E69" s="15" t="inlineStr"/>
+      <c r="F69" s="15" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="G68" s="16" t="inlineStr"/>
-      <c r="H68" s="16" t="inlineStr"/>
-      <c r="I68" s="15" t="inlineStr"/>
-      <c r="J68" s="15" t="inlineStr"/>
-      <c r="K68" s="14" t="inlineStr"/>
-      <c r="L68" s="15" t="inlineStr"/>
-      <c r="M68" s="14" t="inlineStr"/>
-      <c r="N68" s="17" t="n">
+      <c r="G69" s="16" t="inlineStr"/>
+      <c r="H69" s="16" t="inlineStr"/>
+      <c r="I69" s="15" t="inlineStr"/>
+      <c r="J69" s="15" t="inlineStr"/>
+      <c r="K69" s="14" t="inlineStr"/>
+      <c r="L69" s="15" t="inlineStr"/>
+      <c r="M69" s="14" t="inlineStr"/>
+      <c r="N69" s="17" t="n">
         <v>25910.85</v>
       </c>
-      <c r="O68" s="17" t="n">
+      <c r="O69" s="17" t="n">
         <v>2459.59</v>
       </c>
-      <c r="P68" s="18" t="n">
+      <c r="P69" s="18" t="n">
         <v>23451.26</v>
       </c>
-      <c r="Q68" s="16" t="inlineStr"/>
-      <c r="R68" s="15" t="inlineStr">
-        <is>
-          <t>66 trades (62 closed / 4 open)</t>
-        </is>
-      </c>
-      <c r="S68" s="15" t="inlineStr"/>
-      <c r="T68" s="14" t="inlineStr"/>
-      <c r="U68" s="14" t="inlineStr"/>
-      <c r="V68" s="14" t="inlineStr"/>
-      <c r="W68" s="14" t="inlineStr"/>
+      <c r="Q69" s="16" t="inlineStr"/>
+      <c r="R69" s="15" t="inlineStr">
+        <is>
+          <t>67 trades (62 closed / 5 open)</t>
+        </is>
+      </c>
+      <c r="S69" s="15" t="inlineStr"/>
+      <c r="T69" s="14" t="inlineStr"/>
+      <c r="U69" s="14" t="inlineStr"/>
+      <c r="V69" s="14" t="inlineStr"/>
+      <c r="W69" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W67"/>
+  <autoFilter ref="A1:W68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -2323,17 +2323,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>#1ID LINK-USD SHORT</t>
+          <t>#1SW TRX-USD LONG</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>LINK-USD</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2343,46 +2343,46 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+RSI&lt;45</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>50.43</v>
+        <v>66.67</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>18.05</v>
+        <v>51.86</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0</v>
+        <v>-27.64</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="4" t="n">
-        <v>0</v>
+        <v>40.12</v>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v>-67.76000000000001</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0</v>
+        <v>-16.94</v>
       </c>
     </row>
     <row r="28">
@@ -2391,17 +2391,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>#1SW TRX-USD LONG</t>
+          <t>#1ID DOGE-USD SHORT</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>DOGE-USD</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2411,46 +2411,46 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>Price&gt;SMA20+RSI&lt;45</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>66.67</v>
+        <v>50.67</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>51.86</v>
+        <v>31.42</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="N28" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-27.64</v>
+        <v>-88.45</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>40.12</v>
+        <v>12.57</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>-67.76000000000001</v>
+        <v>-101.02</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-16.94</v>
+        <v>-101.02</v>
       </c>
     </row>
     <row r="29">
@@ -2459,66 +2459,66 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>#1ID DOGE-USD SHORT</t>
+          <t>#5SW XLP LONG</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>DOGE-USD</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+RSI&lt;45</t>
+          <t>Range&lt;1%+SMA20&lt;EMA20</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>50.67</v>
+        <v>58.26</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>31.42</v>
+        <v>67.47</v>
       </c>
       <c r="J29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-88.45</v>
+        <v>-149.74</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>12.57</v>
+        <v>20.27</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>-101.02</v>
+        <v>-170.01</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-101.02</v>
+        <v>-85</v>
       </c>
     </row>
     <row r="30">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>#5SW XLP LONG</t>
+          <t>#57SW XLRE LONG</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2552,41 +2552,41 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Range&lt;1%+SMA20&lt;EMA20</t>
+          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&lt;Open</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>58.26</v>
+        <v>69.23</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>67.47</v>
+        <v>16.84</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-149.74</v>
+        <v>-469.04</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>20.27</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>-170.01</v>
+        <v>-479</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-85</v>
+        <v>-479</v>
       </c>
     </row>
     <row r="31">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>#57SW XLRE LONG</t>
+          <t>#3SW XLC LONG</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2620,20 +2620,20 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&lt;Open</t>
+          <t>Price&gt;EMA9+Range&lt;1%</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>69.23</v>
+        <v>53.98</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16.84</v>
+        <v>68.92</v>
       </c>
       <c r="J31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2645,16 +2645,16 @@
         <v>0</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-469.04</v>
+        <v>-750.65</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>10.32</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>-479</v>
+        <v>-760.97</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-479</v>
+        <v>-760.97</v>
       </c>
     </row>
     <row r="32">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>#3SW XLC LONG</t>
+          <t>#31SW QQQ LONG</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2688,20 +2688,20 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;EMA9+Range&lt;1%</t>
+          <t>Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>53.98</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>68.92</v>
+        <v>48.57</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2713,16 +2713,16 @@
         <v>0</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-750.65</v>
+        <v>-865.8099999999999</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.32</v>
+        <v>10.46</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>-760.97</v>
+        <v>-876.27</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-760.97</v>
+        <v>-876.27</v>
       </c>
     </row>
     <row r="33">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>#31SW QQQ LONG</t>
+          <t>#4SW OEF LONG</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2756,41 +2756,41 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+2Red</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>65.29000000000001</v>
+        <v>59.53</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>48.57</v>
+        <v>109.78</v>
       </c>
       <c r="J33" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K33" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-865.8099999999999</v>
+        <v>-982.38</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>10.46</v>
+        <v>50.18</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>-876.27</v>
+        <v>-1032.56</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-876.27</v>
+        <v>-206.51</v>
       </c>
     </row>
     <row r="34">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>#4SW OEF LONG</t>
+          <t>#5SW KBE LONG</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2824,41 +2824,41 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>EMA9&lt;EMA50+Price&gt;EMA50</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>59.53</v>
+        <v>50.67</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>109.78</v>
+        <v>17.55</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="N34" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-982.38</v>
+        <v>-1039.2</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>50.18</v>
+        <v>10.29</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>-1032.56</v>
+        <v>-1049.49</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-206.51</v>
+        <v>-1049.49</v>
       </c>
     </row>
     <row r="35">
@@ -2867,39 +2867,39 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>#5SW KBE LONG</t>
+          <t>#1ID LINK-USD SHORT</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>LINK-USD</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>EMA9&lt;EMA50+Price&gt;EMA50</t>
+          <t>Price&gt;SMA20+RSI&lt;45</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>50.67</v>
+        <v>50.43</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17.55</v>
+        <v>18.05</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>1</v>
@@ -2917,16 +2917,16 @@
         <v>0</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-1039.2</v>
+        <v>-2489.46</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>10.29</v>
+        <v>360.6</v>
       </c>
       <c r="Q35" s="6" t="n">
-        <v>-1049.49</v>
+        <v>-2850.06</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-1049.49</v>
+        <v>-2850.06</v>
       </c>
     </row>
     <row r="36">
@@ -14082,27 +14082,29 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
+      <c r="L2" s="2" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17 01:54:37 IST</t>
+        </is>
+      </c>
       <c r="N2" s="4" t="n">
-        <v>-1150.61</v>
+        <v>-2489.46</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>360.6</v>
       </c>
-      <c r="P2" s="9" t="inlineStr">
-        <is>
-          <t>~-1,511.21 (unrealized)</t>
-        </is>
-      </c>
-      <c r="Q2" s="9" t="inlineStr">
-        <is>
-          <t>~-0.96%</t>
-        </is>
+      <c r="P2" s="6" t="n">
+        <v>-2850.06</v>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v>-2.37</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -14127,7 +14129,7 @@
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>#1ID Price&gt;SMA20+RSI&lt;45</t>
+          <t>#1ID Price&gt;SMA20+RSI&lt;45 | 🎯 SL Hit (live)</t>
         </is>
       </c>
     </row>
@@ -20745,18 +20747,18 @@
       <c r="L70" s="15" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
       <c r="N70" s="17" t="n">
-        <v>25910.85</v>
+        <v>23421.39</v>
       </c>
       <c r="O70" s="17" t="n">
-        <v>2459.59</v>
+        <v>2820.19</v>
       </c>
       <c r="P70" s="18" t="n">
-        <v>23451.26</v>
+        <v>20601.2</v>
       </c>
       <c r="Q70" s="16" t="inlineStr"/>
       <c r="R70" s="15" t="inlineStr">
         <is>
-          <t>68 trades (62 closed / 6 open)</t>
+          <t>68 trades (63 closed / 5 open)</t>
         </is>
       </c>
       <c r="S70" s="15" t="inlineStr"/>

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14184,19 +14184,19 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="4" t="n">
-        <v>-105.08</v>
+        <v>56.8</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>10.44</v>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>~-115.52 (unrealized)</t>
+          <t>~46.36 (unrealized)</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>~-0.20%</t>
+          <t>~+0.11%</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -14281,19 +14281,19 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="4" t="n">
-        <v>-912.42</v>
+        <v>-761.72</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>~-922.84 (unrealized)</t>
+          <t>~-772.14 (unrealized)</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>~-1.75%</t>
+          <t>~-1.46%</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -14378,19 +14378,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>33.55</v>
+        <v>181.74</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~23.05 (unrealized)</t>
+          <t>~171.24 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~+0.06%</t>
+          <t>~+0.35%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -14475,19 +14475,19 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="4" t="n">
-        <v>-18.81</v>
+        <v>-37.62</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P6" s="9" t="inlineStr">
         <is>
-          <t>~-29.27 (unrealized)</t>
+          <t>~-48.08 (unrealized)</t>
         </is>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
-          <t>~-0.04%</t>
+          <t>~-0.07%</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -14572,19 +14572,19 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="4" t="n">
-        <v>-41.56</v>
+        <v>-35.1</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>~-51.74 (unrealized)</t>
+          <t>~-45.28 (unrealized)</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>~-1.22%</t>
+          <t>~-1.03%</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14572,19 +14572,19 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="4" t="n">
-        <v>-35.1</v>
+        <v>-36.77</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>~-45.28 (unrealized)</t>
+          <t>~-46.95 (unrealized)</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>~-1.03%</t>
+          <t>~-1.08%</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -2323,17 +2323,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>#1ID XRP-USD SHORT</t>
+          <t>#1SW TRX-USD LONG</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>XRP-USD</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2343,46 +2343,46 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+RSI&lt;45</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>48.15</v>
+        <v>66.67</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>5.91</v>
+        <v>51.86</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0</v>
+        <v>-27.64</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="4" t="n">
-        <v>0</v>
+        <v>40.12</v>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v>-67.76000000000001</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0</v>
+        <v>-16.94</v>
       </c>
     </row>
     <row r="28">
@@ -2391,17 +2391,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>#1SW TRX-USD LONG</t>
+          <t>#1ID DOGE-USD SHORT</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>DOGE-USD</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2411,46 +2411,46 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>Price&gt;SMA20+RSI&lt;45</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>66.67</v>
+        <v>50.67</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>51.86</v>
+        <v>31.42</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="N28" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-27.64</v>
+        <v>-88.45</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>40.12</v>
+        <v>12.57</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>-67.76000000000001</v>
+        <v>-101.02</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-16.94</v>
+        <v>-101.02</v>
       </c>
     </row>
     <row r="29">
@@ -2459,66 +2459,66 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>#1ID DOGE-USD SHORT</t>
+          <t>#5SW XLP LONG</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>DOGE-USD</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+RSI&lt;45</t>
+          <t>Range&lt;1%+SMA20&lt;EMA20</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>50.67</v>
+        <v>58.26</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>31.42</v>
+        <v>67.47</v>
       </c>
       <c r="J29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-88.45</v>
+        <v>-149.74</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>12.57</v>
+        <v>20.27</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>-101.02</v>
+        <v>-170.01</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-101.02</v>
+        <v>-85</v>
       </c>
     </row>
     <row r="30">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>#5SW XLP LONG</t>
+          <t>#57SW XLRE LONG</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2552,41 +2552,41 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Range&lt;1%+SMA20&lt;EMA20</t>
+          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&lt;Open</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>58.26</v>
+        <v>69.23</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>67.47</v>
+        <v>16.84</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-149.74</v>
+        <v>-469.04</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>20.27</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>-170.01</v>
+        <v>-479</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-85</v>
+        <v>-479</v>
       </c>
     </row>
     <row r="31">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>#57SW XLRE LONG</t>
+          <t>#3SW XLC LONG</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2620,20 +2620,20 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&lt;Open</t>
+          <t>Price&gt;EMA9+Range&lt;1%</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>69.23</v>
+        <v>53.98</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16.84</v>
+        <v>68.92</v>
       </c>
       <c r="J31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2645,16 +2645,16 @@
         <v>0</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-469.04</v>
+        <v>-750.65</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>10.32</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>-479</v>
+        <v>-760.97</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-479</v>
+        <v>-760.97</v>
       </c>
     </row>
     <row r="32">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>#3SW XLC LONG</t>
+          <t>#31SW QQQ LONG</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2688,20 +2688,20 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;EMA9+Range&lt;1%</t>
+          <t>Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>53.98</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>68.92</v>
+        <v>48.57</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2713,16 +2713,16 @@
         <v>0</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-750.65</v>
+        <v>-865.8099999999999</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.32</v>
+        <v>10.46</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>-760.97</v>
+        <v>-876.27</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-760.97</v>
+        <v>-876.27</v>
       </c>
     </row>
     <row r="33">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>#31SW QQQ LONG</t>
+          <t>#4SW OEF LONG</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2756,41 +2756,41 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+2Red</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>65.29000000000001</v>
+        <v>59.53</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>48.57</v>
+        <v>109.78</v>
       </c>
       <c r="J33" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K33" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-865.8099999999999</v>
+        <v>-982.38</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>10.46</v>
+        <v>50.18</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>-876.27</v>
+        <v>-1032.56</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-876.27</v>
+        <v>-206.51</v>
       </c>
     </row>
     <row r="34">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>#4SW OEF LONG</t>
+          <t>#5SW KBE LONG</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2824,41 +2824,41 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>EMA9&lt;EMA50+Price&gt;EMA50</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>59.53</v>
+        <v>50.67</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>109.78</v>
+        <v>17.55</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="N34" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-982.38</v>
+        <v>-1039.2</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>50.18</v>
+        <v>10.29</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>-1032.56</v>
+        <v>-1049.49</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-206.51</v>
+        <v>-1049.49</v>
       </c>
     </row>
     <row r="35">
@@ -2867,39 +2867,39 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>#5SW KBE LONG</t>
+          <t>#1ID LINK-USD SHORT</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>LINK-USD</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>EMA9&lt;EMA50+Price&gt;EMA50</t>
+          <t>Price&gt;SMA20+RSI&lt;45</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>50.67</v>
+        <v>50.43</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17.55</v>
+        <v>18.05</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>1</v>
@@ -2917,16 +2917,16 @@
         <v>0</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-1039.2</v>
+        <v>-2489.46</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>10.29</v>
+        <v>360.6</v>
       </c>
       <c r="Q35" s="6" t="n">
-        <v>-1049.49</v>
+        <v>-2850.06</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-1049.49</v>
+        <v>-2850.06</v>
       </c>
     </row>
     <row r="36">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>#1ID LINK-USD SHORT</t>
+          <t>#1ID XRP-USD SHORT</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>LINK-USD</t>
+          <t>XRP-USD</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>50.43</v>
+        <v>48.15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>18.05</v>
+        <v>5.91</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>1</v>
@@ -2985,16 +2985,16 @@
         <v>0</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>-2489.46</v>
+        <v>-2502.38</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>360.6</v>
+        <v>402.06</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>-2850.06</v>
+        <v>-2904.44</v>
       </c>
       <c r="R36" s="4" t="n">
-        <v>-2850.06</v>
+        <v>-2904.44</v>
       </c>
     </row>
     <row r="37">
@@ -14082,27 +14082,29 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
+      <c r="L2" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17 05:11:30 IST</t>
+        </is>
+      </c>
       <c r="N2" s="4" t="n">
-        <v>-649.16</v>
+        <v>-2502.38</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>402.06</v>
       </c>
-      <c r="P2" s="9" t="inlineStr">
-        <is>
-          <t>~-1,051.22 (unrealized)</t>
-        </is>
-      </c>
-      <c r="Q2" s="9" t="inlineStr">
-        <is>
-          <t>~-0.48%</t>
-        </is>
+      <c r="P2" s="6" t="n">
+        <v>-2904.44</v>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v>-2.17</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -14127,7 +14129,7 @@
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>#1ID Price&gt;SMA20+RSI&lt;45</t>
+          <t>#1ID Price&gt;SMA20+RSI&lt;45 | 🎯 SL Hit (live)</t>
         </is>
       </c>
     </row>
@@ -20941,18 +20943,18 @@
       <c r="L72" s="15" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
       <c r="N72" s="17" t="n">
-        <v>23421.39</v>
+        <v>20919.01</v>
       </c>
       <c r="O72" s="17" t="n">
-        <v>2820.19</v>
+        <v>3222.25</v>
       </c>
       <c r="P72" s="18" t="n">
-        <v>20601.2</v>
+        <v>17696.76</v>
       </c>
       <c r="Q72" s="16" t="inlineStr"/>
       <c r="R72" s="15" t="inlineStr">
         <is>
-          <t>70 trades (63 closed / 7 open)</t>
+          <t>70 trades (64 closed / 6 open)</t>
         </is>
       </c>
       <c r="S72" s="15" t="inlineStr"/>

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -759,45 +759,45 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>#1ID SOL-USD SHORT</t>
+          <t>#3SW XLE LONG</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>SOL-USD</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
+          <t>EMA9&gt;EMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>47.24</v>
+        <v>51.28</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>23.69</v>
+        <v>18.74</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>2</v>
@@ -809,16 +809,16 @@
         <v>100</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>3782.21</v>
+        <v>2085.52</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>573.08</v>
+        <v>20.2</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>3209.13</v>
+        <v>2065.32</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>1604.57</v>
+        <v>1032.66</v>
       </c>
     </row>
     <row r="5">
@@ -827,7 +827,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>#3SW XLE LONG</t>
+          <t>#52SW QQQ LONG</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -852,23 +852,23 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA50+Range&lt;1%</t>
+          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&gt;Open</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>51.28</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>18.74</v>
+        <v>18.68</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>0</v>
@@ -877,16 +877,16 @@
         <v>100</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>2085.52</v>
+        <v>1989.42</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>20.2</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>2065.32</v>
+        <v>1979.47</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>1032.66</v>
+        <v>1979.47</v>
       </c>
     </row>
     <row r="6">
@@ -895,12 +895,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>#52SW QQQ LONG</t>
+          <t>#5ID QQQ LONG</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -920,23 +920,23 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&gt;Open</t>
+          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>71.43000000000001</v>
+        <v>63.38</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>18.68</v>
+        <v>11.65</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>0</v>
@@ -945,16 +945,16 @@
         <v>100</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>1989.42</v>
+        <v>1610.54</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>36.37</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>1979.47</v>
+        <v>1574.17</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>1979.47</v>
+        <v>787.09</v>
       </c>
     </row>
     <row r="7">
@@ -963,17 +963,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>#5ID QQQ LONG</t>
+          <t>#28SW XLK LONG</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -988,20 +988,20 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50</t>
+          <t>Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>63.38</v>
+        <v>63.73</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>11.65</v>
+        <v>50.46</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>2</v>
@@ -1013,16 +1013,16 @@
         <v>100</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1610.54</v>
+        <v>1450.08</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>36.37</v>
+        <v>20.1</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>1574.17</v>
+        <v>1429.98</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>787.09</v>
+        <v>714.99</v>
       </c>
     </row>
     <row r="8">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>#28SW XLK LONG</t>
+          <t>#4SW XLV LONG</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1056,41 +1056,41 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>63.73</v>
+        <v>52.32</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>50.46</v>
+        <v>23.85</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M8" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" s="2" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1450.08</v>
+        <v>1420.63</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>20.1</v>
+        <v>61.23</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>1429.98</v>
+        <v>1359.4</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>714.99</v>
+        <v>226.57</v>
       </c>
     </row>
     <row r="9">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>#4SW XLV LONG</t>
+          <t>#14ID IWM SHORT</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1119,46 +1119,46 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>52.32</v>
+        <v>63.41</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>23.85</v>
+        <v>7.5</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1420.63</v>
+        <v>1182.87</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>61.23</v>
+        <v>19.75</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>1359.4</v>
+        <v>1163.12</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>226.57</v>
+        <v>1163.12</v>
       </c>
     </row>
     <row r="10">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>#14ID IWM SHORT</t>
+          <t>#36ID DIA LONG</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1187,46 +1187,46 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
+          <t>Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>63.41</v>
+        <v>67.86</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>7.5</v>
+        <v>2.52</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1182.87</v>
+        <v>1221.22</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>19.75</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>1163.12</v>
+        <v>1144.54</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1163.12</v>
+        <v>286.13</v>
       </c>
     </row>
     <row r="11">
@@ -1235,22 +1235,22 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>#36ID DIA LONG</t>
+          <t>#935LB NSE LONG</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>LONG_BOUNCE_5m</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>NSE</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1260,41 +1260,41 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red</t>
+          <t>Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down 10:30-12:30</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>67.86</v>
+        <v>54.3</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2.52</v>
+        <v>56</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>50</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1221.22</v>
+        <v>1223.5</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>76.68000000000001</v>
+        <v>377.69</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>1144.54</v>
+        <v>845.8099999999999</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>286.13</v>
+        <v>422.9</v>
       </c>
     </row>
     <row r="12">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>#935LB NSE LONG</t>
+          <t>#31ID SPY LONG</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>LONG_BOUNCE_5m</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>NSE</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1328,17 +1328,17 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down 10:30-12:30</t>
+          <t>Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>54.3</v>
+        <v>63.16</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>56</v>
+        <v>3.67</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1347,22 +1347,22 @@
         <v>1</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1223.5</v>
+        <v>696.96</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>377.69</v>
+        <v>17.95</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>845.8099999999999</v>
+        <v>679.01</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>422.9</v>
+        <v>679.01</v>
       </c>
     </row>
     <row r="13">
@@ -1371,17 +1371,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>#31ID SPY LONG</t>
+          <t>#1SW XLY LONG</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1396,14 +1396,14 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open</t>
+          <t>EMA9&lt;EMA50+RSI&gt;50</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>63.16</v>
+        <v>58.65</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>3.67</v>
+        <v>59.99</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1</v>
@@ -1421,16 +1421,16 @@
         <v>100</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>696.96</v>
+        <v>633.37</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>17.95</v>
+        <v>9.94</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>679.01</v>
+        <v>623.4299999999999</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>679.01</v>
+        <v>623.4299999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>#1SW XLY LONG</t>
+          <t>#37SW QQQ LONG</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1464,17 +1464,17 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>EMA9&lt;EMA50+RSI&gt;50</t>
+          <t>Price&gt;SMA50+EMA9&gt;EMA20+2Red</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>58.65</v>
+        <v>60.94</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>59.99</v>
+        <v>45.8</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>633.37</v>
+        <v>633.8</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>9.94</v>
+        <v>19.8</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>623.4299999999999</v>
+        <v>614</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>623.4299999999999</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>#37SW QQQ LONG</t>
+          <t>#14SW ETH-USD LONG</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1532,14 +1532,14 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA9&gt;EMA20+2Red</t>
+          <t>Price&gt;SMA50+Range&gt;1.5%+2Red</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>60.94</v>
+        <v>63.36</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45.8</v>
+        <v>74.7</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>2</v>
@@ -1557,16 +1557,16 @@
         <v>50</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>633.8</v>
+        <v>777.78</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>19.8</v>
+        <v>285.41</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>614</v>
+        <v>492.37</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>307</v>
+        <v>246.18</v>
       </c>
     </row>
     <row r="16">
@@ -1575,17 +1575,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>#14SW ETH-USD LONG</t>
+          <t>#1ID SOL-USD SHORT</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>SOL-USD</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1595,46 +1595,46 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+Range&gt;1.5%+2Red</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>63.36</v>
+        <v>47.24</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>74.7</v>
+        <v>23.69</v>
       </c>
       <c r="J16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>777.78</v>
+        <v>1386.59</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>285.41</v>
+        <v>943.16</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>492.37</v>
+        <v>443.43</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>246.18</v>
+        <v>147.81</v>
       </c>
     </row>
     <row r="17">
@@ -14181,27 +14181,29 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
+      <c r="L3" s="2" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17 05:42:32 IST</t>
+        </is>
+      </c>
       <c r="N3" s="4" t="n">
-        <v>-571.05</v>
+        <v>-2395.62</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>370.08</v>
       </c>
-      <c r="P3" s="9" t="inlineStr">
-        <is>
-          <t>~-941.13 (unrealized)</t>
-        </is>
-      </c>
-      <c r="Q3" s="9" t="inlineStr">
-        <is>
-          <t>~-0.46%</t>
-        </is>
+      <c r="P3" s="6" t="n">
+        <v>-2765.7</v>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v>-2.24</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
@@ -14226,7 +14228,7 @@
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>#1ID EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
+          <t>#1ID EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50 | 🎯 SL Hit (live)</t>
         </is>
       </c>
     </row>
@@ -20943,18 +20945,18 @@
       <c r="L72" s="15" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
       <c r="N72" s="17" t="n">
-        <v>20919.01</v>
+        <v>18523.39</v>
       </c>
       <c r="O72" s="17" t="n">
-        <v>3222.25</v>
+        <v>3592.33</v>
       </c>
       <c r="P72" s="18" t="n">
-        <v>17696.76</v>
+        <v>14931.06</v>
       </c>
       <c r="Q72" s="16" t="inlineStr"/>
       <c r="R72" s="15" t="inlineStr">
         <is>
-          <t>70 trades (64 closed / 6 open)</t>
+          <t>70 trades (65 closed / 5 open)</t>
         </is>
       </c>
       <c r="S72" s="15" t="inlineStr"/>

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14770,19 +14770,19 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>-42.44</v>
+        <v>-38.34</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>~-52.62 (unrealized)</t>
+          <t>~-48.52 (unrealized)</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>~-1.25%</t>
+          <t>~-1.13%</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14770,19 +14770,19 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>-38.34</v>
+        <v>-40.73</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>~-48.52 (unrealized)</t>
+          <t>~-50.91 (unrealized)</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>~-1.13%</t>
+          <t>~-1.20%</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14770,19 +14770,19 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>-40.73</v>
+        <v>-44.05</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>~-50.91 (unrealized)</t>
+          <t>~-54.23 (unrealized)</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>~-1.20%</t>
+          <t>~-1.30%</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14382,19 +14382,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>56.8</v>
+        <v>1174.34</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.44</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~46.36 (unrealized)</t>
+          <t>~1,163.90 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~+0.11%</t>
+          <t>~+2.25%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -14479,19 +14479,19 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="4" t="n">
-        <v>-761.72</v>
+        <v>-253.45</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P6" s="9" t="inlineStr">
         <is>
-          <t>~-772.14 (unrealized)</t>
+          <t>~-263.87 (unrealized)</t>
         </is>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
-          <t>~-1.46%</t>
+          <t>~-0.49%</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -14576,19 +14576,19 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="4" t="n">
-        <v>181.74</v>
+        <v>-65.23999999999999</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>~171.24 (unrealized)</t>
+          <t>~-75.74 (unrealized)</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>~+0.35%</t>
+          <t>~-0.12%</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -14673,19 +14673,19 @@
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="4" t="n">
-        <v>-37.62</v>
+        <v>-231.99</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>~-48.08 (unrealized)</t>
+          <t>~-242.45 (unrealized)</t>
         </is>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
-          <t>~-0.07%</t>
+          <t>~-0.44%</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -14770,19 +14770,19 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>-44.05</v>
+        <v>-50.17</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>~-54.23 (unrealized)</t>
+          <t>~-60.35 (unrealized)</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>~-1.30%</t>
+          <t>~-1.48%</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14382,19 +14382,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>1174.34</v>
+        <v>1232.56</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.44</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~1,163.90 (unrealized)</t>
+          <t>~1,222.12 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~+2.25%</t>
+          <t>~+2.36%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -14479,19 +14479,19 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="4" t="n">
-        <v>-253.45</v>
+        <v>-149.33</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P6" s="9" t="inlineStr">
         <is>
-          <t>~-263.87 (unrealized)</t>
+          <t>~-159.75 (unrealized)</t>
         </is>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
-          <t>~-0.49%</t>
+          <t>~-0.29%</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -14576,19 +14576,19 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="4" t="n">
-        <v>-65.23999999999999</v>
+        <v>-93.2</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>~-75.74 (unrealized)</t>
+          <t>~-103.70 (unrealized)</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>~-0.12%</t>
+          <t>~-0.18%</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -14673,19 +14673,19 @@
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="4" t="n">
-        <v>-231.99</v>
+        <v>-25.08</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>~-242.45 (unrealized)</t>
+          <t>~-35.54 (unrealized)</t>
         </is>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
-          <t>~-0.44%</t>
+          <t>~-0.05%</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -14770,19 +14770,19 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>-50.17</v>
+        <v>-55.02</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>~-60.35 (unrealized)</t>
+          <t>~-65.20 (unrealized)</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>~-1.48%</t>
+          <t>~-1.62%</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14382,19 +14382,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>1232.56</v>
+        <v>1215.52</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.44</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~1,222.12 (unrealized)</t>
+          <t>~1,205.08 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~+2.36%</t>
+          <t>~+2.33%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -14479,14 +14479,14 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="4" t="n">
-        <v>-149.33</v>
+        <v>-152.07</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P6" s="9" t="inlineStr">
         <is>
-          <t>~-159.75 (unrealized)</t>
+          <t>~-162.49 (unrealized)</t>
         </is>
       </c>
       <c r="Q6" s="9" t="inlineStr">
@@ -14576,19 +14576,19 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="4" t="n">
-        <v>-93.2</v>
+        <v>-74.56</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>~-103.70 (unrealized)</t>
+          <t>~-85.06 (unrealized)</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>~-0.18%</t>
+          <t>~-0.14%</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -14673,19 +14673,19 @@
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="4" t="n">
-        <v>-25.08</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>~-35.54 (unrealized)</t>
+          <t>~61.64 (unrealized)</t>
         </is>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
-          <t>~-0.05%</t>
+          <t>~+0.14%</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -14770,19 +14770,19 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>-55.02</v>
+        <v>-55.66</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>~-65.20 (unrealized)</t>
+          <t>~-65.84 (unrealized)</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>~-1.62%</t>
+          <t>~-1.64%</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14382,19 +14382,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>1215.52</v>
+        <v>1209.84</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.44</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~1,205.08 (unrealized)</t>
+          <t>~1,199.40 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~+2.33%</t>
+          <t>~+2.32%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -14479,19 +14479,19 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="4" t="n">
-        <v>-152.07</v>
+        <v>-126.04</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P6" s="9" t="inlineStr">
         <is>
-          <t>~-162.49 (unrealized)</t>
+          <t>~-136.46 (unrealized)</t>
         </is>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
-          <t>~-0.29%</t>
+          <t>~-0.24%</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -14576,19 +14576,19 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="4" t="n">
-        <v>-74.56</v>
+        <v>-83.88</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>~-85.06 (unrealized)</t>
+          <t>~-94.38 (unrealized)</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>~-0.14%</t>
+          <t>~-0.16%</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -14673,19 +14673,19 @@
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="4" t="n">
-        <v>72.09999999999999</v>
+        <v>59.57</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>~61.64 (unrealized)</t>
+          <t>~49.11 (unrealized)</t>
         </is>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
-          <t>~+0.14%</t>
+          <t>~+0.11%</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -14770,19 +14770,19 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>-55.66</v>
+        <v>-58.09</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>~-65.84 (unrealized)</t>
+          <t>~-68.27 (unrealized)</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>~-1.64%</t>
+          <t>~-1.71%</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14382,19 +14382,19 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>1209.84</v>
+        <v>1275.16</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>10.44</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>~1,199.40 (unrealized)</t>
+          <t>~1,264.72 (unrealized)</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>~+2.32%</t>
+          <t>~+2.44%</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -14479,19 +14479,19 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="4" t="n">
-        <v>-126.04</v>
+        <v>-100.01</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P6" s="9" t="inlineStr">
         <is>
-          <t>~-136.46 (unrealized)</t>
+          <t>~-110.43 (unrealized)</t>
         </is>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
-          <t>~-0.24%</t>
+          <t>~-0.19%</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -14576,19 +14576,19 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="4" t="n">
-        <v>-83.88</v>
+        <v>-149.12</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>~-94.38 (unrealized)</t>
+          <t>~-159.62 (unrealized)</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>~-0.16%</t>
+          <t>~-0.28%</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -14673,19 +14673,19 @@
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="4" t="n">
-        <v>59.57</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>~49.11 (unrealized)</t>
+          <t>~71.05 (unrealized)</t>
         </is>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
-          <t>~+0.11%</t>
+          <t>~+0.16%</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -14770,14 +14770,14 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>-58.09</v>
+        <v>-57.97</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>~-68.27 (unrealized)</t>
+          <t>~-68.15 (unrealized)</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$R$196</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Trades'!$A$1:$W$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Trades'!$A$1:$W$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1338,10 +1338,10 @@
         <v>3.67</v>
       </c>
       <c r="J12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>1</v>
@@ -13889,7 +13889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W72"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14037,27 +14037,27 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>04:42:09 IST</t>
+          <t>01:17:39 IST</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>XRP-USD</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -14066,70 +14066,68 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1.28</v>
+        <v>762.76</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>104702</v>
+        <v>261</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>1.3</v>
+        <v>754.98</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>1.25</v>
+        <v>777.86</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17 05:11:30 IST</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>-2502.38</v>
+        <v>26.1</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>402.06</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v>-2904.44</v>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v>-2.17</v>
+        <v>39.82</v>
+      </c>
+      <c r="P2" s="9" t="inlineStr">
+        <is>
+          <t>~-13.72 (unrealized)</t>
+        </is>
+      </c>
+      <c r="Q2" s="9" t="inlineStr">
+        <is>
+          <t>~+0.01%</t>
+        </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+RSI&lt;45</t>
+          <t>Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>{"2Red": 1.0, "Close": 1.2857, "EMA20": 1.290735, "EMA50": 1.320373, "EMA9": 1.285319, "High": 1.2924, "Low": 1.2799, "Open": 1.2924, "RSI14": 44.647916, "Ret": -0.004799, "SMA20": 1.284855, "SMA50": 1.337968, "Volume": 8068352.0, "_provenance": {"captured_at_ist": "2026-09-17 04:42:09 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "afa975fd79217cbcebf4b115cf3e5ff0792427c665b8bc8d3f8e2bfd1d44404e"}}</t>
+          <t>{"2Red": 0.0, "Close": 762.609924, "EMA20": 760.218296, "EMA50": 761.36909, "EMA9": 760.926447, "High": 763.059998, "Low": 762.140015, "Open": 762.72998, "RSI14": 55.691702, "Ret": -0.000157, "SMA20": 758.950998, "SMA50": 760.860814, "Volume": 4189085.0, "_provenance": {"captured_at_ist": "2026-09-18 01:17:39 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "63233a7a2b8b5a01654b6c13b09c8cc657667721c95a68b316636978fd790567"}}</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>#1ID Price&gt;SMA20+RSI&lt;45 | 🎯 SL Hit (live)</t>
+          <t>#31ID Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open</t>
         </is>
       </c>
     </row>
@@ -14151,7 +14149,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>SOL-USD</t>
+          <t>XRP-USD</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -14165,16 +14163,16 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>97.20999999999999</v>
+        <v>1.28</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1269</v>
+        <v>104702</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>98.86</v>
+        <v>1.3</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>94.48</v>
+        <v>1.25</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
@@ -14182,24 +14180,24 @@
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 05:42:32 IST</t>
+          <t>2026-09-17 05:11:30 IST</t>
         </is>
       </c>
       <c r="N3" s="4" t="n">
-        <v>-2395.62</v>
+        <v>-2502.38</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>370.08</v>
+        <v>402.06</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>-2765.7</v>
+        <v>-2904.44</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>-2.24</v>
+        <v>-2.17</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
@@ -14213,22 +14211,22 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>47.24</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
+          <t>Price&gt;SMA20+RSI&lt;45</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>{"2Red": 1.0, "Close": 97.400002, "EMA20": 97.686447, "EMA50": 98.562736, "EMA9": 97.713368, "High": 98.349998, "Low": 97.360001, "Open": 98.339996, "RSI14": 45.437219, "Ret": -0.009256, "SMA20": 97.394, "SMA50": 98.8962, "Volume": 14413824.0, "_provenance": {"captured_at_ist": "2026-09-17 04:42:09 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "0aebaa23bf1412fdc59c92ba2b2063628551bafdb2c9aae28e4ef1e054a67378"}}</t>
+          <t>{"2Red": 1.0, "Close": 1.2857, "EMA20": 1.290735, "EMA50": 1.320373, "EMA9": 1.285319, "High": 1.2924, "Low": 1.2799, "Open": 1.2924, "RSI14": 44.647916, "Ret": -0.004799, "SMA20": 1.284855, "SMA50": 1.337968, "Volume": 8068352.0, "_provenance": {"captured_at_ist": "2026-09-17 04:42:09 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "afa975fd79217cbcebf4b115cf3e5ff0792427c665b8bc8d3f8e2bfd1d44404e"}}</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>#1ID EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50 | 🎯 SL Hit (live)</t>
+          <t>#1ID Price&gt;SMA20+RSI&lt;45 | 🎯 SL Hit (live)</t>
         </is>
       </c>
     </row>
@@ -14240,7 +14238,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>01:08:10 IST</t>
+          <t>04:42:09 IST</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -14250,7 +14248,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>LINK-USD</t>
+          <t>SOL-USD</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -14264,16 +14262,16 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>10.76</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>11171</v>
+        <v>1269</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>10.95</v>
+        <v>98.86</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>10.47</v>
+        <v>94.48</v>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
@@ -14281,24 +14279,24 @@
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>10.98</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 01:54:37 IST</t>
+          <t>2026-09-17 05:42:32 IST</t>
         </is>
       </c>
       <c r="N4" s="4" t="n">
-        <v>-2489.46</v>
+        <v>-2395.62</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>360.6</v>
+        <v>370.08</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-2850.06</v>
+        <v>-2765.7</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>-2.37</v>
+        <v>-2.24</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
@@ -14312,22 +14310,22 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>47.24</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+RSI&lt;45</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>{"2Red": 0.0, "Close": 10.793, "EMA20": 10.825064, "EMA50": 11.034457, "EMA9": 10.747165, "High": 10.93, "Low": 10.637, "Open": 10.704, "RSI14": 43.70867, "Ret": 0.009352, "SMA20": 10.78955, "SMA50": 11.151, "Volume": 12185504.0, "_provenance": {"captured_at_ist": "2026-09-17 01:08:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "cac9acf106b0a6f7d789b27a6b1478a1066c478185e51b24477b80cc9a94ffaa"}}</t>
+          <t>{"2Red": 1.0, "Close": 97.400002, "EMA20": 97.686447, "EMA50": 98.562736, "EMA9": 97.713368, "High": 98.349998, "Low": 97.360001, "Open": 98.339996, "RSI14": 45.437219, "Ret": -0.009256, "SMA20": 97.394, "SMA50": 98.8962, "Volume": 14413824.0, "_provenance": {"captured_at_ist": "2026-09-17 04:42:09 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "0aebaa23bf1412fdc59c92ba2b2063628551bafdb2c9aae28e4ef1e054a67378"}}</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>#1ID Price&gt;SMA20+RSI&lt;45 | 🎯 SL Hit (live)</t>
+          <t>#1ID EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50 | 🎯 SL Hit (live)</t>
         </is>
       </c>
     </row>
@@ -14339,104 +14337,106 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>00:28:17 IST</t>
+          <t>01:08:10 IST</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>LINK-USD</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>183.76</v>
+        <v>10.76</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>284</v>
+        <v>11171</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>180.07</v>
+        <v>10.95</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>191.09</v>
+        <v>10.47</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17 01:54:37 IST</t>
+        </is>
+      </c>
       <c r="N5" s="4" t="n">
-        <v>1275.16</v>
+        <v>-2489.46</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>10.44</v>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
-        <is>
-          <t>~1,264.72 (unrealized)</t>
-        </is>
-      </c>
-      <c r="Q5" s="9" t="inlineStr">
-        <is>
-          <t>~+2.44%</t>
-        </is>
+        <v>360.6</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>-2850.06</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>-2.37</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>63.73</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
+          <t>Price&gt;SMA20+RSI&lt;45</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 189.495838, "BB_lo": 180.328162, "Close": 183.740005, "EMA20": 185.220461, "EMA200": 165.492268, "EMA50": 183.219192, "EMA9": 185.51008, "High": 185.070007, "Low": 183.460007, "Open": 184.5, "RSI14": 47.830673, "Ret": -0.00293, "SMA20": 184.912, "SMA50": 182.8038, "Volume": 6147600.0, "_provenance": {"captured_at_ist": "2026-09-17 00:28:17 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "40b5431cf114a047302613b8978e7d5624cfcad2013f8ae927bbc041828a6677"}, "high20": 191.75, "high50": 191.75, "low20": 178.820007, "low50": 166.460007}</t>
+          <t>{"2Red": 0.0, "Close": 10.793, "EMA20": 10.825064, "EMA50": 11.034457, "EMA9": 10.747165, "High": 10.93, "Low": 10.637, "Open": 10.704, "RSI14": 43.70867, "Ret": 0.009352, "SMA20": 10.78955, "SMA50": 11.151, "Volume": 12185504.0, "_provenance": {"captured_at_ist": "2026-09-17 01:08:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "cac9acf106b0a6f7d789b27a6b1478a1066c478185e51b24477b80cc9a94ffaa"}}</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>#28SW Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
+          <t>#1ID Price&gt;SMA20+RSI&lt;45 | 🎯 SL Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>00:18:16 IST</t>
+          <t>00:28:17 IST</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -14460,16 +14460,16 @@
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>380.39</v>
+        <v>183.76</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>137</v>
+        <v>284</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>372.74</v>
+        <v>180.07</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>395.56</v>
+        <v>191.09</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
@@ -14479,19 +14479,19 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="4" t="n">
-        <v>-100.01</v>
+        <v>1255.28</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>10.42</v>
+        <v>10.44</v>
       </c>
       <c r="P6" s="9" t="inlineStr">
         <is>
-          <t>~-110.43 (unrealized)</t>
+          <t>~1,244.84 (unrealized)</t>
         </is>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
-          <t>~-0.19%</t>
+          <t>~+2.41%</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -14501,27 +14501,27 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>63.73</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 383.727455, "BB_lo": 375.490547, "Close": 380.350006, "EMA20": 379.149401, "EMA200": 354.178396, "EMA50": 375.052856, "EMA9": 379.809738, "High": 381.670013, "Low": 380.200012, "Open": 380.519989, "RSI14": 53.707446, "Ret": 0.008351, "SMA20": 379.609001, "SMA50": 374.815799, "Volume": 202800.0, "_provenance": {"captured_at_ist": "2026-09-15 00:18:16 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "fd0e07c7006d9e581a4d30f0d710b0d5f91f55641de9d507f3b73b03768e2faa"}, "high20": 385.049988, "high50": 385.049988, "low20": 376.040009, "low50": 358.170013}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 189.495838, "BB_lo": 180.328162, "Close": 183.740005, "EMA20": 185.220461, "EMA200": 165.492268, "EMA50": 183.219192, "EMA9": 185.51008, "High": 185.070007, "Low": 183.460007, "Open": 184.5, "RSI14": 47.830673, "Ret": -0.00293, "SMA20": 184.912, "SMA50": 182.8038, "Volume": 6147600.0, "_provenance": {"captured_at_ist": "2026-09-17 00:28:17 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "40b5431cf114a047302613b8978e7d5624cfcad2013f8ae927bbc041828a6677"}, "high20": 191.75, "high50": 191.75, "low20": 178.820007, "low50": 166.460007}</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>#28SW Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
         </is>
       </c>
     </row>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -14557,16 +14557,16 @@
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>112.61</v>
+        <v>380.39</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>466</v>
+        <v>137</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>110.35</v>
+        <v>372.74</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>117.1</v>
+        <v>395.56</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
@@ -14576,19 +14576,19 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="4" t="n">
-        <v>-149.12</v>
+        <v>-94.53</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10.5</v>
+        <v>10.42</v>
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>~-159.62 (unrealized)</t>
+          <t>~-104.95 (unrealized)</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>~-0.28%</t>
+          <t>~-0.18%</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -14598,27 +14598,27 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>59.53</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;EMA9+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 113.656097, "BB_lo": 110.021903, "Close": 112.599998, "EMA20": 111.705223, "EMA200": 111.692649, "EMA50": 111.394685, "EMA9": 111.897336, "High": 113.040001, "Low": 112.309998, "Open": 112.339996, "RSI14": 53.98306, "Ret": 0.009865, "SMA20": 111.839, "SMA50": 110.8982, "Volume": 3979800.0, "_provenance": {"captured_at_ist": "2026-09-15 00:18:16 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "d624b259f32b23afed94634d2f685958792df81f76287970bd56314d73deee6e"}, "high20": 114.290001, "high50": 114.290001, "low20": 110.25, "low50": 105.254997}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 383.727455, "BB_lo": 375.490547, "Close": 380.350006, "EMA20": 379.149401, "EMA200": 354.178396, "EMA50": 375.052856, "EMA9": 379.809738, "High": 381.670013, "Low": 380.200012, "Open": 380.519989, "RSI14": 53.707446, "Ret": 0.008351, "SMA20": 379.609001, "SMA50": 374.815799, "Volume": 202800.0, "_provenance": {"captured_at_ist": "2026-09-15 00:18:16 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "fd0e07c7006d9e581a4d30f0d710b0d5f91f55641de9d507f3b73b03768e2faa"}, "high20": 385.049988, "high50": 385.049988, "low20": 376.040009, "low50": 358.170013}</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>#3SW Price&gt;EMA9+Range&lt;1%</t>
+          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
     </row>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>00:18:15 IST</t>
+          <t>00:18:16 IST</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -14654,16 +14654,16 @@
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>83.39</v>
+        <v>112.61</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>627</v>
+        <v>466</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>81.70999999999999</v>
+        <v>110.35</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>86.72</v>
+        <v>117.1</v>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
@@ -14673,19 +14673,19 @@
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="4" t="n">
-        <v>81.51000000000001</v>
+        <v>-116.5</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10.46</v>
+        <v>10.5</v>
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>~71.05 (unrealized)</t>
+          <t>~-127.00 (unrealized)</t>
         </is>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
-          <t>~+0.16%</t>
+          <t>~-0.22%</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -14695,49 +14695,49 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>61.78</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>EMA20&lt;EMA50+Range&lt;1%</t>
+          <t>Price&gt;EMA9+Range&lt;1%</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 87.544832, "BB_lo": 82.866166, "Close": 83.379997, "EMA20": 84.743425, "EMA200": 82.927356, "EMA50": 84.782471, "EMA9": 84.151368, "High": 83.690002, "Low": 83.040001, "Open": 83.510002, "RSI14": 40.412033, "Ret": 0.00349, "SMA20": 85.205499, "SMA50": 84.994, "Volume": 10836500.0, "_provenance": {"captured_at_ist": "2026-09-15 00:18:15 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "0799e2a4d605288db1a0c1ff7b2ca5488b29bfdd8b1fd343b412e39dd964746b"}, "high20": 87.470001, "high50": 88.779999, "low20": 82.849998, "low50": 82.769997}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 113.656097, "BB_lo": 110.021903, "Close": 112.599998, "EMA20": 111.705223, "EMA200": 111.692649, "EMA50": 111.394685, "EMA9": 111.897336, "High": 113.040001, "Low": 112.309998, "Open": 112.339996, "RSI14": 53.98306, "Ret": 0.009865, "SMA20": 111.839, "SMA50": 110.8982, "Volume": 3979800.0, "_provenance": {"captured_at_ist": "2026-09-15 00:18:16 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "d624b259f32b23afed94634d2f685958792df81f76287970bd56314d73deee6e"}, "high20": 114.290001, "high50": 114.290001, "low20": 110.25, "low50": 105.254997}</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA20&lt;EMA50+Range&lt;1%</t>
+          <t>#3SW Price&gt;EMA9+Range&lt;1%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>15:01:27 IST</t>
+          <t>00:18:15 IST</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -14750,17 +14750,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G9" s="10" t="n">
-        <v>0.3393</v>
+      <c r="G9" s="4" t="n">
+        <v>83.39</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <v>0.3315</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>0.3518</v>
+        <v>627</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>81.70999999999999</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>86.72</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
@@ -14770,19 +14770,19 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>-57.97</v>
+        <v>40.76</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>10.18</v>
+        <v>10.46</v>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>~-68.15 (unrealized)</t>
+          <t>~30.30 (unrealized)</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>~-1.71%</t>
+          <t>~+0.08%</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -14792,39 +14792,39 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>61.78</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>EMA20&lt;EMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 0.345453, "BB_lo": 0.325368, "Close": 0.338307, "EMA20": 0.336164, "EMA200": 0.325217, "EMA50": 0.333945, "EMA9": 0.3375, "High": 0.341545, "Low": 0.338295, "Open": 0.339846, "RSI14": 54.726192, "Ret": -0.004528, "SMA20": 0.33541, "SMA50": 0.333187, "Volume": 302053356.0, "_provenance": {"captured_at_ist": "2026-09-14 15:01:27 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "65ee6ec20afd1eadd50216b1a8c8746e16e10a009a93786d32249e8209218bb5"}, "high20": 0.346589, "high50": 0.349996, "low20": 0.321569, "low50": 0.321569}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 87.544832, "BB_lo": 82.866166, "Close": 83.379997, "EMA20": 84.743425, "EMA200": 82.927356, "EMA50": 84.782471, "EMA9": 84.151368, "High": 83.690002, "Low": 83.040001, "Open": 83.510002, "RSI14": 40.412033, "Ret": 0.00349, "SMA20": 85.205499, "SMA50": 84.994, "Volume": 10836500.0, "_provenance": {"captured_at_ist": "2026-09-15 00:18:15 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "0799e2a4d605288db1a0c1ff7b2ca5488b29bfdd8b1fd343b412e39dd964746b"}, "high20": 87.470001, "high50": 88.779999, "low20": 82.849998, "low50": 82.769997}</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>#4SW EMA20&lt;EMA50+Range&lt;1%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>00:10:42 IST</t>
+          <t>15:01:27 IST</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -14847,83 +14847,81 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
-        <v>2439.54</v>
+      <c r="G10" s="10" t="n">
+        <v>0.3393</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>2388.36</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>2534.58</v>
+        <v>10000</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>0.3518</v>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L10" s="2" t="n">
-        <v>2532.05</v>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-12 01:01:12 IST</t>
-        </is>
-      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="4" t="n">
-        <v>1850.11</v>
+        <v>-46.6</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>146.37</v>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>1703.74</v>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>3.49</v>
+        <v>10.18</v>
+      </c>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t>~-56.78 (unrealized)</t>
+        </is>
+      </c>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>~-1.37%</t>
+        </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2532.765429, "BB_lo": 2393.56941, "Close": 2437.098633, "EMA20": 2404.555507, "EMA200": 2189.831855, "EMA50": 2222.045575, "EMA9": 2463.211647, "High": 2483.719971, "Low": 2406.906494, "Open": 2466.913086, "RSI14": 57.778434, "Ret": -0.012086, "SMA20": 2463.167419, "SMA50": 2147.895715, "Volume": 16781828594.0, "_provenance": {"captured_at_ist": "2026-09-12 00:10:42 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "1ef31696acc1cd4efe2bcd7470c35cf39eec58504bbcfa1e511fce897866faa4"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 2324.709473, "low50": 1821.485107}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 0.345453, "BB_lo": 0.325368, "Close": 0.338307, "EMA20": 0.336164, "EMA200": 0.325217, "EMA50": 0.333945, "EMA9": 0.3375, "High": 0.341545, "Low": 0.338295, "Open": 0.339846, "RSI14": 54.726192, "Ret": -0.004528, "SMA20": 0.33541, "SMA50": 0.333187, "Volume": 302053356.0, "_provenance": {"captured_at_ist": "2026-09-14 15:01:27 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "65ee6ec20afd1eadd50216b1a8c8746e16e10a009a93786d32249e8209218bb5"}, "high20": 0.346589, "high50": 0.349996, "low20": 0.321569, "low50": 0.321569}</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | 🎯 Target Hit (live)</t>
+          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>11:14:08 IST</t>
+          <t>00:10:42 IST</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -14933,55 +14931,55 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>DOGE-USD</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>0.083828</v>
+          <t>SWING_1d</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>2439.54</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>0.085341</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>0.08155800000000001</v>
+        <v>20</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>2388.36</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>2534.58</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0.08559700000000001</v>
+        <v>2532.05</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 19:38:41 IST</t>
+          <t>2026-09-12 01:01:12 IST</t>
         </is>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-88.45</v>
+        <v>1850.11</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>12.57</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v>-101.02</v>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v>-2.41</v>
+        <v>146.37</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>1703.74</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>3.49</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -14990,27 +14988,27 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>50.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+RSI&lt;45</t>
+          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>{"2Red": 0.0, "Close": 0.08408, "EMA20": 0.08417, "EMA50": 0.085792, "EMA9": 0.083724, "High": 0.08414, "Low": 0.08364, "Open": 0.08372, "RSI14": 44.169679, "Ret": 0.0043, "SMA20": 0.083904, "SMA50": 0.086466, "Volume": 9846336.0, "_provenance": {"captured_at_ist": "2026-09-11 11:14:08 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "52faf51891c7541754ee8666a227d22c17b888d769d3894f56f2ba75ece3eaed"}}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2532.765429, "BB_lo": 2393.56941, "Close": 2437.098633, "EMA20": 2404.555507, "EMA200": 2189.831855, "EMA50": 2222.045575, "EMA9": 2463.211647, "High": 2483.719971, "Low": 2406.906494, "Open": 2466.913086, "RSI14": 57.778434, "Ret": -0.012086, "SMA20": 2463.167419, "SMA50": 2147.895715, "Volume": 16781828594.0, "_provenance": {"captured_at_ist": "2026-09-12 00:10:42 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "1ef31696acc1cd4efe2bcd7470c35cf39eec58504bbcfa1e511fce897866faa4"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 2324.709473, "low50": 1821.485107}</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>#1ID Price&gt;SMA20+RSI&lt;45 | 🎯 SL Hit (live)</t>
+          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | 🎯 Target Hit (live)</t>
         </is>
       </c>
     </row>
@@ -15022,7 +15020,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>00:05:22 IST</t>
+          <t>11:14:08 IST</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -15032,38 +15030,38 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>DOGE-USD</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>2469.38</v>
+          <t>INTRADAY_1h</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>0.083828</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>2417.58</v>
-      </c>
-      <c r="J12" s="8" t="n">
-        <v>2565.59</v>
+        <v>50000</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>0.085341</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>0.08155800000000001</v>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2563.02</v>
+        <v>0.08559700000000001</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -15071,16 +15069,16 @@
         </is>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1779.24</v>
+        <v>-88.45</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>140.75</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>1638.49</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>3.49</v>
+        <v>12.57</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>-101.02</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>-2.41</v>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
@@ -15089,27 +15087,27 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>50.67</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
+          <t>Price&gt;SMA20+RSI&lt;45</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2539.244704, "BB_lo": 2394.908446, "Close": 2466.913818, "EMA20": 2401.129915, "EMA200": 2187.380698, "EMA50": 2213.267899, "EMA9": 2469.739901, "High": 2522.369629, "Low": 2443.702393, "Open": 2484.894287, "RSI14": 60.959164, "Ret": -0.007255, "SMA20": 2467.076575, "SMA50": 2137.823545, "Volume": 14955608804.0, "_provenance": {"captured_at_ist": "2026-09-11 00:05:22 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "d8d364e889190953445a4b086a4c86f37d82d8af7f1f62c9054b85772793509b"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 2222.574707, "low50": 1821.485107}</t>
+          <t>{"2Red": 0.0, "Close": 0.08408, "EMA20": 0.08417, "EMA50": 0.085792, "EMA9": 0.083724, "High": 0.08414, "Low": 0.08364, "Open": 0.08372, "RSI14": 44.169679, "Ret": 0.0043, "SMA20": 0.083904, "SMA50": 0.086466, "Volume": 9846336.0, "_provenance": {"captured_at_ist": "2026-09-11 11:14:08 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "52faf51891c7541754ee8666a227d22c17b888d769d3894f56f2ba75ece3eaed"}}</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | 🎯 Target Hit (live)</t>
+          <t>#1ID Price&gt;SMA20+RSI&lt;45 | 🎯 SL Hit (live)</t>
         </is>
       </c>
     </row>
@@ -15126,12 +15124,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -15145,16 +15143,16 @@
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>716.38</v>
+        <v>2469.38</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>701.98</v>
+        <v>2417.58</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>744.96</v>
+        <v>2565.59</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
@@ -15162,24 +15160,24 @@
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>704.52</v>
+        <v>2563.02</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:37:33 IST</t>
+          <t>2026-09-11 19:38:41 IST</t>
         </is>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-865.8099999999999</v>
+        <v>1779.24</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>10.46</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v>-876.27</v>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v>-1.68</v>
+        <v>140.75</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>1638.49</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>3.49</v>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
@@ -15188,27 +15186,27 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>65.29</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+2Red</t>
+          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 732.086193, "BB_lo": 702.469807, "Close": 716.309998, "EMA20": 714.795564, "EMA200": 664.839596, "EMA50": 710.89305, "EMA9": 715.808843, "High": 719.700012, "Low": 714.02002, "Open": 716.400024, "RSI14": 51.664581, "Ret": -0.002854, "SMA20": 717.278, "SMA50": 711.166399, "Volume": 26659200.0, "_provenance": {"captured_at_ist": "2026-09-11 00:05:22 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "3150d3a7200210926ae4cbca12d82841d05d62f6516aa32b4a5180c4e8d61898"}, "high20": 734.580017, "high50": 737.619995, "low20": 702.700012, "low50": 661.140015}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2539.244704, "BB_lo": 2394.908446, "Close": 2466.913818, "EMA20": 2401.129915, "EMA200": 2187.380698, "EMA50": 2213.267899, "EMA9": 2469.739901, "High": 2522.369629, "Low": 2443.702393, "Open": 2484.894287, "RSI14": 60.959164, "Ret": -0.007255, "SMA20": 2467.076575, "SMA50": 2137.823545, "Volume": 14955608804.0, "_provenance": {"captured_at_ist": "2026-09-11 00:05:22 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "d8d364e889190953445a4b086a4c86f37d82d8af7f1f62c9054b85772793509b"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 2222.574707, "low50": 1821.485107}</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>#31SW Price&gt;SMA50+2Red | Expiry 5d</t>
+          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | 🎯 Target Hit (live)</t>
         </is>
       </c>
     </row>
@@ -15230,7 +15228,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -15244,16 +15242,16 @@
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>166.6</v>
+        <v>716.38</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>314</v>
+        <v>73</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>163.25</v>
+        <v>701.98</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>173.24</v>
+        <v>744.96</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
@@ -15261,7 +15259,7 @@
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>167.5</v>
+        <v>704.52</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -15269,16 +15267,16 @@
         </is>
       </c>
       <c r="N14" s="4" t="n">
-        <v>283.62</v>
+        <v>-865.8099999999999</v>
       </c>
       <c r="O14" s="4" t="n">
         <v>10.46</v>
       </c>
-      <c r="P14" s="5" t="n">
-        <v>273.16</v>
-      </c>
-      <c r="Q14" s="12" t="n">
-        <v>0.52</v>
+      <c r="P14" s="6" t="n">
+        <v>-876.27</v>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v>-1.68</v>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
@@ -15287,49 +15285,49 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>65.29</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 177.039339, "BB_lo": 165.311657, "Close": 166.580002, "EMA20": 169.967704, "EMA200": 155.06167, "EMA50": 165.803089, "EMA9": 170.19262, "High": 167.410004, "Low": 166.389999, "Open": 167.309998, "RSI14": 43.5919, "Ret": -0.003291, "SMA20": 171.175498, "SMA50": 165.980599, "Volume": 8018100.0, "_provenance": {"captured_at_ist": "2026-09-11 00:05:22 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "b1bd4acf19438d5c9145df22921236f8ae2c9a49fd069b3fdf994b5e8ccf5871"}, "high20": 176.600006, "high50": 176.600006, "low20": 165.759995, "low50": 157.229996}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 732.086193, "BB_lo": 702.469807, "Close": 716.309998, "EMA20": 714.795564, "EMA200": 664.839596, "EMA50": 710.89305, "EMA9": 715.808843, "High": 719.700012, "Low": 714.02002, "Open": 716.400024, "RSI14": 51.664581, "Ret": -0.002854, "SMA20": 717.278, "SMA50": 711.166399, "Volume": 26659200.0, "_provenance": {"captured_at_ist": "2026-09-11 00:05:22 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "3150d3a7200210926ae4cbca12d82841d05d62f6516aa32b4a5180c4e8d61898"}, "high20": 734.580017, "high50": 737.619995, "low20": 702.700012, "low50": 661.140015}</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#31SW Price&gt;SMA50+2Red | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>04:11:58 IST</t>
+          <t>00:05:22 IST</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -15343,16 +15341,16 @@
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2487.43</v>
+        <v>166.6</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>19</v>
+        <v>314</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>2435.24</v>
+        <v>163.25</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>2584.34</v>
+        <v>173.24</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
@@ -15360,24 +15358,24 @@
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>2432.8</v>
+        <v>167.5</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 18:11:52 IST</t>
+          <t>2026-09-16 00:37:33 IST</t>
         </is>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1037.88</v>
+        <v>283.62</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>141.78</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v>-1179.66</v>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v>-2.5</v>
+        <v>10.46</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>273.16</v>
+      </c>
+      <c r="Q15" s="12" t="n">
+        <v>0.52</v>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
@@ -15386,39 +15384,39 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+Range&gt;1.5%+2Red</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2555.797457, "BB_lo": 2364.302788, "Close": 2484.941406, "EMA20": 2394.205294, "EMA200": 2184.550101, "EMA50": 2202.915005, "EMA9": 2470.446422, "High": 2506.753174, "Low": 2441.328857, "Open": 2490.919678, "RSI14": 62.903407, "Ret": -0.002415, "SMA20": 2460.050122, "SMA50": 2127.052944, "Volume": 13471038160.0, "_provenance": {"captured_at_ist": "2026-09-10 04:11:58 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "9d935e01f058e194edc4cbc5b22f08a0e6b38c3f190d3dd9f1551d28266ed601"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 1905.082397, "low50": 1821.485107}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 177.039339, "BB_lo": 165.311657, "Close": 166.580002, "EMA20": 169.967704, "EMA200": 155.06167, "EMA50": 165.803089, "EMA9": 170.19262, "High": 167.410004, "Low": 166.389999, "Open": 167.309998, "RSI14": 43.5919, "Ret": -0.003291, "SMA20": 171.175498, "SMA50": 165.980599, "Volume": 8018100.0, "_provenance": {"captured_at_ist": "2026-09-11 00:05:22 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "b1bd4acf19438d5c9145df22921236f8ae2c9a49fd069b3fdf994b5e8ccf5871"}, "high20": 176.600006, "high50": 176.600006, "low20": 165.759995, "low50": 157.229996}</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>#14SW Price&gt;SMA50+Range&gt;1.5%+2Red | SL Hit (intraday)</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>17:10:43 IST</t>
+          <t>04:11:58 IST</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -15428,55 +15426,55 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>SOL-USD</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>103.63</v>
+        <v>2487.43</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1217</v>
+        <v>19</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>105.35</v>
+        <v>2435.24</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>100.68</v>
+        <v>2584.34</v>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>100.83</v>
+        <v>2432.8</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 03:42:13 IST</t>
+          <t>2026-09-10 18:11:52 IST</t>
         </is>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3406.36</v>
+        <v>-1037.88</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>378.35</v>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>3028.01</v>
-      </c>
-      <c r="Q16" s="5" t="n">
-        <v>2.4</v>
+        <v>141.78</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>-1179.66</v>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v>-2.5</v>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
@@ -15485,27 +15483,27 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>47.24</t>
+          <t>63.36</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
+          <t>Price&gt;SMA50+Range&gt;1.5%+2Red</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>{"2Red": 0.0, "Close": 103.790001, "EMA20": 103.838416, "EMA50": 103.876237, "EMA9": 103.993741, "High": 104.050003, "Low": 103.480003, "Open": 103.489998, "RSI14": 49.770588, "Ret": 0.002802, "SMA20": 103.7825, "SMA50": 103.7752, "Volume": 17383936.0, "_provenance": {"captured_at_ist": "2026-09-09 17:10:43 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "9aaf3858637b395153a1eb6f1f3f5a4337236e3bc92c730aee983cd6ceb4eec1"}}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2555.797457, "BB_lo": 2364.302788, "Close": 2484.941406, "EMA20": 2394.205294, "EMA200": 2184.550101, "EMA50": 2202.915005, "EMA9": 2470.446422, "High": 2506.753174, "Low": 2441.328857, "Open": 2490.919678, "RSI14": 62.903407, "Ret": -0.002415, "SMA20": 2460.050122, "SMA50": 2127.052944, "Volume": 13471038160.0, "_provenance": {"captured_at_ist": "2026-09-10 04:11:58 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "9d935e01f058e194edc4cbc5b22f08a0e6b38c3f190d3dd9f1551d28266ed601"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 1905.082397, "low50": 1821.485107}</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>#1ID EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50 | 🎯 Target Hit (live)</t>
+          <t>#14SW Price&gt;SMA50+Range&gt;1.5%+2Red | SL Hit (intraday)</t>
         </is>
       </c>
     </row>
@@ -15517,65 +15515,65 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>00:20:42 IST</t>
+          <t>17:10:43 IST</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>SOL-USD</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>171.47</v>
+        <v>103.63</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>314</v>
+        <v>1217</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>168.02</v>
+        <v>105.35</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>178.31</v>
+        <v>100.68</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>168</v>
+        <v>100.83</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 01:02:44 IST</t>
+          <t>2026-09-10 03:42:13 IST</t>
         </is>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1088.58</v>
+        <v>3406.36</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>10.77</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v>-1099.35</v>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v>-2.04</v>
+        <v>378.35</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>3028.01</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>2.4</v>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
@@ -15584,49 +15582,49 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>47.24</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 176.798755, "BB_lo": 165.82624, "Close": 171.449997, "EMA20": 170.660546, "EMA200": 154.818785, "EMA50": 165.715924, "EMA9": 172.087216, "High": 172.529999, "Low": 171.240005, "Open": 171.389999, "RSI14": 55.529727, "Ret": -0.010447, "SMA20": 171.312498, "SMA50": 165.727999, "Volume": 6083000.0, "_provenance": {"captured_at_ist": "2026-09-09 00:20:42 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "44670098855ad96888cc2dab18b682407e5130dfe00fe74e11bc4ccf032eec28"}, "high20": 176.600006, "high50": 176.600006, "low20": 162.919998, "low50": 153.589996}</t>
+          <t>{"2Red": 0.0, "Close": 103.790001, "EMA20": 103.838416, "EMA50": 103.876237, "EMA9": 103.993741, "High": 104.050003, "Low": 103.480003, "Open": 103.489998, "RSI14": 49.770588, "Ret": 0.002802, "SMA20": 103.7825, "SMA50": 103.7752, "Volume": 17383936.0, "_provenance": {"captured_at_ist": "2026-09-09 17:10:43 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "9aaf3858637b395153a1eb6f1f3f5a4337236e3bc92c730aee983cd6ceb4eec1"}}</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | 🎯 SL Hit (live)</t>
+          <t>#1ID EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50 | 🎯 Target Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>11:22:34 IST</t>
+          <t>00:20:42 IST</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -15639,17 +15637,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G18" s="10" t="n">
-        <v>0.3349</v>
+      <c r="G18" s="4" t="n">
+        <v>171.47</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <v>0.3272</v>
-      </c>
-      <c r="J18" s="11" t="n">
-        <v>0.3473</v>
+        <v>314</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>168.02</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>178.31</v>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
@@ -15657,24 +15655,24 @@
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0.3384</v>
+        <v>168</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 16:01:47 IST</t>
+          <t>2026-09-09 01:02:44 IST</t>
         </is>
       </c>
       <c r="N18" s="4" t="n">
-        <v>35.01</v>
+        <v>-1088.58</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>24.96</v>
-      </c>
-      <c r="Q18" s="12" t="n">
-        <v>0.75</v>
+        <v>10.77</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>-1099.35</v>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v>-2.04</v>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
@@ -15683,49 +15681,49 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>66.28</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 0.34818, "BB_lo": 0.323418, "Close": 0.333927, "EMA20": 0.333584, "EMA200": 0.324153, "EMA50": 0.332375, "EMA9": 0.332427, "High": 0.334747, "Low": 0.331477, "Open": 0.331539, "RSI14": 50.659837, "Ret": 0.007209, "SMA20": 0.335799, "SMA50": 0.331667, "Volume": 308281984.0, "_provenance": {"captured_at_ist": "2026-09-07 11:22:34 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "7600fa929fe73fa7401d6bfbe86db098b69cda878289f54ac466b6c9a918540c"}, "high20": 0.349996, "high50": 0.349996, "low20": 0.321569, "low50": 0.321457}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 176.798755, "BB_lo": 165.82624, "Close": 171.449997, "EMA20": 170.660546, "EMA200": 154.818785, "EMA50": 165.715924, "EMA9": 172.087216, "High": 172.529999, "Low": 171.240005, "Open": 171.389999, "RSI14": 55.529727, "Ret": -0.010447, "SMA20": 171.312498, "SMA50": 165.727999, "Volume": 6083000.0, "_provenance": {"captured_at_ist": "2026-09-09 00:20:42 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "44670098855ad96888cc2dab18b682407e5130dfe00fe74e11bc4ccf032eec28"}, "high20": 176.600006, "high50": 176.600006, "low20": 162.919998, "low50": 153.589996}</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>#2SW Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | 🎯 SL Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>00:01:07 IST</t>
+          <t>11:22:34 IST</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -15738,17 +15736,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
-        <v>384.36</v>
+      <c r="G19" s="10" t="n">
+        <v>0.3349</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>133</v>
-      </c>
-      <c r="I19" s="8" t="n">
-        <v>376.63</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>399.69</v>
+        <v>10000</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>0.3473</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
@@ -15756,24 +15754,24 @@
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>378.76</v>
+        <v>0.3384</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 00:01:43 IST</t>
+          <t>2026-09-12 16:01:47 IST</t>
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-744.52</v>
+        <v>35.01</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v>-754.74</v>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v>-1.48</v>
+        <v>10.05</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="Q19" s="12" t="n">
+        <v>0.75</v>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
@@ -15782,27 +15780,27 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>66.28</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 384.914412, "BB_lo": 375.582585, "Close": 384.320007, "EMA20": 378.7841, "EMA200": 352.821272, "EMA50": 374.004443, "EMA9": 380.273856, "High": 385.049988, "Low": 381.329987, "Open": 381.329987, "RSI14": 62.100647, "Ret": 0.011235, "SMA20": 380.248499, "SMA50": 373.018998, "Volume": 152400.0, "_provenance": {"captured_at_ist": "2026-09-05 00:01:07 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "abfffaa65e4253b95842b79cc0c4fd24b91e723a3bb5a1c71936a4e0ad957b60"}, "high20": 384.809998, "high50": 384.820007, "low20": 376.040009, "low50": 354.809998}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 0.34818, "BB_lo": 0.323418, "Close": 0.333927, "EMA20": 0.333584, "EMA200": 0.324153, "EMA50": 0.332375, "EMA9": 0.332427, "High": 0.334747, "Low": 0.331477, "Open": 0.331539, "RSI14": 50.659837, "Ret": 0.007209, "SMA20": 0.335799, "SMA50": 0.331667, "Volume": 308281984.0, "_provenance": {"captured_at_ist": "2026-09-07 11:22:34 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "7600fa929fe73fa7401d6bfbe86db098b69cda878289f54ac466b6c9a918540c"}, "high20": 0.349996, "high50": 0.349996, "low20": 0.321569, "low50": 0.321457}</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#2SW Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -15824,7 +15822,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -15838,16 +15836,16 @@
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>69.12</v>
+        <v>384.36</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>744</v>
+        <v>133</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>67.73</v>
+        <v>376.63</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>71.87</v>
+        <v>399.69</v>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
@@ -15855,24 +15853,24 @@
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>67.72</v>
+        <v>378.76</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 19:02:45 IST</t>
+          <t>2026-09-10 00:01:43 IST</t>
         </is>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1039.2</v>
+        <v>-744.52</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>10.29</v>
+        <v>10.22</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-1049.49</v>
+        <v>-754.74</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>-2.04</v>
+        <v>-1.48</v>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
@@ -15881,39 +15879,39 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>50.67</t>
+          <t>59.53</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>EMA9&lt;EMA50+Price&gt;EMA50</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 71.993154, "BB_lo": 66.775846, "Close": 69.110001, "EMA20": 68.962509, "EMA200": 64.180507, "EMA50": 68.553847, "EMA9": 68.515681, "High": 69.43, "Low": 68.519997, "Open": 68.690002, "RSI14": 50.566608, "Ret": 0.011119, "SMA20": 69.3845, "SMA50": 69.3494, "Volume": 1003500.0, "_provenance": {"captured_at_ist": "2026-09-05 00:01:07 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "06ac2e6e1d165122d46e93bfcd73629fb535999a67502c91a31dd356f9c3e061"}, "high20": 71.919998, "high50": 71.919998, "low20": 66.809998, "low50": 66.809998}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 384.914412, "BB_lo": 375.582585, "Close": 384.320007, "EMA20": 378.7841, "EMA200": 352.821272, "EMA50": 374.004443, "EMA9": 380.273856, "High": 385.049988, "Low": 381.329987, "Open": 381.329987, "RSI14": 62.100647, "Ret": 0.011235, "SMA20": 380.248499, "SMA50": 373.018998, "Volume": 152400.0, "_provenance": {"captured_at_ist": "2026-09-05 00:01:07 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "abfffaa65e4253b95842b79cc0c4fd24b91e723a3bb5a1c71936a4e0ad957b60"}, "high20": 384.809998, "high50": 384.820007, "low20": 376.040009, "low50": 354.809998}</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>#5SW EMA9&lt;EMA50+Price&gt;EMA50 | 🎯 SL Hit (live)</t>
+          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>00:18:23 IST</t>
+          <t>00:01:07 IST</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -15923,7 +15921,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -15937,16 +15935,16 @@
         </is>
       </c>
       <c r="G21" s="4" t="n">
-        <v>183.62</v>
+        <v>69.12</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>280</v>
+        <v>744</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>179.93</v>
+        <v>67.73</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>190.94</v>
+        <v>71.87</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
@@ -15954,24 +15952,24 @@
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>188.07</v>
+        <v>67.72</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:20:41 IST</t>
+          <t>2026-09-09 19:02:45 IST</t>
         </is>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1245.66</v>
+        <v>-1039.2</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>10.28</v>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v>1235.38</v>
-      </c>
-      <c r="Q21" s="5" t="n">
-        <v>2.4</v>
+        <v>10.29</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>-1049.49</v>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v>-2.04</v>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
@@ -15980,27 +15978,27 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>63.73</t>
+          <t>50.67</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
+          <t>EMA9&lt;EMA50+Price&gt;EMA50</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 191.712855, "BB_lo": 179.688148, "Close": 183.600006, "EMA20": 184.253928, "EMA200": 163.733288, "EMA50": 182.113823, "EMA9": 184.580211, "High": 183.779999, "Low": 182.270004, "Open": 183.460007, "RSI14": 49.503374, "Ret": -0.000218, "SMA20": 185.700501, "SMA50": 182.494601, "Volume": 5698700.0, "_provenance": {"captured_at_ist": "2026-09-04 00:18:23 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "6b9dec175776d38099bfb1914d0a25629c9baa7f345badebe6a04ece751808ef"}, "high20": 191.75, "high50": 191.75, "low20": 178.820007, "low50": 166.460007}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 71.993154, "BB_lo": 66.775846, "Close": 69.110001, "EMA20": 68.962509, "EMA200": 64.180507, "EMA50": 68.553847, "EMA9": 68.515681, "High": 69.43, "Low": 68.519997, "Open": 68.690002, "RSI14": 50.566608, "Ret": 0.011119, "SMA20": 69.3845, "SMA50": 69.3494, "Volume": 1003500.0, "_provenance": {"captured_at_ist": "2026-09-05 00:01:07 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "06ac2e6e1d165122d46e93bfcd73629fb535999a67502c91a31dd356f9c3e061"}, "high20": 71.919998, "high50": 71.919998, "low20": 66.809998, "low50": 66.809998}</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>#28SW Price&gt;SMA50+EMA20&gt;EMA50+2Red | Expiry 5d</t>
+          <t>#5SW EMA9&lt;EMA50+Price&gt;EMA50 | 🎯 SL Hit (live)</t>
         </is>
       </c>
     </row>
@@ -16017,12 +16015,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -16036,16 +16034,16 @@
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2393.89</v>
+        <v>183.62</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>2343.67</v>
+        <v>179.93</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>2487.16</v>
+        <v>190.94</v>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
@@ -16053,24 +16051,24 @@
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2484.67</v>
+        <v>188.07</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 01:13:45 IST</t>
+          <t>2026-09-09 00:20:41 IST</t>
         </is>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1815.66</v>
+        <v>1245.66</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>143.63</v>
+        <v>10.28</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>1672.03</v>
+        <v>1235.38</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>3.49</v>
+        <v>2.4</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
@@ -16079,49 +16077,49 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>63.73</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+Range&gt;1.5%+2Red</t>
+          <t>Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2795.732764, "BB_lo": 1802.401318, "Close": 2391.500977, "EMA20": 2315.842983, "EMA200": 2165.750484, "EMA50": 2125.223481, "EMA9": 2416.411271, "High": 2427.401611, "Low": 2356.188232, "Open": 2417.828369, "RSI14": 61.419955, "Ret": -0.010894, "SMA20": 2299.067041, "SMA50": 2053.502986, "Volume": 14227785690.0, "_provenance": {"captured_at_ist": "2026-09-04 00:18:23 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "bceb614e24f483f8b97a38b58fddecc676f19d19395d1082c77cf9b320b6f87a"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 1861.92041, "low50": 1772.0177}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 191.712855, "BB_lo": 179.688148, "Close": 183.600006, "EMA20": 184.253928, "EMA200": 163.733288, "EMA50": 182.113823, "EMA9": 184.580211, "High": 183.779999, "Low": 182.270004, "Open": 183.460007, "RSI14": 49.503374, "Ret": -0.000218, "SMA20": 185.700501, "SMA50": 182.494601, "Volume": 5698700.0, "_provenance": {"captured_at_ist": "2026-09-04 00:18:23 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "6b9dec175776d38099bfb1914d0a25629c9baa7f345badebe6a04ece751808ef"}, "high20": 191.75, "high50": 191.75, "low20": 178.820007, "low50": 166.460007}</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>#14SW Price&gt;SMA50+Range&gt;1.5%+2Red | 🎯 Target Hit (live)</t>
+          <t>#28SW Price&gt;SMA50+EMA20&gt;EMA50+2Red | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>00:20:14 IST</t>
+          <t>00:18:23 IST</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -16135,16 +16133,16 @@
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>52.08</v>
+        <v>2393.89</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>966</v>
+        <v>20</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>51.03</v>
+        <v>2343.67</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>54.15</v>
+        <v>2487.16</v>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
@@ -16152,24 +16150,24 @@
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>52.43</v>
+        <v>2484.67</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:47:43 IST</t>
+          <t>2026-09-04 01:13:45 IST</t>
         </is>
       </c>
       <c r="N23" s="4" t="n">
-        <v>342.69</v>
+        <v>1815.66</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>10.06</v>
+        <v>143.63</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>332.63</v>
-      </c>
-      <c r="Q23" s="12" t="n">
-        <v>0.66</v>
+        <v>1672.03</v>
+      </c>
+      <c r="Q23" s="5" t="n">
+        <v>3.49</v>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
@@ -16178,97 +16176,97 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>63.36</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+Range&gt;1.5%+2Red</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 53.933542, "BB_lo": 51.668459, "Close": 52.07, "EMA20": 52.631511, "EMA200": 49.788698, "EMA50": 52.014955, "EMA9": 52.846097, "High": 52.459999, "Low": 52.02, "Open": 52.439999, "RSI14": 46.449627, "Ret": -0.011767, "SMA20": 52.801, "SMA50": 51.74, "Volume": 15500500.0, "_provenance": {"captured_at_ist": "2026-09-03 00:20:14 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "4c008560e6adf2a2b92f03ff3aba914bff4c1422744acab60897e94b0403e513"}, "high20": 54.189999, "high50": 54.189999, "low20": 51.029999, "low50": 49.849998}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 2795.732764, "BB_lo": 1802.401318, "Close": 2391.500977, "EMA20": 2315.842983, "EMA200": 2165.750484, "EMA50": 2125.223481, "EMA9": 2416.411271, "High": 2427.401611, "Low": 2356.188232, "Open": 2417.828369, "RSI14": 61.419955, "Ret": -0.010894, "SMA20": 2299.067041, "SMA50": 2053.502986, "Volume": 14227785690.0, "_provenance": {"captured_at_ist": "2026-09-04 00:18:23 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "bceb614e24f483f8b97a38b58fddecc676f19d19395d1082c77cf9b320b6f87a"}, "high20": 2564.274414, "high50": 2564.274414, "low20": 1861.92041, "low50": 1772.0177}</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>#5SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#14SW Price&gt;SMA50+Range&gt;1.5%+2Red | 🎯 Target Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>04:45:09 IST</t>
+          <t>00:20:14 IST</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>SOL-USD</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>103.03</v>
+        <v>52.08</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>630</v>
+        <v>966</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>104.73</v>
+        <v>51.03</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>100.08</v>
+        <v>54.15</v>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>102.43</v>
+        <v>52.43</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 16:46:47 IST</t>
+          <t>2026-09-08 00:47:43 IST</t>
         </is>
       </c>
       <c r="N24" s="4" t="n">
-        <v>375.85</v>
+        <v>342.69</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>194.73</v>
+        <v>10.06</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>181.12</v>
+        <v>332.63</v>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>0.28</v>
+        <v>0.66</v>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
@@ -16277,97 +16275,97 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>47.24</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t>{"2Red": 1.0, "Close": 103.18, "EMA20": 103.411299, "EMA50": 103.800477, "EMA9": 103.432655, "High": 103.779999, "Low": 103.099998, "Open": 103.720001, "RSI14": 47.470892, "Ret": -0.004438, "SMA20": 103.072001, "SMA50": 104.206801, "Volume": 1157376.0, "_provenance": {"captured_at_ist": "2026-09-01 04:45:09 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "ef6d7a045ffc2750af734b317d97fc5a28f2a347c94512fa8743ba341861e0eb"}}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 53.933542, "BB_lo": 51.668459, "Close": 52.07, "EMA20": 52.631511, "EMA200": 49.788698, "EMA50": 52.014955, "EMA9": 52.846097, "High": 52.459999, "Low": 52.02, "Open": 52.439999, "RSI14": 46.449627, "Ret": -0.011767, "SMA20": 52.801, "SMA50": 51.74, "Volume": 15500500.0, "_provenance": {"captured_at_ist": "2026-09-03 00:20:14 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "4c008560e6adf2a2b92f03ff3aba914bff4c1422744acab60897e94b0403e513"}, "high20": 54.189999, "high50": 54.189999, "low20": 51.029999, "low50": 49.849998}</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>#1ID EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50 | Expiry 12h</t>
+          <t>#5SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>20:17:47 IST</t>
+          <t>04:45:09 IST</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>SOL-USD</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>171.18</v>
+        <v>103.03</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>299</v>
+        <v>630</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>167.74</v>
+        <v>104.73</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>178.01</v>
+        <v>100.08</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>171.43</v>
+        <v>102.43</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05 05:30:00 IST</t>
+          <t>2026-09-01 16:46:47 IST</t>
         </is>
       </c>
       <c r="N25" s="4" t="n">
-        <v>75.59999999999999</v>
+        <v>375.85</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>10.24</v>
+        <v>194.73</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>65.36</v>
+        <v>181.12</v>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
@@ -16376,27 +16374,27 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>47.24</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 177.80833, "BB_lo": 160.692668, "Close": 171.160004, "EMA20": 169.767931, "EMA200": 153.951283, "EMA50": 164.324372, "EMA9": 172.083661, "High": 171.710007, "Low": 170.589996, "Open": 171.429993, "RSI14": 57.156114, "Ret": -0.002448, "SMA20": 169.250499, "SMA50": 163.729879, "Volume": 4879300.0, "_provenance": {"captured_at_ist": "2026-08-31 20:17:47 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "9c5b13218a3d2ce328cb2f2e7d32803533390f839d04812e416383140bb7e387"}, "high20": 176.600006, "high50": 176.600006, "low20": 160.729996, "low50": 148.136666}</t>
+          <t>{"2Red": 1.0, "Close": 103.18, "EMA20": 103.411299, "EMA50": 103.800477, "EMA9": 103.432655, "High": 103.779999, "Low": 103.099998, "Open": 103.720001, "RSI14": 47.470892, "Ret": -0.004438, "SMA20": 103.072001, "SMA50": 104.206801, "Volume": 1157376.0, "_provenance": {"captured_at_ist": "2026-09-01 04:45:09 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "ef6d7a045ffc2750af734b317d97fc5a28f2a347c94512fa8743ba341861e0eb"}}</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#1ID EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50 | Expiry 12h</t>
         </is>
       </c>
     </row>
@@ -16418,7 +16416,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -16432,16 +16430,16 @@
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>62.69</v>
+        <v>171.18</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>818</v>
+        <v>299</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>61.43</v>
+        <v>167.74</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>65.19</v>
+        <v>178.01</v>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
@@ -16449,24 +16447,24 @@
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>65.18000000000001</v>
+        <v>171.43</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:56:58 IST</t>
+          <t>2026-09-05 05:30:00 IST</t>
         </is>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2039.67</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>10.26</v>
+        <v>10.24</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>2029.41</v>
-      </c>
-      <c r="Q26" s="5" t="n">
-        <v>3.96</v>
+        <v>65.36</v>
+      </c>
+      <c r="Q26" s="12" t="n">
+        <v>0.13</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
@@ -16475,39 +16473,39 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA50+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 65.566256, "BB_lo": 56.952745, "Close": 62.68, "EMA20": 61.482668, "EMA200": 54.449219, "EMA50": 59.472604, "EMA9": 62.477193, "High": 62.740002, "Low": 62.119999, "Open": 62.349998, "RSI14": 62.129968, "Ret": 0.006261, "SMA20": 61.259501, "SMA50": 58.1441, "Volume": 20599600.0, "_provenance": {"captured_at_ist": "2026-08-31 20:17:47 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "f528add80b6c836a8e80c29430bea8d83def03a9307763f51342341e85b6e147"}, "high20": 64.699997, "high50": 64.699997, "low20": 57.110001, "low50": 52.619999}</t>
+          <t>{"2Green": 0.0, "2Red": 1.0, "BB_hi": 177.80833, "BB_lo": 160.692668, "Close": 171.160004, "EMA20": 169.767931, "EMA200": 153.951283, "EMA50": 164.324372, "EMA9": 172.083661, "High": 171.710007, "Low": 170.589996, "Open": 171.429993, "RSI14": 57.156114, "Ret": -0.002448, "SMA20": 169.250499, "SMA50": 163.729879, "Volume": 4879300.0, "_provenance": {"captured_at_ist": "2026-08-31 20:17:47 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "9c5b13218a3d2ce328cb2f2e7d32803533390f839d04812e416383140bb7e387"}, "high20": 176.600006, "high50": 176.600006, "low20": 160.729996, "low50": 148.136666}</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>#3SW EMA9&gt;EMA50+Range&lt;1% | Target Hit</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>01:26:29 IST</t>
+          <t>20:17:47 IST</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -16517,7 +16515,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -16527,45 +16525,45 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>767.04</v>
+        <v>62.69</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>136</v>
+        <v>818</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>759.22</v>
+        <v>61.43</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>782.23</v>
+        <v>65.19</v>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>769.79</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 00:57:20 IST</t>
+          <t>2026-09-03 00:56:58 IST</t>
         </is>
       </c>
       <c r="N27" s="4" t="n">
-        <v>373.46</v>
+        <v>2039.67</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>20.86</v>
+        <v>10.26</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>352.6</v>
-      </c>
-      <c r="Q27" s="12" t="n">
-        <v>0.34</v>
+        <v>2029.41</v>
+      </c>
+      <c r="Q27" s="5" t="n">
+        <v>3.96</v>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
@@ -16574,27 +16572,27 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>62.35</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
+          <t>EMA9&gt;EMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t>{"2Red": 0.0, "Close": 766.890015, "EMA20": 765.466694, "EMA50": 766.617135, "EMA9": 765.635192, "High": 767.349976, "Low": 765.52002, "Open": 765.609985, "RSI14": 55.731638, "Ret": 0.001672, "SMA20": 764.880759, "SMA50": 766.460079, "Volume": 3674140.0, "_provenance": {"captured_at_ist": "2026-08-27 01:26:29 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "3784c4c96c4bf403350ccfce032c365669554989a59e5f375dc6129ba567d139"}}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 65.566256, "BB_lo": 56.952745, "Close": 62.68, "EMA20": 61.482668, "EMA200": 54.449219, "EMA50": 59.472604, "EMA9": 62.477193, "High": 62.740002, "Low": 62.119999, "Open": 62.349998, "RSI14": 62.129968, "Ret": 0.006261, "SMA20": 61.259501, "SMA50": 58.1441, "Volume": 20599600.0, "_provenance": {"captured_at_ist": "2026-08-31 20:17:47 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "f528add80b6c836a8e80c29430bea8d83def03a9307763f51342341e85b6e147"}, "high20": 64.699997, "high50": 64.699997, "low20": 57.110001, "low50": 52.619999}</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>#16ID Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | Expiry 6h</t>
+          <t>#3SW EMA9&gt;EMA50+Range&lt;1% | Target Hit</t>
         </is>
       </c>
     </row>
@@ -16606,7 +16604,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>01:26:20 IST</t>
+          <t>01:26:29 IST</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -16616,7 +16614,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -16626,45 +16624,45 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>86.53</v>
+        <v>767.04</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>596</v>
+        <v>136</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>84.79000000000001</v>
+        <v>759.22</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>89.98</v>
+        <v>782.23</v>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>85.03</v>
+        <v>769.79</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 01:27:38 IST</t>
+          <t>2026-08-28 00:57:20 IST</t>
         </is>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-893.11</v>
+        <v>373.46</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v>-903.42</v>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v>-1.75</v>
+        <v>20.86</v>
+      </c>
+      <c r="P28" s="5" t="n">
+        <v>352.6</v>
+      </c>
+      <c r="Q28" s="12" t="n">
+        <v>0.34</v>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
@@ -16673,27 +16671,27 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>62.35</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>Range&lt;1%+SMA20&lt;EMA20</t>
+          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 87.262889, "BB_lo": 83.993112, "Close": 86.519997, "EMA20": 85.651886, "EMA200": 82.697308, "EMA50": 84.933173, "EMA9": 86.092409, "High": 87.010002, "Low": 86.25, "Open": 86.860001, "RSI14": 55.279506, "Ret": -0.010635, "SMA20": 85.628, "SMA50": 84.784211, "Volume": 7022700.0, "_provenance": {"captured_at_ist": "2026-08-27 01:26:20 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "4ec100efbb7eae0f145aebe59fea065b45da569430baeb0ea99b3a12db3915e9"}, "high20": 88.779999, "high50": 88.779999, "low20": 83.860001, "low50": 82.150002}</t>
+          <t>{"2Red": 0.0, "Close": 766.890015, "EMA20": 765.466694, "EMA50": 766.617135, "EMA9": 765.635192, "High": 767.349976, "Low": 765.52002, "Open": 765.609985, "RSI14": 55.731638, "Ret": 0.001672, "SMA20": 764.880759, "SMA50": 766.460079, "Volume": 3674140.0, "_provenance": {"captured_at_ist": "2026-08-27 01:26:29 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "3784c4c96c4bf403350ccfce032c365669554989a59e5f375dc6129ba567d139"}}</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>#5SW Range&lt;1%+SMA20&lt;EMA20 | Expiry 5d</t>
+          <t>#16ID Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -16715,7 +16713,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -16729,16 +16727,16 @@
         </is>
       </c>
       <c r="G29" s="4" t="n">
-        <v>113.19</v>
+        <v>86.53</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>456</v>
+        <v>596</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>110.92</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>117.71</v>
+        <v>89.98</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
@@ -16746,7 +16744,7 @@
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>111.54</v>
+        <v>85.03</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
@@ -16754,16 +16752,16 @@
         </is>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-750.65</v>
+        <v>-893.11</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>10.32</v>
+        <v>10.31</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-760.97</v>
+        <v>-903.42</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>-1.47</v>
+        <v>-1.75</v>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
@@ -16772,39 +16770,39 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>58.26</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;EMA9+Range&lt;1%</t>
+          <t>Range&lt;1%+SMA20&lt;EMA20</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 114.093707, "BB_lo": 107.914293, "Close": 113.18, "EMA20": 111.174983, "EMA200": 111.655481, "EMA50": 111.050282, "EMA9": 111.73869, "High": 113.275002, "Low": 112.294998, "Open": 112.410004, "RSI14": 58.133522, "Ret": 0.007657, "SMA20": 111.004, "SMA50": 110.009402, "Volume": 2701500.0, "_provenance": {"captured_at_ist": "2026-08-27 01:26:20 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "6517b7ae823c6f80e30c2d50df07393a2cb922775b5ebecb2ca0cf654bc08aff"}, "high20": 113.5, "high50": 114.029999, "low20": 105.492996, "low50": 105.029999}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 87.262889, "BB_lo": 83.993112, "Close": 86.519997, "EMA20": 85.651886, "EMA200": 82.697308, "EMA50": 84.933173, "EMA9": 86.092409, "High": 87.010002, "Low": 86.25, "Open": 86.860001, "RSI14": 55.279506, "Ret": -0.010635, "SMA20": 85.628, "SMA50": 84.784211, "Volume": 7022700.0, "_provenance": {"captured_at_ist": "2026-08-27 01:26:20 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "4ec100efbb7eae0f145aebe59fea065b45da569430baeb0ea99b3a12db3915e9"}, "high20": 88.779999, "high50": 88.779999, "low20": 83.860001, "low50": 82.150002}</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>#3SW Price&gt;EMA9+Range&lt;1% | Expiry 5d</t>
+          <t>#5SW Range&lt;1%+SMA20&lt;EMA20 | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>00:19:41 IST</t>
+          <t>01:26:20 IST</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -16814,7 +16812,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -16828,16 +16826,16 @@
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>377.11</v>
+        <v>113.19</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>133</v>
+        <v>456</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>369.53</v>
+        <v>110.92</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>392.15</v>
+        <v>117.71</v>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
@@ -16845,24 +16843,24 @@
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>379.32</v>
+        <v>111.54</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31 12:20:47 IST</t>
+          <t>2026-09-01 01:27:38 IST</t>
         </is>
       </c>
       <c r="N30" s="4" t="n">
-        <v>294.2</v>
+        <v>-750.65</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>284.17</v>
-      </c>
-      <c r="Q30" s="12" t="n">
-        <v>0.57</v>
+        <v>10.32</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v>-760.97</v>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v>-1.47</v>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
@@ -16876,34 +16874,34 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>Range&lt;1%+SMA20&lt;EMA20</t>
+          <t>Price&gt;EMA9+Range&lt;1%</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 390.418284, "BB_lo": 363.717712, "Close": 377.070007, "EMA20": 377.20007, "EMA200": 349.68499, "EMA50": 371.828667, "EMA9": 378.840176, "High": 378.0, "Low": 376.480011, "Open": 377.920013, "RSI14": 52.14451, "Ret": -0.003093, "SMA20": 377.067998, "SMA50": 371.565996, "Volume": 2963600.0, "_provenance": {"captured_at_ist": "2026-08-26 00:19:41 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "7d4507f7724401cf8e473ac67923b34d856a349cb42c70c444777355cfcb7c9b"}, "high20": 385.119995, "high50": 385.119995, "low20": 360.200012, "low50": 356.723865}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 114.093707, "BB_lo": 107.914293, "Close": 113.18, "EMA20": 111.174983, "EMA200": 111.655481, "EMA50": 111.050282, "EMA9": 111.73869, "High": 113.275002, "Low": 112.294998, "Open": 112.410004, "RSI14": 58.133522, "Ret": 0.007657, "SMA20": 111.004, "SMA50": 110.009402, "Volume": 2701500.0, "_provenance": {"captured_at_ist": "2026-08-27 01:26:20 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "6517b7ae823c6f80e30c2d50df07393a2cb922775b5ebecb2ca0cf654bc08aff"}, "high20": 113.5, "high50": 114.029999, "low20": 105.492996, "low50": 105.029999}</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>#3SW Range&lt;1%+SMA20&lt;EMA20 | Expiry 5d</t>
+          <t>#3SW Price&gt;EMA9+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>00:21:29 IST</t>
+          <t>00:19:41 IST</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -16913,7 +16911,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>VTI</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -16927,16 +16925,16 @@
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>174.55</v>
+        <v>377.11</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>275</v>
+        <v>133</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>171.04</v>
+        <v>369.53</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>181.51</v>
+        <v>392.15</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
@@ -16944,24 +16942,24 @@
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>171.02</v>
+        <v>379.32</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:08:12 IST</t>
+          <t>2026-08-31 12:20:47 IST</t>
         </is>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-969.95</v>
+        <v>294.2</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v>-979.55</v>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v>-2.04</v>
+        <v>10.03</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>284.17</v>
+      </c>
+      <c r="Q31" s="12" t="n">
+        <v>0.57</v>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
@@ -16970,39 +16968,39 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>Range&lt;1%+SMA20&lt;EMA20</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 175.864131, "BB_lo": 159.419869, "Close": 174.529999, "EMA20": 168.30809, "EMA200": 154.030413, "EMA50": 162.961143, "EMA9": 171.440751, "High": 174.830002, "Low": 173.330002, "Open": 174.410004, "RSI14": 68.059204, "Ret": -0.000515, "SMA20": 167.642, "SMA50": 162.1152, "Volume": 4415397.0, "_provenance": {"captured_at_ist": "2026-08-25 00:21:29 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "0e5a554d6cdf867147a863dbaa87285229b6bdde8405ef04e62d923f28408cf2"}, "high20": 176.600006, "high50": 176.600006, "low20": 160.729996, "low50": 148.789993}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 390.418284, "BB_lo": 363.717712, "Close": 377.070007, "EMA20": 377.20007, "EMA200": 349.68499, "EMA50": 371.828667, "EMA9": 378.840176, "High": 378.0, "Low": 376.480011, "Open": 377.920013, "RSI14": 52.14451, "Ret": -0.003093, "SMA20": 377.067998, "SMA50": 371.565996, "Volume": 2963600.0, "_provenance": {"captured_at_ist": "2026-08-26 00:19:41 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "7d4507f7724401cf8e473ac67923b34d856a349cb42c70c444777355cfcb7c9b"}, "high20": 385.119995, "high50": 385.119995, "low20": 360.200012, "low50": 356.723865}</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | ðŸŽ¯ SL Hit (live)</t>
+          <t>#3SW Range&lt;1%+SMA20&lt;EMA20 | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>07:49:44 IST</t>
+          <t>00:21:29 IST</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -17012,7 +17010,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -17026,16 +17024,16 @@
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>713.51</v>
+        <v>174.55</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>68</v>
+        <v>275</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>699.17</v>
+        <v>171.04</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>741.98</v>
+        <v>181.51</v>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
@@ -17043,24 +17041,24 @@
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>716.36</v>
+        <v>171.02</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 08:16:22 IST</t>
+          <t>2026-08-28 21:08:12 IST</t>
         </is>
       </c>
       <c r="N32" s="4" t="n">
-        <v>193.69</v>
+        <v>-969.95</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>183.99</v>
-      </c>
-      <c r="Q32" s="12" t="n">
-        <v>0.38</v>
+        <v>9.6</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v>-979.55</v>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v>-2.04</v>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
@@ -17069,39 +17067,39 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>RSI&gt;50+SMA20&lt;SMA50</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 749.746157, "BB_lo": 668.630845, "Close": 713.440002, "EMA20": 714.415351, "EMA200": 659.614421, "EMA50": 708.78849, "EMA9": 717.391898, "High": 715.669983, "Low": 709.200012, "Open": 715.22998, "RSI14": 50.149844, "Ret": 0.003531, "SMA20": 709.188501, "SMA50": 713.441602, "Volume": 33297600.0, "_provenance": {"captured_at_ist": "2026-08-24 07:49:44 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "89a195f1c565d7eeec6103b45df5fc0c4a8cd08b92109c8f6c78f6dbe7e34347"}, "high20": 734.580017, "high50": 745.450012, "low20": 661.140015, "low50": 661.140015}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 175.864131, "BB_lo": 159.419869, "Close": 174.529999, "EMA20": 168.30809, "EMA200": 154.030413, "EMA50": 162.961143, "EMA9": 171.440751, "High": 174.830002, "Low": 173.330002, "Open": 174.410004, "RSI14": 68.059204, "Ret": -0.000515, "SMA20": 167.642, "SMA50": 162.1152, "Volume": 4415397.0, "_provenance": {"captured_at_ist": "2026-08-25 00:21:29 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "0e5a554d6cdf867147a863dbaa87285229b6bdde8405ef04e62d923f28408cf2"}, "high20": 176.600006, "high50": 176.600006, "low20": 160.729996, "low50": 148.789993}</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>#66SW RSI&gt;50+SMA20&lt;SMA50 | Expiry 5d</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | ðŸŽ¯ SL Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>07:51:10 IST</t>
+          <t>07:49:44 IST</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -17111,7 +17109,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -17125,16 +17123,16 @@
         </is>
       </c>
       <c r="G33" s="4" t="n">
-        <v>45.08</v>
+        <v>713.51</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1105</v>
+        <v>68</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>44.18</v>
+        <v>699.17</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>46.88</v>
+        <v>741.98</v>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
@@ -17142,24 +17140,24 @@
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>44.66</v>
+        <v>716.36</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 09:07:28 IST</t>
+          <t>2026-08-29 08:16:22 IST</t>
         </is>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-469.04</v>
+        <v>193.69</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v>-479</v>
-      </c>
-      <c r="Q33" s="13" t="n">
-        <v>-0.96</v>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>183.99</v>
+      </c>
+      <c r="Q33" s="12" t="n">
+        <v>0.38</v>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
@@ -17168,27 +17166,27 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>66</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&lt;Open</t>
+          <t>RSI&gt;50+SMA20&lt;SMA50</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 46.03132, "BB_lo": 44.109681, "Close": 45.080002, "EMA20": 44.957695, "EMA200": 43.466243, "EMA50": 44.780011, "EMA9": 44.94812, "High": 45.255001, "Low": 44.933998, "Open": 45.200001, "RSI14": 51.888379, "Ret": 0.0, "SMA20": 45.0705, "SMA50": 44.8678, "Volume": 3968900.0, "_provenance": {"captured_at_ist": "2026-08-23 07:51:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "45c6a11f08d41357e9b6038a6644a0c54ee887b4d9d2010526bd8ea4b0ea5250"}, "high20": 46.455002, "high50": 46.455002, "low20": 44.009998, "low50": 43.48}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 749.746157, "BB_lo": 668.630845, "Close": 713.440002, "EMA20": 714.415351, "EMA200": 659.614421, "EMA50": 708.78849, "EMA9": 717.391898, "High": 715.669983, "Low": 709.200012, "Open": 715.22998, "RSI14": 50.149844, "Ret": 0.003531, "SMA20": 709.188501, "SMA50": 713.441602, "Volume": 33297600.0, "_provenance": {"captured_at_ist": "2026-08-24 07:49:44 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "89a195f1c565d7eeec6103b45df5fc0c4a8cd08b92109c8f6c78f6dbe7e34347"}, "high20": 734.580017, "high50": 745.450012, "low20": 661.140015, "low50": 661.140015}</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>#57SW Price&gt;SMA20+EMA9&lt;EMA20+Close&lt;Open | Expiry 5d</t>
+          <t>#66SW RSI&gt;50+SMA20&lt;SMA50 | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -17205,12 +17203,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -17223,17 +17221,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G34" s="10" t="n">
-        <v>0.3462</v>
+      <c r="G34" s="4" t="n">
+        <v>45.08</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I34" s="11" t="n">
-        <v>0.3382</v>
-      </c>
-      <c r="J34" s="11" t="n">
-        <v>0.3589</v>
+        <v>1105</v>
+      </c>
+      <c r="I34" s="8" t="n">
+        <v>44.18</v>
+      </c>
+      <c r="J34" s="8" t="n">
+        <v>46.88</v>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
@@ -17241,24 +17239,24 @@
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0.3372</v>
+        <v>44.66</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 02:06:32 IST</t>
+          <t>2026-08-28 09:07:28 IST</t>
         </is>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-90.15000000000001</v>
+        <v>-469.04</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>10.39</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-100.54</v>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v>-2.9</v>
+        <v>-479</v>
+      </c>
+      <c r="Q34" s="13" t="n">
+        <v>-0.96</v>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
@@ -17267,27 +17265,27 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>57</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&lt;Open</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 0.342604, "BB_lo": 0.322249, "Close": 0.345137, "EMA20": 0.333753, "EMA200": 0.322532, "EMA50": 0.330808, "EMA9": 0.337211, "High": 0.345367, "Low": 0.34419, "Open": 0.344229, "RSI14": 75.347643, "Ret": 0.005205, "SMA20": 0.332427, "SMA50": 0.329547, "Volume": 896564352.0, "_provenance": {"captured_at_ist": "2026-08-23 07:51:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "841d75978c0b90d3d955daa219375d748b86c110612710892971f186fbc6b405"}, "high20": 0.34335, "high50": 0.34335, "low20": 0.325217, "low50": 0.316794}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 46.03132, "BB_lo": 44.109681, "Close": 45.080002, "EMA20": 44.957695, "EMA200": 43.466243, "EMA50": 44.780011, "EMA9": 44.94812, "High": 45.255001, "Low": 44.933998, "Open": 45.200001, "RSI14": 51.888379, "Ret": 0.0, "SMA20": 45.0705, "SMA50": 44.8678, "Volume": 3968900.0, "_provenance": {"captured_at_ist": "2026-08-23 07:51:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "45c6a11f08d41357e9b6038a6644a0c54ee887b4d9d2010526bd8ea4b0ea5250"}, "high20": 46.455002, "high50": 46.455002, "low20": 44.009998, "low50": 43.48}</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | ðŸŽ¯ SL Hit (live)</t>
+          <t>#57SW Price&gt;SMA20+EMA9&lt;EMA20+Close&lt;Open | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -17304,12 +17302,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -17322,17 +17320,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
-        <v>377.9</v>
+      <c r="G35" s="10" t="n">
+        <v>0.3462</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>130</v>
-      </c>
-      <c r="I35" s="8" t="n">
-        <v>370.3</v>
-      </c>
-      <c r="J35" s="8" t="n">
-        <v>392.97</v>
+        <v>10000</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="J35" s="11" t="n">
+        <v>0.3589</v>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
@@ -17340,24 +17338,24 @@
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>380.85</v>
+        <v>0.3372</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 09:07:28 IST</t>
+          <t>2026-08-26 02:06:32 IST</t>
         </is>
       </c>
       <c r="N35" s="4" t="n">
-        <v>383.75</v>
+        <v>-90.15000000000001</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v>373.92</v>
-      </c>
-      <c r="Q35" s="12" t="n">
-        <v>0.76</v>
+        <v>10.39</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v>-100.54</v>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v>-2.9</v>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
@@ -17366,39 +17364,39 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 391.993875, "BB_lo": 360.752118, "Close": 377.859985, "EMA20": 377.034739, "EMA200": 351.317404, "EMA50": 371.633734, "EMA9": 379.076055, "High": 379.179993, "Low": 376.839996, "Open": 377.890015, "RSI14": 53.807886, "Ret": 0.003106, "SMA20": 376.372997, "SMA50": 370.408998, "Volume": 141700.0, "_provenance": {"captured_at_ist": "2026-08-23 07:51:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "dc46343d0c2668e3d0437189c8457963c0a5445a4be1eb6c84facfbc8ebd4d16"}, "high20": 384.820007, "high50": 384.820007, "low20": 358.170013, "low50": 354.809998}</t>
+          <t>{"2Green": 1.0, "2Red": 0.0, "BB_hi": 0.342604, "BB_lo": 0.322249, "Close": 0.345137, "EMA20": 0.333753, "EMA200": 0.322532, "EMA50": 0.330808, "EMA9": 0.337211, "High": 0.345367, "Low": 0.34419, "Open": 0.344229, "RSI14": 75.347643, "Ret": 0.005205, "SMA20": 0.332427, "SMA50": 0.329547, "Volume": 896564352.0, "_provenance": {"captured_at_ist": "2026-08-23 07:51:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "841d75978c0b90d3d955daa219375d748b86c110612710892971f186fbc6b405"}, "high20": 0.34335, "high50": 0.34335, "low20": 0.325217, "low50": 0.316794}</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | ðŸŽ¯ SL Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>00:19:34 IST</t>
+          <t>07:51:10 IST</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -17408,7 +17406,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -17422,16 +17420,16 @@
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>63.56</v>
+        <v>377.9</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>782</v>
+        <v>130</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>62.28</v>
+        <v>370.3</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>66.09999999999999</v>
+        <v>392.97</v>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
@@ -17439,24 +17437,24 @@
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>63.62</v>
+        <v>380.85</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24 00:57:24 IST</t>
+          <t>2026-08-28 09:07:28 IST</t>
         </is>
       </c>
       <c r="N36" s="4" t="n">
-        <v>45.85</v>
+        <v>383.75</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>9.94</v>
+        <v>9.83</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>35.91</v>
+        <v>373.92</v>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
@@ -17465,27 +17463,27 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>59.53</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA50+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t>{"EMA200": 54.253942, "Open": 63.41, "2Red": 0.0, "Volume": 20822618.0, "EMA20": 59.820197, "BB_lo": 56.181538, "EMA50": 58.261513, "SMA50": 57.1629, "low20": 57.110001, "RSI14": 72.551139, "low50": 52.619999, "EMA9": 61.242966, "2Green": 1.0, "Ret": 0.01558, "Low": 63.115002, "high50": 62.689999, "High": 63.709999, "Close": 63.555, "BB_hi": 63.099963, "SMA20": 59.64075, "high20": 62.689999}</t>
+          <t>{"2Green": 0.0, "2Red": 0.0, "BB_hi": 391.993875, "BB_lo": 360.752118, "Close": 377.859985, "EMA20": 377.034739, "EMA200": 351.317404, "EMA50": 371.633734, "EMA9": 379.076055, "High": 379.179993, "Low": 376.839996, "Open": 377.890015, "RSI14": 53.807886, "Ret": 0.003106, "SMA20": 376.372997, "SMA50": 370.408998, "Volume": 141700.0, "_provenance": {"captured_at_ist": "2026-08-23 07:51:10 IST", "provider": "market_data.download", "provider_chain": ["yfinance", "yahoo_chart", "nasdaq_or_binance", "ohlc_cache"], "snapshot_sha256": "dc46343d0c2668e3d0437189c8457963c0a5445a4be1eb6c84facfbc8ebd4d16"}, "high20": 384.820007, "high50": 384.820007, "low20": 358.170013, "low50": 354.809998}</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>#3SW EMA9&gt;EMA50+Range&lt;1% | Expiry 5d</t>
+          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -17497,7 +17495,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>00:19:33 IST</t>
+          <t>00:19:34 IST</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -17507,7 +17505,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -17521,16 +17519,16 @@
         </is>
       </c>
       <c r="G37" s="4" t="n">
-        <v>717.71</v>
+        <v>63.56</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>69</v>
+        <v>782</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>703.29</v>
+        <v>62.28</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>746.35</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
@@ -17538,7 +17536,7 @@
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>713.34</v>
+        <v>63.62</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
@@ -17546,16 +17544,16 @@
         </is>
       </c>
       <c r="N37" s="4" t="n">
-        <v>-301.62</v>
+        <v>45.85</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v>-311.52</v>
-      </c>
-      <c r="Q37" s="13" t="n">
-        <v>-0.63</v>
+        <v>9.94</v>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>35.91</v>
+      </c>
+      <c r="Q37" s="12" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
@@ -17564,39 +17562,39 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>60.94</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA9&gt;EMA20+2Red</t>
+          <t>EMA9&gt;EMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>{"EMA200": 658.01956, "Open": 720.219971, "2Red": 1.0, "Volume": 38190856.0, "EMA20": 714.783424, "BB_lo": 663.9257, "EMA50": 708.199326, "SMA50": 712.987002, "low20": 661.140015, "RSI14": 52.242633, "low50": 661.140015, "EMA9": 721.308924, "2Green": 0.0, "Ret": -0.016756, "Low": 715.919983, "high50": 745.450012, "High": 722.130005, "Close": 717.640015, "BB_hi": 748.573299, "SMA20": 706.2495, "high20": 734.580017}</t>
+          <t>{"EMA200": 54.253942, "Open": 63.41, "2Red": 0.0, "Volume": 20822618.0, "EMA20": 59.820197, "BB_lo": 56.181538, "EMA50": 58.261513, "SMA50": 57.1629, "low20": 57.110001, "RSI14": 72.551139, "low50": 52.619999, "EMA9": 61.242966, "2Green": 1.0, "Ret": 0.01558, "Low": 63.115002, "high50": 62.689999, "High": 63.709999, "Close": 63.555, "BB_hi": 63.099963, "SMA20": 59.64075, "high20": 62.689999}</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>#37SW Price&gt;SMA50+EMA9&gt;EMA20+2Red | Expiry 5d</t>
+          <t>#3SW EMA9&gt;EMA50+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>00:20:52 IST</t>
+          <t>00:19:33 IST</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -17606,7 +17604,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -17620,16 +17618,16 @@
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>380.99</v>
+        <v>717.71</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>373.33</v>
+        <v>703.29</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>396.19</v>
+        <v>746.35</v>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
@@ -17637,24 +17635,24 @@
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>377.74</v>
+        <v>713.34</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23 00:57:48 IST</t>
+          <t>2026-08-24 00:57:24 IST</t>
         </is>
       </c>
       <c r="N38" s="4" t="n">
-        <v>-438.45</v>
+        <v>-301.62</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>10.29</v>
+        <v>9.9</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-448.74</v>
+        <v>-311.52</v>
       </c>
       <c r="Q38" s="13" t="n">
-        <v>-0.87</v>
+        <v>-0.63</v>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
@@ -17663,49 +17661,49 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>37</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>60.94</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+EMA9&gt;EMA20+2Red</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t>{"2Green": 0.0, "BB_lo": 356.336918, "BB_hi": 391.566088, "EMA50": 370.481576, "SMA50": 369.201801, "high20": 384.820007, "low50": 354.809998, "Open": 382.649994, "Volume": 101666.0, "2Red": 1.0, "EMA200": 350.231559, "RSI14": 60.286192, "low20": 358.170013, "Ret": -0.00413, "EMA20": 376.443558, "high50": 384.820007, "Low": 380.609985, "Close": 380.950104, "EMA9": 380.399819, "SMA20": 373.951503, "High": 382.875}</t>
+          <t>{"EMA200": 658.01956, "Open": 720.219971, "2Red": 1.0, "Volume": 38190856.0, "EMA20": 714.783424, "BB_lo": 663.9257, "EMA50": 708.199326, "SMA50": 712.987002, "low20": 661.140015, "RSI14": 52.242633, "low50": 661.140015, "EMA9": 721.308924, "2Green": 0.0, "Ret": -0.016756, "Low": 715.919983, "high50": 745.450012, "High": 722.130005, "Close": 717.640015, "BB_hi": 748.573299, "SMA20": 706.2495, "high20": 734.580017}</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#37SW Price&gt;SMA50+EMA9&gt;EMA20+2Red | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>11:52:58 IST</t>
+          <t>00:20:52 IST</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>VASWANI.NS</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -17715,45 +17713,45 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>LONG_BOUNCE_5m</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v>46.63</v>
+        <v>380.99</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1333</v>
+        <v>135</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>45.88</v>
+        <v>373.33</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>48.33</v>
+        <v>396.19</v>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>45.83</v>
+        <v>377.74</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17 12:09:41 IST</t>
+          <t>2026-08-23 00:57:48 IST</t>
         </is>
       </c>
       <c r="N39" s="4" t="n">
-        <v>-1066.4</v>
+        <v>-438.45</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>186.47</v>
+        <v>10.29</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-1252.87</v>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v>-2.02</v>
+        <v>-448.74</v>
+      </c>
+      <c r="Q39" s="13" t="n">
+        <v>-0.87</v>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
@@ -17762,27 +17760,27 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>59.53</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t>Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down 10:30-12:30</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t>{"Close": 46.58, "Volume": 1153, "VolAvg20": 237.0, "RSI14": 31.4, "Drop_pct": 8.31, "BelowVWAP": true, "VWAPDown": true, "NIFTY_gap_pct": -0.09}</t>
+          <t>{"2Green": 0.0, "BB_lo": 356.336918, "BB_hi": 391.566088, "EMA50": 370.481576, "SMA50": 369.201801, "high20": 384.820007, "low50": 354.809998, "Open": 382.649994, "Volume": 101666.0, "2Red": 1.0, "EMA200": 350.231559, "RSI14": 60.286192, "low20": 358.170013, "Ret": -0.00413, "EMA20": 376.443558, "high50": 384.820007, "Low": 380.609985, "Close": 380.950104, "EMA9": 380.399819, "SMA20": 373.951503, "High": 382.875}</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>#935ID Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down | ðŸŽ¯ SL Hit (live)</t>
+          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -17794,7 +17792,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>11:10:50 IST</t>
+          <t>11:52:58 IST</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -17804,7 +17802,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>LAXMIINDIA.NS</t>
+          <t>VASWANI.NS</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -17818,16 +17816,16 @@
         </is>
       </c>
       <c r="G40" s="4" t="n">
-        <v>124.98</v>
+        <v>46.63</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>510</v>
+        <v>1333</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>123.02</v>
+        <v>45.88</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>129.57</v>
+        <v>48.33</v>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
@@ -17835,24 +17833,24 @@
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>129.47</v>
+        <v>45.83</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17 14:43:12 IST</t>
+          <t>2026-08-17 12:09:41 IST</t>
         </is>
       </c>
       <c r="N40" s="4" t="n">
-        <v>2289.9</v>
+        <v>-1066.4</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>191.22</v>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v>2098.68</v>
-      </c>
-      <c r="Q40" s="5" t="n">
-        <v>3.29</v>
+        <v>186.47</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v>-1252.87</v>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v>-2.02</v>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
@@ -17876,34 +17874,34 @@
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t>{"Close": 124.89, "Volume": 16581, "VolAvg20": 2144.0, "RSI14": 40.9, "Drop_pct": 3.7, "BelowVWAP": true, "VWAPDown": true, "NIFTY_gap_pct": -0.09}</t>
+          <t>{"Close": 46.58, "Volume": 1153, "VolAvg20": 237.0, "RSI14": 31.4, "Drop_pct": 8.31, "BelowVWAP": true, "VWAPDown": true, "NIFTY_gap_pct": -0.09}</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>#935ID Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down | ðŸŽ¯ Target Hit (live)</t>
+          <t>#935ID Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down | ðŸŽ¯ SL Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>07:48:23 IST</t>
+          <t>11:10:50 IST</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>LAXMIINDIA.NS</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -17913,45 +17911,45 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>LONG_BOUNCE_5m</t>
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1880</v>
+        <v>124.98</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>25</v>
+        <v>510</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>1840.56</v>
+        <v>123.02</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>1953.24</v>
+        <v>129.57</v>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1951.29</v>
+        <v>129.47</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 20:30:05 IST</t>
+          <t>2026-08-17 14:43:12 IST</t>
         </is>
       </c>
       <c r="N41" s="4" t="n">
-        <v>1782.17</v>
+        <v>2289.9</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>141</v>
+        <v>191.22</v>
       </c>
       <c r="P41" s="5" t="n">
-        <v>1641.17</v>
+        <v>2098.68</v>
       </c>
       <c r="Q41" s="5" t="n">
-        <v>3.49</v>
+        <v>3.29</v>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
@@ -17960,27 +17958,27 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
+          <t>Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down 10:30-12:30</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>{"High": 1881.228882, "Ret": -0.001345, "low20": 1821.485107, "2Green": 0.0, "high50": 1976.460205, "RSI14": 50.528767, "EMA50": 1864.50293, "Close": 1878.119995, "EMA200": 2128.981002, "SMA20": 1888.450458, "Open": 1880.982056, "low50": 1510.505859, "high20": 1976.460205, "BB_hi": 1932.730084, "Volume": 3153563392.0, "BB_lo": 1844.170831, "Low": 1876.0802, "EMA9": 1884.579071, "EMA20": 1882.056983, "SMA50": 1830.116287, "2Red": 1.0}</t>
+          <t>{"Close": 124.89, "Volume": 16581, "VolAvg20": 2144.0, "RSI14": 40.9, "Drop_pct": 3.7, "BelowVWAP": true, "VWAPDown": true, "NIFTY_gap_pct": -0.09}</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | ðŸŽ¯ Target Hit (live)</t>
+          <t>#935ID Long L1: 5m -3.5%/90m vol2.5x RSI&lt;=45 gap1.5 below-VWAP&amp;down | ðŸŽ¯ Target Hit (live)</t>
         </is>
       </c>
     </row>
@@ -18002,7 +18000,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -18015,17 +18013,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G42" s="10" t="n">
-        <v>0.332</v>
+      <c r="G42" s="4" t="n">
+        <v>1880</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I42" s="11" t="n">
-        <v>0.3244</v>
-      </c>
-      <c r="J42" s="11" t="n">
-        <v>0.3442</v>
+        <v>25</v>
+      </c>
+      <c r="I42" s="8" t="n">
+        <v>1840.56</v>
+      </c>
+      <c r="J42" s="8" t="n">
+        <v>1953.24</v>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
@@ -18033,24 +18031,24 @@
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0.3369</v>
+        <v>1951.29</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21 07:50:22 IST</t>
+          <t>2026-08-19 20:30:05 IST</t>
         </is>
       </c>
       <c r="N42" s="4" t="n">
-        <v>48.75</v>
+        <v>1782.17</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>141</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>38.79</v>
+        <v>1641.17</v>
       </c>
       <c r="Q42" s="5" t="n">
-        <v>1.17</v>
+        <v>3.49</v>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
@@ -18059,27 +18057,27 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t>{"High": 0.330999, "Ret": -0.004433, "low20": 0.323269, "2Green": 0.0, "high50": 0.337903, "RSI14": 53.511744, "EMA50": 0.328876, "Close": 0.330981, "EMA200": 0.321504, "SMA20": 0.32883, "Open": 0.330921, "low50": 0.314034, "high20": 0.337903, "BB_hi": 0.335516, "Volume": 317728800.0, "BB_lo": 0.322143, "Low": 0.330715, "EMA9": 0.331613, "EMA20": 0.33003, "SMA50": 0.327135, "2Red": 1.0}</t>
+          <t>{"High": 1881.228882, "Ret": -0.001345, "low20": 1821.485107, "2Green": 0.0, "high50": 1976.460205, "RSI14": 50.528767, "EMA50": 1864.50293, "Close": 1878.119995, "EMA200": 2128.981002, "SMA20": 1888.450458, "Open": 1880.982056, "low50": 1510.505859, "high20": 1976.460205, "BB_hi": 1932.730084, "Volume": 3153563392.0, "BB_lo": 1844.170831, "Low": 1876.0802, "EMA9": 1884.579071, "EMA20": 1882.056983, "SMA50": 1830.116287, "2Red": 1.0}</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
+          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | ðŸŽ¯ Target Hit (live)</t>
         </is>
       </c>
     </row>
@@ -18096,12 +18094,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -18114,17 +18112,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G43" s="4" t="n">
-        <v>167.39</v>
+      <c r="G43" s="10" t="n">
+        <v>0.332</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>305</v>
-      </c>
-      <c r="I43" s="8" t="n">
-        <v>164.02</v>
-      </c>
-      <c r="J43" s="8" t="n">
-        <v>174.06</v>
+        <v>10000</v>
+      </c>
+      <c r="I43" s="11" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="J43" s="11" t="n">
+        <v>0.3442</v>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
@@ -18132,24 +18130,24 @@
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>174.04</v>
+        <v>0.3369</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 19:18:22 IST</t>
+          <t>2026-08-21 07:50:22 IST</t>
         </is>
       </c>
       <c r="N43" s="4" t="n">
-        <v>2029.04</v>
+        <v>48.75</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>10.21</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>2018.83</v>
+        <v>38.79</v>
       </c>
       <c r="Q43" s="5" t="n">
-        <v>3.95</v>
+        <v>1.17</v>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
@@ -18158,27 +18156,27 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t>{"High": 167.770004, "Ret": -0.005998, "low20": 157.229996, "2Green": 0.0, "high50": 169.710007, "RSI14": 61.944112, "EMA50": 160.375176, "Close": 167.369995, "EMA200": 152.877762, "SMA20": 164.259, "Open": 167.660004, "low50": 146.070007, "high20": 169.710007, "BB_hi": 170.39623, "Volume": 5020700.0, "BB_lo": 158.121771, "Low": 166.449997, "EMA9": 166.656228, "EMA20": 164.675214, "SMA50": 159.8202, "2Red": 1.0}</t>
+          <t>{"High": 0.330999, "Ret": -0.004433, "low20": 0.323269, "2Green": 0.0, "high50": 0.337903, "RSI14": 53.511744, "EMA50": 0.328876, "Close": 0.330981, "EMA200": 0.321504, "SMA20": 0.32883, "Open": 0.330921, "low50": 0.314034, "high20": 0.337903, "BB_hi": 0.335516, "Volume": 317728800.0, "BB_lo": 0.322143, "Low": 0.330715, "EMA9": 0.331613, "EMA20": 0.33003, "SMA50": 0.327135, "2Red": 1.0}</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | ðŸŽ¯ Target Hit (live)</t>
+          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -18200,7 +18198,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -18214,16 +18212,16 @@
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>52.55</v>
+        <v>167.39</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>972</v>
+        <v>305</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>51.49</v>
+        <v>164.02</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>54.64</v>
+        <v>174.06</v>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
@@ -18231,24 +18229,24 @@
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>52.41</v>
+        <v>174.04</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21 07:50:22 IST</t>
+          <t>2026-08-19 19:18:22 IST</t>
         </is>
       </c>
       <c r="N44" s="4" t="n">
-        <v>-131.46</v>
+        <v>2029.04</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v>-141.68</v>
-      </c>
-      <c r="Q44" s="13" t="n">
-        <v>-0.28</v>
+        <v>10.21</v>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>2018.83</v>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>3.95</v>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
@@ -18257,39 +18255,39 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t>{"High": 52.650002, "Ret": 0.004397, "low20": 49.849998, "2Green": 0.0, "high50": 53.599998, "RSI14": 55.668613, "EMA50": 51.516289, "Close": 52.540001, "EMA200": 49.67764, "SMA20": 51.7285, "Open": 52.459999, "low50": 49.57, "high20": 53.599998, "BB_hi": 53.772381, "Volume": 7479000.0, "BB_lo": 49.684619, "Low": 52.27, "EMA9": 52.4289, "EMA20": 51.988963, "SMA50": 51.383, "2Red": 0.0}</t>
+          <t>{"High": 167.770004, "Ret": -0.005998, "low20": 157.229996, "2Green": 0.0, "high50": 169.710007, "RSI14": 61.944112, "EMA50": 160.375176, "Close": 167.369995, "EMA200": 152.877762, "SMA20": 164.259, "Open": 167.660004, "low50": 146.070007, "high20": 169.710007, "BB_hi": 170.39623, "Volume": 5020700.0, "BB_lo": 158.121771, "Low": 166.449997, "EMA9": 166.656228, "EMA20": 164.675214, "SMA50": 159.8202, "2Red": 1.0}</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>#2SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | ðŸŽ¯ Target Hit (live)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>00:20:31 IST</t>
+          <t>07:48:23 IST</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -18299,7 +18297,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -18313,16 +18311,16 @@
         </is>
       </c>
       <c r="G45" s="4" t="n">
-        <v>381.8</v>
+        <v>52.55</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>131</v>
+        <v>972</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>374.12</v>
+        <v>51.49</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>397.03</v>
+        <v>54.64</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
@@ -18330,24 +18328,24 @@
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>380.91</v>
+        <v>52.41</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18 00:20:50 IST</t>
+          <t>2026-08-21 07:50:22 IST</t>
         </is>
       </c>
       <c r="N45" s="4" t="n">
-        <v>-116.33</v>
+        <v>-131.46</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>10</v>
+        <v>10.22</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>-126.33</v>
+        <v>-141.68</v>
       </c>
       <c r="Q45" s="13" t="n">
-        <v>-0.25</v>
+        <v>-0.28</v>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
@@ -18356,12 +18354,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
@@ -18371,24 +18369,24 @@
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t>{"Low": 380.838501, "EMA9": 378.755146, "Ret": 0.002468, "High": 382.554993, "BB_lo": 355.440257, "SMA20": 371.858, "RSI14": 63.686748, "EMA20": 374.422536, "low20": 358.170013, "high50": 384.820007, "2Red": 0.0, "SMA50": 368.8264, "Open": 382.660004, "2Green": 0.0, "high20": 384.820007, "EMA200": 349.15793, "Close": 381.76001, "low50": 354.809998, "BB_hi": 388.275744, "Volume": 171118.0, "EMA50": 368.980107}</t>
+          <t>{"High": 52.650002, "Ret": 0.004397, "low20": 49.849998, "2Green": 0.0, "high50": 53.599998, "RSI14": 55.668613, "EMA50": 51.516289, "Close": 52.540001, "EMA200": 49.67764, "SMA20": 51.7285, "Open": 52.459999, "low50": 49.57, "high20": 53.599998, "BB_hi": 53.772381, "Volume": 7479000.0, "BB_lo": 49.684619, "Low": 52.27, "EMA9": 52.4289, "EMA20": 51.988963, "SMA50": 51.383, "2Red": 0.0}</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#2SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>00:43:12 IST</t>
+          <t>00:20:31 IST</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -18398,7 +18396,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -18412,16 +18410,16 @@
         </is>
       </c>
       <c r="G46" s="4" t="n">
-        <v>717.42</v>
+        <v>381.8</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>69</v>
+        <v>131</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>703</v>
+        <v>374.12</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>746.04</v>
+        <v>397.03</v>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
@@ -18429,24 +18427,24 @@
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>730.98</v>
+        <v>380.91</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17 00:56:07 IST</t>
+          <t>2026-08-18 00:20:50 IST</t>
         </is>
       </c>
       <c r="N46" s="4" t="n">
-        <v>935.42</v>
+        <v>-116.33</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v>925.52</v>
-      </c>
-      <c r="Q46" s="5" t="n">
-        <v>1.87</v>
+        <v>10</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v>-126.33</v>
+      </c>
+      <c r="Q46" s="13" t="n">
+        <v>-0.25</v>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
@@ -18455,49 +18453,49 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>60.94</t>
+          <t>59.53</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA9&gt;EMA20+2Red</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>{"Volume": 22313421.0, "BB_lo": 665.286184, "SMA20": 700.678995, "high20": 728.539978, "low20": 661.140015, "low50": 661.140015, "High": 723.299988, "2Red": 1.0, "RSI14": 54.565075, "high50": 748.650024, "SMA50": 713.8536, "2Green": 0.0, "Open": 723.299988, "EMA200": 654.275205, "EMA50": 704.048659, "BB_hi": 736.071805, "Low": 715.789978, "EMA9": 711.374496, "Ret": -0.004883, "Close": 717.349976, "EMA20": 707.041668}</t>
+          <t>{"Low": 380.838501, "EMA9": 378.755146, "Ret": 0.002468, "High": 382.554993, "BB_lo": 355.440257, "SMA20": 371.858, "RSI14": 63.686748, "EMA20": 374.422536, "low20": 358.170013, "high50": 384.820007, "2Red": 0.0, "SMA50": 368.8264, "Open": 382.660004, "2Green": 0.0, "high20": 384.820007, "EMA200": 349.15793, "Close": 381.76001, "low50": 354.809998, "BB_hi": 388.275744, "Volume": 171118.0, "EMA50": 368.980107}</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>#37SW Price&gt;SMA50+EMA9&gt;EMA20+2Red | Expiry 5d</t>
+          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>00:37:04 IST</t>
+          <t>00:43:12 IST</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -18511,16 +18509,16 @@
         </is>
       </c>
       <c r="G47" s="4" t="n">
-        <v>1874.1</v>
+        <v>717.42</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>1834.79</v>
+        <v>703</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>1947.12</v>
+        <v>746.04</v>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
@@ -18528,24 +18526,24 @@
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1880.51</v>
+        <v>730.98</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16 00:56:05 IST</t>
+          <t>2026-08-17 00:56:07 IST</t>
         </is>
       </c>
       <c r="N47" s="4" t="n">
-        <v>160.19</v>
+        <v>935.42</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>140.56</v>
+        <v>9.9</v>
       </c>
       <c r="P47" s="5" t="n">
-        <v>19.63</v>
-      </c>
-      <c r="Q47" s="12" t="n">
-        <v>0.04</v>
+        <v>925.52</v>
+      </c>
+      <c r="Q47" s="5" t="n">
+        <v>1.87</v>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
@@ -18554,27 +18552,27 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>60.94</t>
         </is>
       </c>
       <c r="U47" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
+          <t>Price&gt;SMA50+EMA9&gt;EMA20+2Red</t>
         </is>
       </c>
       <c r="V47" s="3" t="inlineStr">
         <is>
-          <t>{"BB_hi": 1951.082913, "EMA20": 1883.245495, "high20": 1976.460205, "Open": 1908.93103, "EMA200": 2141.746334, "Volume": 9096837120.0, "low50": 1510.505859, "Low": 1868.057739, "2Red": 1.0, "RSI14": 49.831146, "EMA9": 1893.674853, "BB_lo": 1835.426218, "2Green": 0.0, "high50": 1976.460205, "Close": 1872.22998, "SMA20": 1893.254565, "High": 1928.543091, "EMA50": 1861.015458, "low20": 1821.485107, "SMA50": 1805.156021, "Ret": -0.019098}</t>
+          <t>{"Volume": 22313421.0, "BB_lo": 665.286184, "SMA20": 700.678995, "high20": 728.539978, "low20": 661.140015, "low50": 661.140015, "High": 723.299988, "2Red": 1.0, "RSI14": 54.565075, "high50": 748.650024, "SMA50": 713.8536, "2Green": 0.0, "Open": 723.299988, "EMA200": 654.275205, "EMA50": 704.048659, "BB_hi": 736.071805, "Low": 715.789978, "EMA9": 711.374496, "Ret": -0.004883, "Close": 717.349976, "EMA20": 707.041668}</t>
         </is>
       </c>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | Expiry 5d</t>
+          <t>#37SW Price&gt;SMA50+EMA9&gt;EMA20+2Red | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -18596,7 +18594,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -18609,17 +18607,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G48" s="10" t="n">
-        <v>0.331</v>
+      <c r="G48" s="4" t="n">
+        <v>1874.1</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I48" s="11" t="n">
-        <v>0.3241</v>
-      </c>
-      <c r="J48" s="11" t="n">
-        <v>0.3439</v>
+        <v>25</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>1834.79</v>
+      </c>
+      <c r="J48" s="8" t="n">
+        <v>1947.12</v>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
@@ -18627,7 +18625,7 @@
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0.3304</v>
+        <v>1880.51</v>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
@@ -18635,16 +18633,16 @@
         </is>
       </c>
       <c r="N48" s="4" t="n">
-        <v>-5.56</v>
+        <v>160.19</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v>-15.49</v>
-      </c>
-      <c r="Q48" s="13" t="n">
-        <v>-0.47</v>
+        <v>140.56</v>
+      </c>
+      <c r="P48" s="5" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="Q48" s="12" t="n">
+        <v>0.04</v>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
@@ -18653,27 +18651,27 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="U48" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>Price&lt;SMA20+Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="V48" s="3" t="inlineStr">
         <is>
-          <t>{"BB_hi": 0.332258, "EMA20": 0.327832, "high20": 0.333079, "Open": 0.329585, "EMA200": 0.32088, "Volume": 869478144.0, "low50": 0.314034, "Low": 0.329472, "2Red": 0.0, "RSI14": 57.524103, "EMA9": 0.328473, "BB_lo": 0.323712, "2Green": 1.0, "high50": 0.333832, "Close": 0.330694, "SMA20": 0.327985, "High": 0.331578, "EMA50": 0.327842, "low20": 0.323269, "SMA50": 0.326432, "Ret": 0.003357}</t>
+          <t>{"BB_hi": 1951.082913, "EMA20": 1883.245495, "high20": 1976.460205, "Open": 1908.93103, "EMA200": 2141.746334, "Volume": 9096837120.0, "low50": 1510.505859, "Low": 1868.057739, "2Red": 1.0, "RSI14": 49.831146, "EMA9": 1893.674853, "BB_lo": 1835.426218, "2Green": 0.0, "high50": 1976.460205, "Close": 1872.22998, "SMA20": 1893.254565, "High": 1928.543091, "EMA50": 1861.015458, "low20": 1821.485107, "SMA50": 1805.156021, "Ret": -0.019098}</t>
         </is>
       </c>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
+          <t>#32SW Price&lt;SMA20+Price&gt;SMA50+2Red | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -18690,12 +18688,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -18708,17 +18706,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G49" s="4" t="n">
-        <v>84.8</v>
+      <c r="G49" s="10" t="n">
+        <v>0.331</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>587</v>
-      </c>
-      <c r="I49" s="8" t="n">
-        <v>83.09</v>
-      </c>
-      <c r="J49" s="8" t="n">
-        <v>88.18000000000001</v>
+        <v>10000</v>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="J49" s="11" t="n">
+        <v>0.3439</v>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
@@ -18726,7 +18724,7 @@
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>86.06999999999999</v>
+        <v>0.3304</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -18734,16 +18732,16 @@
         </is>
       </c>
       <c r="N49" s="4" t="n">
-        <v>743.37</v>
+        <v>-5.56</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="P49" s="5" t="n">
-        <v>733.41</v>
-      </c>
-      <c r="Q49" s="5" t="n">
-        <v>1.47</v>
+        <v>9.93</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v>-15.49</v>
+      </c>
+      <c r="Q49" s="13" t="n">
+        <v>-0.47</v>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
@@ -18752,39 +18750,39 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="U49" s="3" t="inlineStr">
         <is>
-          <t>Range&lt;1%+SMA20&lt;EMA20</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V49" s="3" t="inlineStr">
         <is>
-          <t>{"BB_hi": 87.086251, "EMA20": 84.986252, "high20": 88.779999, "Open": 84.660004, "EMA200": 83.124135, "Volume": 4681010.0, "low50": 81.480003, "Low": 84.330002, "2Red": 0.0, "RSI14": 49.564668, "EMA9": 85.140171, "BB_lo": 82.854749, "2Green": 0.0, "high50": 88.779999, "Close": 84.790001, "SMA20": 84.9705, "High": 85.044998, "EMA50": 84.555905, "low20": 82.809998, "SMA50": 84.312, "Ret": -0.003877}</t>
+          <t>{"BB_hi": 0.332258, "EMA20": 0.327832, "high20": 0.333079, "Open": 0.329585, "EMA200": 0.32088, "Volume": 869478144.0, "low50": 0.314034, "Low": 0.329472, "2Red": 0.0, "RSI14": 57.524103, "EMA9": 0.328473, "BB_lo": 0.323712, "2Green": 1.0, "high50": 0.333832, "Close": 0.330694, "SMA20": 0.327985, "High": 0.331578, "EMA50": 0.327842, "low20": 0.323269, "SMA50": 0.326432, "Ret": 0.003357}</t>
         </is>
       </c>
       <c r="W49" s="3" t="inlineStr">
         <is>
-          <t>#5SW Range&lt;1%+SMA20&lt;EMA20 | Expiry 5d</t>
+          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>05:40:03 IST</t>
+          <t>00:37:04 IST</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -18794,7 +18792,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -18808,16 +18806,16 @@
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>185.35</v>
+        <v>84.8</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>265</v>
+        <v>587</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>181.62</v>
+        <v>83.09</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>192.74</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
@@ -18825,24 +18823,24 @@
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>186.12</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 08:36:01 IST</t>
+          <t>2026-08-16 00:56:05 IST</t>
         </is>
       </c>
       <c r="N50" s="4" t="n">
-        <v>204.42</v>
+        <v>743.37</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>9.82</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>194.6</v>
-      </c>
-      <c r="Q50" s="12" t="n">
-        <v>0.4</v>
+        <v>733.41</v>
+      </c>
+      <c r="Q50" s="5" t="n">
+        <v>1.47</v>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
@@ -18851,27 +18849,27 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T50" s="3" t="inlineStr">
         <is>
-          <t>63.73</t>
+          <t>58.26</t>
         </is>
       </c>
       <c r="U50" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
+          <t>Range&lt;1%+SMA20&lt;EMA20</t>
         </is>
       </c>
       <c r="V50" s="3" t="inlineStr">
         <is>
-          <t>{"EMA50": 178.417894, "Close": 185.330002, "Volume": 6431938.0, "RSI14": 56.546346, "High": 186.910004, "2Red": 1.0, "Ret": -0.00312, "Low": 182.070007, "EMA20": 179.791718, "EMA9": 180.620244, "Open": 183.190002, "SMA50": 183.268401, "SMA20": 178.784}</t>
+          <t>{"BB_hi": 87.086251, "EMA20": 84.986252, "high20": 88.779999, "Open": 84.660004, "EMA200": 83.124135, "Volume": 4681010.0, "low50": 81.480003, "Low": 84.330002, "2Red": 0.0, "RSI14": 49.564668, "EMA9": 85.140171, "BB_lo": 82.854749, "2Green": 0.0, "high50": 88.779999, "Close": 84.790001, "SMA20": 84.9705, "High": 85.044998, "EMA50": 84.555905, "low20": 82.809998, "SMA50": 84.312, "Ret": -0.003877}</t>
         </is>
       </c>
       <c r="W50" s="3" t="inlineStr">
         <is>
-          <t>#28SW Price&gt;SMA50+EMA20&gt;EMA50+2Red | Expiry 5d</t>
+          <t>#5SW Range&lt;1%+SMA20&lt;EMA20 | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -18893,7 +18891,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -18907,16 +18905,16 @@
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>381.22</v>
+        <v>185.35</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>129</v>
+        <v>265</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>373.56</v>
+        <v>181.62</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>396.43</v>
+        <v>192.74</v>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
@@ -18924,7 +18922,7 @@
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>380.7</v>
+        <v>186.12</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -18932,16 +18930,16 @@
         </is>
       </c>
       <c r="N51" s="4" t="n">
-        <v>-66.83</v>
+        <v>204.42</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v>-76.67</v>
-      </c>
-      <c r="Q51" s="13" t="n">
-        <v>-0.16</v>
+        <v>9.82</v>
+      </c>
+      <c r="P51" s="5" t="n">
+        <v>194.6</v>
+      </c>
+      <c r="Q51" s="12" t="n">
+        <v>0.4</v>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
@@ -18950,39 +18948,39 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T51" s="3" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>63.73</t>
         </is>
       </c>
       <c r="U51" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+EMA20&gt;EMA50+2Red</t>
         </is>
       </c>
       <c r="V51" s="3" t="inlineStr">
         <is>
-          <t>{"EMA50": 366.698569, "Close": 381.179993, "Volume": 145727.0, "RSI14": 65.09971, "High": 382.63501, "2Red": 0.0, "Ret": 0.001129, "Low": 380.350006, "EMA20": 370.650953, "EMA9": 374.081113, "Open": 381.549988, "SMA50": 368.3698, "SMA20": 369.739}</t>
+          <t>{"EMA50": 178.417894, "Close": 185.330002, "Volume": 6431938.0, "RSI14": 56.546346, "High": 186.910004, "2Red": 1.0, "Ret": -0.00312, "Low": 182.070007, "EMA20": 179.791718, "EMA9": 180.620244, "Open": 183.190002, "SMA50": 183.268401, "SMA20": 178.784}</t>
         </is>
       </c>
       <c r="W51" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#28SW Price&gt;SMA50+EMA20&gt;EMA50+2Red | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>01:17:18 IST</t>
+          <t>05:40:03 IST</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -18992,7 +18990,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -19006,16 +19004,16 @@
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>719.29</v>
+        <v>381.22</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>704.9</v>
+        <v>373.56</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>748.0599999999999</v>
+        <v>396.43</v>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
@@ -19023,24 +19021,24 @@
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>720.8</v>
+        <v>380.7</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 01:36:05 IST</t>
+          <t>2026-08-12 08:36:01 IST</t>
         </is>
       </c>
       <c r="N52" s="4" t="n">
-        <v>105.55</v>
+        <v>-66.83</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>10.07</v>
-      </c>
-      <c r="P52" s="5" t="n">
-        <v>95.48</v>
-      </c>
-      <c r="Q52" s="12" t="n">
-        <v>0.19</v>
+        <v>9.84</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v>-76.67</v>
+      </c>
+      <c r="Q52" s="13" t="n">
+        <v>-0.16</v>
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
@@ -19049,27 +19047,27 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T52" s="3" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>59.53</t>
         </is>
       </c>
       <c r="U52" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA9&lt;EMA20</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V52" s="3" t="inlineStr">
         <is>
-          <t>{"Volume": 28061644.0, "RSI14": 56.167234, "EMA20": 701.326904, "EMA9": 700.684364, "Low": 719.26001, "SMA50": 715.048199, "EMA50": 701.5317, "High": 728.539978, "2Red": 0.0, "Close": 719.289978, "SMA20": 700.994495, "Open": 726.224976, "Ret": -0.0063}</t>
+          <t>{"EMA50": 366.698569, "Close": 381.179993, "Volume": 145727.0, "RSI14": 65.09971, "High": 382.63501, "2Red": 0.0, "Ret": 0.001129, "Low": 380.350006, "EMA20": 370.650953, "EMA9": 374.081113, "Open": 381.549988, "SMA50": 368.3698, "SMA20": 369.739}</t>
         </is>
       </c>
       <c r="W52" s="3" t="inlineStr">
         <is>
-          <t>#50SW Price&gt;SMA50+EMA9&lt;EMA20 | Expiry 5d</t>
+          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -19091,7 +19089,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -19105,16 +19103,16 @@
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>52.72</v>
+        <v>719.29</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>969</v>
+        <v>70</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>51.67</v>
+        <v>704.9</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>54.83</v>
+        <v>748.0599999999999</v>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
@@ -19122,7 +19120,7 @@
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>53.18</v>
+        <v>720.8</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
@@ -19130,16 +19128,16 @@
         </is>
       </c>
       <c r="N53" s="4" t="n">
-        <v>450.27</v>
+        <v>105.55</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>10.22</v>
+        <v>10.07</v>
       </c>
       <c r="P53" s="5" t="n">
-        <v>440.05</v>
+        <v>95.48</v>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>0.86</v>
+        <v>0.19</v>
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
@@ -19148,49 +19146,49 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="T53" s="3" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="U53" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>Price&gt;SMA50+EMA9&lt;EMA20</t>
         </is>
       </c>
       <c r="V53" s="3" t="inlineStr">
         <is>
-          <t>{"Volume": 9101653.0, "RSI14": 59.972956, "EMA20": 51.291376, "EMA9": 51.578998, "Low": 52.474998, "SMA50": 51.1821, "EMA50": 51.139325, "High": 52.959999, "2Red": 0.0, "Close": 52.724998, "SMA20": 51.00325, "Open": 52.59, "Ret": 0.013942}</t>
+          <t>{"Volume": 28061644.0, "RSI14": 56.167234, "EMA20": 701.326904, "EMA9": 700.684364, "Low": 719.26001, "SMA50": 715.048199, "EMA50": 701.5317, "High": 728.539978, "2Red": 0.0, "Close": 719.289978, "SMA20": 700.994495, "Open": 726.224976, "Ret": -0.0063}</t>
         </is>
       </c>
       <c r="W53" s="3" t="inlineStr">
         <is>
-          <t>#2SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#50SW Price&gt;SMA50+EMA9&lt;EMA20 | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>15:13:11 IST</t>
+          <t>01:17:18 IST</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -19203,17 +19201,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G54" s="10" t="n">
-        <v>0.3281</v>
+      <c r="G54" s="4" t="n">
+        <v>52.72</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I54" s="11" t="n">
-        <v>0.3215</v>
-      </c>
-      <c r="J54" s="11" t="n">
-        <v>0.3412</v>
+        <v>969</v>
+      </c>
+      <c r="I54" s="8" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="J54" s="8" t="n">
+        <v>54.83</v>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
@@ -19221,24 +19219,24 @@
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0.33</v>
+        <v>53.18</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 15:13:13 IST</t>
+          <t>2026-08-11 01:36:05 IST</t>
         </is>
       </c>
       <c r="N54" s="4" t="n">
-        <v>19.32</v>
+        <v>450.27</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>9.84</v>
+        <v>10.22</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>9.48</v>
+        <v>440.05</v>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>0.29</v>
+        <v>0.86</v>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
@@ -19247,27 +19245,27 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T54" s="3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="U54" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V54" s="3" t="inlineStr">
         <is>
-          <t>{"Open": 0.326938, "2Red": 0.0, "Low": 0.326183, "EMA50": 0.327684, "High": 0.328078, "Volume": 546277952.0, "Close": 0.328078, "SMA20": 0.327438, "SMA50": 0.32597, "EMA9": 0.327405, "Ret": 0.003497, "RSI14": 51.70969, "EMA20": 0.327265}</t>
+          <t>{"Volume": 9101653.0, "RSI14": 59.972956, "EMA20": 51.291376, "EMA9": 51.578998, "Low": 52.474998, "SMA50": 51.1821, "EMA50": 51.139325, "High": 52.959999, "2Red": 0.0, "Close": 52.724998, "SMA20": 51.00325, "Open": 52.59, "Ret": 0.013942}</t>
         </is>
       </c>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
+          <t>#2SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -19284,12 +19282,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -19302,17 +19300,17 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G55" s="4" t="n">
-        <v>118.29</v>
+      <c r="G55" s="10" t="n">
+        <v>0.3281</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>420</v>
-      </c>
-      <c r="I55" s="8" t="n">
-        <v>115.92</v>
-      </c>
-      <c r="J55" s="8" t="n">
-        <v>123.02</v>
+        <v>10000</v>
+      </c>
+      <c r="I55" s="11" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="J55" s="11" t="n">
+        <v>0.3412</v>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
@@ -19320,7 +19318,7 @@
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>119.8</v>
+        <v>0.33</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -19328,16 +19326,16 @@
         </is>
       </c>
       <c r="N55" s="4" t="n">
-        <v>633.37</v>
+        <v>19.32</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>9.94</v>
+        <v>9.84</v>
       </c>
       <c r="P55" s="5" t="n">
-        <v>623.4299999999999</v>
-      </c>
-      <c r="Q55" s="5" t="n">
-        <v>1.25</v>
+        <v>9.48</v>
+      </c>
+      <c r="Q55" s="12" t="n">
+        <v>0.29</v>
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
@@ -19351,22 +19349,22 @@
       </c>
       <c r="T55" s="3" t="inlineStr">
         <is>
-          <t>58.65</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="U55" s="3" t="inlineStr">
         <is>
-          <t>EMA9&lt;EMA50+RSI&gt;50</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="V55" s="3" t="inlineStr">
         <is>
-          <t>{"Open": 117.529999, "2Red": 0.0, "Low": 117.120003, "EMA50": 115.501689, "High": 118.57, "Volume": 10500800.0, "Close": 118.290001, "SMA20": 114.6345, "SMA50": 116.0852, "EMA9": 115.004317, "Ret": 0.000677, "RSI14": 59.157988, "EMA20": 114.786415}</t>
+          <t>{"Open": 0.326938, "2Red": 0.0, "Low": 0.326183, "EMA50": 0.327684, "High": 0.328078, "Volume": 546277952.0, "Close": 0.328078, "SMA20": 0.327438, "SMA50": 0.32597, "EMA9": 0.327405, "Ret": 0.003497, "RSI14": 51.70969, "EMA20": 0.327265}</t>
         </is>
       </c>
       <c r="W55" s="3" t="inlineStr">
         <is>
-          <t>#1SW EMA9&lt;EMA50+RSI&gt;50 | Expiry 5d</t>
+          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -19388,7 +19386,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -19402,16 +19400,16 @@
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>162.1</v>
+        <v>118.29</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>307</v>
+        <v>420</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>158.86</v>
+        <v>115.92</v>
       </c>
       <c r="J56" s="8" t="n">
-        <v>168.58</v>
+        <v>123.02</v>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
@@ -19419,7 +19417,7 @@
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>165.65</v>
+        <v>119.8</v>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
@@ -19427,16 +19425,16 @@
         </is>
       </c>
       <c r="N56" s="4" t="n">
-        <v>1090.9</v>
+        <v>633.37</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.94</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>1080.95</v>
+        <v>623.4299999999999</v>
       </c>
       <c r="Q56" s="5" t="n">
-        <v>2.17</v>
+        <v>1.25</v>
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
@@ -19445,39 +19443,39 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T56" s="3" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>58.65</t>
         </is>
       </c>
       <c r="U56" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>EMA9&lt;EMA50+RSI&gt;50</t>
         </is>
       </c>
       <c r="V56" s="3" t="inlineStr">
         <is>
-          <t>{"Open": 162.0, "2Red": 1.0, "Low": 160.970001, "EMA50": 157.880967, "High": 162.490005, "Volume": 15121700.0, "Close": 162.100006, "SMA20": 161.822, "SMA50": 156.9082, "EMA9": 162.798107, "Ret": -0.000863, "RSI14": 53.812337, "EMA20": 161.631372}</t>
+          <t>{"Open": 117.529999, "2Red": 0.0, "Low": 117.120003, "EMA50": 115.501689, "High": 118.57, "Volume": 10500800.0, "Close": 118.290001, "SMA20": 114.6345, "SMA50": 116.0852, "EMA9": 115.004317, "Ret": 0.000677, "RSI14": 59.157988, "EMA20": 114.786415}</t>
         </is>
       </c>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
+          <t>#1SW EMA9&lt;EMA50+RSI&gt;50 | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>01:18:05 IST</t>
+          <t>15:13:11 IST</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -19487,7 +19485,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -19501,16 +19499,16 @@
         </is>
       </c>
       <c r="G57" s="4" t="n">
-        <v>700.39</v>
+        <v>162.1</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>71</v>
+        <v>307</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>686.38</v>
+        <v>158.86</v>
       </c>
       <c r="J57" s="8" t="n">
-        <v>728.41</v>
+        <v>168.58</v>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
@@ -19518,24 +19516,24 @@
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>728.41</v>
+        <v>165.65</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>19:55:15 IST</t>
+          <t>2026-08-10 15:13:13 IST</t>
         </is>
       </c>
       <c r="N57" s="4" t="n">
-        <v>1989.42</v>
+        <v>1090.9</v>
       </c>
       <c r="O57" s="4" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="P57" s="5" t="n">
-        <v>1979.47</v>
+        <v>1080.95</v>
       </c>
       <c r="Q57" s="5" t="n">
-        <v>3.98</v>
+        <v>2.17</v>
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
@@ -19544,39 +19542,39 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T57" s="3" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>52.32</t>
         </is>
       </c>
       <c r="U57" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&gt;Open</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="V57" s="3" t="inlineStr">
         <is>
-          <t>{"Close": 700.390015, "Ret": 0.018024, "Low": 685.820007, "High": 701.590027, "Volume": 36459876.0, "EMA20": 696.896645, "SMA20": 699.896997, "2Red": 0.0, "EMA9": 689.142707, "RSI14": 50.141657, "SMA50": 714.8328, "Open": 688.340027, "EMA50": 699.878887}</t>
+          <t>{"Open": 162.0, "2Red": 1.0, "Low": 160.970001, "EMA50": 157.880967, "High": 162.490005, "Volume": 15121700.0, "Close": 162.100006, "SMA20": 161.822, "SMA50": 156.9082, "EMA9": 162.798107, "Ret": -0.000863, "RSI14": 53.812337, "EMA20": 161.631372}</t>
         </is>
       </c>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>#52SW Price&gt;SMA20+EMA9&lt;EMA20+Close&gt;Open | ðŸŽ¯ Target Hit (live)</t>
+          <t>#4SW EMA9&gt;EMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>23:32:54 IST</t>
+          <t>01:18:05 IST</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -19586,7 +19584,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -19596,45 +19594,45 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="G58" s="4" t="n">
-        <v>745.84</v>
+        <v>700.39</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>738.38</v>
+        <v>686.38</v>
       </c>
       <c r="J58" s="8" t="n">
-        <v>760.76</v>
+        <v>728.41</v>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>757.5700000000001</v>
+        <v>728.41</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>23:00:00 IST</t>
+          <t>19:55:15 IST</t>
         </is>
       </c>
       <c r="N58" s="4" t="n">
-        <v>1395.87</v>
+        <v>1989.42</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>17.75</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="P58" s="5" t="n">
-        <v>1378.12</v>
+        <v>1979.47</v>
       </c>
       <c r="Q58" s="5" t="n">
-        <v>1.55</v>
+        <v>3.98</v>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
@@ -19643,27 +19641,27 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>52</t>
         </is>
       </c>
       <c r="T58" s="3" t="inlineStr">
         <is>
-          <t>60.24</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="U58" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
+          <t>Price&gt;SMA20+EMA9&lt;EMA20+Close&gt;Open</t>
         </is>
       </c>
       <c r="V58" s="3" t="inlineStr">
         <is>
-          <t>{"EMA9": 741.70706, "Open": 744.429993, "Low": 743.98999, "Volume": 4072705.0, "RSI14": 62.13446, "Ret": 0.002512, "EMA50": 740.609545, "High": 746.400024, "SMA50": 739.652488, "2Red": 0.0, "SMA20": 738.535001, "EMA20": 740.044973, "Close": 746.289978}</t>
+          <t>{"Close": 700.390015, "Ret": 0.018024, "Low": 685.820007, "High": 701.590027, "Volume": 36459876.0, "EMA20": 696.896645, "SMA20": 699.896997, "2Red": 0.0, "EMA9": 689.142707, "RSI14": 50.141657, "SMA50": 714.8328, "Open": 688.340027, "EMA50": 699.878887}</t>
         </is>
       </c>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>#32ID Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | Expiry 6h</t>
+          <t>#52SW Price&gt;SMA20+EMA9&lt;EMA20+Close&gt;Open | ðŸŽ¯ Target Hit (live)</t>
         </is>
       </c>
     </row>
@@ -19675,7 +19673,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>21:47:39 IST</t>
+          <t>23:32:54 IST</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -19685,7 +19683,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -19699,16 +19697,16 @@
         </is>
       </c>
       <c r="G59" s="4" t="n">
-        <v>174.29</v>
+        <v>745.84</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>497</v>
+        <v>119</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>172.55</v>
+        <v>738.38</v>
       </c>
       <c r="J59" s="8" t="n">
-        <v>177.78</v>
+        <v>760.76</v>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
@@ -19716,24 +19714,24 @@
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>177.6</v>
+        <v>757.5700000000001</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>21:00:00 IST</t>
+          <t>23:00:00 IST</t>
         </is>
       </c>
       <c r="N59" s="4" t="n">
-        <v>1646.31</v>
+        <v>1395.87</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>17.32</v>
+        <v>17.75</v>
       </c>
       <c r="P59" s="5" t="n">
-        <v>1628.99</v>
+        <v>1378.12</v>
       </c>
       <c r="Q59" s="5" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
@@ -19742,27 +19740,27 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T59" s="3" t="inlineStr">
         <is>
-          <t>67.35</t>
+          <t>60.24</t>
         </is>
       </c>
       <c r="U59" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20</t>
+          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
         </is>
       </c>
       <c r="V59" s="3" t="inlineStr">
         <is>
-          <t>{"SMA20": 171.96953, "EMA9": 173.971593, "EMA20": 173.252314, "Ret": -0.00379, "SMA50": 174.765609, "High": 174.869995, "Volume": 1112891.0, "Close": 173.5, "Open": 174.179993, "2Red": 1.0, "RSI14": 50.495204, "Low": 173.100006, "EMA50": 174.378064}</t>
+          <t>{"EMA9": 741.70706, "Open": 744.429993, "Low": 743.98999, "Volume": 4072705.0, "RSI14": 62.13446, "Ret": 0.002512, "EMA50": 740.609545, "High": 746.400024, "SMA50": 739.652488, "2Red": 0.0, "SMA20": 738.535001, "EMA20": 740.044973, "Close": 746.289978}</t>
         </is>
       </c>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>#3ID Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20 | Expiry 6h</t>
+          <t>#32ID Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19772,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>21:07:14 IST</t>
+          <t>21:47:39 IST</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -19798,16 +19796,16 @@
         </is>
       </c>
       <c r="G60" s="4" t="n">
-        <v>173.95</v>
+        <v>174.29</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="I60" s="8" t="n">
-        <v>172.21</v>
+        <v>172.55</v>
       </c>
       <c r="J60" s="8" t="n">
-        <v>177.43</v>
+        <v>177.78</v>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
@@ -19815,24 +19813,24 @@
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>176.43</v>
+        <v>177.6</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>20:00:00 IST</t>
+          <t>21:00:00 IST</t>
         </is>
       </c>
       <c r="N60" s="4" t="n">
-        <v>1207.76</v>
+        <v>1646.31</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>16.94</v>
+        <v>17.32</v>
       </c>
       <c r="P60" s="5" t="n">
-        <v>1190.82</v>
+        <v>1628.99</v>
       </c>
       <c r="Q60" s="5" t="n">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
@@ -19856,7 +19854,7 @@
       </c>
       <c r="V60" s="3" t="inlineStr">
         <is>
-          <t>{"RSI14": 50.452183, "2Red": 1.0, "High": 174.869995, "EMA50": 174.377476, "Ret": -0.003876, "SMA50": 174.765309, "Low": 173.100006, "Close": 173.485001, "Volume": 1102438.0, "SMA20": 171.96878, "EMA20": 173.250885, "Open": 174.179993, "EMA9": 173.968593}</t>
+          <t>{"SMA20": 171.96953, "EMA9": 173.971593, "EMA20": 173.252314, "Ret": -0.00379, "SMA50": 174.765609, "High": 174.869995, "Volume": 1112891.0, "Close": 173.5, "Open": 174.179993, "2Red": 1.0, "RSI14": 50.495204, "Low": 173.100006, "EMA50": 174.378064}</t>
         </is>
       </c>
       <c r="W60" s="3" t="inlineStr">
@@ -19873,7 +19871,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>20:27:40 IST</t>
+          <t>21:07:14 IST</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -19897,16 +19895,16 @@
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>174.64</v>
+        <v>173.95</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>172.89</v>
+        <v>172.21</v>
       </c>
       <c r="J61" s="8" t="n">
-        <v>178.13</v>
+        <v>177.43</v>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
@@ -19914,24 +19912,24 @@
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>176.19</v>
+        <v>176.43</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>19:00:00 IST</t>
+          <t>20:00:00 IST</t>
         </is>
       </c>
       <c r="N61" s="4" t="n">
-        <v>759.5</v>
+        <v>1207.76</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>17.11</v>
+        <v>16.94</v>
       </c>
       <c r="P61" s="5" t="n">
-        <v>742.39</v>
-      </c>
-      <c r="Q61" s="12" t="n">
-        <v>0.87</v>
+        <v>1190.82</v>
+      </c>
+      <c r="Q61" s="5" t="n">
+        <v>1.41</v>
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
@@ -19955,7 +19953,7 @@
       </c>
       <c r="V61" s="3" t="inlineStr">
         <is>
-          <t>{"SMA20": 171.86253, "RSI14": 52.463695, "Ret": -0.008821, "EMA9": 174.089491, "2Red": 0.0, "Low": 172.699997, "Close": 174.160004, "SMA50": 174.896011, "EMA20": 173.226242, "EMA50": 174.413903, "Open": 177.460007, "Volume": 2974398.0, "High": 178.619995}</t>
+          <t>{"RSI14": 50.452183, "2Red": 1.0, "High": 174.869995, "EMA50": 174.377476, "Ret": -0.003876, "SMA50": 174.765309, "Low": 173.100006, "Close": 173.485001, "Volume": 1102438.0, "SMA20": 171.96878, "EMA20": 173.250885, "Open": 174.179993, "EMA9": 173.968593}</t>
         </is>
       </c>
       <c r="W61" s="3" t="inlineStr">
@@ -19972,7 +19970,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>02:09:08 IST</t>
+          <t>20:27:40 IST</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -19982,7 +19980,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -19996,16 +19994,16 @@
         </is>
       </c>
       <c r="G62" s="4" t="n">
-        <v>683.6</v>
+        <v>174.64</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>132</v>
+        <v>490</v>
       </c>
       <c r="I62" s="8" t="n">
-        <v>676.76</v>
+        <v>172.89</v>
       </c>
       <c r="J62" s="8" t="n">
-        <v>697.27</v>
+        <v>178.13</v>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
@@ -20013,21 +20011,21 @@
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>689.7</v>
+        <v>176.19</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>00:00:00 IST</t>
+          <t>19:00:00 IST</t>
         </is>
       </c>
       <c r="N62" s="4" t="n">
-        <v>805.2</v>
+        <v>759.5</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>18.05</v>
+        <v>17.11</v>
       </c>
       <c r="P62" s="5" t="n">
-        <v>787.15</v>
+        <v>742.39</v>
       </c>
       <c r="Q62" s="12" t="n">
         <v>0.87</v>
@@ -20039,27 +20037,27 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T62" s="3" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>67.35</t>
         </is>
       </c>
       <c r="U62" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50</t>
+          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20</t>
         </is>
       </c>
       <c r="V62" s="3" t="inlineStr">
         <is>
-          <t>{"Volume": 10064291.0, "SMA20": 675.475238, "EMA20": 678.396981, "EMA50": 684.292339, "Close": 683.599976, "Low": 682.900024, "Open": 683.820007, "High": 684.349976, "Ret": -0.000351, "SMA50": 685.204755, "2Red": 0.0, "RSI14": 54.801846, "EMA9": 679.813964}</t>
+          <t>{"SMA20": 171.86253, "RSI14": 52.463695, "Ret": -0.008821, "EMA9": 174.089491, "2Red": 0.0, "Low": 172.699997, "Close": 174.160004, "SMA50": 174.896011, "EMA20": 173.226242, "EMA50": 174.413903, "Open": 177.460007, "Volume": 2974398.0, "High": 178.619995}</t>
         </is>
       </c>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>#5ID Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50 | Expiry 6h</t>
+          <t>#3ID Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20 | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -20081,7 +20079,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -20095,16 +20093,16 @@
         </is>
       </c>
       <c r="G63" s="4" t="n">
-        <v>741.73</v>
+        <v>683.6</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="I63" s="8" t="n">
-        <v>734.3099999999999</v>
+        <v>676.76</v>
       </c>
       <c r="J63" s="8" t="n">
-        <v>756.5599999999999</v>
+        <v>697.27</v>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
@@ -20112,7 +20110,7 @@
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>747.49</v>
+        <v>689.7</v>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
@@ -20120,16 +20118,16 @@
         </is>
       </c>
       <c r="N63" s="4" t="n">
-        <v>696.96</v>
+        <v>805.2</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>17.95</v>
+        <v>18.05</v>
       </c>
       <c r="P63" s="5" t="n">
-        <v>679.01</v>
+        <v>787.15</v>
       </c>
       <c r="Q63" s="12" t="n">
-        <v>0.76</v>
+        <v>0.87</v>
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
@@ -20138,27 +20136,27 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T63" s="3" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>63.38</t>
         </is>
       </c>
       <c r="U63" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open</t>
+          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50</t>
         </is>
       </c>
       <c r="V63" s="3" t="inlineStr">
         <is>
-          <t>{"Volume": 12583754.0, "SMA20": 738.175507, "EMA20": 738.518298, "EMA50": 740.197673, "Close": 741.72998, "Low": 741.0, "Open": 741.77002, "High": 742.099976, "Ret": -6.7e-05, "SMA50": 740.120288, "2Red": 0.0, "RSI14": 55.502244, "EMA9": 739.15355}</t>
+          <t>{"Volume": 10064291.0, "SMA20": 675.475238, "EMA20": 678.396981, "EMA50": 684.292339, "Close": 683.599976, "Low": 682.900024, "Open": 683.820007, "High": 684.349976, "Ret": -0.000351, "SMA50": 685.204755, "2Red": 0.0, "RSI14": 54.801846, "EMA9": 679.813964}</t>
         </is>
       </c>
       <c r="W63" s="3" t="inlineStr">
         <is>
-          <t>#31ID Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open | Expiry 6h</t>
+          <t>#5ID Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50 | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -20170,7 +20168,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>01:14:10 IST</t>
+          <t>02:09:08 IST</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -20180,7 +20178,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -20194,16 +20192,16 @@
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>683.6900000000001</v>
+        <v>741.73</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="I64" s="8" t="n">
-        <v>676.85</v>
+        <v>734.3099999999999</v>
       </c>
       <c r="J64" s="8" t="n">
-        <v>697.36</v>
+        <v>756.5599999999999</v>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
@@ -20211,7 +20209,7 @@
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>689.7</v>
+        <v>747.49</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
@@ -20219,16 +20217,16 @@
         </is>
       </c>
       <c r="N64" s="4" t="n">
-        <v>805.34</v>
+        <v>696.96</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>18.32</v>
+        <v>17.95</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>787.02</v>
+        <v>679.01</v>
       </c>
       <c r="Q64" s="12" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
@@ -20237,39 +20235,39 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T64" s="3" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="U64" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50</t>
+          <t>Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open</t>
         </is>
       </c>
       <c r="V64" s="3" t="inlineStr">
         <is>
-          <t>{"Volume": 6303349.0, "Ret": 0.002213, "EMA20": 677.849297, "EMA9": 678.867461, "2Red": 0.0, "SMA50": 685.700555, "SMA20": 674.813739, "Low": 681.51001, "EMA50": 684.320598, "Open": 682.325012, "High": 685.119995, "RSI14": 55.076392, "Close": 683.840027}</t>
+          <t>{"Volume": 12583754.0, "SMA20": 738.175507, "EMA20": 738.518298, "EMA50": 740.197673, "Close": 741.72998, "Low": 741.0, "Open": 741.77002, "High": 742.099976, "Ret": -6.7e-05, "SMA50": 740.120288, "2Red": 0.0, "RSI14": 55.502244, "EMA9": 739.15355}</t>
         </is>
       </c>
       <c r="W64" s="3" t="inlineStr">
         <is>
-          <t>#5ID Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50 | Expiry 6h</t>
+          <t>#31ID Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open | Expiry 6h</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>22:16:13 IST</t>
+          <t>01:14:10 IST</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -20279,7 +20277,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -20293,16 +20291,16 @@
         </is>
       </c>
       <c r="G65" s="4" t="n">
-        <v>517.88</v>
+        <v>683.6900000000001</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>512.7</v>
+        <v>676.85</v>
       </c>
       <c r="J65" s="8" t="n">
-        <v>528.24</v>
+        <v>697.36</v>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
@@ -20310,24 +20308,24 @@
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>519.65</v>
+        <v>689.7</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>21:00:00 IST</t>
+          <t>00:00:00 IST</t>
         </is>
       </c>
       <c r="N65" s="4" t="n">
-        <v>316.83</v>
+        <v>805.34</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>18.54</v>
+        <v>18.32</v>
       </c>
       <c r="P65" s="5" t="n">
-        <v>298.29</v>
+        <v>787.02</v>
       </c>
       <c r="Q65" s="12" t="n">
-        <v>0.32</v>
+        <v>0.86</v>
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
@@ -20336,23 +20334,27 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T65" s="3" t="inlineStr">
         <is>
-          <t>60.16</t>
+          <t>63.38</t>
         </is>
       </c>
       <c r="U65" s="3" t="inlineStr">
         <is>
-          <t>RSI&lt;45+EMA20&gt;EMA50+Close&lt;Open+2Red</t>
-        </is>
-      </c>
-      <c r="V65" s="3" t="inlineStr"/>
+          <t>Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50</t>
+        </is>
+      </c>
+      <c r="V65" s="3" t="inlineStr">
+        <is>
+          <t>{"Volume": 6303349.0, "Ret": 0.002213, "EMA20": 677.849297, "EMA9": 678.867461, "2Red": 0.0, "SMA50": 685.700555, "SMA20": 674.813739, "Low": 681.51001, "EMA50": 684.320598, "Open": 682.325012, "High": 685.119995, "RSI14": 55.076392, "Close": 683.840027}</t>
+        </is>
+      </c>
       <c r="W65" s="3" t="inlineStr">
         <is>
-          <t>#13ID RSI&lt;45+EMA20&gt;EMA50+Close&lt;Open+2Red | Expiry 6h</t>
+          <t>#5ID Price&gt;SMA20+Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50 | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -20364,7 +20366,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>21:32:32 IST</t>
+          <t>22:16:13 IST</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -20388,16 +20390,16 @@
         </is>
       </c>
       <c r="G66" s="4" t="n">
-        <v>517.9</v>
+        <v>517.88</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I66" s="8" t="n">
-        <v>512.72</v>
+        <v>512.7</v>
       </c>
       <c r="J66" s="8" t="n">
-        <v>528.26</v>
+        <v>528.24</v>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
@@ -20413,13 +20415,13 @@
         </is>
       </c>
       <c r="N66" s="4" t="n">
-        <v>316.75</v>
+        <v>316.83</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>18.75</v>
+        <v>18.54</v>
       </c>
       <c r="P66" s="5" t="n">
-        <v>298</v>
+        <v>298.29</v>
       </c>
       <c r="Q66" s="12" t="n">
         <v>0.32</v>
@@ -20431,23 +20433,23 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>13</t>
         </is>
       </c>
       <c r="T66" s="3" t="inlineStr">
         <is>
-          <t>67.86</t>
+          <t>60.16</t>
         </is>
       </c>
       <c r="U66" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red</t>
+          <t>RSI&lt;45+EMA20&gt;EMA50+Close&lt;Open+2Red</t>
         </is>
       </c>
       <c r="V66" s="3" t="inlineStr"/>
       <c r="W66" s="3" t="inlineStr">
         <is>
-          <t>#36ID Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red | Expiry 6h</t>
+          <t>#13ID RSI&lt;45+EMA20&gt;EMA50+Close&lt;Open+2Red | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -20459,7 +20461,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>20:59:02 IST</t>
+          <t>21:32:32 IST</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -20483,16 +20485,16 @@
         </is>
       </c>
       <c r="G67" s="4" t="n">
-        <v>518.55</v>
+        <v>517.9</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I67" s="8" t="n">
-        <v>513.37</v>
+        <v>512.72</v>
       </c>
       <c r="J67" s="8" t="n">
-        <v>528.9299999999999</v>
+        <v>528.26</v>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
@@ -20500,24 +20502,24 @@
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>516.52</v>
+        <v>519.65</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>20:00:00 IST</t>
+          <t>21:00:00 IST</t>
         </is>
       </c>
       <c r="N67" s="4" t="n">
-        <v>-372.4</v>
+        <v>316.75</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>18.98</v>
-      </c>
-      <c r="P67" s="6" t="n">
-        <v>-391.38</v>
-      </c>
-      <c r="Q67" s="13" t="n">
-        <v>-0.41</v>
+        <v>18.75</v>
+      </c>
+      <c r="P67" s="5" t="n">
+        <v>298</v>
+      </c>
+      <c r="Q67" s="12" t="n">
+        <v>0.32</v>
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
@@ -20554,7 +20556,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>20:11:02 IST</t>
+          <t>20:59:02 IST</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -20578,16 +20580,16 @@
         </is>
       </c>
       <c r="G68" s="4" t="n">
-        <v>518.47</v>
+        <v>518.55</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I68" s="8" t="n">
-        <v>513.28</v>
+        <v>513.37</v>
       </c>
       <c r="J68" s="8" t="n">
-        <v>528.83</v>
+        <v>528.9299999999999</v>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
@@ -20595,24 +20597,24 @@
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>518.47</v>
+        <v>516.52</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>19:00:00 IST</t>
-        </is>
-      </c>
-      <c r="N68" s="10" t="n">
-        <v>-0.92</v>
+          <t>20:00:00 IST</t>
+        </is>
+      </c>
+      <c r="N68" s="4" t="n">
+        <v>-372.4</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>19.08</v>
+        <v>18.98</v>
       </c>
       <c r="P68" s="6" t="n">
-        <v>-20</v>
+        <v>-391.38</v>
       </c>
       <c r="Q68" s="13" t="n">
-        <v>-0.02</v>
+        <v>-0.41</v>
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
@@ -20649,7 +20651,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>01:14:16 IST</t>
+          <t>20:11:02 IST</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -20659,7 +20661,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -20673,16 +20675,16 @@
         </is>
       </c>
       <c r="G69" s="4" t="n">
-        <v>741.2</v>
+        <v>518.47</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>133</v>
+        <v>184</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>733.79</v>
+        <v>513.28</v>
       </c>
       <c r="J69" s="8" t="n">
-        <v>756.02</v>
+        <v>528.83</v>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
@@ -20690,24 +20692,24 @@
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>733.79</v>
+        <v>518.47</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>20:00:00 IST</t>
-        </is>
-      </c>
-      <c r="N69" s="4" t="n">
-        <v>-985.53</v>
+          <t>19:00:00 IST</t>
+        </is>
+      </c>
+      <c r="N69" s="10" t="n">
+        <v>-0.92</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>19.72</v>
+        <v>19.08</v>
       </c>
       <c r="P69" s="6" t="n">
-        <v>-1005.25</v>
-      </c>
-      <c r="Q69" s="6" t="n">
-        <v>-1.02</v>
+        <v>-20</v>
+      </c>
+      <c r="Q69" s="13" t="n">
+        <v>-0.02</v>
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
@@ -20716,35 +20718,35 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T69" s="3" t="inlineStr">
         <is>
-          <t>60.24</t>
+          <t>67.86</t>
         </is>
       </c>
       <c r="U69" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
+          <t>Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red</t>
         </is>
       </c>
       <c r="V69" s="3" t="inlineStr"/>
       <c r="W69" s="3" t="inlineStr">
         <is>
-          <t>#32ID Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | SL Hit</t>
+          <t>#36ID Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red | Expiry 6h</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>23:22:38 IST</t>
+          <t>01:14:16 IST</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -20754,12 +20756,12 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -20768,16 +20770,16 @@
         </is>
       </c>
       <c r="G70" s="4" t="n">
-        <v>293.1</v>
+        <v>741.2</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>337</v>
+        <v>133</v>
       </c>
       <c r="I70" s="8" t="n">
-        <v>296.03</v>
+        <v>733.79</v>
       </c>
       <c r="J70" s="8" t="n">
-        <v>287.24</v>
+        <v>756.02</v>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
@@ -20785,24 +20787,24 @@
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>289.59</v>
+        <v>733.79</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>22:00:00 IST</t>
+          <t>20:00:00 IST</t>
         </is>
       </c>
       <c r="N70" s="4" t="n">
-        <v>1182.87</v>
+        <v>-985.53</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="P70" s="5" t="n">
-        <v>1163.12</v>
-      </c>
-      <c r="Q70" s="5" t="n">
-        <v>1.18</v>
+        <v>19.72</v>
+      </c>
+      <c r="P70" s="6" t="n">
+        <v>-1005.25</v>
+      </c>
+      <c r="Q70" s="6" t="n">
+        <v>-1.02</v>
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
@@ -20811,35 +20813,35 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T70" s="3" t="inlineStr">
         <is>
-          <t>63.41</t>
+          <t>60.24</t>
         </is>
       </c>
       <c r="U70" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
+          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
         </is>
       </c>
       <c r="V70" s="3" t="inlineStr"/>
       <c r="W70" s="3" t="inlineStr">
         <is>
-          <t>#14ID Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | Expiry 6h</t>
+          <t>#32ID Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | SL Hit</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>23:32:56 IST</t>
+          <t>23:22:38 IST</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -20849,12 +20851,12 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -20863,16 +20865,16 @@
         </is>
       </c>
       <c r="G71" s="4" t="n">
-        <v>520.27</v>
+        <v>293.1</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>191</v>
+        <v>337</v>
       </c>
       <c r="I71" s="8" t="n">
-        <v>515.0599999999999</v>
+        <v>296.03</v>
       </c>
       <c r="J71" s="8" t="n">
-        <v>530.67</v>
+        <v>287.24</v>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
@@ -20880,24 +20882,24 @@
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>526.96</v>
+        <v>289.59</v>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>23:00:00 IST</t>
+          <t>22:00:00 IST</t>
         </is>
       </c>
       <c r="N71" s="4" t="n">
-        <v>1277.79</v>
+        <v>1182.87</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>19.87</v>
+        <v>19.75</v>
       </c>
       <c r="P71" s="5" t="n">
-        <v>1257.92</v>
+        <v>1163.12</v>
       </c>
       <c r="Q71" s="5" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
@@ -20906,67 +20908,162 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T71" s="3" t="inlineStr">
         <is>
-          <t>67.86</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="U71" s="3" t="inlineStr">
         <is>
-          <t>Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red</t>
+          <t>Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
         </is>
       </c>
       <c r="V71" s="3" t="inlineStr"/>
       <c r="W71" s="3" t="inlineStr">
         <is>
+          <t>#14ID Price&lt;SMA50+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open | Expiry 6h</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>23:32:56 IST</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>DIA</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>INTRADAY_1h</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>520.27</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>191</v>
+      </c>
+      <c r="I72" s="8" t="n">
+        <v>515.0599999999999</v>
+      </c>
+      <c r="J72" s="8" t="n">
+        <v>530.67</v>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>526.96</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>23:00:00 IST</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="n">
+        <v>1277.79</v>
+      </c>
+      <c r="O72" s="4" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="P72" s="5" t="n">
+        <v>1257.92</v>
+      </c>
+      <c r="Q72" s="5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="T72" s="3" t="inlineStr">
+        <is>
+          <t>67.86</t>
+        </is>
+      </c>
+      <c r="U72" s="3" t="inlineStr">
+        <is>
+          <t>Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red</t>
+        </is>
+      </c>
+      <c r="V72" s="3" t="inlineStr"/>
+      <c r="W72" s="3" t="inlineStr">
+        <is>
           <t>#36ID Price&lt;SMA50+EMA9&gt;EMA20+Close&lt;Open+2Red | Expiry 6h</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="14" t="inlineStr"/>
-      <c r="B72" s="14" t="inlineStr"/>
-      <c r="C72" s="15" t="inlineStr"/>
-      <c r="D72" s="15" t="inlineStr"/>
-      <c r="E72" s="15" t="inlineStr"/>
-      <c r="F72" s="15" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr"/>
+      <c r="B73" s="14" t="inlineStr"/>
+      <c r="C73" s="15" t="inlineStr"/>
+      <c r="D73" s="15" t="inlineStr"/>
+      <c r="E73" s="15" t="inlineStr"/>
+      <c r="F73" s="15" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="G72" s="16" t="inlineStr"/>
-      <c r="H72" s="16" t="inlineStr"/>
-      <c r="I72" s="15" t="inlineStr"/>
-      <c r="J72" s="15" t="inlineStr"/>
-      <c r="K72" s="14" t="inlineStr"/>
-      <c r="L72" s="15" t="inlineStr"/>
-      <c r="M72" s="14" t="inlineStr"/>
-      <c r="N72" s="17" t="n">
+      <c r="G73" s="16" t="inlineStr"/>
+      <c r="H73" s="16" t="inlineStr"/>
+      <c r="I73" s="15" t="inlineStr"/>
+      <c r="J73" s="15" t="inlineStr"/>
+      <c r="K73" s="14" t="inlineStr"/>
+      <c r="L73" s="15" t="inlineStr"/>
+      <c r="M73" s="14" t="inlineStr"/>
+      <c r="N73" s="17" t="n">
         <v>18523.39</v>
       </c>
-      <c r="O72" s="17" t="n">
+      <c r="O73" s="17" t="n">
         <v>3592.33</v>
       </c>
-      <c r="P72" s="18" t="n">
+      <c r="P73" s="18" t="n">
         <v>14931.06</v>
       </c>
-      <c r="Q72" s="16" t="inlineStr"/>
-      <c r="R72" s="15" t="inlineStr">
-        <is>
-          <t>70 trades (65 closed / 5 open)</t>
-        </is>
-      </c>
-      <c r="S72" s="15" t="inlineStr"/>
-      <c r="T72" s="14" t="inlineStr"/>
-      <c r="U72" s="14" t="inlineStr"/>
-      <c r="V72" s="14" t="inlineStr"/>
-      <c r="W72" s="14" t="inlineStr"/>
+      <c r="Q73" s="16" t="inlineStr"/>
+      <c r="R73" s="15" t="inlineStr">
+        <is>
+          <t>71 trades (65 closed / 6 open)</t>
+        </is>
+      </c>
+      <c r="S73" s="15" t="inlineStr"/>
+      <c r="T73" s="14" t="inlineStr"/>
+      <c r="U73" s="14" t="inlineStr"/>
+      <c r="V73" s="14" t="inlineStr"/>
+      <c r="W73" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W71"/>
+  <autoFilter ref="A1:W72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14085,19 +14085,19 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>26.1</v>
+        <v>-20.88</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>39.82</v>
       </c>
       <c r="P2" s="9" t="inlineStr">
         <is>
-          <t>~-13.72 (unrealized)</t>
+          <t>~-60.70 (unrealized)</t>
         </is>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>~+0.01%</t>
+          <t>~-0.01%</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -14479,19 +14479,19 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="4" t="n">
-        <v>1255.28</v>
+        <v>1221.2</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>10.44</v>
       </c>
       <c r="P6" s="9" t="inlineStr">
         <is>
-          <t>~1,244.84 (unrealized)</t>
+          <t>~1,210.76 (unrealized)</t>
         </is>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
-          <t>~+2.41%</t>
+          <t>~+2.34%</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -14576,19 +14576,19 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="4" t="n">
-        <v>-94.53</v>
+        <v>-101.38</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>~-104.95 (unrealized)</t>
+          <t>~-111.80 (unrealized)</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>~-0.18%</t>
+          <t>~-0.19%</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -14673,19 +14673,19 @@
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="4" t="n">
-        <v>-116.5</v>
+        <v>-121.16</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>~-127.00 (unrealized)</t>
+          <t>~-131.66 (unrealized)</t>
         </is>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
-          <t>~-0.22%</t>
+          <t>~-0.23%</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -14770,19 +14770,19 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>40.76</v>
+        <v>62.7</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>~30.30 (unrealized)</t>
+          <t>~52.24 (unrealized)</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>~+0.08%</t>
+          <t>~+0.12%</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -14867,19 +14867,19 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="4" t="n">
-        <v>-46.6</v>
+        <v>-43.87</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>~-56.78 (unrealized)</t>
+          <t>~-54.05 (unrealized)</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>~-1.37%</t>
+          <t>~-1.29%</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14867,19 +14867,19 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="4" t="n">
-        <v>-43.87</v>
+        <v>-49.29</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>~-54.05 (unrealized)</t>
+          <t>~-59.47 (unrealized)</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>~-1.29%</t>
+          <t>~-1.45%</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14867,19 +14867,19 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="4" t="n">
-        <v>-49.29</v>
+        <v>-47.4</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>~-59.47 (unrealized)</t>
+          <t>~-57.58 (unrealized)</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>~-1.45%</t>
+          <t>~-1.40%</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14867,19 +14867,19 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="4" t="n">
-        <v>-47.4</v>
+        <v>-35.57</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>~-57.58 (unrealized)</t>
+          <t>~-45.75 (unrealized)</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>~-1.40%</t>
+          <t>~-1.05%</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14867,19 +14867,19 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="4" t="n">
-        <v>-35.57</v>
+        <v>-35.21</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>~-45.75 (unrealized)</t>
+          <t>~-45.39 (unrealized)</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>~-1.05%</t>
+          <t>~-1.04%</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14867,19 +14867,19 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="4" t="n">
-        <v>-35.21</v>
+        <v>-27.81</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>~-45.39 (unrealized)</t>
+          <t>~-37.99 (unrealized)</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>~-1.04%</t>
+          <t>~-0.82%</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -109,6 +109,9 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -119,9 +122,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1303,17 +1303,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>#31ID SPY LONG</t>
+          <t>#1SW XLY LONG</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1328,20 +1328,20 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open</t>
+          <t>EMA9&lt;EMA50+RSI&gt;50</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>63.16</v>
+        <v>58.65</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3.67</v>
+        <v>59.99</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>1</v>
@@ -1353,16 +1353,16 @@
         <v>100</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>696.96</v>
+        <v>633.37</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>17.95</v>
+        <v>9.94</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>679.01</v>
+        <v>623.4299999999999</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>679.01</v>
+        <v>623.4299999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>#1SW XLY LONG</t>
+          <t>#37SW QQQ LONG</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>EMA9&lt;EMA50+RSI&gt;50</t>
+          <t>Price&gt;SMA50+EMA9&gt;EMA20+2Red</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>58.65</v>
+        <v>60.94</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>59.99</v>
+        <v>45.8</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1415,22 +1415,22 @@
         <v>1</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>633.37</v>
+        <v>633.8</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>9.94</v>
+        <v>19.8</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>623.4299999999999</v>
+        <v>614</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>623.4299999999999</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>#37SW QQQ LONG</t>
+          <t>#14SW ETH-USD LONG</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1464,14 +1464,14 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+EMA9&gt;EMA20+2Red</t>
+          <t>Price&gt;SMA50+Range&gt;1.5%+2Red</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>60.94</v>
+        <v>63.36</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45.8</v>
+        <v>74.7</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>2</v>
@@ -1489,16 +1489,16 @@
         <v>50</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>633.8</v>
+        <v>777.78</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>19.8</v>
+        <v>285.41</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>614</v>
+        <v>492.37</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>307</v>
+        <v>246.18</v>
       </c>
     </row>
     <row r="15">
@@ -1507,17 +1507,17 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>#14SW ETH-USD LONG</t>
+          <t>#1ID SOL-USD SHORT</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>SOL-USD</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1527,46 +1527,46 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+Range&gt;1.5%+2Red</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>63.36</v>
+        <v>47.24</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>74.7</v>
+        <v>23.69</v>
       </c>
       <c r="J15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>777.78</v>
+        <v>1386.59</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>285.41</v>
+        <v>943.16</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>492.37</v>
+        <v>443.43</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>246.18</v>
+        <v>147.81</v>
       </c>
     </row>
     <row r="16">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>#1ID SOL-USD SHORT</t>
+          <t>#32ID SPY LONG</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1585,56 +1585,56 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>SOL-USD</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+RSI&lt;50</t>
+          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>47.24</v>
+        <v>60.24</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>23.69</v>
+        <v>3.27</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1386.59</v>
+        <v>410.34</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>943.16</v>
+        <v>37.47</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>443.43</v>
+        <v>372.87</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>147.81</v>
+        <v>186.43</v>
       </c>
     </row>
     <row r="17">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>#32ID SPY LONG</t>
+          <t>#16ID SPY LONG</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1672,13 +1672,13 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>60.24</v>
+        <v>62.35</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3.27</v>
+        <v>6.99</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1687,22 +1687,22 @@
         <v>1</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>410.34</v>
+        <v>373.46</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>37.47</v>
+        <v>20.86</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>372.87</v>
+        <v>352.6</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>186.43</v>
+        <v>352.6</v>
       </c>
     </row>
     <row r="18">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>#16ID SPY LONG</t>
+          <t>#5SW XLB LONG</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1736,14 +1736,14 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+EMA9&gt;EMA20+EMA20&lt;EMA50+Close&gt;Open</t>
+          <t>EMA9&gt;EMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>62.35</v>
+        <v>50.21</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>6.99</v>
+        <v>11.26</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>1</v>
@@ -1761,16 +1761,16 @@
         <v>100</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>373.46</v>
+        <v>342.69</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>20.86</v>
+        <v>10.06</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>352.6</v>
+        <v>332.63</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>352.6</v>
+        <v>332.63</v>
       </c>
     </row>
     <row r="19">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>#5SW XLB LONG</t>
+          <t>#2SW XLB LONG</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1804,17 +1804,17 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Range&lt;1%</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>50.21</v>
+        <v>51.71</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>11.26</v>
+        <v>23.19</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1823,22 +1823,22 @@
         <v>1</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>342.69</v>
+        <v>318.81</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>10.06</v>
+        <v>20.44</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>332.63</v>
+        <v>298.37</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>332.63</v>
+        <v>149.19</v>
       </c>
     </row>
     <row r="20">
@@ -1847,17 +1847,17 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>#2SW XLB LONG</t>
+          <t>#13ID DIA LONG</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>RSI&lt;45+EMA20&gt;EMA50+Close&lt;Open+2Red</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>51.71</v>
+        <v>60.16</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>23.19</v>
+        <v>7.88</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1891,22 +1891,22 @@
         <v>1</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>318.81</v>
+        <v>316.83</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>20.44</v>
+        <v>18.54</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>298.37</v>
+        <v>298.29</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>149.19</v>
+        <v>298.29</v>
       </c>
     </row>
     <row r="21">
@@ -1915,17 +1915,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>#13ID DIA LONG</t>
+          <t>#3SW VTI LONG</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>VTI</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1940,14 +1940,14 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>RSI&lt;45+EMA20&gt;EMA50+Close&lt;Open+2Red</t>
+          <t>Range&lt;1%+SMA20&lt;EMA20</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>60.16</v>
+        <v>60.9</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7.88</v>
+        <v>112.53</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>1</v>
@@ -1965,16 +1965,16 @@
         <v>100</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>316.83</v>
+        <v>294.2</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>18.54</v>
+        <v>10.03</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>298.29</v>
+        <v>284.17</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>298.29</v>
+        <v>284.17</v>
       </c>
     </row>
     <row r="22">
@@ -1983,17 +1983,17 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>#3SW VTI LONG</t>
+          <t>#31ID SPY LONG</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2008,17 +2008,17 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Range&lt;1%+SMA20&lt;EMA20</t>
+          <t>Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>60.9</v>
+        <v>63.16</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>112.53</v>
+        <v>3.67</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -2027,22 +2027,22 @@
         <v>1</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>294.2</v>
+        <v>244.84</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>10.03</v>
+        <v>57.77</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>284.17</v>
+        <v>187.07</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>284.17</v>
+        <v>93.53</v>
       </c>
     </row>
     <row r="23">
@@ -14082,27 +14082,29 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
+      <c r="L2" s="2" t="n">
+        <v>761.03</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:47:46 IST</t>
+        </is>
+      </c>
       <c r="N2" s="4" t="n">
-        <v>-20.88</v>
+        <v>-452.12</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>39.82</v>
       </c>
-      <c r="P2" s="9" t="inlineStr">
-        <is>
-          <t>~-60.70 (unrealized)</t>
-        </is>
-      </c>
-      <c r="Q2" s="9" t="inlineStr">
-        <is>
-          <t>~-0.01%</t>
-        </is>
+      <c r="P2" s="6" t="n">
+        <v>-491.94</v>
+      </c>
+      <c r="Q2" s="9" t="n">
+        <v>-0.25</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -14127,7 +14129,7 @@
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>#31ID Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open</t>
+          <t>#31ID Price&gt;SMA50+EMA20&lt;EMA50+Close&lt;Open | Expiry 6h</t>
         </is>
       </c>
     </row>
@@ -14484,12 +14486,12 @@
       <c r="O6" s="4" t="n">
         <v>10.44</v>
       </c>
-      <c r="P6" s="9" t="inlineStr">
+      <c r="P6" s="10" t="inlineStr">
         <is>
           <t>~1,210.76 (unrealized)</t>
         </is>
       </c>
-      <c r="Q6" s="9" t="inlineStr">
+      <c r="Q6" s="10" t="inlineStr">
         <is>
           <t>~+2.34%</t>
         </is>
@@ -14581,12 +14583,12 @@
       <c r="O7" s="4" t="n">
         <v>10.42</v>
       </c>
-      <c r="P7" s="9" t="inlineStr">
+      <c r="P7" s="10" t="inlineStr">
         <is>
           <t>~-111.80 (unrealized)</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="Q7" s="10" t="inlineStr">
         <is>
           <t>~-0.19%</t>
         </is>
@@ -14678,12 +14680,12 @@
       <c r="O8" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="P8" s="9" t="inlineStr">
+      <c r="P8" s="10" t="inlineStr">
         <is>
           <t>~-131.66 (unrealized)</t>
         </is>
       </c>
-      <c r="Q8" s="9" t="inlineStr">
+      <c r="Q8" s="10" t="inlineStr">
         <is>
           <t>~-0.23%</t>
         </is>
@@ -14775,12 +14777,12 @@
       <c r="O9" s="4" t="n">
         <v>10.46</v>
       </c>
-      <c r="P9" s="9" t="inlineStr">
+      <c r="P9" s="10" t="inlineStr">
         <is>
           <t>~52.24 (unrealized)</t>
         </is>
       </c>
-      <c r="Q9" s="9" t="inlineStr">
+      <c r="Q9" s="10" t="inlineStr">
         <is>
           <t>~+0.12%</t>
         </is>
@@ -14847,16 +14849,16 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="11" t="n">
         <v>0.3393</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="I10" s="11" t="n">
+      <c r="I10" s="12" t="n">
         <v>0.3315</v>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="J10" s="12" t="n">
         <v>0.3518</v>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -14872,12 +14874,12 @@
       <c r="O10" s="4" t="n">
         <v>10.18</v>
       </c>
-      <c r="P10" s="9" t="inlineStr">
+      <c r="P10" s="10" t="inlineStr">
         <is>
           <t>~-37.99 (unrealized)</t>
         </is>
       </c>
-      <c r="Q10" s="9" t="inlineStr">
+      <c r="Q10" s="10" t="inlineStr">
         <is>
           <t>~-0.82%</t>
         </is>
@@ -15043,16 +15045,16 @@
           <t>INTRADAY_1h</t>
         </is>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="11" t="n">
         <v>0.083828</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>50000</v>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="12" t="n">
         <v>0.085341</v>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="J12" s="12" t="n">
         <v>0.08155800000000001</v>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -15374,7 +15376,7 @@
       <c r="P15" s="5" t="n">
         <v>273.16</v>
       </c>
-      <c r="Q15" s="12" t="n">
+      <c r="Q15" s="13" t="n">
         <v>0.52</v>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -15736,16 +15738,16 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="G19" s="11" t="n">
         <v>0.3349</v>
       </c>
       <c r="H19" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="I19" s="11" t="n">
+      <c r="I19" s="12" t="n">
         <v>0.3272</v>
       </c>
-      <c r="J19" s="11" t="n">
+      <c r="J19" s="12" t="n">
         <v>0.3473</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -15770,7 +15772,7 @@
       <c r="P19" s="5" t="n">
         <v>24.96</v>
       </c>
-      <c r="Q19" s="12" t="n">
+      <c r="Q19" s="13" t="n">
         <v>0.75</v>
       </c>
       <c r="R19" s="2" t="inlineStr">
@@ -16265,7 +16267,7 @@
       <c r="P24" s="5" t="n">
         <v>332.63</v>
       </c>
-      <c r="Q24" s="12" t="n">
+      <c r="Q24" s="13" t="n">
         <v>0.66</v>
       </c>
       <c r="R24" s="2" t="inlineStr">
@@ -16364,7 +16366,7 @@
       <c r="P25" s="5" t="n">
         <v>181.12</v>
       </c>
-      <c r="Q25" s="12" t="n">
+      <c r="Q25" s="13" t="n">
         <v>0.28</v>
       </c>
       <c r="R25" s="2" t="inlineStr">
@@ -16463,7 +16465,7 @@
       <c r="P26" s="5" t="n">
         <v>65.36</v>
       </c>
-      <c r="Q26" s="12" t="n">
+      <c r="Q26" s="13" t="n">
         <v>0.13</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -16661,7 +16663,7 @@
       <c r="P28" s="5" t="n">
         <v>352.6</v>
       </c>
-      <c r="Q28" s="12" t="n">
+      <c r="Q28" s="13" t="n">
         <v>0.34</v>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -16958,7 +16960,7 @@
       <c r="P31" s="5" t="n">
         <v>284.17</v>
       </c>
-      <c r="Q31" s="12" t="n">
+      <c r="Q31" s="13" t="n">
         <v>0.57</v>
       </c>
       <c r="R31" s="2" t="inlineStr">
@@ -17156,7 +17158,7 @@
       <c r="P33" s="5" t="n">
         <v>183.99</v>
       </c>
-      <c r="Q33" s="12" t="n">
+      <c r="Q33" s="13" t="n">
         <v>0.38</v>
       </c>
       <c r="R33" s="2" t="inlineStr">
@@ -17255,7 +17257,7 @@
       <c r="P34" s="6" t="n">
         <v>-479</v>
       </c>
-      <c r="Q34" s="13" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-0.96</v>
       </c>
       <c r="R34" s="2" t="inlineStr">
@@ -17320,16 +17322,16 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G35" s="10" t="n">
+      <c r="G35" s="11" t="n">
         <v>0.3462</v>
       </c>
       <c r="H35" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="I35" s="11" t="n">
+      <c r="I35" s="12" t="n">
         <v>0.3382</v>
       </c>
-      <c r="J35" s="11" t="n">
+      <c r="J35" s="12" t="n">
         <v>0.3589</v>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -17453,7 +17455,7 @@
       <c r="P36" s="5" t="n">
         <v>373.92</v>
       </c>
-      <c r="Q36" s="12" t="n">
+      <c r="Q36" s="13" t="n">
         <v>0.76</v>
       </c>
       <c r="R36" s="2" t="inlineStr">
@@ -17552,7 +17554,7 @@
       <c r="P37" s="5" t="n">
         <v>35.91</v>
       </c>
-      <c r="Q37" s="12" t="n">
+      <c r="Q37" s="13" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="R37" s="2" t="inlineStr">
@@ -17651,7 +17653,7 @@
       <c r="P38" s="6" t="n">
         <v>-311.52</v>
       </c>
-      <c r="Q38" s="13" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-0.63</v>
       </c>
       <c r="R38" s="2" t="inlineStr">
@@ -17750,7 +17752,7 @@
       <c r="P39" s="6" t="n">
         <v>-448.74</v>
       </c>
-      <c r="Q39" s="13" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-0.87</v>
       </c>
       <c r="R39" s="2" t="inlineStr">
@@ -18112,16 +18114,16 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G43" s="10" t="n">
+      <c r="G43" s="11" t="n">
         <v>0.332</v>
       </c>
       <c r="H43" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="I43" s="11" t="n">
+      <c r="I43" s="12" t="n">
         <v>0.3244</v>
       </c>
-      <c r="J43" s="11" t="n">
+      <c r="J43" s="12" t="n">
         <v>0.3442</v>
       </c>
       <c r="K43" s="3" t="inlineStr">
@@ -18344,7 +18346,7 @@
       <c r="P45" s="6" t="n">
         <v>-141.68</v>
       </c>
-      <c r="Q45" s="13" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-0.28</v>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -18443,7 +18445,7 @@
       <c r="P46" s="6" t="n">
         <v>-126.33</v>
       </c>
-      <c r="Q46" s="13" t="n">
+      <c r="Q46" s="9" t="n">
         <v>-0.25</v>
       </c>
       <c r="R46" s="2" t="inlineStr">
@@ -18641,7 +18643,7 @@
       <c r="P48" s="5" t="n">
         <v>19.63</v>
       </c>
-      <c r="Q48" s="12" t="n">
+      <c r="Q48" s="13" t="n">
         <v>0.04</v>
       </c>
       <c r="R48" s="2" t="inlineStr">
@@ -18706,16 +18708,16 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G49" s="10" t="n">
+      <c r="G49" s="11" t="n">
         <v>0.331</v>
       </c>
       <c r="H49" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="I49" s="11" t="n">
+      <c r="I49" s="12" t="n">
         <v>0.3241</v>
       </c>
-      <c r="J49" s="11" t="n">
+      <c r="J49" s="12" t="n">
         <v>0.3439</v>
       </c>
       <c r="K49" s="3" t="inlineStr">
@@ -18740,7 +18742,7 @@
       <c r="P49" s="6" t="n">
         <v>-15.49</v>
       </c>
-      <c r="Q49" s="13" t="n">
+      <c r="Q49" s="9" t="n">
         <v>-0.47</v>
       </c>
       <c r="R49" s="2" t="inlineStr">
@@ -18938,7 +18940,7 @@
       <c r="P51" s="5" t="n">
         <v>194.6</v>
       </c>
-      <c r="Q51" s="12" t="n">
+      <c r="Q51" s="13" t="n">
         <v>0.4</v>
       </c>
       <c r="R51" s="2" t="inlineStr">
@@ -19037,7 +19039,7 @@
       <c r="P52" s="6" t="n">
         <v>-76.67</v>
       </c>
-      <c r="Q52" s="13" t="n">
+      <c r="Q52" s="9" t="n">
         <v>-0.16</v>
       </c>
       <c r="R52" s="2" t="inlineStr">
@@ -19136,7 +19138,7 @@
       <c r="P53" s="5" t="n">
         <v>95.48</v>
       </c>
-      <c r="Q53" s="12" t="n">
+      <c r="Q53" s="13" t="n">
         <v>0.19</v>
       </c>
       <c r="R53" s="2" t="inlineStr">
@@ -19235,7 +19237,7 @@
       <c r="P54" s="5" t="n">
         <v>440.05</v>
       </c>
-      <c r="Q54" s="12" t="n">
+      <c r="Q54" s="13" t="n">
         <v>0.86</v>
       </c>
       <c r="R54" s="2" t="inlineStr">
@@ -19300,16 +19302,16 @@
           <t>SWING_1d</t>
         </is>
       </c>
-      <c r="G55" s="10" t="n">
+      <c r="G55" s="11" t="n">
         <v>0.3281</v>
       </c>
       <c r="H55" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="I55" s="11" t="n">
+      <c r="I55" s="12" t="n">
         <v>0.3215</v>
       </c>
-      <c r="J55" s="11" t="n">
+      <c r="J55" s="12" t="n">
         <v>0.3412</v>
       </c>
       <c r="K55" s="3" t="inlineStr">
@@ -19334,7 +19336,7 @@
       <c r="P55" s="5" t="n">
         <v>9.48</v>
       </c>
-      <c r="Q55" s="12" t="n">
+      <c r="Q55" s="13" t="n">
         <v>0.29</v>
       </c>
       <c r="R55" s="2" t="inlineStr">
@@ -20027,7 +20029,7 @@
       <c r="P62" s="5" t="n">
         <v>742.39</v>
       </c>
-      <c r="Q62" s="12" t="n">
+      <c r="Q62" s="13" t="n">
         <v>0.87</v>
       </c>
       <c r="R62" s="2" t="inlineStr">
@@ -20126,7 +20128,7 @@
       <c r="P63" s="5" t="n">
         <v>787.15</v>
       </c>
-      <c r="Q63" s="12" t="n">
+      <c r="Q63" s="13" t="n">
         <v>0.87</v>
       </c>
       <c r="R63" s="2" t="inlineStr">
@@ -20225,7 +20227,7 @@
       <c r="P64" s="5" t="n">
         <v>679.01</v>
       </c>
-      <c r="Q64" s="12" t="n">
+      <c r="Q64" s="13" t="n">
         <v>0.76</v>
       </c>
       <c r="R64" s="2" t="inlineStr">
@@ -20324,7 +20326,7 @@
       <c r="P65" s="5" t="n">
         <v>787.02</v>
       </c>
-      <c r="Q65" s="12" t="n">
+      <c r="Q65" s="13" t="n">
         <v>0.86</v>
       </c>
       <c r="R65" s="2" t="inlineStr">
@@ -20423,7 +20425,7 @@
       <c r="P66" s="5" t="n">
         <v>298.29</v>
       </c>
-      <c r="Q66" s="12" t="n">
+      <c r="Q66" s="13" t="n">
         <v>0.32</v>
       </c>
       <c r="R66" s="2" t="inlineStr">
@@ -20518,7 +20520,7 @@
       <c r="P67" s="5" t="n">
         <v>298</v>
       </c>
-      <c r="Q67" s="12" t="n">
+      <c r="Q67" s="13" t="n">
         <v>0.32</v>
       </c>
       <c r="R67" s="2" t="inlineStr">
@@ -20613,7 +20615,7 @@
       <c r="P68" s="6" t="n">
         <v>-391.38</v>
       </c>
-      <c r="Q68" s="13" t="n">
+      <c r="Q68" s="9" t="n">
         <v>-0.41</v>
       </c>
       <c r="R68" s="2" t="inlineStr">
@@ -20699,7 +20701,7 @@
           <t>19:00:00 IST</t>
         </is>
       </c>
-      <c r="N69" s="10" t="n">
+      <c r="N69" s="11" t="n">
         <v>-0.92</v>
       </c>
       <c r="O69" s="4" t="n">
@@ -20708,7 +20710,7 @@
       <c r="P69" s="6" t="n">
         <v>-20</v>
       </c>
-      <c r="Q69" s="13" t="n">
+      <c r="Q69" s="9" t="n">
         <v>-0.02</v>
       </c>
       <c r="R69" s="2" t="inlineStr">
@@ -21042,18 +21044,18 @@
       <c r="L73" s="15" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
       <c r="N73" s="17" t="n">
-        <v>18523.39</v>
+        <v>18071.27</v>
       </c>
       <c r="O73" s="17" t="n">
-        <v>3592.33</v>
+        <v>3632.15</v>
       </c>
       <c r="P73" s="18" t="n">
-        <v>14931.06</v>
+        <v>14439.12</v>
       </c>
       <c r="Q73" s="16" t="inlineStr"/>
       <c r="R73" s="15" t="inlineStr">
         <is>
-          <t>71 trades (65 closed / 6 open)</t>
+          <t>71 trades (66 closed / 5 open)</t>
         </is>
       </c>
       <c r="S73" s="15" t="inlineStr"/>

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14481,19 +14481,19 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="4" t="n">
-        <v>1221.2</v>
+        <v>1669.92</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>10.44</v>
       </c>
       <c r="P6" s="10" t="inlineStr">
         <is>
-          <t>~1,210.76 (unrealized)</t>
+          <t>~1,659.48 (unrealized)</t>
         </is>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
-          <t>~+2.34%</t>
+          <t>~+3.20%</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -14578,19 +14578,19 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="4" t="n">
-        <v>-101.38</v>
+        <v>-49.32</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>10.42</v>
       </c>
       <c r="P7" s="10" t="inlineStr">
         <is>
-          <t>~-111.80 (unrealized)</t>
+          <t>~-59.74 (unrealized)</t>
         </is>
       </c>
       <c r="Q7" s="10" t="inlineStr">
         <is>
-          <t>~-0.19%</t>
+          <t>~-0.09%</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -14675,19 +14675,19 @@
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="4" t="n">
-        <v>-121.16</v>
+        <v>-838.8</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="P8" s="10" t="inlineStr">
         <is>
-          <t>~-131.66 (unrealized)</t>
+          <t>~-849.30 (unrealized)</t>
         </is>
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
-          <t>~-0.23%</t>
+          <t>~-1.60%</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -14772,19 +14772,19 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>62.7</v>
+        <v>-369.93</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.46</v>
       </c>
       <c r="P9" s="10" t="inlineStr">
         <is>
-          <t>~52.24 (unrealized)</t>
+          <t>~-380.39 (unrealized)</t>
         </is>
       </c>
       <c r="Q9" s="10" t="inlineStr">
         <is>
-          <t>~+0.12%</t>
+          <t>~-0.71%</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -14869,19 +14869,19 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="4" t="n">
-        <v>-27.81</v>
+        <v>-7.82</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P10" s="10" t="inlineStr">
         <is>
-          <t>~-37.99 (unrealized)</t>
+          <t>~-18.00 (unrealized)</t>
         </is>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
-          <t>~-0.82%</t>
+          <t>~-0.23%</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14869,19 +14869,19 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="4" t="n">
-        <v>-7.82</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P10" s="10" t="inlineStr">
         <is>
-          <t>~-18.00 (unrealized)</t>
+          <t>~-18.55 (unrealized)</t>
         </is>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
-          <t>~-0.23%</t>
+          <t>~-0.25%</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14869,19 +14869,19 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="4" t="n">
-        <v>-8.369999999999999</v>
+        <v>-9.4</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.18</v>
       </c>
       <c r="P10" s="10" t="inlineStr">
         <is>
-          <t>~-18.55 (unrealized)</t>
+          <t>~-19.58 (unrealized)</t>
         </is>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
-          <t>~-0.25%</t>
+          <t>~-0.28%</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -2323,17 +2323,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>#1SW TRX-USD LONG</t>
+          <t>#1ID DOGE-USD SHORT</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>DOGE-USD</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2343,46 +2343,46 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>Price&gt;SMA20+RSI&lt;45</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>66.67</v>
+        <v>50.67</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>51.86</v>
+        <v>31.42</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L27" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="N27" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-27.64</v>
+        <v>-88.45</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>40.12</v>
+        <v>12.57</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>-67.76000000000001</v>
+        <v>-101.02</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-16.94</v>
+        <v>-101.02</v>
       </c>
     </row>
     <row r="28">
@@ -2391,17 +2391,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>#1ID DOGE-USD SHORT</t>
+          <t>#1SW TRX-USD LONG</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>DOGE-USD</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2411,46 +2411,46 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+RSI&lt;45</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>50.67</v>
+        <v>66.67</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>31.42</v>
+        <v>51.86</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-88.45</v>
+        <v>-52.01</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>12.57</v>
+        <v>50.3</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>-101.02</v>
+        <v>-102.31</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-101.02</v>
+        <v>-20.46</v>
       </c>
     </row>
     <row r="29">
@@ -14866,27 +14866,29 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
+      <c r="L10" s="2" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19 18:49:29 IST</t>
+        </is>
+      </c>
       <c r="N10" s="4" t="n">
-        <v>-9.4</v>
+        <v>-24.37</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>10.18</v>
       </c>
-      <c r="P10" s="10" t="inlineStr">
-        <is>
-          <t>~-19.58 (unrealized)</t>
-        </is>
-      </c>
-      <c r="Q10" s="10" t="inlineStr">
-        <is>
-          <t>~-0.28%</t>
-        </is>
+      <c r="P10" s="6" t="n">
+        <v>-34.55</v>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v>-1.02</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -14911,7 +14913,7 @@
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>#1SW EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -21044,18 +21046,18 @@
       <c r="L73" s="15" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
       <c r="N73" s="17" t="n">
-        <v>18071.27</v>
+        <v>18046.9</v>
       </c>
       <c r="O73" s="17" t="n">
-        <v>3632.15</v>
+        <v>3642.33</v>
       </c>
       <c r="P73" s="18" t="n">
-        <v>14439.12</v>
+        <v>14404.57</v>
       </c>
       <c r="Q73" s="16" t="inlineStr"/>
       <c r="R73" s="15" t="inlineStr">
         <is>
-          <t>71 trades (66 closed / 5 open)</t>
+          <t>71 trades (67 closed / 4 open)</t>
         </is>
       </c>
       <c r="S73" s="15" t="inlineStr"/>

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -2255,66 +2255,66 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>#4SW XLP LONG</t>
+          <t>#1ID DOGE-USD SHORT</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>SWING_1d</t>
+          <t>INTRADAY_1h</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>DOGE-USD</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CRYPTO</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>EMA20&lt;EMA50+Range&lt;1%</t>
+          <t>Price&gt;SMA20+RSI&lt;45</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>61.78</v>
+        <v>50.67</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>70.52</v>
+        <v>31.42</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0</v>
+        <v>-88.45</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="4" t="n">
-        <v>0</v>
+        <v>12.57</v>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v>-101.02</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0</v>
+        <v>-101.02</v>
       </c>
     </row>
     <row r="27">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>#1ID DOGE-USD SHORT</t>
+          <t>#1SW TRX-USD LONG</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>INTRADAY_1h</t>
+          <t>SWING_1d</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>DOGE-USD</t>
+          <t>TRX-USD</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2343,46 +2343,46 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA20+RSI&lt;45</t>
+          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>50.67</v>
+        <v>66.67</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>31.42</v>
+        <v>51.86</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-88.45</v>
+        <v>-52.01</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>12.57</v>
+        <v>50.3</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>-101.02</v>
+        <v>-102.31</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-101.02</v>
+        <v>-20.46</v>
       </c>
     </row>
     <row r="28">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>#1SW TRX-USD LONG</t>
+          <t>#5SW XLP LONG</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>TRX-USD</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>CRYPTO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2416,41 +2416,41 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>EMA9&gt;EMA20+Price&gt;SMA50+Range&lt;1%</t>
+          <t>Range&lt;1%+SMA20&lt;EMA20</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>66.67</v>
+        <v>58.26</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>51.86</v>
+        <v>67.47</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-52.01</v>
+        <v>-149.74</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>50.3</v>
+        <v>20.27</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>-102.31</v>
+        <v>-170.01</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-20.46</v>
+        <v>-85</v>
       </c>
     </row>
     <row r="29">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>#5SW XLP LONG</t>
+          <t>#4SW XLP LONG</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2484,41 +2484,41 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Range&lt;1%+SMA20&lt;EMA20</t>
+          <t>EMA20&lt;EMA50+Range&lt;1%</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>58.26</v>
+        <v>61.78</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>67.47</v>
+        <v>70.52</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-149.74</v>
+        <v>-375.12</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>20.27</v>
+        <v>10.46</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>-170.01</v>
+        <v>-385.58</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-85</v>
+        <v>-385.58</v>
       </c>
     </row>
     <row r="30">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>#3SW XLC LONG</t>
+          <t>#31SW QQQ LONG</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2620,20 +2620,20 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;EMA9+Range&lt;1%</t>
+          <t>Price&gt;SMA50+2Red</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>53.98</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>68.92</v>
+        <v>48.57</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2645,16 +2645,16 @@
         <v>0</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-750.65</v>
+        <v>-865.8099999999999</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.32</v>
+        <v>10.46</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>-760.97</v>
+        <v>-876.27</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-760.97</v>
+        <v>-876.27</v>
       </c>
     </row>
     <row r="32">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>#31SW QQQ LONG</t>
+          <t>#5SW KBE LONG</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2688,14 +2688,14 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Price&gt;SMA50+2Red</t>
+          <t>EMA9&lt;EMA50+Price&gt;EMA50</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>65.29000000000001</v>
+        <v>50.67</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>48.57</v>
+        <v>17.55</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1</v>
@@ -2713,16 +2713,16 @@
         <v>0</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-865.8099999999999</v>
+        <v>-1039.2</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.46</v>
+        <v>10.29</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>-876.27</v>
+        <v>-1049.49</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-876.27</v>
+        <v>-1049.49</v>
       </c>
     </row>
     <row r="33">
@@ -2769,28 +2769,28 @@
         <v>6</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-982.38</v>
+        <v>-1036.91</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>50.18</v>
+        <v>60.6</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>-1032.56</v>
+        <v>-1097.51</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-206.51</v>
+        <v>-182.92</v>
       </c>
     </row>
     <row r="34">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>#5SW KBE LONG</t>
+          <t>#3SW XLC LONG</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2824,17 +2824,17 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>EMA9&lt;EMA50+Price&gt;EMA50</t>
+          <t>Price&gt;EMA9+Range&lt;1%</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>50.67</v>
+        <v>53.98</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>17.55</v>
+        <v>68.92</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2843,22 +2843,22 @@
         <v>0</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1039.2</v>
+        <v>-1594.61</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>10.29</v>
+        <v>20.82</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>-1049.49</v>
+        <v>-1615.43</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-1049.49</v>
+        <v>-807.72</v>
       </c>
     </row>
     <row r="35">
@@ -14575,27 +14575,29 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
+      <c r="L7" s="2" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:30:00 IST</t>
+        </is>
+      </c>
       <c r="N7" s="4" t="n">
-        <v>-49.32</v>
+        <v>-54.53</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>10.42</v>
       </c>
-      <c r="P7" s="10" t="inlineStr">
-        <is>
-          <t>~-59.74 (unrealized)</t>
-        </is>
-      </c>
-      <c r="Q7" s="10" t="inlineStr">
-        <is>
-          <t>~-0.09%</t>
-        </is>
+      <c r="P7" s="6" t="n">
+        <v>-64.95</v>
+      </c>
+      <c r="Q7" s="9" t="n">
+        <v>-0.12</v>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -14620,7 +14622,7 @@
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1%</t>
+          <t>#4SW EMA9&gt;EMA20+Price&gt;SMA20+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -14672,27 +14674,29 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr"/>
+      <c r="L8" s="2" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:30:00 IST</t>
+        </is>
+      </c>
       <c r="N8" s="4" t="n">
-        <v>-838.8</v>
+        <v>-843.96</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="P8" s="10" t="inlineStr">
-        <is>
-          <t>~-849.30 (unrealized)</t>
-        </is>
-      </c>
-      <c r="Q8" s="10" t="inlineStr">
-        <is>
-          <t>~-1.60%</t>
-        </is>
+      <c r="P8" s="6" t="n">
+        <v>-854.46</v>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v>-1.63</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -14717,7 +14721,7 @@
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>#3SW Price&gt;EMA9+Range&lt;1%</t>
+          <t>#3SW Price&gt;EMA9+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -14769,27 +14773,29 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
+      <c r="L9" s="2" t="n">
+        <v>82.79000000000001</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:30:00 IST</t>
+        </is>
+      </c>
       <c r="N9" s="4" t="n">
-        <v>-369.93</v>
+        <v>-375.12</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>10.46</v>
       </c>
-      <c r="P9" s="10" t="inlineStr">
-        <is>
-          <t>~-380.39 (unrealized)</t>
-        </is>
-      </c>
-      <c r="Q9" s="10" t="inlineStr">
-        <is>
-          <t>~-0.71%</t>
-        </is>
+      <c r="P9" s="6" t="n">
+        <v>-385.58</v>
+      </c>
+      <c r="Q9" s="9" t="n">
+        <v>-0.74</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -14814,7 +14820,7 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>#4SW EMA20&lt;EMA50+Range&lt;1%</t>
+          <t>#4SW EMA20&lt;EMA50+Range&lt;1% | Expiry 5d</t>
         </is>
       </c>
     </row>
@@ -21046,18 +21052,18 @@
       <c r="L73" s="15" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
       <c r="N73" s="17" t="n">
-        <v>18046.9</v>
+        <v>16773.29</v>
       </c>
       <c r="O73" s="17" t="n">
-        <v>3642.33</v>
+        <v>3673.71</v>
       </c>
       <c r="P73" s="18" t="n">
-        <v>14404.57</v>
+        <v>13099.58</v>
       </c>
       <c r="Q73" s="16" t="inlineStr"/>
       <c r="R73" s="15" t="inlineStr">
         <is>
-          <t>71 trades (67 closed / 4 open)</t>
+          <t>71 trades (70 closed / 1 open)</t>
         </is>
       </c>
       <c r="S73" s="15" t="inlineStr"/>

--- a/logs/strategy_report.xlsx
+++ b/logs/strategy_report.xlsx
@@ -14481,19 +14481,19 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="4" t="n">
-        <v>1669.92</v>
+        <v>1658.56</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>10.44</v>
       </c>
       <c r="P6" s="10" t="inlineStr">
         <is>
-          <t>~1,659.48 (unrealized)</t>
+          <t>~1,648.12 (unrealized)</t>
         </is>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
-          <t>~+3.20%</t>
+          <t>~+3.18%</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
